--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -513,43 +513,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rucula-unidade-201006</t>
+          <t>matte-leao-limao-pet-1-5l-118222</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rúcula Unidade</t>
+          <t>Matte Leão Limão Pet 1,5L</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>201006</t>
+          <t>118222</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A rúcula é uma hortaliça de baixa caloria (aprox. 29 kcal/100g) e rica em nutrientes como vitaminas A, C e K, além de cálcio, ferro e potássio. Seus principais benefícios incluem ação antioxidante, fortalecimento do sistema imunológico, melhoria da saúde ocular e óssea, auxílio na digestão, controle do colesterol e redução de riscos cardiovasculares.A melhor forma de comer rúcula é crua em saladas, temperada com azeite, sal e limão, mas também é versátil em pratos quentes como massas, risotos e sanduíches, ou refogada rapidamente</t>
+          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3.79</v>
+        <v>7.49</v>
       </c>
       <c r="F2" t="n">
-        <v>3.79</v>
+        <v>8.99</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3040890/VF4qT-qqCUAAAAAAAAHLpQ.jpg?v=637792545082200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -562,21 +562,21 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>2000015</v>
+        <v>2000010</v>
       </c>
       <c r="P2" t="n">
         <v>99999</v>
@@ -723,7 +723,7 @@
         <v>2001056</v>
       </c>
       <c r="P4" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="5">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="F8" t="n">
         <v>1.53</v>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5.99</v>
+        <v>5.39</v>
       </c>
       <c r="F10" t="n">
         <v>5.99</v>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3.39</v>
+        <v>2.99</v>
       </c>
       <c r="F13" t="n">
         <v>3.39</v>
@@ -1377,29 +1377,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>morango-250g-289612</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Morango 250g</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>289612</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
+          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>10.99</v>
+        <v>8.99</v>
       </c>
       <c r="F14" t="n">
-        <v>10.99</v>
+        <v>9.99</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1449,43 +1449,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>morango-250g-289612</t>
+          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Morango 250g</t>
+          <t>Detergente Para Louças Odd Clear 500ml</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>289612</t>
+          <t>982911</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
+          <t>ODD voltou!Alto rendimento , controle de odor.</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9.99</v>
+        <v>1.9</v>
       </c>
       <c r="F15" t="n">
-        <v>9.99</v>
+        <v>2.49</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1498,21 +1498,21 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>LIMPPANO</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2000015</v>
+        <v>2001341</v>
       </c>
       <c r="P15" t="n">
         <v>99999</v>
@@ -1521,39 +1521,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
+        </is>
+      </c>
       <c r="E16" t="n">
-        <v>5.99</v>
+        <v>9.99</v>
       </c>
       <c r="F16" t="n">
-        <v>5.99</v>
+        <v>10.99</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1566,21 +1570,21 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2001952</v>
+        <v>2000015</v>
       </c>
       <c r="P16" t="n">
         <v>99999</v>
@@ -1657,48 +1661,48 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>couve-flor-unidade-189111</t>
+          <t>limao-cariorta-1kg-98981</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Couve Flor Unidade</t>
+          <t>Limão Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>189111</t>
+          <t>98981</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9.99</v>
+        <v>11.99</v>
       </c>
       <c r="F18" t="n">
-        <v>9.99</v>
+        <v>11.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1706,21 +1710,21 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P18" t="n">
         <v>99999</v>
@@ -1729,48 +1733,44 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>limao-cariorta-1kg-98981</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Limão Cariorta 1Kg</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>98981</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Cariorta selecionados de coração.</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
       <c r="F19" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1778,21 +1778,21 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2001012</v>
+        <v>2001952</v>
       </c>
       <c r="P19" t="n">
         <v>99999</v>
@@ -1801,43 +1801,43 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
+          <t>couve-flor-unidade-189111</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Odd Clear 500ml</t>
+          <t>Couve Flor Unidade</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>982911</t>
+          <t>189111</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ODD voltou!Alto rendimento , controle de odor.</t>
+          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.9</v>
+        <v>9.59</v>
       </c>
       <c r="F20" t="n">
-        <v>2.49</v>
+        <v>9.99</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1850,21 +1850,21 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>LIMPPANO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2001341</v>
+        <v>2000015</v>
       </c>
       <c r="P20" t="n">
         <v>99999</v>
@@ -1873,70 +1873,70 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
+          <t>mamao-papaia-cariorta-12kg-99007</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
+          <t>Mamão Papaia Cariorta 1,2kg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>429376</t>
+          <t>99007</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.99</v>
+        <v>9.99</v>
       </c>
       <c r="F21" t="n">
-        <v>3.99</v>
+        <v>9.99</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>2000027</v>
+        <v>2001012</v>
       </c>
       <c r="P21" t="n">
         <v>99999</v>
@@ -1945,70 +1945,70 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mamao-papaia-cariorta-12kg-99007</t>
+          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mamão Papaia Cariorta 1,2kg</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>99007</t>
+          <t>429376</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>9.99</v>
+        <v>3.99</v>
       </c>
       <c r="F22" t="n">
-        <v>9.99</v>
+        <v>3.99</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2001012</v>
+        <v>2000027</v>
       </c>
       <c r="P22" t="n">
         <v>99999</v>
@@ -2089,43 +2089,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>coentro-unidade-200930</t>
+          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Coentro Unidade</t>
+          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>200930</t>
+          <t>100510</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
+          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.79</v>
+        <v>1.89</v>
       </c>
       <c r="F24" t="n">
-        <v>3.79</v>
+        <v>2.69</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2138,21 +2138,21 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>LIMPOL</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>2000015</v>
+        <v>2001413</v>
       </c>
       <c r="P24" t="n">
         <v>99999</v>
@@ -2161,43 +2161,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
+          <t>coentro-unidade-200930</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
+          <t>Coentro Unidade</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>129887</t>
+          <t>200930</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>12.99</v>
+        <v>2.99</v>
       </c>
       <c r="F25" t="n">
-        <v>12.99</v>
+        <v>3.79</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2210,21 +2210,21 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>2001401</v>
+        <v>2000015</v>
       </c>
       <c r="P25" t="n">
         <v>99999</v>
@@ -2233,43 +2233,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>100510</t>
+          <t>129887</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
+          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.79</v>
+        <v>12.99</v>
       </c>
       <c r="F26" t="n">
-        <v>2.79</v>
+        <v>12.99</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2282,21 +2282,21 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>LIMPOL</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>2001413</v>
+        <v>2001401</v>
       </c>
       <c r="P26" t="n">
         <v>99999</v>
@@ -2377,43 +2377,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
+          <t>abobrinha-italiana-unidade-423513</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>290564</t>
+          <t>423513</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>24.99</v>
+        <v>3.5</v>
       </c>
       <c r="F28" t="n">
-        <v>26.99</v>
+        <v>3.5</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-12-07T00:00:00Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2426,24 +2426,24 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>SADIA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>2000057</v>
+        <v>2000015</v>
       </c>
       <c r="P28" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="29">
@@ -2521,43 +2521,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-unidade-423513</t>
+          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>5106753</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3.5</v>
+        <v>11.99</v>
       </c>
       <c r="F30" t="n">
-        <v>3.5</v>
+        <v>11.99</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2020-12-07T00:00:00Z</t>
+          <t>2021-01-11T00:00:00Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2570,21 +2570,21 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2000015</v>
+        <v>2003319</v>
       </c>
       <c r="P30" t="n">
         <v>99999</v>
@@ -2593,43 +2593,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
+          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
+          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5106753</t>
+          <t>290564</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
+          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>11.99</v>
+        <v>24.99</v>
       </c>
       <c r="F31" t="n">
-        <v>11.99</v>
+        <v>26.99</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2021-01-11T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2642,21 +2642,21 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>SADIA</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>2003319</v>
+        <v>2000057</v>
       </c>
       <c r="P31" t="n">
         <v>99999</v>
@@ -2665,43 +2665,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>105287</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>7.99</v>
+        <v>4.39</v>
       </c>
       <c r="F32" t="n">
-        <v>7.99</v>
+        <v>5.69</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2020-07-06T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2714,21 +2714,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>DONA BENTA</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2000701</v>
+        <v>2000400</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2737,43 +2737,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
+          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>364738</t>
+          <t>105287</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4.89</v>
+        <v>7.99</v>
       </c>
       <c r="F33" t="n">
-        <v>4.89</v>
+        <v>7.99</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-07-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2786,21 +2786,21 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>DONA BENTA</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2000043</v>
+        <v>2000701</v>
       </c>
       <c r="P33" t="n">
         <v>99999</v>
@@ -2809,43 +2809,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>364738</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4.39</v>
+        <v>4.89</v>
       </c>
       <c r="F34" t="n">
-        <v>5.69</v>
+        <v>4.89</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2858,21 +2858,21 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>2000400</v>
+        <v>2000043</v>
       </c>
       <c r="P34" t="n">
         <v>99999</v>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3.79</v>
+        <v>2.99</v>
       </c>
       <c r="F37" t="n">
         <v>3.79</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3.79</v>
+        <v>2.99</v>
       </c>
       <c r="F38" t="n">
         <v>3.79</v>
@@ -3169,70 +3169,70 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
+          <t>cebola-roxa-400g-38393</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
+          <t>Cebola Roxa 400g</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>981168</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
+          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>32.19</v>
+        <v>7.99</v>
       </c>
       <c r="F39" t="n">
-        <v>32.19</v>
+        <v>7.99</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2020-09-22T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>NEVE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>2000291</v>
+        <v>2000015</v>
       </c>
       <c r="P39" t="n">
         <v>99999</v>
@@ -3313,43 +3313,43 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>981168</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6.99</v>
+        <v>26.9</v>
       </c>
       <c r="F41" t="n">
-        <v>6.99</v>
+        <v>32.19</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-22T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3362,21 +3362,21 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>NEVE</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2001532</v>
+        <v>2000291</v>
       </c>
       <c r="P41" t="n">
         <v>99999</v>
@@ -3385,43 +3385,43 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cebola-roxa-400g-38393</t>
+          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cebola Roxa 400g</t>
+          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>99279</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
+          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>7.99</v>
+        <v>59.99</v>
       </c>
       <c r="F42" t="n">
-        <v>7.99</v>
+        <v>59.99</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-05-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3430,25 +3430,25 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P42" t="n">
         <v>99999</v>
@@ -3457,70 +3457,70 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>99279</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>59.99</v>
+        <v>6.99</v>
       </c>
       <c r="F43" t="n">
-        <v>59.99</v>
+        <v>6.99</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2020-05-27T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>24684</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>2001012</v>
+        <v>2001532</v>
       </c>
       <c r="P43" t="n">
         <v>99999</v>
@@ -3529,43 +3529,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>matte-leao-natural-pet-15l-118214</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Matte Leão Natural Pet 1,5L</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>118214</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>37.9</v>
+        <v>7.49</v>
       </c>
       <c r="F44" t="n">
-        <v>37.9</v>
+        <v>8.99</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3578,21 +3578,21 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>2001329</v>
+        <v>2000010</v>
       </c>
       <c r="P44" t="n">
         <v>99999</v>
@@ -3673,43 +3673,43 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>matte-leao-natural-pet-15l-118214</t>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Matte Leão Natural Pet 1,5L</t>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>118214</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>7.49</v>
+        <v>37.9</v>
       </c>
       <c r="F46" t="n">
-        <v>8.99</v>
+        <v>37.9</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-07-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3722,21 +3722,21 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>MELITTA</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>2000010</v>
+        <v>2001329</v>
       </c>
       <c r="P46" t="n">
         <v>99999</v>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5.99</v>
+        <v>4.85</v>
       </c>
       <c r="F48" t="n">
         <v>5.99</v>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3.79</v>
+        <v>2.99</v>
       </c>
       <c r="F49" t="n">
         <v>3.79</v>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7.49</v>
+        <v>8.99</v>
       </c>
       <c r="F2" t="n">
         <v>8.99</v>
@@ -723,7 +723,7 @@
         <v>2001056</v>
       </c>
       <c r="P4" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7.98</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F5" t="n">
         <v>8.789999999999999</v>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.29</v>
+        <v>5.29</v>
       </c>
       <c r="F6" t="n">
         <v>5.29</v>
@@ -873,43 +873,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>uva-preta-sem-semente-500-g-674583</t>
+          <t>tomate-italiano-unidade-495212</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Uva Preta Sem Semente 500g</t>
+          <t>Tomate Italiano Unidade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>674583</t>
+          <t>495212</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
+          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>11.99</v>
+        <v>1.18</v>
       </c>
       <c r="F7" t="n">
-        <v>11.99</v>
+        <v>1.53</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -945,43 +945,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tomate-italiano-unidade-495212</t>
+          <t>uva-preta-sem-semente-500-g-674583</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tomate Italiano Unidade</t>
+          <t>Uva Preta Sem Semente 500g</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>495212</t>
+          <t>674583</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
+          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.18</v>
+        <v>11.99</v>
       </c>
       <c r="F8" t="n">
-        <v>1.53</v>
+        <v>11.99</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1089,43 +1089,43 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>manga-palmer-unidade-5130760</t>
+          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Manga Palmer Unidade</t>
+          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5130760</t>
+          <t>828025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
+          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5.39</v>
+        <v>43.9</v>
       </c>
       <c r="F10" t="n">
-        <v>5.99</v>
+        <v>43.9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2023-02-16T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1138,21 +1138,21 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PILAO</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2000015</v>
+        <v>2000070</v>
       </c>
       <c r="P10" t="n">
         <v>99999</v>
@@ -1161,43 +1161,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
+          <t>manga-palmer-unidade-5130760</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
+          <t>Manga Palmer Unidade</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>828025</t>
+          <t>5130760</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
+          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>29.98</v>
+        <v>5.39</v>
       </c>
       <c r="F11" t="n">
-        <v>43.9</v>
+        <v>5.99</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2023-02-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1210,21 +1210,21 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>31902</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>PILAO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2000070</v>
+        <v>2000015</v>
       </c>
       <c r="P11" t="n">
         <v>99999</v>
@@ -1233,70 +1233,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>batata-inglesa-cariorta-12kg-98698</t>
+          <t>cheiro-verde-unidade-201049</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Batata Inglesa Cariorta 1,2Kg</t>
+          <t>Cheiro Verde Unidade</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>201049</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.99</v>
+        <v>2.99</v>
       </c>
       <c r="F12" t="n">
-        <v>7.99</v>
+        <v>3.39</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P12" t="n">
         <v>99999</v>
@@ -1305,70 +1305,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cheiro-verde-unidade-201049</t>
+          <t>batata-inglesa-cariorta-12kg-98698</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cheiro Verde Unidade</t>
+          <t>Batata Inglesa Cariorta 1,2Kg</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>201049</t>
+          <t>98698</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.99</v>
+        <v>7.99</v>
       </c>
       <c r="F13" t="n">
-        <v>3.39</v>
+        <v>7.99</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P13" t="n">
         <v>99999</v>
@@ -1449,43 +1449,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Odd Clear 500ml</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>982911</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ODD voltou!Alto rendimento , controle de odor.</t>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.9</v>
+        <v>9.99</v>
       </c>
       <c r="F15" t="n">
-        <v>2.49</v>
+        <v>10.99</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1498,21 +1498,21 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>LIMPPANO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2001341</v>
+        <v>2000015</v>
       </c>
       <c r="P15" t="n">
         <v>99999</v>
@@ -1521,70 +1521,66 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Pão Francês Panetto  60g Com 4 unidades</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
-        </is>
-      </c>
+          <t>96318</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
       <c r="F16" t="n">
-        <v>10.99</v>
+        <v>24.99</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2024-01-31T00:00:00Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PANETTO</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2000015</v>
+        <v>2000307</v>
       </c>
       <c r="P16" t="n">
         <v>99999</v>
@@ -1593,66 +1589,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
+          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pão Francês Panetto  60g Com 4 unidades</t>
+          <t>Detergente Para Louças Odd Clear 500ml</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>96318</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>982911</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ODD voltou!Alto rendimento , controle de odor.</t>
+        </is>
+      </c>
       <c r="E17" t="n">
-        <v>24.99</v>
+        <v>1.9</v>
       </c>
       <c r="F17" t="n">
-        <v>24.99</v>
+        <v>2.49</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2024-01-31T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>PANETTO</t>
+          <t>LIMPPANO</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2000307</v>
+        <v>2001341</v>
       </c>
       <c r="P17" t="n">
         <v>99999</v>
@@ -1661,48 +1661,44 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>limao-cariorta-1kg-98981</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Limão Cariorta 1Kg</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>98981</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Cariorta selecionados de coração.</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
       <c r="F18" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1710,21 +1706,21 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2001012</v>
+        <v>2001952</v>
       </c>
       <c r="P18" t="n">
         <v>99999</v>
@@ -1733,44 +1729,48 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>limao-cariorta-1kg-98981</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Limão Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>98981</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Cariorta selecionados de coração.</t>
+        </is>
+      </c>
       <c r="E19" t="n">
-        <v>5.99</v>
+        <v>11.99</v>
       </c>
       <c r="F19" t="n">
-        <v>5.99</v>
+        <v>11.99</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1778,21 +1778,21 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2001952</v>
+        <v>2001012</v>
       </c>
       <c r="P19" t="n">
         <v>99999</v>
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.89</v>
+        <v>2.69</v>
       </c>
       <c r="F24" t="n">
         <v>2.69</v>
@@ -2233,43 +2233,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
+          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
+          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>129887</t>
+          <t>1180320</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>12.99</v>
+        <v>2.99</v>
       </c>
       <c r="F26" t="n">
-        <v>12.99</v>
+        <v>2.99</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2025-07-17T00:00:00Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2282,21 +2282,21 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>BOMBRIL</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>2001401</v>
+        <v>2001389</v>
       </c>
       <c r="P26" t="n">
         <v>99999</v>
@@ -2305,43 +2305,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1180320</t>
+          <t>129887</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
+          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.99</v>
+        <v>12.99</v>
       </c>
       <c r="F27" t="n">
-        <v>2.99</v>
+        <v>12.99</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2025-07-17T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2354,21 +2354,21 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>41057</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>BOMBRIL</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>2001389</v>
+        <v>2001401</v>
       </c>
       <c r="P27" t="n">
         <v>99999</v>
@@ -2449,29 +2449,29 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>leite-uht-piracanjuba-integral-1l-865427</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Leite Uht Piracanjuba Integral 1L</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>865427</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5.59</v>
+        <v>5.69</v>
       </c>
       <c r="F29" t="n">
-        <v>5.59</v>
+        <v>5.69</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2480,12 +2480,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2017-04-12T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2498,21 +2498,21 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2002038</v>
+        <v>2000400</v>
       </c>
       <c r="P29" t="n">
         <v>99999</v>
@@ -2521,43 +2521,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
+          <t>leite-uht-piracanjuba-integral-1l-865427</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
+          <t>Leite Uht Piracanjuba Integral 1L</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5106753</t>
+          <t>865427</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
+          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>11.99</v>
+        <v>5.59</v>
       </c>
       <c r="F30" t="n">
-        <v>11.99</v>
+        <v>5.59</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2021-01-11T00:00:00Z</t>
+          <t>2017-04-12T00:00:00Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2570,21 +2570,21 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>23232</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>23158</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2003319</v>
+        <v>2002038</v>
       </c>
       <c r="P30" t="n">
         <v>99999</v>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>24.99</v>
+        <v>26.99</v>
       </c>
       <c r="F31" t="n">
         <v>26.99</v>
@@ -2665,43 +2665,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>5106753</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4.39</v>
+        <v>11.99</v>
       </c>
       <c r="F32" t="n">
-        <v>5.69</v>
+        <v>11.99</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2021-01-11T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2714,21 +2714,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2000400</v>
+        <v>2003319</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2737,43 +2737,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
+          <t>sal-refinado-iodado-ita-1kg-117293</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>105287</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>7.99</v>
+        <v>3.65</v>
       </c>
       <c r="F33" t="n">
-        <v>7.99</v>
+        <v>3.65</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2020-07-06T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2786,21 +2786,21 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>DONA BENTA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2000701</v>
+        <v>2000066</v>
       </c>
       <c r="P33" t="n">
         <v>99999</v>
@@ -2809,43 +2809,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
+          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>364738</t>
+          <t>105287</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4.89</v>
+        <v>5.99</v>
       </c>
       <c r="F34" t="n">
-        <v>4.89</v>
+        <v>7.99</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-07-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2858,21 +2858,21 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>DONA BENTA</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>2000043</v>
+        <v>2000701</v>
       </c>
       <c r="P34" t="n">
         <v>99999</v>
@@ -2881,43 +2881,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sal-refinado-iodado-ita-1kg-117293</t>
+          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>364738</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3.65</v>
+        <v>4.89</v>
       </c>
       <c r="F35" t="n">
-        <v>3.65</v>
+        <v>4.89</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2930,21 +2930,21 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2000066</v>
+        <v>2000043</v>
       </c>
       <c r="P35" t="n">
         <v>99999</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3.69</v>
+        <v>4.99</v>
       </c>
       <c r="F36" t="n">
         <v>4.99</v>
@@ -3091,7 +3091,7 @@
         <v>2000015</v>
       </c>
       <c r="P37" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>26.9</v>
+        <v>32.19</v>
       </c>
       <c r="F41" t="n">
         <v>32.19</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>7.49</v>
+        <v>8.99</v>
       </c>
       <c r="F44" t="n">
         <v>8.99</v>
@@ -3601,43 +3601,43 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pao-de-forma-plus-vita-tradicional-500-g-252921</t>
+          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pão de Forma Tradicional Plusvita 480g</t>
+          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>252921</t>
+          <t>818640</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Versátil, prático e para qualquer momento, trazendo a energia necessária para o seu dia. Perfeito para sanduíches, torradas, receitas para o café da manhã, café da tarde, almoço e jantar</t>
+          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>9.98</v>
+        <v>4.99</v>
       </c>
       <c r="F45" t="n">
-        <v>9.98</v>
+        <v>4.99</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-11-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3663691/VF4qT-qqCUAAAAAAAAb-gA.jpg?v=638592874910030000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3650,21 +3650,21 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>9715</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>PLUS VITA</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2000316</v>
+        <v>2002038</v>
       </c>
       <c r="P45" t="n">
         <v>99999</v>
@@ -3673,48 +3673,44 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>abobrinha-italiana-cariorta-1kg-98663</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Abobrinha Italiana Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>103845</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
-        </is>
-      </c>
+          <t>98663</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>37.9</v>
+        <v>10.99</v>
       </c>
       <c r="F46" t="n">
-        <v>37.9</v>
+        <v>10.99</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3722,21 +3718,21 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>2001329</v>
+        <v>2001012</v>
       </c>
       <c r="P46" t="n">
         <v>99999</v>
@@ -3745,44 +3741,48 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-cariorta-1kg-98663</t>
+          <t>alface-crespa-unidade-200875</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Cariorta 1Kg</t>
+          <t>Alface Crespa Unidade</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>98663</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>200875</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
+        </is>
+      </c>
       <c r="E47" t="n">
-        <v>10.99</v>
+        <v>2.99</v>
       </c>
       <c r="F47" t="n">
-        <v>10.99</v>
+        <v>3.79</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3790,21 +3790,21 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P47" t="n">
         <v>99999</v>
@@ -3885,43 +3885,43 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>alface-crespa-unidade-200875</t>
+          <t>pao-de-forma-plus-vita-tradicional-500-g-252921</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Alface Crespa Unidade</t>
+          <t>Pão de Forma Tradicional Plusvita 480g</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>200875</t>
+          <t>252921</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
+          <t>Versátil, prático e para qualquer momento, trazendo a energia necessária para o seu dia. Perfeito para sanduíches, torradas, receitas para o café da manhã, café da tarde, almoço e jantar</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2.99</v>
+        <v>9.98</v>
       </c>
       <c r="F49" t="n">
-        <v>3.79</v>
+        <v>9.98</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>183</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3663691/VF4qT-qqCUAAAAAAAAb-gA.jpg?v=638592874910030000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3934,21 +3934,21 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PLUS VITA</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2000015</v>
+        <v>2000316</v>
       </c>
       <c r="P49" t="n">
         <v>99999</v>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -801,43 +801,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
+          <t>tomate-italiano-unidade-495212</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Tomate Italiano Unidade</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>140805</t>
+          <t>495212</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5.29</v>
+        <v>1.7</v>
       </c>
       <c r="F6" t="n">
-        <v>5.29</v>
+        <v>1.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2020-09-25T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -850,21 +850,21 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>SAO LOURENCO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2000145</v>
+        <v>2000015</v>
       </c>
       <c r="P6" t="n">
         <v>99999</v>
@@ -873,43 +873,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tomate-italiano-unidade-495212</t>
+          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tomate Italiano Unidade</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>495212</t>
+          <t>140805</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.18</v>
+        <v>4.49</v>
       </c>
       <c r="F7" t="n">
-        <v>1.53</v>
+        <v>5.29</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-25T00:00:00Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -922,21 +922,21 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SAO LOURENCO</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2000015</v>
+        <v>2000145</v>
       </c>
       <c r="P7" t="n">
         <v>99999</v>
@@ -1017,33 +1017,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mucarela-em-fatias-92363</t>
+          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Muçarela  em Fatias 200g</t>
+          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>92363</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Muçarela em Fatias</t>
+          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>59.9</v>
+        <v>24.99</v>
       </c>
       <c r="F9" t="n">
-        <v>59.9</v>
+        <v>24.99</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1053,37 +1053,37 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2000015</v>
+        <v>2003319</v>
       </c>
       <c r="P9" t="n">
-        <v>99999</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>43.9</v>
+        <v>29.98</v>
       </c>
       <c r="F10" t="n">
         <v>43.9</v>
@@ -1161,61 +1161,61 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>manga-palmer-unidade-5130760</t>
+          <t>mucarela-em-fatias-92363</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Manga Palmer Unidade</t>
+          <t>Muçarela  em Fatias 200g</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5130760</t>
+          <t>92363</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
+          <t>Muçarela em Fatias</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.39</v>
+        <v>59.9</v>
       </c>
       <c r="F11" t="n">
-        <v>5.99</v>
+        <v>59.9</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2023-02-16T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1233,43 +1233,43 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cheiro-verde-unidade-201049</t>
+          <t>manga-palmer-unidade-5130760</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cheiro Verde Unidade</t>
+          <t>Manga Palmer Unidade</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>201049</t>
+          <t>5130760</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.99</v>
+        <v>5.99</v>
       </c>
       <c r="F12" t="n">
-        <v>3.39</v>
+        <v>5.99</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2023-02-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>31902</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1305,70 +1305,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>batata-inglesa-cariorta-12kg-98698</t>
+          <t>cheiro-verde-unidade-201049</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Batata Inglesa Cariorta 1,2Kg</t>
+          <t>Cheiro Verde Unidade</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>201049</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7.99</v>
+        <v>3.39</v>
       </c>
       <c r="F13" t="n">
-        <v>7.99</v>
+        <v>3.39</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P13" t="n">
         <v>99999</v>
@@ -1377,70 +1377,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>morango-250g-289612</t>
+          <t>batata-inglesa-cariorta-12kg-98698</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Morango 250g</t>
+          <t>Batata Inglesa Cariorta 1,2Kg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>289612</t>
+          <t>98698</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>8.99</v>
+        <v>7.99</v>
       </c>
       <c r="F14" t="n">
-        <v>9.99</v>
+        <v>7.99</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P14" t="n">
         <v>99999</v>
@@ -1449,43 +1449,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>9.99</v>
+        <v>4.79</v>
       </c>
       <c r="F15" t="n">
-        <v>10.99</v>
+        <v>5.99</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1498,21 +1494,21 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2000015</v>
+        <v>2001952</v>
       </c>
       <c r="P15" t="n">
         <v>99999</v>
@@ -1521,66 +1517,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
+          <t>morango-250g-289612</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pão Francês Panetto  60g Com 4 unidades</t>
+          <t>Morango 250g</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>96318</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>289612</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
+        </is>
+      </c>
       <c r="E16" t="n">
-        <v>24.99</v>
+        <v>9.99</v>
       </c>
       <c r="F16" t="n">
-        <v>24.99</v>
+        <v>9.99</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2024-01-31T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>PANETTO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2000307</v>
+        <v>2000015</v>
       </c>
       <c r="P16" t="n">
         <v>99999</v>
@@ -1661,39 +1661,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
+        </is>
+      </c>
       <c r="E18" t="n">
-        <v>5.99</v>
+        <v>10.99</v>
       </c>
       <c r="F18" t="n">
-        <v>5.99</v>
+        <v>10.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1706,21 +1710,21 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2001952</v>
+        <v>2000015</v>
       </c>
       <c r="P18" t="n">
         <v>99999</v>
@@ -1729,43 +1733,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>limao-cariorta-1kg-98981</t>
+          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Limão Cariorta 1Kg</t>
+          <t>Pão Francês Panetto  60g Com 4 unidades</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>98981</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Cariorta selecionados de coração.</t>
-        </is>
-      </c>
+          <t>96318</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>11.99</v>
+        <v>24.99</v>
       </c>
       <c r="F19" t="n">
-        <v>11.99</v>
+        <v>24.99</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2024-01-31T00:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1774,25 +1774,25 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>PANETTO</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2001012</v>
+        <v>2000307</v>
       </c>
       <c r="P19" t="n">
         <v>99999</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9.59</v>
+        <v>9.99</v>
       </c>
       <c r="F20" t="n">
         <v>9.99</v>
@@ -1873,17 +1873,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mamao-papaia-cariorta-12kg-99007</t>
+          <t>limao-cariorta-1kg-98981</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mamão Papaia Cariorta 1,2kg</t>
+          <t>Limão Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>99007</t>
+          <t>98981</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9.99</v>
+        <v>11.99</v>
       </c>
       <c r="F21" t="n">
-        <v>9.99</v>
+        <v>11.99</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1918,16 +1918,16 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1945,70 +1945,70 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
+          <t>mamao-papaia-cariorta-12kg-99007</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
+          <t>Mamão Papaia Cariorta 1,2kg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>429376</t>
+          <t>99007</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3.99</v>
+        <v>9.99</v>
       </c>
       <c r="F22" t="n">
-        <v>3.99</v>
+        <v>9.99</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2000027</v>
+        <v>2001012</v>
       </c>
       <c r="P22" t="n">
         <v>99999</v>
@@ -2161,43 +2161,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>coentro-unidade-200930</t>
+          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Coentro Unidade</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>200930</t>
+          <t>429376</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
       <c r="F25" t="n">
-        <v>3.79</v>
+        <v>3.99</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2210,21 +2210,21 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>2000015</v>
+        <v>2000027</v>
       </c>
       <c r="P25" t="n">
         <v>99999</v>
@@ -2233,43 +2233,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
+          <t>coentro-unidade-200930</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
+          <t>Coentro Unidade</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1180320</t>
+          <t>200930</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
+          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.99</v>
+        <v>3.79</v>
       </c>
       <c r="F26" t="n">
-        <v>2.99</v>
+        <v>3.79</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2025-07-17T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2282,21 +2282,21 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>41057</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>BOMBRIL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>2001389</v>
+        <v>2000015</v>
       </c>
       <c r="P26" t="n">
         <v>99999</v>
@@ -2305,43 +2305,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
+          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
+          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>129887</t>
+          <t>1180320</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>12.99</v>
+        <v>2.99</v>
       </c>
       <c r="F27" t="n">
-        <v>12.99</v>
+        <v>2.99</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2025-07-17T00:00:00Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2354,21 +2354,21 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>BOMBRIL</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>2001401</v>
+        <v>2001389</v>
       </c>
       <c r="P27" t="n">
         <v>99999</v>
@@ -2377,43 +2377,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-unidade-423513</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>129887</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3.5</v>
+        <v>12.99</v>
       </c>
       <c r="F28" t="n">
-        <v>3.5</v>
+        <v>12.99</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2020-12-07T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2426,21 +2426,21 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>2000015</v>
+        <v>2001401</v>
       </c>
       <c r="P28" t="n">
         <v>99999</v>
@@ -2449,43 +2449,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>abobrinha-italiana-unidade-423513</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>423513</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5.69</v>
+        <v>4.2</v>
       </c>
       <c r="F29" t="n">
-        <v>5.69</v>
+        <v>4.2</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-12-07T00:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2498,21 +2498,21 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2000400</v>
+        <v>2000015</v>
       </c>
       <c r="P29" t="n">
         <v>99999</v>
@@ -2521,29 +2521,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>leite-uht-piracanjuba-integral-1l-865427</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Leite Uht Piracanjuba Integral 1L</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>865427</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5.59</v>
+        <v>4.38</v>
       </c>
       <c r="F30" t="n">
-        <v>5.59</v>
+        <v>5.69</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2017-04-12T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2570,21 +2570,21 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2002038</v>
+        <v>2000400</v>
       </c>
       <c r="P30" t="n">
         <v>99999</v>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>26.99</v>
+        <v>23.99</v>
       </c>
       <c r="F31" t="n">
         <v>26.99</v>
@@ -2665,43 +2665,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
+          <t>leite-uht-piracanjuba-integral-1l-865427</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
+          <t>Leite Uht Piracanjuba Integral 1L</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>5106753</t>
+          <t>865427</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
+          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>11.99</v>
+        <v>5.59</v>
       </c>
       <c r="F32" t="n">
-        <v>11.99</v>
+        <v>5.59</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2021-01-11T00:00:00Z</t>
+          <t>2017-04-12T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2714,21 +2714,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>23232</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>23158</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2003319</v>
+        <v>2002038</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2737,43 +2737,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>sal-refinado-iodado-ita-1kg-117293</t>
+          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>105287</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3.65</v>
+        <v>5.99</v>
       </c>
       <c r="F33" t="n">
-        <v>3.65</v>
+        <v>7.99</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-07-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2786,21 +2786,21 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>DONA BENTA</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2000066</v>
+        <v>2000701</v>
       </c>
       <c r="P33" t="n">
         <v>99999</v>
@@ -2809,43 +2809,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
+          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>105287</t>
+          <t>364738</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5.99</v>
+        <v>4.89</v>
       </c>
       <c r="F34" t="n">
-        <v>7.99</v>
+        <v>4.89</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2020-07-06T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2858,21 +2858,21 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>DONA BENTA</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>2000701</v>
+        <v>2000043</v>
       </c>
       <c r="P34" t="n">
         <v>99999</v>
@@ -2881,43 +2881,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
+          <t>sal-refinado-iodado-ita-1kg-117293</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>364738</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4.89</v>
+        <v>3.65</v>
       </c>
       <c r="F35" t="n">
-        <v>4.89</v>
+        <v>3.65</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2930,21 +2930,21 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2000043</v>
+        <v>2000066</v>
       </c>
       <c r="P35" t="n">
         <v>99999</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4.99</v>
+        <v>3.69</v>
       </c>
       <c r="F36" t="n">
         <v>4.99</v>
@@ -3025,43 +3025,43 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>espinafre-unidade-200948</t>
+          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Espinafre Unidade</t>
+          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>200948</t>
+          <t>5106753</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
+          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2.99</v>
+        <v>11.99</v>
       </c>
       <c r="F37" t="n">
-        <v>3.79</v>
+        <v>11.99</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2021-01-11T00:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3074,52 +3074,52 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2000015</v>
+        <v>2003319</v>
       </c>
       <c r="P37" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>couve-manteiga-unidade-201235</t>
+          <t>cebola-roxa-400g-38393</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Couve Manteiga Unidade</t>
+          <t>Cebola Roxa 400g</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>201235</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
+          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2.99</v>
+        <v>7.99</v>
       </c>
       <c r="F38" t="n">
-        <v>3.79</v>
+        <v>7.99</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3128,30 +3128,30 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3169,29 +3169,29 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cebola-roxa-400g-38393</t>
+          <t>couve-manteiga-unidade-201235</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cebola Roxa 400g</t>
+          <t>Couve Manteiga Unidade</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>201235</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
+          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>7.99</v>
+        <v>3.79</v>
       </c>
       <c r="F39" t="n">
-        <v>7.99</v>
+        <v>3.79</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3200,30 +3200,30 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3385,70 +3385,70 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>99279</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>59.99</v>
+        <v>5.99</v>
       </c>
       <c r="F42" t="n">
-        <v>59.99</v>
+        <v>6.99</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2020-05-27T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>24684</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2001012</v>
+        <v>2001532</v>
       </c>
       <c r="P42" t="n">
         <v>99999</v>
@@ -3457,70 +3457,70 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>99279</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6.99</v>
+        <v>59.99</v>
       </c>
       <c r="F43" t="n">
-        <v>6.99</v>
+        <v>59.99</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-05-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>2001532</v>
+        <v>2001012</v>
       </c>
       <c r="P43" t="n">
         <v>99999</v>
@@ -3601,48 +3601,44 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
+          <t>abobrinha-italiana-cariorta-1kg-98663</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
+          <t>Abobrinha Italiana Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>818640</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
-        </is>
-      </c>
+          <t>98663</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>4.99</v>
+        <v>12.99</v>
       </c>
       <c r="F45" t="n">
-        <v>4.99</v>
+        <v>12.99</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2020-11-26T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3650,21 +3646,21 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2002038</v>
+        <v>2001012</v>
       </c>
       <c r="P45" t="n">
         <v>99999</v>
@@ -3673,44 +3669,48 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-cariorta-1kg-98663</t>
+          <t>alface-crespa-unidade-200875</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Cariorta 1Kg</t>
+          <t>Alface Crespa Unidade</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>98663</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>200875</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
+        </is>
+      </c>
       <c r="E46" t="n">
-        <v>10.99</v>
+        <v>3.79</v>
       </c>
       <c r="F46" t="n">
-        <v>10.99</v>
+        <v>3.79</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3718,21 +3718,21 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P46" t="n">
         <v>99999</v>
@@ -3741,61 +3741,61 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>alface-crespa-unidade-200875</t>
+          <t>melao-amarelo-metade-1-3-kg-63606</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Alface Crespa Unidade</t>
+          <t>Melão Amarelo Metade 1,3kg</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>200875</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
+          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2.99</v>
+        <v>5.99</v>
       </c>
       <c r="F47" t="n">
-        <v>3.79</v>
+        <v>5.99</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3813,70 +3813,70 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>melao-amarelo-metade-1-3-kg-63606</t>
+          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Melão Amarelo Metade 1,3kg</t>
+          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>818640</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
+          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4.85</v>
+        <v>4.99</v>
       </c>
       <c r="F48" t="n">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-11-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>2000015</v>
+        <v>2002038</v>
       </c>
       <c r="P48" t="n">
         <v>99999</v>
@@ -3885,43 +3885,43 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pao-de-forma-plus-vita-tradicional-500-g-252921</t>
+          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pão de Forma Tradicional Plusvita 480g</t>
+          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>252921</t>
+          <t>1105795</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Versátil, prático e para qualquer momento, trazendo a energia necessária para o seu dia. Perfeito para sanduíches, torradas, receitas para o café da manhã, café da tarde, almoço e jantar</t>
+          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>9.98</v>
+        <v>3.97</v>
       </c>
       <c r="F49" t="n">
-        <v>9.98</v>
+        <v>5.99</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2023-07-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3663691/VF4qT-qqCUAAAAAAAAb-gA.jpg?v=638592874910030000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3934,21 +3934,21 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>9715</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>PLUS VITA</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2000316</v>
+        <v>2000017</v>
       </c>
       <c r="P49" t="n">
         <v>99999</v>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -1017,43 +1017,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
+          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
+          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>370550</t>
+          <t>828025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
+          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>24.99</v>
+        <v>29.98</v>
       </c>
       <c r="F9" t="n">
-        <v>24.99</v>
+        <v>43.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1066,66 +1066,66 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>PILAO</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2003319</v>
+        <v>2000070</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
+          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
+          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>828025</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
+          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>29.98</v>
+        <v>24.99</v>
       </c>
       <c r="F10" t="n">
-        <v>43.9</v>
+        <v>24.99</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1138,24 +1138,24 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>PILAO</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2000070</v>
+        <v>2003319</v>
       </c>
       <c r="P10" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -1305,43 +1305,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cheiro-verde-unidade-201049</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cheiro Verde Unidade</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>201049</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>3.39</v>
+        <v>4.79</v>
       </c>
       <c r="F13" t="n">
-        <v>3.39</v>
+        <v>5.99</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1354,21 +1350,21 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2000015</v>
+        <v>2001952</v>
       </c>
       <c r="P13" t="n">
         <v>99999</v>
@@ -1377,70 +1373,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>batata-inglesa-cariorta-12kg-98698</t>
+          <t>cheiro-verde-unidade-201049</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Batata Inglesa Cariorta 1,2Kg</t>
+          <t>Cheiro Verde Unidade</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>201049</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7.99</v>
+        <v>3.39</v>
       </c>
       <c r="F14" t="n">
-        <v>7.99</v>
+        <v>3.39</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P14" t="n">
         <v>99999</v>
@@ -1449,66 +1445,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>batata-inglesa-cariorta-12kg-98698</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Batata Inglesa Cariorta 1,2Kg</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>98698</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Cariorta selecionados de coração.</t>
+        </is>
+      </c>
       <c r="E15" t="n">
-        <v>4.79</v>
+        <v>7.99</v>
       </c>
       <c r="F15" t="n">
-        <v>5.99</v>
+        <v>7.99</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2001952</v>
+        <v>2001012</v>
       </c>
       <c r="P15" t="n">
         <v>99999</v>
@@ -1517,43 +1517,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>morango-250g-289612</t>
+          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Morango 250g</t>
+          <t>Detergente Para Louças Odd Clear 500ml</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>289612</t>
+          <t>982911</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
+          <t>ODD voltou!Alto rendimento , controle de odor.</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>9.99</v>
+        <v>1.9</v>
       </c>
       <c r="F16" t="n">
-        <v>9.99</v>
+        <v>2.49</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1566,21 +1566,21 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>LIMPPANO</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2000015</v>
+        <v>2001341</v>
       </c>
       <c r="P16" t="n">
         <v>99999</v>
@@ -1589,43 +1589,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
+          <t>morango-250g-289612</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Odd Clear 500ml</t>
+          <t>Morango 250g</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>982911</t>
+          <t>289612</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ODD voltou!Alto rendimento , controle de odor.</t>
+          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.9</v>
+        <v>9.99</v>
       </c>
       <c r="F17" t="n">
-        <v>2.49</v>
+        <v>9.99</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1638,21 +1638,21 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>LIMPPANO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2001341</v>
+        <v>2000015</v>
       </c>
       <c r="P17" t="n">
         <v>99999</v>
@@ -2161,43 +2161,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
+          <t>coentro-unidade-200930</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
+          <t>Coentro Unidade</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>429376</t>
+          <t>200930</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3.99</v>
+        <v>3.79</v>
       </c>
       <c r="F25" t="n">
-        <v>3.99</v>
+        <v>3.79</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2210,21 +2210,21 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>2000027</v>
+        <v>2000015</v>
       </c>
       <c r="P25" t="n">
         <v>99999</v>
@@ -2233,43 +2233,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>coentro-unidade-200930</t>
+          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Coentro Unidade</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>200930</t>
+          <t>429376</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3.79</v>
+        <v>3.99</v>
       </c>
       <c r="F26" t="n">
-        <v>3.79</v>
+        <v>3.99</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2282,21 +2282,21 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>2000015</v>
+        <v>2000027</v>
       </c>
       <c r="P26" t="n">
         <v>99999</v>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>23.99</v>
+        <v>26.99</v>
       </c>
       <c r="F31" t="n">
         <v>26.99</v>
@@ -2659,7 +2659,7 @@
         <v>2000057</v>
       </c>
       <c r="P31" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
@@ -2881,43 +2881,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sal-refinado-iodado-ita-1kg-117293</t>
+          <t>milho-em-conserva-quero-lata-200g-476625</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Milho em Conserva Quero Lata 200g</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>476625</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3.65</v>
+        <v>4.99</v>
       </c>
       <c r="F35" t="n">
-        <v>3.65</v>
+        <v>4.99</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2930,21 +2930,21 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>QUERO</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2000066</v>
+        <v>2001778</v>
       </c>
       <c r="P35" t="n">
         <v>99999</v>
@@ -2953,43 +2953,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>milho-em-conserva-quero-lata-200g-476625</t>
+          <t>sal-refinado-iodado-ita-1kg-117293</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Milho em Conserva Quero Lata 200g</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>476625</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3.69</v>
+        <v>4.39</v>
       </c>
       <c r="F36" t="n">
-        <v>4.99</v>
+        <v>4.39</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3002,21 +3002,21 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>QUERO</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2001778</v>
+        <v>2000066</v>
       </c>
       <c r="P36" t="n">
         <v>99999</v>
@@ -3025,142 +3025,142 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
+          <t>cebola-roxa-400g-38393</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
+          <t>Cebola Roxa 400g</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5106753</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
+          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>11.99</v>
+        <v>7.99</v>
       </c>
       <c r="F37" t="n">
-        <v>11.99</v>
+        <v>7.99</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2021-01-11T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2003319</v>
+        <v>2000015</v>
       </c>
       <c r="P37" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cebola-roxa-400g-38393</t>
+          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cebola Roxa 400g</t>
+          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>5106753</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
+          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>7.99</v>
+        <v>11.99</v>
       </c>
       <c r="F38" t="n">
-        <v>7.99</v>
+        <v>11.99</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2021-01-11T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>2000015</v>
+        <v>2003319</v>
       </c>
       <c r="P38" t="n">
         <v>99999</v>
@@ -3313,43 +3313,43 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>981168</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>32.19</v>
+        <v>5.99</v>
       </c>
       <c r="F41" t="n">
-        <v>32.19</v>
+        <v>6.99</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2020-09-22T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3362,21 +3362,21 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>NEVE</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2000291</v>
+        <v>2001532</v>
       </c>
       <c r="P41" t="n">
         <v>99999</v>
@@ -3385,43 +3385,43 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>981168</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5.99</v>
+        <v>32.19</v>
       </c>
       <c r="F42" t="n">
-        <v>6.99</v>
+        <v>32.19</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-22T00:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3434,21 +3434,21 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>NEVE</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2001532</v>
+        <v>2000291</v>
       </c>
       <c r="P42" t="n">
         <v>99999</v>
@@ -3885,43 +3885,43 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1105795</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3.97</v>
+        <v>31.98</v>
       </c>
       <c r="F49" t="n">
-        <v>5.99</v>
+        <v>37.9</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2023-07-26T00:00:00Z</t>
+          <t>2020-07-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3934,24 +3934,24 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>MELITTA</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2000017</v>
+        <v>2001329</v>
       </c>
       <c r="P49" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -585,115 +585,115 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cebola-cariorta-kg</t>
+          <t>ovos-brancos-jumbo-mantiqueira-com-10-unidades-437638</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cebola Cariorta Kg</t>
+          <t>Ovos Brancos Jumbo Mantiqueira Com 10 Unidades</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43567</t>
+          <t>437638</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>Os Ovos Jumbo Mantiqueira possuem maior tamanho, ideais para quem busca uma alimentação rica em vitaminas, proteínas e minerais, ou para quem gosta de um maior rendimento em suas receitas. Um único ovo contém quase todos os nutrientes necessários para manter o corpo saudável, fortalecendo os ossos e auxiliando em dietas para perda de peso ou ganho de massa.O Ovo Jumbo Mantiqueira é um produto da linha Especial da marca e possui a qualidade superior, passando por um moderno sistema de seleção, limpeza e embalagem sem contato de mãos humanas.Especificações:Ovos maiores, tamanho família.Embalagem com 10 unidades.Ovos brancos e vermelhos tipo jumbo categoria A.</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5.49</v>
+        <v>10.9</v>
       </c>
       <c r="F3" t="n">
-        <v>5.49</v>
+        <v>10.9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2004-12-30T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3348135/VF4qT-qqCUAAAAAAAAXJHg.jpg?v=638461541793230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3976126/VF4qT-qqCUAAAAAAAAh4RA.jpg?v=638769994856100000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>35728</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>35656</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>MANTIQUEIRA</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2001012</v>
+        <v>2001056</v>
       </c>
       <c r="P3" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ovos-brancos-jumbo-mantiqueira-com-10-unidades-437638</t>
+          <t>alcool-montenegro-46-1-l-780570</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ovos Brancos Jumbo Mantiqueira Com 10 Unidades</t>
+          <t>Álcool Montenegro 46% 1 L</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>437638</t>
+          <t>780570</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Os Ovos Jumbo Mantiqueira possuem maior tamanho, ideais para quem busca uma alimentação rica em vitaminas, proteínas e minerais, ou para quem gosta de um maior rendimento em suas receitas. Um único ovo contém quase todos os nutrientes necessários para manter o corpo saudável, fortalecendo os ossos e auxiliando em dietas para perda de peso ou ganho de massa.O Ovo Jumbo Mantiqueira é um produto da linha Especial da marca e possui a qualidade superior, passando por um moderno sistema de seleção, limpeza e embalagem sem contato de mãos humanas.Especificações:Ovos maiores, tamanho família.Embalagem com 10 unidades.Ovos brancos e vermelhos tipo jumbo categoria A.</t>
+          <t>Álcool Montenegro 46% 1 L</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10.9</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>10.9</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-10-06T10:47:00Z</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3976126/VF4qT-qqCUAAAAAAAAh4RA.jpg?v=638769994856100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051579/VF4qT-qqCUAAAAAAAAG3pQ.jpg?v=637793390624870000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -706,66 +706,66 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>11598</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>MANTIQUEIRA</t>
+          <t>MONTENEGRO</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>2001056</v>
+        <v>2000527</v>
       </c>
       <c r="P4" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>alcool-montenegro-46-1-l-780570</t>
+          <t>tomate-italiano-unidade-495212</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Álcool Montenegro 46% 1 L</t>
+          <t>Tomate Italiano Unidade</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>780570</t>
+          <t>495212</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Álcool Montenegro 46% 1 L</t>
+          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8.789999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="F5" t="n">
-        <v>8.789999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2020-10-06T10:47:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051579/VF4qT-qqCUAAAAAAAAG3pQ.jpg?v=637793390624870000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -778,21 +778,21 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>11598</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>MONTENEGRO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2000527</v>
+        <v>2000015</v>
       </c>
       <c r="P5" t="n">
         <v>99999</v>
@@ -801,43 +801,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tomate-italiano-unidade-495212</t>
+          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tomate Italiano Unidade</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>495212</t>
+          <t>140805</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.7</v>
+        <v>4.49</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7</v>
+        <v>5.29</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-25T00:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -850,21 +850,21 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SAO LOURENCO</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2000015</v>
+        <v>2000145</v>
       </c>
       <c r="P6" t="n">
         <v>99999</v>
@@ -873,43 +873,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
+          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>140805</t>
+          <t>828025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.49</v>
+        <v>29.98</v>
       </c>
       <c r="F7" t="n">
-        <v>5.29</v>
+        <v>43.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2020-09-25T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -922,21 +922,21 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>SAO LOURENCO</t>
+          <t>PILAO</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2000145</v>
+        <v>2000070</v>
       </c>
       <c r="P7" t="n">
         <v>99999</v>
@@ -945,43 +945,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>uva-preta-sem-semente-500-g-674583</t>
+          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Uva Preta Sem Semente 500g</t>
+          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>674583</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
+          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>11.99</v>
+        <v>24.99</v>
       </c>
       <c r="F8" t="n">
-        <v>11.99</v>
+        <v>24.99</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -994,66 +994,66 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2000015</v>
+        <v>2003319</v>
       </c>
       <c r="P8" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
+          <t>uva-preta-sem-semente-500-g-674583</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
+          <t>Uva Preta Sem Semente 500g</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>828025</t>
+          <t>674583</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
+          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>29.98</v>
+        <v>11.99</v>
       </c>
       <c r="F9" t="n">
-        <v>43.9</v>
+        <v>11.99</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1066,21 +1066,21 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>PILAO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2000070</v>
+        <v>2000015</v>
       </c>
       <c r="P9" t="n">
         <v>99999</v>
@@ -1089,33 +1089,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
+          <t>mucarela-em-fatias-92363</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
+          <t>Muçarela  em Fatias 200g</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>370550</t>
+          <t>92363</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
+          <t>Muçarela em Fatias</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>24.99</v>
+        <v>59.9</v>
       </c>
       <c r="F10" t="n">
-        <v>24.99</v>
+        <v>59.9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1125,106 +1125,102 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2003319</v>
+        <v>2000015</v>
       </c>
       <c r="P10" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mucarela-em-fatias-92363</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Muçarela  em Fatias 200g</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>92363</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Muçarela em Fatias</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>59.9</v>
+        <v>4.79</v>
       </c>
       <c r="F11" t="n">
-        <v>59.9</v>
+        <v>5.99</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2000015</v>
+        <v>2001952</v>
       </c>
       <c r="P11" t="n">
         <v>99999</v>
@@ -1305,39 +1301,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>cheiro-verde-unidade-201049</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Cheiro Verde Unidade</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>201049</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+        </is>
+      </c>
       <c r="E13" t="n">
-        <v>4.79</v>
+        <v>3.39</v>
       </c>
       <c r="F13" t="n">
-        <v>5.99</v>
+        <v>3.39</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1350,21 +1350,21 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2001952</v>
+        <v>2000015</v>
       </c>
       <c r="P13" t="n">
         <v>99999</v>
@@ -1373,70 +1373,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cheiro-verde-unidade-201049</t>
+          <t>batata-inglesa-cariorta-12kg-98698</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cheiro Verde Unidade</t>
+          <t>Batata Inglesa Cariorta 1,2Kg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>201049</t>
+          <t>98698</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3.39</v>
+        <v>7.99</v>
       </c>
       <c r="F14" t="n">
-        <v>3.39</v>
+        <v>7.99</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P14" t="n">
         <v>99999</v>
@@ -1445,70 +1445,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>batata-inglesa-cariorta-12kg-98698</t>
+          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Batata Inglesa Cariorta 1,2Kg</t>
+          <t>Detergente Para Louças Odd Clear 500ml</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>982911</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>ODD voltou!Alto rendimento , controle de odor.</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7.99</v>
+        <v>1.9</v>
       </c>
       <c r="F15" t="n">
-        <v>7.99</v>
+        <v>2.49</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>LIMPPANO</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2001012</v>
+        <v>2001341</v>
       </c>
       <c r="P15" t="n">
         <v>99999</v>
@@ -1517,43 +1517,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
+          <t>morango-250g-289612</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Odd Clear 500ml</t>
+          <t>Morango 250g</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>982911</t>
+          <t>289612</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ODD voltou!Alto rendimento , controle de odor.</t>
+          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.9</v>
+        <v>9.99</v>
       </c>
       <c r="F16" t="n">
-        <v>2.49</v>
+        <v>9.99</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1566,21 +1566,21 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>LIMPPANO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2001341</v>
+        <v>2000015</v>
       </c>
       <c r="P16" t="n">
         <v>99999</v>
@@ -1589,29 +1589,29 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>morango-250g-289612</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Morango 250g</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>289612</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
       <c r="F17" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1661,70 +1661,66 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Pão Francês Panetto  60g Com 4 unidades</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
-        </is>
-      </c>
+          <t>96318</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>10.99</v>
+        <v>24.99</v>
       </c>
       <c r="F18" t="n">
-        <v>10.99</v>
+        <v>24.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2024-01-31T00:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PANETTO</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2000015</v>
+        <v>2000307</v>
       </c>
       <c r="P18" t="n">
         <v>99999</v>
@@ -1733,39 +1729,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
+          <t>limao-cariorta-1kg-98981</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pão Francês Panetto  60g Com 4 unidades</t>
+          <t>Limão Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>96318</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>98981</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Cariorta selecionados de coração.</t>
+        </is>
+      </c>
       <c r="E19" t="n">
-        <v>24.99</v>
+        <v>11.99</v>
       </c>
       <c r="F19" t="n">
-        <v>24.99</v>
+        <v>11.99</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2024-01-31T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1774,25 +1774,25 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>PANETTO</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2000307</v>
+        <v>2001012</v>
       </c>
       <c r="P19" t="n">
         <v>99999</v>
@@ -1801,22 +1801,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>couve-flor-unidade-189111</t>
+          <t>mamao-papaia-cariorta-12kg-99007</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Couve Flor Unidade</t>
+          <t>Mamão Papaia Cariorta 1,2kg</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>189111</t>
+          <t>99007</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1827,44 +1827,44 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P20" t="n">
         <v>99999</v>
@@ -1873,48 +1873,48 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>limao-cariorta-1kg-98981</t>
+          <t>couve-flor-unidade-189111</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Limão Cariorta 1Kg</t>
+          <t>Couve Flor Unidade</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>98981</t>
+          <t>189111</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>11.99</v>
+        <v>9.99</v>
       </c>
       <c r="F21" t="n">
-        <v>11.99</v>
+        <v>9.99</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1922,21 +1922,21 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P21" t="n">
         <v>99999</v>
@@ -1945,70 +1945,70 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mamao-papaia-cariorta-12kg-99007</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-238cm×218cm-50-unidades-129879</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mamão Papaia Cariorta 1,2kg</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel 23,8cm×21,8cm 50 Unidades</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>99007</t>
+          <t>129879</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel 23,8cm×21,8cm 50 Unidades</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>9.99</v>
+        <v>6.19</v>
       </c>
       <c r="F22" t="n">
-        <v>9.99</v>
+        <v>6.19</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3239421/VF4qT-qqCUAAAAAAAAVSfw.jpg?v=638362188224230000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2001012</v>
+        <v>2001400</v>
       </c>
       <c r="P22" t="n">
         <v>99999</v>
@@ -2017,43 +2017,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-238cm×218cm-50-unidades-129879</t>
+          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel 23,8cm×21,8cm 50 Unidades</t>
+          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>129879</t>
+          <t>100510</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel 23,8cm×21,8cm 50 Unidades</t>
+          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6.19</v>
+        <v>2.69</v>
       </c>
       <c r="F23" t="n">
-        <v>6.19</v>
+        <v>2.69</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3239421/VF4qT-qqCUAAAAAAAAVSfw.jpg?v=638362188224230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2066,21 +2066,21 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>9438</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>LIMPOL</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>2001400</v>
+        <v>2001413</v>
       </c>
       <c r="P23" t="n">
         <v>99999</v>
@@ -2089,43 +2089,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
+          <t>coentro-unidade-200930</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
+          <t>Coentro Unidade</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>100510</t>
+          <t>200930</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
+          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.69</v>
+        <v>3.79</v>
       </c>
       <c r="F24" t="n">
-        <v>2.69</v>
+        <v>3.79</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2138,21 +2138,21 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>LIMPOL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>2001413</v>
+        <v>2000015</v>
       </c>
       <c r="P24" t="n">
         <v>99999</v>
@@ -2161,43 +2161,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>coentro-unidade-200930</t>
+          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Coentro Unidade</t>
+          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>200930</t>
+          <t>1180320</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
+          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3.79</v>
+        <v>2.99</v>
       </c>
       <c r="F25" t="n">
-        <v>3.79</v>
+        <v>2.99</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2025-07-17T00:00:00Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2210,21 +2210,21 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>BOMBRIL</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>2000015</v>
+        <v>2001389</v>
       </c>
       <c r="P25" t="n">
         <v>99999</v>
@@ -2305,43 +2305,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1180320</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.99</v>
+        <v>4.38</v>
       </c>
       <c r="F27" t="n">
-        <v>2.99</v>
+        <v>5.69</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2025-07-17T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2354,21 +2354,21 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>41057</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>BOMBRIL</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>2001389</v>
+        <v>2000400</v>
       </c>
       <c r="P27" t="n">
         <v>99999</v>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="F29" t="n">
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2521,29 +2521,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>leite-uht-piracanjuba-integral-1l-865427</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Leite Uht Piracanjuba Integral 1L</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>865427</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4.38</v>
+        <v>5.59</v>
       </c>
       <c r="F30" t="n">
-        <v>5.69</v>
+        <v>5.59</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2017-04-12T00:00:00Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2570,21 +2570,21 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>23232</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>23158</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2000400</v>
+        <v>2002038</v>
       </c>
       <c r="P30" t="n">
         <v>99999</v>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>26.99</v>
+        <v>23.99</v>
       </c>
       <c r="F31" t="n">
         <v>26.99</v>
@@ -2659,49 +2659,49 @@
         <v>2000057</v>
       </c>
       <c r="P31" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>leite-uht-piracanjuba-integral-1l-865427</t>
+          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Leite Uht Piracanjuba Integral 1L</t>
+          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>865427</t>
+          <t>364738</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
+          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5.59</v>
+        <v>4.89</v>
       </c>
       <c r="F32" t="n">
-        <v>5.59</v>
+        <v>4.89</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2017-04-12T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2714,21 +2714,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2002038</v>
+        <v>2000043</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2737,43 +2737,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
+          <t>sal-refinado-iodado-ita-1kg-117293</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>105287</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5.99</v>
+        <v>4.39</v>
       </c>
       <c r="F33" t="n">
-        <v>7.99</v>
+        <v>4.39</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2020-07-06T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2786,21 +2786,21 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>DONA BENTA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2000701</v>
+        <v>2000066</v>
       </c>
       <c r="P33" t="n">
         <v>99999</v>
@@ -2809,43 +2809,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
+          <t>milho-em-conserva-quero-lata-200g-476625</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
+          <t>Milho em Conserva Quero Lata 200g</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>364738</t>
+          <t>476625</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
+          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4.89</v>
+        <v>3.69</v>
       </c>
       <c r="F34" t="n">
-        <v>4.89</v>
+        <v>4.99</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2858,21 +2858,21 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>QUERO</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>2000043</v>
+        <v>2001778</v>
       </c>
       <c r="P34" t="n">
         <v>99999</v>
@@ -2881,43 +2881,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>milho-em-conserva-quero-lata-200g-476625</t>
+          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Milho em Conserva Quero Lata 200g</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>476625</t>
+          <t>105287</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
       <c r="F35" t="n">
-        <v>4.99</v>
+        <v>7.99</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-07-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2930,21 +2930,21 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>QUERO</t>
+          <t>DONA BENTA</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2001778</v>
+        <v>2000701</v>
       </c>
       <c r="P35" t="n">
         <v>99999</v>
@@ -2953,43 +2953,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>sal-refinado-iodado-ita-1kg-117293</t>
+          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>429392</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4.39</v>
+        <v>4.99</v>
       </c>
       <c r="F36" t="n">
-        <v>4.39</v>
+        <v>5.69</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3002,21 +3002,21 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2000066</v>
+        <v>2000027</v>
       </c>
       <c r="P36" t="n">
         <v>99999</v>
@@ -3025,115 +3025,115 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cebola-roxa-400g-38393</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cebola Roxa 400g</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>7.99</v>
+        <v>5.99</v>
       </c>
       <c r="F37" t="n">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2000015</v>
+        <v>2001532</v>
       </c>
       <c r="P37" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
+          <t>couve-manteiga-unidade-201235</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
+          <t>Couve Manteiga Unidade</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5106753</t>
+          <t>201235</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
+          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>11.99</v>
+        <v>3.79</v>
       </c>
       <c r="F38" t="n">
-        <v>11.99</v>
+        <v>3.79</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2021-01-11T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3146,21 +3146,21 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>2003319</v>
+        <v>2000015</v>
       </c>
       <c r="P38" t="n">
         <v>99999</v>
@@ -3169,29 +3169,29 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>couve-manteiga-unidade-201235</t>
+          <t>cebola-roxa-400g-38393</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Couve Manteiga Unidade</t>
+          <t>Cebola Roxa 400g</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>201235</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
+          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3.79</v>
+        <v>7.99</v>
       </c>
       <c r="F39" t="n">
-        <v>3.79</v>
+        <v>7.99</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3200,30 +3200,30 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3235,49 +3235,49 @@
         <v>2000015</v>
       </c>
       <c r="P39" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
+          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
+          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>429392</t>
+          <t>981168</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4.99</v>
+        <v>32.19</v>
       </c>
       <c r="F40" t="n">
-        <v>5.69</v>
+        <v>32.19</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-09-22T00:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3290,21 +3290,21 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>NEVE</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>2000027</v>
+        <v>2000291</v>
       </c>
       <c r="P40" t="n">
         <v>99999</v>
@@ -3313,43 +3313,43 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>5106753</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5.99</v>
+        <v>11.99</v>
       </c>
       <c r="F41" t="n">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2021-01-11T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3362,21 +3362,21 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2001532</v>
+        <v>2003319</v>
       </c>
       <c r="P41" t="n">
         <v>99999</v>
@@ -3385,43 +3385,43 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
+          <t>espinafre-unidade-200948</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
+          <t>Espinafre Unidade</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>981168</t>
+          <t>200948</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
+          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>32.19</v>
+        <v>3.79</v>
       </c>
       <c r="F42" t="n">
-        <v>32.19</v>
+        <v>3.79</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2020-09-22T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3434,93 +3434,93 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>NEVE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2000291</v>
+        <v>2000015</v>
       </c>
       <c r="P42" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
+          <t>matte-leao-natural-pet-15l-118214</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
+          <t>Matte Leão Natural Pet 1,5L</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>99279</t>
+          <t>118214</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
+          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>59.99</v>
+        <v>8.99</v>
       </c>
       <c r="F43" t="n">
-        <v>59.99</v>
+        <v>8.99</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2020-05-27T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>24684</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>2001012</v>
+        <v>2000010</v>
       </c>
       <c r="P43" t="n">
         <v>99999</v>
@@ -3529,70 +3529,70 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>matte-leao-natural-pet-15l-118214</t>
+          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Matte Leão Natural Pet 1,5L</t>
+          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>118214</t>
+          <t>99279</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
+          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>8.99</v>
+        <v>59.99</v>
       </c>
       <c r="F44" t="n">
-        <v>8.99</v>
+        <v>59.99</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-05-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>2000010</v>
+        <v>2001012</v>
       </c>
       <c r="P44" t="n">
         <v>99999</v>
@@ -3601,44 +3601,48 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-cariorta-1kg-98663</t>
+          <t>alface-crespa-unidade-200875</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Cariorta 1Kg</t>
+          <t>Alface Crespa Unidade</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>98663</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>200875</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
+        </is>
+      </c>
       <c r="E45" t="n">
-        <v>12.99</v>
+        <v>3.79</v>
       </c>
       <c r="F45" t="n">
-        <v>12.99</v>
+        <v>3.79</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3646,21 +3650,21 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P45" t="n">
         <v>99999</v>
@@ -3669,43 +3673,43 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>alface-crespa-unidade-200875</t>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Alface Crespa Unidade</t>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>200875</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3.79</v>
+        <v>31.98</v>
       </c>
       <c r="F46" t="n">
-        <v>3.79</v>
+        <v>37.9</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-07-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3718,21 +3722,21 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>MELITTA</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>2000015</v>
+        <v>2001329</v>
       </c>
       <c r="P46" t="n">
         <v>99999</v>
@@ -3741,43 +3745,39 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>melao-amarelo-metade-1-3-kg-63606</t>
+          <t>abobrinha-italiana-cariorta-1kg-98663</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Melão Amarelo Metade 1,3kg</t>
+          <t>Abobrinha Italiana Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>63606</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
-        </is>
-      </c>
+          <t>98663</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>5.99</v>
+        <v>16.99</v>
       </c>
       <c r="F47" t="n">
-        <v>5.99</v>
+        <v>16.99</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3786,25 +3786,25 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P47" t="n">
         <v>99999</v>
@@ -3813,70 +3813,70 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
+          <t>melao-amarelo-metade-1-3-kg-63606</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
+          <t>Melão Amarelo Metade 1,3kg</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>818640</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
+          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4.99</v>
+        <v>7.99</v>
       </c>
       <c r="F48" t="n">
-        <v>4.99</v>
+        <v>7.99</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2020-11-26T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>2002038</v>
+        <v>2000015</v>
       </c>
       <c r="P48" t="n">
         <v>99999</v>
@@ -3885,43 +3885,43 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>1105795</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>31.98</v>
+        <v>3.97</v>
       </c>
       <c r="F49" t="n">
-        <v>37.9</v>
+        <v>5.99</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2023-07-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3934,24 +3934,24 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2001329</v>
+        <v>2000017</v>
       </c>
       <c r="P49" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
   </sheetData>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -729,43 +729,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tomate-italiano-unidade-495212</t>
+          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tomate Italiano Unidade</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>495212</t>
+          <t>140805</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.7</v>
+        <v>4.49</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7</v>
+        <v>5.29</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-25T00:00:00Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -778,21 +778,21 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SAO LOURENCO</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2000015</v>
+        <v>2000145</v>
       </c>
       <c r="P5" t="n">
         <v>99999</v>
@@ -801,43 +801,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
+          <t>tomate-italiano-unidade-495212</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Tomate Italiano Unidade</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>140805</t>
+          <t>495212</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.49</v>
+        <v>1.7</v>
       </c>
       <c r="F6" t="n">
-        <v>5.29</v>
+        <v>1.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2020-09-25T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -850,21 +850,21 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>SAO LOURENCO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2000145</v>
+        <v>2000015</v>
       </c>
       <c r="P6" t="n">
         <v>99999</v>
@@ -1161,39 +1161,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>manga-palmer-unidade-5130760</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Manga Palmer Unidade</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>5130760</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
+        </is>
+      </c>
       <c r="E11" t="n">
-        <v>4.79</v>
+        <v>5.99</v>
       </c>
       <c r="F11" t="n">
         <v>5.99</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2023-02-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1206,21 +1210,21 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>31902</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2001952</v>
+        <v>2000015</v>
       </c>
       <c r="P11" t="n">
         <v>99999</v>
@@ -1229,43 +1233,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>manga-palmer-unidade-5130760</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Manga Palmer Unidade</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5130760</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>5.99</v>
+        <v>4.79</v>
       </c>
       <c r="F12" t="n">
         <v>5.99</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2023-02-16T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1278,21 +1278,21 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2000015</v>
+        <v>2001952</v>
       </c>
       <c r="P12" t="n">
         <v>99999</v>
@@ -1301,70 +1301,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cheiro-verde-unidade-201049</t>
+          <t>batata-inglesa-cariorta-12kg-98698</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cheiro Verde Unidade</t>
+          <t>Batata Inglesa Cariorta 1,2Kg</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>201049</t>
+          <t>98698</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3.39</v>
+        <v>7.99</v>
       </c>
       <c r="F13" t="n">
-        <v>3.39</v>
+        <v>7.99</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P13" t="n">
         <v>99999</v>
@@ -1373,70 +1373,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>batata-inglesa-cariorta-12kg-98698</t>
+          <t>cheiro-verde-unidade-201049</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Batata Inglesa Cariorta 1,2Kg</t>
+          <t>Cheiro Verde Unidade</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>201049</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7.99</v>
+        <v>3.39</v>
       </c>
       <c r="F14" t="n">
-        <v>7.99</v>
+        <v>3.39</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P14" t="n">
         <v>99999</v>
@@ -1589,70 +1589,66 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Pão Francês Panetto  60g Com 4 unidades</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
-        </is>
-      </c>
+          <t>96318</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>10.99</v>
+        <v>24.99</v>
       </c>
       <c r="F17" t="n">
-        <v>10.99</v>
+        <v>24.99</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2024-01-31T00:00:00Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PANETTO</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2000015</v>
+        <v>2000307</v>
       </c>
       <c r="P17" t="n">
         <v>99999</v>
@@ -1661,66 +1657,70 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pão Francês Panetto  60g Com 4 unidades</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>96318</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
+        </is>
+      </c>
       <c r="E18" t="n">
-        <v>24.99</v>
+        <v>10.99</v>
       </c>
       <c r="F18" t="n">
-        <v>24.99</v>
+        <v>10.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2024-01-31T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>PANETTO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2000307</v>
+        <v>2000015</v>
       </c>
       <c r="P18" t="n">
         <v>99999</v>
@@ -1729,17 +1729,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>limao-cariorta-1kg-98981</t>
+          <t>mamao-papaia-cariorta-12kg-99007</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Limão Cariorta 1Kg</t>
+          <t>Mamão Papaia Cariorta 1,2kg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>98981</t>
+          <t>99007</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>11.99</v>
+        <v>9.99</v>
       </c>
       <c r="F19" t="n">
-        <v>11.99</v>
+        <v>9.99</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1774,16 +1774,16 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1801,17 +1801,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mamao-papaia-cariorta-12kg-99007</t>
+          <t>limao-cariorta-1kg-98981</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mamão Papaia Cariorta 1,2kg</t>
+          <t>Limão Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>99007</t>
+          <t>98981</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9.99</v>
+        <v>11.99</v>
       </c>
       <c r="F20" t="n">
-        <v>9.99</v>
+        <v>11.99</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1846,16 +1846,16 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2233,43 +2233,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>429376</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3.99</v>
+        <v>4.38</v>
       </c>
       <c r="F26" t="n">
-        <v>3.99</v>
+        <v>5.69</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2282,21 +2282,21 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>2000027</v>
+        <v>2000400</v>
       </c>
       <c r="P26" t="n">
         <v>99999</v>
@@ -2305,43 +2305,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>364738</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4.38</v>
+        <v>4.89</v>
       </c>
       <c r="F27" t="n">
-        <v>5.69</v>
+        <v>4.89</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2354,21 +2354,21 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>2000400</v>
+        <v>2000043</v>
       </c>
       <c r="P27" t="n">
         <v>99999</v>
@@ -2377,43 +2377,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
+          <t>abobrinha-italiana-unidade-423513</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>129887</t>
+          <t>423513</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>12.99</v>
+        <v>5.25</v>
       </c>
       <c r="F28" t="n">
-        <v>12.99</v>
+        <v>5.25</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-12-07T00:00:00Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2426,21 +2426,21 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>2001401</v>
+        <v>2000015</v>
       </c>
       <c r="P28" t="n">
         <v>99999</v>
@@ -2449,43 +2449,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-unidade-423513</t>
+          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>290564</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5.25</v>
+        <v>23.99</v>
       </c>
       <c r="F29" t="n">
-        <v>5.25</v>
+        <v>26.99</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2020-12-07T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2498,21 +2498,21 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SADIA</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2000015</v>
+        <v>2000057</v>
       </c>
       <c r="P29" t="n">
         <v>99999</v>
@@ -2593,43 +2593,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
+          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>290564</t>
+          <t>429376</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>23.99</v>
+        <v>3.99</v>
       </c>
       <c r="F31" t="n">
-        <v>26.99</v>
+        <v>3.99</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2642,21 +2642,21 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>SADIA</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>2000057</v>
+        <v>2000027</v>
       </c>
       <c r="P31" t="n">
         <v>99999</v>
@@ -2665,43 +2665,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>364738</t>
+          <t>129887</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
+          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4.89</v>
+        <v>12.99</v>
       </c>
       <c r="F32" t="n">
-        <v>4.89</v>
+        <v>12.99</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2714,21 +2714,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2000043</v>
+        <v>2001401</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2737,43 +2737,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>sal-refinado-iodado-ita-1kg-117293</t>
+          <t>milho-em-conserva-quero-lata-200g-476625</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Milho em Conserva Quero Lata 200g</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>476625</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4.39</v>
+        <v>3.69</v>
       </c>
       <c r="F33" t="n">
-        <v>4.39</v>
+        <v>4.99</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2786,21 +2786,21 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>QUERO</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2000066</v>
+        <v>2001778</v>
       </c>
       <c r="P33" t="n">
         <v>99999</v>
@@ -2809,43 +2809,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>milho-em-conserva-quero-lata-200g-476625</t>
+          <t>sal-refinado-iodado-ita-1kg-117293</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Milho em Conserva Quero Lata 200g</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>476625</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3.69</v>
+        <v>4.39</v>
       </c>
       <c r="F34" t="n">
-        <v>4.99</v>
+        <v>4.39</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2858,66 +2858,66 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>QUERO</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>2001778</v>
+        <v>2000066</v>
       </c>
       <c r="P34" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
+          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>105287</t>
+          <t>429392</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
       <c r="F35" t="n">
-        <v>7.99</v>
+        <v>5.69</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-07-06T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2930,21 +2930,21 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>DONA BENTA</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2000701</v>
+        <v>2000027</v>
       </c>
       <c r="P35" t="n">
         <v>99999</v>
@@ -2953,43 +2953,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>429392</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
       <c r="F36" t="n">
-        <v>5.69</v>
+        <v>6.99</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3002,21 +3002,21 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2000027</v>
+        <v>2001532</v>
       </c>
       <c r="P36" t="n">
         <v>99999</v>
@@ -3025,43 +3025,43 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>105287</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>5.99</v>
       </c>
       <c r="F37" t="n">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-07-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3074,21 +3074,21 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>DONA BENTA</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2001532</v>
+        <v>2000701</v>
       </c>
       <c r="P37" t="n">
         <v>99999</v>
@@ -3097,29 +3097,29 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>couve-manteiga-unidade-201235</t>
+          <t>cebola-roxa-400g-38393</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Couve Manteiga Unidade</t>
+          <t>Cebola Roxa 400g</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>201235</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
+          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3.79</v>
+        <v>7.99</v>
       </c>
       <c r="F38" t="n">
-        <v>3.79</v>
+        <v>7.99</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3128,30 +3128,30 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3163,35 +3163,35 @@
         <v>2000015</v>
       </c>
       <c r="P38" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cebola-roxa-400g-38393</t>
+          <t>couve-manteiga-unidade-201235</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cebola Roxa 400g</t>
+          <t>Couve Manteiga Unidade</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>201235</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
+          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>7.99</v>
+        <v>3.79</v>
       </c>
       <c r="F39" t="n">
-        <v>7.99</v>
+        <v>3.79</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3200,30 +3200,30 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3235,7 +3235,7 @@
         <v>2000015</v>
       </c>
       <c r="P39" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="40">
@@ -3601,61 +3601,61 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>alface-crespa-unidade-200875</t>
+          <t>melao-amarelo-metade-1-3-kg-63606</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Alface Crespa Unidade</t>
+          <t>Melão Amarelo Metade 1,3kg</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>200875</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
+          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3.79</v>
+        <v>7.99</v>
       </c>
       <c r="F45" t="n">
-        <v>3.79</v>
+        <v>7.99</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3673,48 +3673,44 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>abobrinha-italiana-cariorta-1kg-98663</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Abobrinha Italiana Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>103845</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
-        </is>
-      </c>
+          <t>98663</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>31.98</v>
+        <v>16.99</v>
       </c>
       <c r="F46" t="n">
-        <v>37.9</v>
+        <v>16.99</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3722,21 +3718,21 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>2001329</v>
+        <v>2001012</v>
       </c>
       <c r="P46" t="n">
         <v>99999</v>
@@ -3745,44 +3741,48 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-cariorta-1kg-98663</t>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Cariorta 1Kg</t>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>98663</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>103845</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+        </is>
+      </c>
       <c r="E47" t="n">
-        <v>16.99</v>
+        <v>31.98</v>
       </c>
       <c r="F47" t="n">
-        <v>16.99</v>
+        <v>37.9</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-07-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3790,21 +3790,21 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>MELITTA</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>2001012</v>
+        <v>2001329</v>
       </c>
       <c r="P47" t="n">
         <v>99999</v>
@@ -3813,61 +3813,61 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>melao-amarelo-metade-1-3-kg-63606</t>
+          <t>alface-crespa-unidade-200875</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Melão Amarelo Metade 1,3kg</t>
+          <t>Alface Crespa Unidade</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>200875</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
+          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>7.99</v>
+        <v>3.79</v>
       </c>
       <c r="F48" t="n">
-        <v>7.99</v>
+        <v>3.79</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,43 +513,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>matte-leao-limao-pet-1-5l-118222</t>
+          <t>rucula-unidade-201006</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Matte Leão Limão Pet 1,5L</t>
+          <t>Rúcula Unidade</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>118222</t>
+          <t>201006</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
+          <t>A rúcula é uma hortaliça de baixa caloria (aprox. 29 kcal/100g) e rica em nutrientes como vitaminas A, C e K, além de cálcio, ferro e potássio. Seus principais benefícios incluem ação antioxidante, fortalecimento do sistema imunológico, melhoria da saúde ocular e óssea, auxílio na digestão, controle do colesterol e redução de riscos cardiovasculares.A melhor forma de comer rúcula é crua em saladas, temperada com azeite, sal e limão, mas também é versátil em pratos quentes como massas, risotos e sanduíches, ou refogada rapidamente</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8.99</v>
+        <v>2.99</v>
       </c>
       <c r="F2" t="n">
-        <v>8.99</v>
+        <v>3.79</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3040890/VF4qT-qqCUAAAAAAAAHLpQ.jpg?v=637792545082200000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -562,21 +562,21 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>2000010</v>
+        <v>2000015</v>
       </c>
       <c r="P2" t="n">
         <v>99999</v>
@@ -585,43 +585,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ovos-brancos-jumbo-mantiqueira-com-10-unidades-437638</t>
+          <t>matte-leao-limao-pet-1-5l-118222</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ovos Brancos Jumbo Mantiqueira Com 10 Unidades</t>
+          <t>Matte Leão Limão Pet 1,5L</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>437638</t>
+          <t>118222</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Os Ovos Jumbo Mantiqueira possuem maior tamanho, ideais para quem busca uma alimentação rica em vitaminas, proteínas e minerais, ou para quem gosta de um maior rendimento em suas receitas. Um único ovo contém quase todos os nutrientes necessários para manter o corpo saudável, fortalecendo os ossos e auxiliando em dietas para perda de peso ou ganho de massa.O Ovo Jumbo Mantiqueira é um produto da linha Especial da marca e possui a qualidade superior, passando por um moderno sistema de seleção, limpeza e embalagem sem contato de mãos humanas.Especificações:Ovos maiores, tamanho família.Embalagem com 10 unidades.Ovos brancos e vermelhos tipo jumbo categoria A.</t>
+          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10.9</v>
+        <v>8.99</v>
       </c>
       <c r="F3" t="n">
-        <v>10.9</v>
+        <v>8.99</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3976126/VF4qT-qqCUAAAAAAAAh4RA.jpg?v=638769994856100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -634,66 +634,66 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MANTIQUEIRA</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2001056</v>
+        <v>2000010</v>
       </c>
       <c r="P3" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>alcool-montenegro-46-1-l-780570</t>
+          <t>ovos-brancos-jumbo-mantiqueira-com-10-unidades-437638</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Álcool Montenegro 46% 1 L</t>
+          <t>Ovos Brancos Jumbo Mantiqueira Com 10 Unidades</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>780570</t>
+          <t>437638</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Álcool Montenegro 46% 1 L</t>
+          <t>Os Ovos Jumbo Mantiqueira possuem maior tamanho, ideais para quem busca uma alimentação rica em vitaminas, proteínas e minerais, ou para quem gosta de um maior rendimento em suas receitas. Um único ovo contém quase todos os nutrientes necessários para manter o corpo saudável, fortalecendo os ossos e auxiliando em dietas para perda de peso ou ganho de massa.O Ovo Jumbo Mantiqueira é um produto da linha Especial da marca e possui a qualidade superior, passando por um moderno sistema de seleção, limpeza e embalagem sem contato de mãos humanas.Especificações:Ovos maiores, tamanho família.Embalagem com 10 unidades.Ovos brancos e vermelhos tipo jumbo categoria A.</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8.789999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="F4" t="n">
-        <v>8.789999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2020-10-06T10:47:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051579/VF4qT-qqCUAAAAAAAAG3pQ.jpg?v=637793390624870000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3976126/VF4qT-qqCUAAAAAAAAh4RA.jpg?v=638769994856100000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -706,66 +706,66 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>11598</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>MONTENEGRO</t>
+          <t>MANTIQUEIRA</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>2000527</v>
+        <v>2001056</v>
       </c>
       <c r="P4" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
+          <t>alcool-montenegro-46-1-l-780570</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Álcool Montenegro 46% 1 L</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>140805</t>
+          <t>780570</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Álcool Montenegro 46% 1 L</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4.49</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>5.29</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2020-09-25T00:00:00Z</t>
+          <t>2020-10-06T10:47:00Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051579/VF4qT-qqCUAAAAAAAAG3pQ.jpg?v=637793390624870000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -778,21 +778,21 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>11598</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>SAO LOURENCO</t>
+          <t>MONTENEGRO</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2000145</v>
+        <v>2000527</v>
       </c>
       <c r="P5" t="n">
         <v>99999</v>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="F6" t="n">
         <v>1.7</v>
@@ -873,43 +873,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
+          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>828025</t>
+          <t>140805</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>29.98</v>
+        <v>4.49</v>
       </c>
       <c r="F7" t="n">
-        <v>43.9</v>
+        <v>5.29</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-25T00:00:00Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -922,21 +922,21 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>PILAO</t>
+          <t>SAO LOURENCO</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2000070</v>
+        <v>2000145</v>
       </c>
       <c r="P7" t="n">
         <v>99999</v>
@@ -945,43 +945,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
+          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
+          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>370550</t>
+          <t>828025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
+          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>24.99</v>
+        <v>29.98</v>
       </c>
       <c r="F8" t="n">
-        <v>24.99</v>
+        <v>43.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -994,66 +994,66 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>PILAO</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2003319</v>
+        <v>2000070</v>
       </c>
       <c r="P8" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>uva-preta-sem-semente-500-g-674583</t>
+          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Uva Preta Sem Semente 500g</t>
+          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>674583</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
+          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>11.99</v>
+        <v>24.99</v>
       </c>
       <c r="F9" t="n">
-        <v>11.99</v>
+        <v>24.99</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1066,24 +1066,24 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2000015</v>
+        <v>2003319</v>
       </c>
       <c r="P9" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -1161,29 +1161,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>manga-palmer-unidade-5130760</t>
+          <t>uva-preta-sem-semente-500-g-674583</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Manga Palmer Unidade</t>
+          <t>Uva Preta Sem Semente 500g</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5130760</t>
+          <t>674583</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
+          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.99</v>
+        <v>11.99</v>
       </c>
       <c r="F11" t="n">
-        <v>5.99</v>
+        <v>11.99</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2023-02-16T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1233,39 +1233,43 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>manga-palmer-unidade-5130760</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Manga Palmer Unidade</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>5130760</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
+        </is>
+      </c>
       <c r="E12" t="n">
-        <v>4.79</v>
+        <v>4.77</v>
       </c>
       <c r="F12" t="n">
         <v>5.99</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2023-02-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1278,21 +1282,21 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>31902</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2001952</v>
+        <v>2000015</v>
       </c>
       <c r="P12" t="n">
         <v>99999</v>
@@ -1301,70 +1305,66 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>batata-inglesa-cariorta-12kg-98698</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Batata Inglesa Cariorta 1,2Kg</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>98698</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Cariorta selecionados de coração.</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>7.99</v>
+        <v>4.79</v>
       </c>
       <c r="F13" t="n">
-        <v>7.99</v>
+        <v>5.99</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2001012</v>
+        <v>2001952</v>
       </c>
       <c r="P13" t="n">
         <v>99999</v>
@@ -1373,70 +1373,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cheiro-verde-unidade-201049</t>
+          <t>batata-inglesa-cariorta-12kg-98698</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cheiro Verde Unidade</t>
+          <t>Batata Inglesa Cariorta 1,2Kg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>201049</t>
+          <t>98698</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3.39</v>
+        <v>7.99</v>
       </c>
       <c r="F14" t="n">
-        <v>3.39</v>
+        <v>7.99</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P14" t="n">
         <v>99999</v>
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.9</v>
+        <v>2.49</v>
       </c>
       <c r="F15" t="n">
         <v>2.49</v>
@@ -1517,43 +1517,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>morango-250g-289612</t>
+          <t>cheiro-verde-unidade-201049</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Morango 250g</t>
+          <t>Cheiro Verde Unidade</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>289612</t>
+          <t>201049</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
+          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>9.99</v>
+        <v>2.99</v>
       </c>
       <c r="F16" t="n">
-        <v>9.99</v>
+        <v>3.39</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1589,39 +1589,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
+          <t>mamao-papaia-cariorta-12kg-99007</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pão Francês Panetto  60g Com 4 unidades</t>
+          <t>Mamão Papaia Cariorta 1,2kg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>96318</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>99007</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Cariorta selecionados de coração.</t>
+        </is>
+      </c>
       <c r="E17" t="n">
-        <v>24.99</v>
+        <v>9.99</v>
       </c>
       <c r="F17" t="n">
-        <v>24.99</v>
+        <v>9.99</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2024-01-31T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1630,25 +1634,25 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.24</v>
+        <v>1.2</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>PANETTO</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2000307</v>
+        <v>2001012</v>
       </c>
       <c r="P17" t="n">
         <v>99999</v>
@@ -1657,70 +1661,66 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Pão Francês Panetto  60g Com 4 unidades</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
-        </is>
-      </c>
+          <t>96318</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>10.99</v>
+        <v>24.99</v>
       </c>
       <c r="F18" t="n">
-        <v>10.99</v>
+        <v>24.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2024-01-31T00:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PANETTO</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2000015</v>
+        <v>2000307</v>
       </c>
       <c r="P18" t="n">
         <v>99999</v>
@@ -1729,22 +1729,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mamao-papaia-cariorta-12kg-99007</t>
+          <t>morango-250g-289612</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mamão Papaia Cariorta 1,2kg</t>
+          <t>Morango 250g</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>99007</t>
+          <t>289612</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1755,44 +1755,44 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P19" t="n">
         <v>99999</v>
@@ -1801,48 +1801,48 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>limao-cariorta-1kg-98981</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Limão Cariorta 1Kg</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>98981</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>11.99</v>
+        <v>9.99</v>
       </c>
       <c r="F20" t="n">
-        <v>11.99</v>
+        <v>10.99</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1850,21 +1850,21 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P20" t="n">
         <v>99999</v>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9.99</v>
+        <v>9.59</v>
       </c>
       <c r="F21" t="n">
         <v>9.99</v>
@@ -1945,48 +1945,48 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-238cm×218cm-50-unidades-129879</t>
+          <t>limao-cariorta-1kg-98981</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel 23,8cm×21,8cm 50 Unidades</t>
+          <t>Limão Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>129879</t>
+          <t>98981</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel 23,8cm×21,8cm 50 Unidades</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6.19</v>
+        <v>11.99</v>
       </c>
       <c r="F22" t="n">
-        <v>6.19</v>
+        <v>11.99</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3239421/VF4qT-qqCUAAAAAAAAVSfw.jpg?v=638362188224230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1994,21 +1994,21 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>9438</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2001400</v>
+        <v>2001012</v>
       </c>
       <c r="P22" t="n">
         <v>99999</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.69</v>
+        <v>2.29</v>
       </c>
       <c r="F23" t="n">
         <v>2.69</v>
@@ -2089,43 +2089,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>coentro-unidade-200930</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-238cm×218cm-50-unidades-129879</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Coentro Unidade</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel 23,8cm×21,8cm 50 Unidades</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>200930</t>
+          <t>129879</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel 23,8cm×21,8cm 50 Unidades</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.79</v>
+        <v>6.19</v>
       </c>
       <c r="F24" t="n">
-        <v>3.79</v>
+        <v>6.19</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3239421/VF4qT-qqCUAAAAAAAAVSfw.jpg?v=638362188224230000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2138,21 +2138,21 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>2000015</v>
+        <v>2001400</v>
       </c>
       <c r="P24" t="n">
         <v>99999</v>
@@ -2161,43 +2161,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
+          <t>coentro-unidade-200930</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
+          <t>Coentro Unidade</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1180320</t>
+          <t>200930</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
+          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
         </is>
       </c>
       <c r="E25" t="n">
         <v>2.99</v>
       </c>
       <c r="F25" t="n">
-        <v>2.99</v>
+        <v>3.79</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2025-07-17T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2210,21 +2210,21 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>41057</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>BOMBRIL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>2001389</v>
+        <v>2000015</v>
       </c>
       <c r="P25" t="n">
         <v>99999</v>
@@ -2233,43 +2233,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>1180320</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4.38</v>
+        <v>2.99</v>
       </c>
       <c r="F26" t="n">
-        <v>5.69</v>
+        <v>2.99</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2025-07-17T00:00:00Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2282,21 +2282,21 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>BOMBRIL</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>2000400</v>
+        <v>2001389</v>
       </c>
       <c r="P26" t="n">
         <v>99999</v>
@@ -2377,43 +2377,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-unidade-423513</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5.25</v>
+        <v>4.38</v>
       </c>
       <c r="F28" t="n">
-        <v>5.25</v>
+        <v>5.69</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2020-12-07T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2426,21 +2426,21 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>2000015</v>
+        <v>2000400</v>
       </c>
       <c r="P28" t="n">
         <v>99999</v>
@@ -2449,43 +2449,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
+          <t>abobrinha-italiana-unidade-423513</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>290564</t>
+          <t>423513</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>23.99</v>
+        <v>5.25</v>
       </c>
       <c r="F29" t="n">
-        <v>26.99</v>
+        <v>5.25</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-12-07T00:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2498,21 +2498,21 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>SADIA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2000057</v>
+        <v>2000015</v>
       </c>
       <c r="P29" t="n">
         <v>99999</v>
@@ -2521,43 +2521,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>leite-uht-piracanjuba-integral-1l-865427</t>
+          <t>milho-em-conserva-quero-lata-200g-476625</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Leite Uht Piracanjuba Integral 1L</t>
+          <t>Milho em Conserva Quero Lata 200g</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>865427</t>
+          <t>476625</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
+          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5.59</v>
+        <v>3.69</v>
       </c>
       <c r="F30" t="n">
-        <v>5.59</v>
+        <v>4.99</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2017-04-12T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2570,21 +2570,21 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>QUERO</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2002038</v>
+        <v>2001778</v>
       </c>
       <c r="P30" t="n">
         <v>99999</v>
@@ -2593,43 +2593,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
+          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
+          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>429376</t>
+          <t>290564</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3.99</v>
+        <v>23.99</v>
       </c>
       <c r="F31" t="n">
-        <v>3.99</v>
+        <v>26.99</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2642,66 +2642,66 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>SADIA</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>2000027</v>
+        <v>2000057</v>
       </c>
       <c r="P31" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
+          <t>leite-uht-piracanjuba-integral-1l-865427</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
+          <t>Leite Uht Piracanjuba Integral 1L</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>129887</t>
+          <t>865427</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>12.99</v>
+        <v>5.59</v>
       </c>
       <c r="F32" t="n">
-        <v>12.99</v>
+        <v>5.59</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2017-04-12T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2714,21 +2714,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>23232</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>23158</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2001401</v>
+        <v>2002038</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2737,43 +2737,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>milho-em-conserva-quero-lata-200g-476625</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Milho em Conserva Quero Lata 200g</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>476625</t>
+          <t>129887</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
+          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3.69</v>
+        <v>12.99</v>
       </c>
       <c r="F33" t="n">
-        <v>4.99</v>
+        <v>12.99</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2786,21 +2786,21 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>QUERO</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2001778</v>
+        <v>2001401</v>
       </c>
       <c r="P33" t="n">
         <v>99999</v>
@@ -2809,43 +2809,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sal-refinado-iodado-ita-1kg-117293</t>
+          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>429376</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4.39</v>
+        <v>3.99</v>
       </c>
       <c r="F34" t="n">
-        <v>4.39</v>
+        <v>3.99</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2858,66 +2858,66 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>2000066</v>
+        <v>2000027</v>
       </c>
       <c r="P34" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
+          <t>sal-refinado-iodado-ita-1kg-117293</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>429392</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4.99</v>
+        <v>4.39</v>
       </c>
       <c r="F35" t="n">
-        <v>5.69</v>
+        <v>4.39</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2930,21 +2930,21 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2000027</v>
+        <v>2000066</v>
       </c>
       <c r="P35" t="n">
         <v>99999</v>
@@ -2953,43 +2953,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>429392</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
       <c r="F36" t="n">
-        <v>6.99</v>
+        <v>5.69</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3002,21 +3002,21 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2001532</v>
+        <v>2000027</v>
       </c>
       <c r="P36" t="n">
         <v>99999</v>
@@ -3025,43 +3025,43 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>105287</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>5.99</v>
       </c>
       <c r="F37" t="n">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2020-07-06T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3074,21 +3074,21 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>DONA BENTA</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2000701</v>
+        <v>2001532</v>
       </c>
       <c r="P37" t="n">
         <v>99999</v>
@@ -3097,29 +3097,29 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cebola-roxa-400g-38393</t>
+          <t>couve-manteiga-unidade-201235</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cebola Roxa 400g</t>
+          <t>Couve Manteiga Unidade</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>201235</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
+          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>7.99</v>
+        <v>2.99</v>
       </c>
       <c r="F38" t="n">
-        <v>7.99</v>
+        <v>3.79</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3128,30 +3128,30 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3163,49 +3163,49 @@
         <v>2000015</v>
       </c>
       <c r="P38" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>couve-manteiga-unidade-201235</t>
+          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Couve Manteiga Unidade</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>201235</t>
+          <t>105287</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3.79</v>
+        <v>5.99</v>
       </c>
       <c r="F39" t="n">
-        <v>3.79</v>
+        <v>7.99</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-07-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3218,21 +3218,21 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>DONA BENTA</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>2000015</v>
+        <v>2000701</v>
       </c>
       <c r="P39" t="n">
         <v>99999</v>
@@ -3241,73 +3241,73 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
+          <t>cebola-roxa-400g-38393</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
+          <t>Cebola Roxa 400g</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>981168</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
+          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>32.19</v>
+        <v>7.99</v>
       </c>
       <c r="F40" t="n">
-        <v>32.19</v>
+        <v>7.99</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2020-09-22T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>NEVE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>2000291</v>
+        <v>2000015</v>
       </c>
       <c r="P40" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41">
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3.79</v>
+        <v>2.99</v>
       </c>
       <c r="F42" t="n">
         <v>3.79</v>
@@ -3457,43 +3457,43 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>matte-leao-natural-pet-15l-118214</t>
+          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Matte Leão Natural Pet 1,5L</t>
+          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>118214</t>
+          <t>981168</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
+          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8.99</v>
+        <v>32.19</v>
       </c>
       <c r="F43" t="n">
-        <v>8.99</v>
+        <v>32.19</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-09-22T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3506,21 +3506,21 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>NEVE</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>2000010</v>
+        <v>2000291</v>
       </c>
       <c r="P43" t="n">
         <v>99999</v>
@@ -3601,70 +3601,70 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>melao-amarelo-metade-1-3-kg-63606</t>
+          <t>matte-leao-natural-pet-15l-118214</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Melão Amarelo Metade 1,3kg</t>
+          <t>Matte Leão Natural Pet 1,5L</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>118214</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
+          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>7.99</v>
+        <v>8.99</v>
       </c>
       <c r="F45" t="n">
-        <v>7.99</v>
+        <v>8.99</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2000015</v>
+        <v>2000010</v>
       </c>
       <c r="P45" t="n">
         <v>99999</v>
@@ -3741,70 +3741,70 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>melao-amarelo-metade-1-3-kg-63606</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Melão Amarelo Metade 1,3kg</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>31.98</v>
+        <v>6.99</v>
       </c>
       <c r="F47" t="n">
-        <v>37.9</v>
+        <v>7.99</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>2001329</v>
+        <v>2000015</v>
       </c>
       <c r="P47" t="n">
         <v>99999</v>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3.79</v>
+        <v>2.99</v>
       </c>
       <c r="F48" t="n">
         <v>3.79</v>
@@ -3885,72 +3885,144 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>103845</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="F49" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2020-07-13T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>MELITTA</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>2001329</v>
+      </c>
+      <c r="P49" t="n">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>1105795</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
-      <c r="E49" t="n">
+      <c r="E50" t="n">
         <v>3.97</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F50" t="n">
         <v>5.99</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>2023-07-26T00:00:00Z</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="K49" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" t="inlineStr">
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>33955</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>33882</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>PIRAQUE</t>
         </is>
       </c>
-      <c r="O49" t="n">
+      <c r="O50" t="n">
         <v>2000017</v>
       </c>
-      <c r="P49" t="n">
+      <c r="P50" t="n">
         <v>99999</v>
       </c>
     </row>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,43 +513,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rucula-unidade-201006</t>
+          <t>matte-leao-limao-pet-1-5l-118222</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rúcula Unidade</t>
+          <t>Matte Leão Limão Pet 1,5L</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>201006</t>
+          <t>118222</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A rúcula é uma hortaliça de baixa caloria (aprox. 29 kcal/100g) e rica em nutrientes como vitaminas A, C e K, além de cálcio, ferro e potássio. Seus principais benefícios incluem ação antioxidante, fortalecimento do sistema imunológico, melhoria da saúde ocular e óssea, auxílio na digestão, controle do colesterol e redução de riscos cardiovasculares.A melhor forma de comer rúcula é crua em saladas, temperada com azeite, sal e limão, mas também é versátil em pratos quentes como massas, risotos e sanduíches, ou refogada rapidamente</t>
+          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2.99</v>
+        <v>7.49</v>
       </c>
       <c r="F2" t="n">
-        <v>3.79</v>
+        <v>8.99</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3040890/VF4qT-qqCUAAAAAAAAHLpQ.jpg?v=637792545082200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -562,21 +562,21 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>2000015</v>
+        <v>2000010</v>
       </c>
       <c r="P2" t="n">
         <v>99999</v>
@@ -585,43 +585,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>matte-leao-limao-pet-1-5l-118222</t>
+          <t>alcool-montenegro-46-1-l-780570</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Matte Leão Limão Pet 1,5L</t>
+          <t>Álcool Montenegro 46% 1 L</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>118222</t>
+          <t>780570</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
+          <t>Álcool Montenegro 46% 1 L</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8.99</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>8.99</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-10-06T10:47:00Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051579/VF4qT-qqCUAAAAAAAAG3pQ.jpg?v=637793390624870000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -634,21 +634,21 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>11598</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>MONTENEGRO</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2000010</v>
+        <v>2000527</v>
       </c>
       <c r="P3" t="n">
         <v>99999</v>
@@ -657,33 +657,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ovos-brancos-jumbo-mantiqueira-com-10-unidades-437638</t>
+          <t>tomate-italiano-unidade-495212</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ovos Brancos Jumbo Mantiqueira Com 10 Unidades</t>
+          <t>Tomate Italiano Unidade</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>437638</t>
+          <t>495212</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Os Ovos Jumbo Mantiqueira possuem maior tamanho, ideais para quem busca uma alimentação rica em vitaminas, proteínas e minerais, ou para quem gosta de um maior rendimento em suas receitas. Um único ovo contém quase todos os nutrientes necessários para manter o corpo saudável, fortalecendo os ossos e auxiliando em dietas para perda de peso ou ganho de massa.O Ovo Jumbo Mantiqueira é um produto da linha Especial da marca e possui a qualidade superior, passando por um moderno sistema de seleção, limpeza e embalagem sem contato de mãos humanas.Especificações:Ovos maiores, tamanho família.Embalagem com 10 unidades.Ovos brancos e vermelhos tipo jumbo categoria A.</t>
+          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10.9</v>
+        <v>1.18</v>
       </c>
       <c r="F4" t="n">
-        <v>10.9</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3976126/VF4qT-qqCUAAAAAAAAh4RA.jpg?v=638769994856100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -706,66 +706,66 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>MANTIQUEIRA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>2001056</v>
+        <v>2000015</v>
       </c>
       <c r="P4" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>alcool-montenegro-46-1-l-780570</t>
+          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Álcool Montenegro 46% 1 L</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>780570</t>
+          <t>140805</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Álcool Montenegro 46% 1 L</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8.789999999999999</v>
+        <v>4.29</v>
       </c>
       <c r="F5" t="n">
-        <v>8.789999999999999</v>
+        <v>5.29</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2020-10-06T10:47:00Z</t>
+          <t>2020-09-25T00:00:00Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051579/VF4qT-qqCUAAAAAAAAG3pQ.jpg?v=637793390624870000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -778,21 +778,21 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>11598</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>MONTENEGRO</t>
+          <t>SAO LOURENCO</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2000527</v>
+        <v>2000145</v>
       </c>
       <c r="P5" t="n">
         <v>99999</v>
@@ -801,43 +801,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tomate-italiano-unidade-495212</t>
+          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tomate Italiano Unidade</t>
+          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>495212</t>
+          <t>828025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
+          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.18</v>
+        <v>29.98</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7</v>
+        <v>43.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -850,21 +850,21 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PILAO</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2000015</v>
+        <v>2000070</v>
       </c>
       <c r="P6" t="n">
         <v>99999</v>
@@ -873,43 +873,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
+          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>140805</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.49</v>
+        <v>24.99</v>
       </c>
       <c r="F7" t="n">
-        <v>5.29</v>
+        <v>24.99</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2020-09-25T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -922,93 +922,93 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>SAO LOURENCO</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2000145</v>
+        <v>2003319</v>
       </c>
       <c r="P7" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
+          <t>mucarela-em-fatias-92363</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
+          <t>Muçarela  em Fatias 200g</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>828025</t>
+          <t>92363</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
+          <t>Muçarela em Fatias</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>29.98</v>
+        <v>59.9</v>
       </c>
       <c r="F8" t="n">
-        <v>43.9</v>
+        <v>59.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>PILAO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2000070</v>
+        <v>2000015</v>
       </c>
       <c r="P8" t="n">
         <v>99999</v>
@@ -1017,43 +1017,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
+          <t>manga-palmer-unidade-5130760</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
+          <t>Manga Palmer Unidade</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>370550</t>
+          <t>5130760</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
+          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>24.99</v>
+        <v>4.77</v>
       </c>
       <c r="F9" t="n">
-        <v>24.99</v>
+        <v>5.99</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2023-02-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1066,84 +1066,84 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>31902</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2003319</v>
+        <v>2000015</v>
       </c>
       <c r="P9" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mucarela-em-fatias-92363</t>
+          <t>uva-preta-sem-semente-500-g-674583</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Muçarela  em Fatias 200g</t>
+          <t>Uva Preta Sem Semente 500g</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>92363</t>
+          <t>674583</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Muçarela em Fatias</t>
+          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>59.9</v>
+        <v>11.99</v>
       </c>
       <c r="F10" t="n">
-        <v>59.9</v>
+        <v>11.99</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1161,43 +1161,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>uva-preta-sem-semente-500-g-674583</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Uva Preta Sem Semente 500g</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>674583</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
       <c r="F11" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1210,93 +1206,93 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2000015</v>
+        <v>2001952</v>
       </c>
       <c r="P11" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>manga-palmer-unidade-5130760</t>
+          <t>batata-inglesa-cariorta-12kg-98698</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Manga Palmer Unidade</t>
+          <t>Batata Inglesa Cariorta 1,2Kg</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5130760</t>
+          <t>98698</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4.77</v>
+        <v>7.99</v>
       </c>
       <c r="F12" t="n">
-        <v>5.99</v>
+        <v>7.99</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2023-02-16T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P12" t="n">
         <v>99999</v>
@@ -1305,29 +1301,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Detergente Para Louças Odd Clear 500ml</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>982911</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ODD voltou!Alto rendimento , controle de odor.</t>
+        </is>
+      </c>
       <c r="E13" t="n">
-        <v>4.79</v>
+        <v>1.9</v>
       </c>
       <c r="F13" t="n">
-        <v>5.99</v>
+        <v>2.49</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1350,21 +1350,21 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>LIMPPANO</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2001952</v>
+        <v>2001341</v>
       </c>
       <c r="P13" t="n">
         <v>99999</v>
@@ -1373,70 +1373,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>batata-inglesa-cariorta-12kg-98698</t>
+          <t>cheiro-verde-unidade-201049</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Batata Inglesa Cariorta 1,2Kg</t>
+          <t>Cheiro Verde Unidade</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>201049</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7.99</v>
+        <v>2.99</v>
       </c>
       <c r="F14" t="n">
-        <v>7.99</v>
+        <v>3.39</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P14" t="n">
         <v>99999</v>
@@ -1445,70 +1445,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
+          <t>mamao-papaia-cariorta-12kg-99007</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Odd Clear 500ml</t>
+          <t>Mamão Papaia Cariorta 1,2kg</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>982911</t>
+          <t>99007</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ODD voltou!Alto rendimento , controle de odor.</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2.49</v>
+        <v>9.99</v>
       </c>
       <c r="F15" t="n">
-        <v>2.49</v>
+        <v>9.99</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>LIMPPANO</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2001341</v>
+        <v>2001012</v>
       </c>
       <c r="P15" t="n">
         <v>99999</v>
@@ -1517,70 +1517,66 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cheiro-verde-unidade-201049</t>
+          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cheiro Verde Unidade</t>
+          <t>Pão Francês Panetto  60g Com 4 unidades</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>201049</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
-        </is>
-      </c>
+          <t>96318</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>2.99</v>
+        <v>24.99</v>
       </c>
       <c r="F16" t="n">
-        <v>3.39</v>
+        <v>24.99</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2024-01-31T00:00:00Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PANETTO</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2000015</v>
+        <v>2000307</v>
       </c>
       <c r="P16" t="n">
         <v>99999</v>
@@ -1589,70 +1585,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mamao-papaia-cariorta-12kg-99007</t>
+          <t>couve-flor-unidade-189111</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mamão Papaia Cariorta 1,2kg</t>
+          <t>Couve Flor Unidade</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>99007</t>
+          <t>189111</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9.99</v>
+        <v>9.59</v>
       </c>
       <c r="F17" t="n">
         <v>9.99</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P17" t="n">
         <v>99999</v>
@@ -1661,66 +1657,70 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
+          <t>morango-250g-289612</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pão Francês Panetto  60g Com 4 unidades</t>
+          <t>Morango 250g</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>96318</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>289612</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
+        </is>
+      </c>
       <c r="E18" t="n">
-        <v>24.99</v>
+        <v>8.99</v>
       </c>
       <c r="F18" t="n">
-        <v>24.99</v>
+        <v>9.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2024-01-31T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>PANETTO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2000307</v>
+        <v>2000015</v>
       </c>
       <c r="P18" t="n">
         <v>99999</v>
@@ -1729,29 +1729,29 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>morango-250g-289612</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Morango 250g</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>289612</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>9.99</v>
       </c>
       <c r="F19" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1801,48 +1801,48 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>limao-cariorta-1kg-98981</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Limão Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>98981</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9.99</v>
+        <v>11.99</v>
       </c>
       <c r="F20" t="n">
-        <v>10.99</v>
+        <v>11.99</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1850,21 +1850,21 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P20" t="n">
         <v>99999</v>
@@ -1873,43 +1873,43 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>couve-flor-unidade-189111</t>
+          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Couve Flor Unidade</t>
+          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>189111</t>
+          <t>100510</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
+          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9.59</v>
+        <v>2.29</v>
       </c>
       <c r="F21" t="n">
-        <v>9.99</v>
+        <v>2.69</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1922,21 +1922,21 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>LIMPOL</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>2000015</v>
+        <v>2001413</v>
       </c>
       <c r="P21" t="n">
         <v>99999</v>
@@ -1945,48 +1945,48 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>limao-cariorta-1kg-98981</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-238cm×218cm-50-unidades-129879</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Limão Cariorta 1Kg</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel 23,8cm×21,8cm 50 Unidades</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>98981</t>
+          <t>129879</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel 23,8cm×21,8cm 50 Unidades</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>11.99</v>
+        <v>6.19</v>
       </c>
       <c r="F22" t="n">
-        <v>11.99</v>
+        <v>6.19</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3239421/VF4qT-qqCUAAAAAAAAVSfw.jpg?v=638362188224230000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1994,66 +1994,66 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2001012</v>
+        <v>2001400</v>
       </c>
       <c r="P22" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
+          <t>coentro-unidade-200930</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
+          <t>Coentro Unidade</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>100510</t>
+          <t>200930</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
+          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.29</v>
+        <v>2.99</v>
       </c>
       <c r="F23" t="n">
-        <v>2.69</v>
+        <v>3.79</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2066,21 +2066,21 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>LIMPOL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>2001413</v>
+        <v>2000015</v>
       </c>
       <c r="P23" t="n">
         <v>99999</v>
@@ -2089,43 +2089,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-238cm×218cm-50-unidades-129879</t>
+          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel 23,8cm×21,8cm 50 Unidades</t>
+          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>129879</t>
+          <t>1180320</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel 23,8cm×21,8cm 50 Unidades</t>
+          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6.19</v>
+        <v>2.79</v>
       </c>
       <c r="F24" t="n">
-        <v>6.19</v>
+        <v>2.79</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2025-07-17T00:00:00Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3239421/VF4qT-qqCUAAAAAAAAVSfw.jpg?v=638362188224230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2138,21 +2138,21 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>9438</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>BOMBRIL</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>2001400</v>
+        <v>2001389</v>
       </c>
       <c r="P24" t="n">
         <v>99999</v>
@@ -2161,43 +2161,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>coentro-unidade-200930</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Coentro Unidade</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>200930</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.99</v>
+        <v>5.69</v>
       </c>
       <c r="F25" t="n">
-        <v>3.79</v>
+        <v>5.69</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2210,21 +2210,21 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>2000015</v>
+        <v>2000400</v>
       </c>
       <c r="P25" t="n">
         <v>99999</v>
@@ -2233,43 +2233,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
+          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
+          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1180320</t>
+          <t>364738</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
+          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.99</v>
+        <v>4.89</v>
       </c>
       <c r="F26" t="n">
-        <v>2.99</v>
+        <v>4.89</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2025-07-17T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2282,21 +2282,21 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>41057</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>BOMBRIL</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>2001389</v>
+        <v>2000043</v>
       </c>
       <c r="P26" t="n">
         <v>99999</v>
@@ -2305,43 +2305,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
+          <t>abobrinha-italiana-unidade-423513</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>364738</t>
+          <t>423513</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4.89</v>
+        <v>5.25</v>
       </c>
       <c r="F27" t="n">
-        <v>4.89</v>
+        <v>5.25</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-12-07T00:00:00Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2354,21 +2354,21 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>2000043</v>
+        <v>2000015</v>
       </c>
       <c r="P27" t="n">
         <v>99999</v>
@@ -2377,43 +2377,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>290564</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4.38</v>
+        <v>23.99</v>
       </c>
       <c r="F28" t="n">
-        <v>5.69</v>
+        <v>26.99</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2426,21 +2426,21 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>SADIA</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>2000400</v>
+        <v>2000057</v>
       </c>
       <c r="P28" t="n">
         <v>99999</v>
@@ -2449,43 +2449,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-unidade-423513</t>
+          <t>milho-em-conserva-quero-lata-200g-476625</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Milho em Conserva Quero Lata 200g</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>476625</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5.25</v>
+        <v>3.69</v>
       </c>
       <c r="F29" t="n">
-        <v>5.25</v>
+        <v>4.99</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2020-12-07T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2498,21 +2498,21 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>QUERO</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2000015</v>
+        <v>2001778</v>
       </c>
       <c r="P29" t="n">
         <v>99999</v>
@@ -2521,43 +2521,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>milho-em-conserva-quero-lata-200g-476625</t>
+          <t>leite-uht-piracanjuba-integral-1l-865427</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Milho em Conserva Quero Lata 200g</t>
+          <t>Leite Uht Piracanjuba Integral 1L</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>476625</t>
+          <t>865427</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
+          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3.69</v>
+        <v>5.59</v>
       </c>
       <c r="F30" t="n">
-        <v>4.99</v>
+        <v>5.59</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2017-04-12T00:00:00Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2570,21 +2570,21 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>23232</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>23158</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>QUERO</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2001778</v>
+        <v>2002038</v>
       </c>
       <c r="P30" t="n">
         <v>99999</v>
@@ -2593,43 +2593,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>290564</t>
+          <t>129887</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
+          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>23.99</v>
+        <v>12.99</v>
       </c>
       <c r="F31" t="n">
-        <v>26.99</v>
+        <v>12.99</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2642,66 +2642,66 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>SADIA</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>2000057</v>
+        <v>2001401</v>
       </c>
       <c r="P31" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>leite-uht-piracanjuba-integral-1l-865427</t>
+          <t>sal-refinado-iodado-ita-1kg-117293</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Leite Uht Piracanjuba Integral 1L</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>865427</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5.59</v>
+        <v>4.39</v>
       </c>
       <c r="F32" t="n">
-        <v>5.59</v>
+        <v>4.39</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2017-04-12T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2714,21 +2714,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2002038</v>
+        <v>2000066</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2737,43 +2737,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
+          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>129887</t>
+          <t>429376</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>12.99</v>
+        <v>3.99</v>
       </c>
       <c r="F33" t="n">
-        <v>12.99</v>
+        <v>3.99</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2786,21 +2786,21 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2001401</v>
+        <v>2000027</v>
       </c>
       <c r="P33" t="n">
         <v>99999</v>
@@ -2809,29 +2809,29 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
+          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>429376</t>
+          <t>429392</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
       <c r="F34" t="n">
-        <v>3.99</v>
+        <v>5.69</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2881,43 +2881,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sal-refinado-iodado-ita-1kg-117293</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4.39</v>
+        <v>6.99</v>
       </c>
       <c r="F35" t="n">
-        <v>4.39</v>
+        <v>6.99</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2930,21 +2930,21 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2000066</v>
+        <v>2001532</v>
       </c>
       <c r="P35" t="n">
         <v>99999</v>
@@ -2953,43 +2953,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
+          <t>couve-manteiga-unidade-201235</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
+          <t>Couve Manteiga Unidade</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>429392</t>
+          <t>201235</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4.99</v>
+        <v>3.79</v>
       </c>
       <c r="F36" t="n">
-        <v>5.69</v>
+        <v>3.79</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3002,21 +3002,21 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2000027</v>
+        <v>2000015</v>
       </c>
       <c r="P36" t="n">
         <v>99999</v>
@@ -3025,70 +3025,70 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>cebola-roxa-400g-38393</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Cebola Roxa 400g</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5.99</v>
+        <v>7.99</v>
       </c>
       <c r="F37" t="n">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2001532</v>
+        <v>2000015</v>
       </c>
       <c r="P37" t="n">
         <v>99999</v>
@@ -3097,43 +3097,43 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>couve-manteiga-unidade-201235</t>
+          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Couve Manteiga Unidade</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>201235</t>
+          <t>105287</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2.99</v>
+        <v>7.99</v>
       </c>
       <c r="F38" t="n">
-        <v>3.79</v>
+        <v>7.99</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-07-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3146,21 +3146,21 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>DONA BENTA</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>2000015</v>
+        <v>2000701</v>
       </c>
       <c r="P38" t="n">
         <v>99999</v>
@@ -3169,48 +3169,44 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
+          <t>abobrinha-italiana-cariorta-1kg-98663</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Abobrinha Italiana Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>105287</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
-        </is>
-      </c>
+          <t>98663</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>5.99</v>
+        <v>16.99</v>
       </c>
       <c r="F39" t="n">
-        <v>7.99</v>
+        <v>16.99</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2020-07-06T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -3218,21 +3214,21 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>DONA BENTA</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>2000701</v>
+        <v>2001012</v>
       </c>
       <c r="P39" t="n">
         <v>99999</v>
@@ -3241,33 +3237,33 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cebola-roxa-400g-38393</t>
+          <t>melao-amarelo-metade-1-3-kg-63606</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cebola Roxa 400g</t>
+          <t>Melão Amarelo Metade 1,3kg</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
+          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
       <c r="F40" t="n">
         <v>7.99</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3277,7 +3273,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3286,16 +3282,16 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3307,49 +3303,49 @@
         <v>2000015</v>
       </c>
       <c r="P40" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
+          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
+          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5106753</t>
+          <t>981168</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
+          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>11.99</v>
+        <v>32.19</v>
       </c>
       <c r="F41" t="n">
-        <v>11.99</v>
+        <v>32.19</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2021-01-11T00:00:00Z</t>
+          <t>2020-09-22T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3362,21 +3358,21 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>NEVE</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2003319</v>
+        <v>2000291</v>
       </c>
       <c r="P41" t="n">
         <v>99999</v>
@@ -3385,115 +3381,115 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>espinafre-unidade-200948</t>
+          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Espinafre Unidade</t>
+          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>200948</t>
+          <t>99279</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
+          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2.99</v>
+        <v>59.99</v>
       </c>
       <c r="F42" t="n">
-        <v>3.79</v>
+        <v>59.99</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-05-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P42" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
+          <t>alface-crespa-unidade-200875</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
+          <t>Alface Crespa Unidade</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>981168</t>
+          <t>200875</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
+          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>32.19</v>
+        <v>2.99</v>
       </c>
       <c r="F43" t="n">
-        <v>32.19</v>
+        <v>3.79</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2020-09-22T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3506,21 +3502,21 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>NEVE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>2000291</v>
+        <v>2000015</v>
       </c>
       <c r="P43" t="n">
         <v>99999</v>
@@ -3529,70 +3525,70 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
+          <t>matte-leao-natural-pet-15l-118214</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
+          <t>Matte Leão Natural Pet 1,5L</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>99279</t>
+          <t>118214</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
+          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>59.99</v>
+        <v>7.49</v>
       </c>
       <c r="F44" t="n">
-        <v>59.99</v>
+        <v>8.99</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2020-05-27T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>24684</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>2001012</v>
+        <v>2000010</v>
       </c>
       <c r="P44" t="n">
         <v>99999</v>
@@ -3601,43 +3597,43 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>matte-leao-natural-pet-15l-118214</t>
+          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Matte Leão Natural Pet 1,5L</t>
+          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>118214</t>
+          <t>1105795</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
+          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>8.99</v>
+        <v>3.99</v>
       </c>
       <c r="F45" t="n">
-        <v>8.99</v>
+        <v>5.99</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2023-07-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3650,21 +3646,21 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2000010</v>
+        <v>2000017</v>
       </c>
       <c r="P45" t="n">
         <v>99999</v>
@@ -3673,44 +3669,48 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-cariorta-1kg-98663</t>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Cariorta 1Kg</t>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>98663</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>103845</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+        </is>
+      </c>
       <c r="E46" t="n">
-        <v>16.99</v>
+        <v>29.98</v>
       </c>
       <c r="F46" t="n">
-        <v>16.99</v>
+        <v>37.9</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-07-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3718,93 +3718,93 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>MELITTA</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>2001012</v>
+        <v>2001329</v>
       </c>
       <c r="P46" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>melao-amarelo-metade-1-3-kg-63606</t>
+          <t>azeite-italiano-extra-virgem-due-500ml-5472040</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Melão Amarelo Metade 1,3kg</t>
+          <t>Azeite Italiano Extravirgem Due 500ml</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>5472040</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
+          <t>O azeite Due é um blend de azeites do Mediterrâneo que confere um resultado clássico e ideal para o cotidiano da cozinha. Sua elaboração conta com uma seleção cautelosamente realizada pelo Expert em Azeites e Temperos Marcelo Scofano, que anualmente viaja à Toscana (Itália), onde o azeite é produzido, para cuidar de cada detalhe pessoalmente.Due é um azeite clássico, ideal para o dia a dia da cozinha: marinados, refogados, emulsão de molhos, finalização de saladas, massas e pratos do cotidiano. O azeite clássico é extraído de azeitonas maduras. Possui sabor amendoado, com notas amargas e picantes em equilíbrio.O azeite Due faz parte da grupo de marcas exclusivas Zona Sul, criada e pensada com carinho para os cariocas de coração. O planejamento de cada produto exclusivo conta com a participação dos Experts Zona Sul em todo o processo, até chegar na sua mesa. E com a linha Due não é diferente!</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6.99</v>
+        <v>24.98</v>
       </c>
       <c r="F47" t="n">
-        <v>7.99</v>
+        <v>29.97</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>597</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2025-05-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4116721/VF4qT-qqCUAAAAAAAAiyjQ.jpg?v=638846625781330000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>40224</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>40151</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>DUE</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>2000015</v>
+        <v>2005138</v>
       </c>
       <c r="P47" t="n">
         <v>99999</v>
@@ -3813,43 +3813,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>alface-crespa-unidade-200875</t>
+          <t>pao-de-forma-plus-vita-tradicional-500-g-252921</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Alface Crespa Unidade</t>
+          <t>Pão de Forma Tradicional Plusvita 480g</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>200875</t>
+          <t>252921</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
+          <t>Versátil, prático e para qualquer momento, trazendo a energia necessária para o seu dia. Perfeito para sanduíches, torradas, receitas para o café da manhã, café da tarde, almoço e jantar</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2.99</v>
+        <v>9.98</v>
       </c>
       <c r="F48" t="n">
-        <v>3.79</v>
+        <v>9.98</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>183</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3663691/VF4qT-qqCUAAAAAAAAb-gA.jpg?v=638592874910030000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3862,21 +3862,21 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PLUS VITA</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>2000015</v>
+        <v>2000316</v>
       </c>
       <c r="P48" t="n">
         <v>99999</v>
@@ -3885,144 +3885,72 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>abobora-japonesa-pedaco-500g-38229</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Abóbora Japonesa Pedaço 500g</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>38229</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+          <t>Embalagem com 1 pedaço.</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>31.98</v>
+        <v>4.99</v>
       </c>
       <c r="F49" t="n">
-        <v>37.9</v>
+        <v>4.99</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3096862/VF4qT-qqCUAAAAAAAAS9Tw.jpg?v=638235593168230000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2001329</v>
+        <v>2000015</v>
       </c>
       <c r="P49" t="n">
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1105795</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="F50" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2023-07-26T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>33955</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>33882</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>PIRAQUE</t>
-        </is>
-      </c>
-      <c r="O50" t="n">
-        <v>2000017</v>
-      </c>
-      <c r="P50" t="n">
         <v>99999</v>
       </c>
     </row>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -513,43 +513,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>matte-leao-limao-pet-1-5l-118222</t>
+          <t>rucula-unidade-201006</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Matte Leão Limão Pet 1,5L</t>
+          <t>Rúcula Unidade</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>118222</t>
+          <t>201006</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
+          <t>A rúcula é uma hortaliça de baixa caloria (aprox. 29 kcal/100g) e rica em nutrientes como vitaminas A, C e K, além de cálcio, ferro e potássio. Seus principais benefícios incluem ação antioxidante, fortalecimento do sistema imunológico, melhoria da saúde ocular e óssea, auxílio na digestão, controle do colesterol e redução de riscos cardiovasculares.A melhor forma de comer rúcula é crua em saladas, temperada com azeite, sal e limão, mas também é versátil em pratos quentes como massas, risotos e sanduíches, ou refogada rapidamente</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7.49</v>
+        <v>3.79</v>
       </c>
       <c r="F2" t="n">
-        <v>8.99</v>
+        <v>3.79</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3040890/VF4qT-qqCUAAAAAAAAHLpQ.jpg?v=637792545082200000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -562,21 +562,21 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>2000010</v>
+        <v>2000015</v>
       </c>
       <c r="P2" t="n">
         <v>99999</v>
@@ -585,43 +585,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>alcool-montenegro-46-1-l-780570</t>
+          <t>matte-leao-limao-pet-1-5l-118222</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Álcool Montenegro 46% 1 L</t>
+          <t>Matte Leão Limão Pet 1,5L</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>780570</t>
+          <t>118222</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Álcool Montenegro 46% 1 L</t>
+          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8.789999999999999</v>
+        <v>7.49</v>
       </c>
       <c r="F3" t="n">
-        <v>8.789999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2020-10-06T10:47:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051579/VF4qT-qqCUAAAAAAAAG3pQ.jpg?v=637793390624870000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -634,21 +634,21 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>11598</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MONTENEGRO</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2000527</v>
+        <v>2000010</v>
       </c>
       <c r="P3" t="n">
         <v>99999</v>
@@ -657,33 +657,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tomate-italiano-unidade-495212</t>
+          <t>ovos-brancos-jumbo-mantiqueira-com-10-unidades-437638</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tomate Italiano Unidade</t>
+          <t>Ovos Brancos Jumbo Mantiqueira Com 10 Unidades</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>495212</t>
+          <t>437638</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
+          <t>Os Ovos Jumbo Mantiqueira possuem maior tamanho, ideais para quem busca uma alimentação rica em vitaminas, proteínas e minerais, ou para quem gosta de um maior rendimento em suas receitas. Um único ovo contém quase todos os nutrientes necessários para manter o corpo saudável, fortalecendo os ossos e auxiliando em dietas para perda de peso ou ganho de massa.O Ovo Jumbo Mantiqueira é um produto da linha Especial da marca e possui a qualidade superior, passando por um moderno sistema de seleção, limpeza e embalagem sem contato de mãos humanas.Especificações:Ovos maiores, tamanho família.Embalagem com 10 unidades.Ovos brancos e vermelhos tipo jumbo categoria A.</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.18</v>
+        <v>10.9</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7</v>
+        <v>10.9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3976126/VF4qT-qqCUAAAAAAAAh4RA.jpg?v=638769994856100000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -706,21 +706,21 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>MANTIQUEIRA</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>2000015</v>
+        <v>2001056</v>
       </c>
       <c r="P4" t="n">
         <v>99999</v>
@@ -729,43 +729,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
+          <t>alcool-montenegro-46-1-l-780570</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Álcool Montenegro 46% 1 L</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>140805</t>
+          <t>780570</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Álcool Montenegro 46% 1 L</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4.29</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>5.29</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2020-09-25T00:00:00Z</t>
+          <t>2020-10-06T10:47:00Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051579/VF4qT-qqCUAAAAAAAAG3pQ.jpg?v=637793390624870000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -778,21 +778,21 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>11598</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>SAO LOURENCO</t>
+          <t>MONTENEGRO</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2000145</v>
+        <v>2000527</v>
       </c>
       <c r="P5" t="n">
         <v>99999</v>
@@ -801,43 +801,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
+          <t>tomate-italiano-unidade-495212</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
+          <t>Tomate Italiano Unidade</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>828025</t>
+          <t>495212</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
+          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>29.98</v>
+        <v>1.96</v>
       </c>
       <c r="F6" t="n">
-        <v>43.9</v>
+        <v>1.96</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -850,21 +850,21 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>PILAO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2000070</v>
+        <v>2000015</v>
       </c>
       <c r="P6" t="n">
         <v>99999</v>
@@ -873,43 +873,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
+          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>370550</t>
+          <t>140805</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>24.99</v>
+        <v>4.29</v>
       </c>
       <c r="F7" t="n">
-        <v>24.99</v>
+        <v>5.29</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-25T00:00:00Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -922,93 +922,93 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>SAO LOURENCO</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2003319</v>
+        <v>2000145</v>
       </c>
       <c r="P7" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mucarela-em-fatias-92363</t>
+          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Muçarela  em Fatias 200g</t>
+          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>92363</t>
+          <t>828025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Muçarela em Fatias</t>
+          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>59.9</v>
+        <v>43.9</v>
       </c>
       <c r="F8" t="n">
-        <v>59.9</v>
+        <v>43.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PILAO</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2000015</v>
+        <v>2000070</v>
       </c>
       <c r="P8" t="n">
         <v>99999</v>
@@ -1017,43 +1017,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>manga-palmer-unidade-5130760</t>
+          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Manga Palmer Unidade</t>
+          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5130760</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
+          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.77</v>
+        <v>24.99</v>
       </c>
       <c r="F9" t="n">
-        <v>5.99</v>
+        <v>24.99</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2023-02-16T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1066,21 +1066,21 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2000015</v>
+        <v>2003319</v>
       </c>
       <c r="P9" t="n">
         <v>99999</v>
@@ -1089,29 +1089,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>uva-preta-sem-semente-500-g-674583</t>
+          <t>manga-palmer-unidade-5130760</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Uva Preta Sem Semente 500g</t>
+          <t>Manga Palmer Unidade</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>674583</t>
+          <t>5130760</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
+          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
       <c r="F10" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2023-02-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>31902</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1161,138 +1161,142 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>mucarela-em-fatias-92363</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Muçarela  em Fatias 200g</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>92363</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Muçarela em Fatias</t>
+        </is>
+      </c>
       <c r="E11" t="n">
-        <v>5.99</v>
+        <v>59.9</v>
       </c>
       <c r="F11" t="n">
-        <v>5.99</v>
+        <v>59.9</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2001952</v>
+        <v>2000015</v>
       </c>
       <c r="P11" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>batata-inglesa-cariorta-12kg-98698</t>
+          <t>uva-preta-sem-semente-500-g-674583</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Batata Inglesa Cariorta 1,2Kg</t>
+          <t>Uva Preta Sem Semente 500g</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>674583</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.99</v>
+        <v>11.99</v>
       </c>
       <c r="F12" t="n">
-        <v>7.99</v>
+        <v>11.99</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P12" t="n">
         <v>99999</v>
@@ -1301,70 +1305,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
+          <t>batata-inglesa-cariorta-12kg-98698</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Odd Clear 500ml</t>
+          <t>Batata Inglesa Cariorta 1,2Kg</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>982911</t>
+          <t>98698</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ODD voltou!Alto rendimento , controle de odor.</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.9</v>
+        <v>7.99</v>
       </c>
       <c r="F13" t="n">
-        <v>2.49</v>
+        <v>7.99</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>LIMPPANO</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2001341</v>
+        <v>2001012</v>
       </c>
       <c r="P13" t="n">
         <v>99999</v>
@@ -1373,43 +1377,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cheiro-verde-unidade-201049</t>
+          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cheiro Verde Unidade</t>
+          <t>Detergente Para Louças Odd Clear 500ml</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>201049</t>
+          <t>982911</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+          <t>ODD voltou!Alto rendimento , controle de odor.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.99</v>
+        <v>1.9</v>
       </c>
       <c r="F14" t="n">
-        <v>3.39</v>
+        <v>2.49</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1422,21 +1426,21 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>LIMPPANO</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2000015</v>
+        <v>2001341</v>
       </c>
       <c r="P14" t="n">
         <v>99999</v>
@@ -1445,70 +1449,66 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mamao-papaia-cariorta-12kg-99007</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mamão Papaia Cariorta 1,2kg</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>99007</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Cariorta selecionados de coração.</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>9.99</v>
+        <v>5.99</v>
       </c>
       <c r="F15" t="n">
-        <v>9.99</v>
+        <v>5.99</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2001012</v>
+        <v>2001952</v>
       </c>
       <c r="P15" t="n">
         <v>99999</v>
@@ -1517,66 +1517,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
+          <t>cheiro-verde-unidade-201049</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pão Francês Panetto  60g Com 4 unidades</t>
+          <t>Cheiro Verde Unidade</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>96318</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>201049</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+        </is>
+      </c>
       <c r="E16" t="n">
-        <v>24.99</v>
+        <v>3.39</v>
       </c>
       <c r="F16" t="n">
-        <v>24.99</v>
+        <v>3.39</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2024-01-31T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>PANETTO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2000307</v>
+        <v>2000015</v>
       </c>
       <c r="P16" t="n">
         <v>99999</v>
@@ -1585,70 +1589,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>couve-flor-unidade-189111</t>
+          <t>mamao-papaia-cariorta-12kg-99007</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Couve Flor Unidade</t>
+          <t>Mamão Papaia Cariorta 1,2kg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>189111</t>
+          <t>99007</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9.59</v>
+        <v>9.99</v>
       </c>
       <c r="F17" t="n">
         <v>9.99</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P17" t="n">
         <v>99999</v>
@@ -1676,7 +1680,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8.99</v>
+        <v>9.99</v>
       </c>
       <c r="F18" t="n">
         <v>9.99</v>
@@ -1729,43 +1733,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>couve-flor-unidade-189111</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Couve Flor Unidade</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>189111</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
+          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>9.99</v>
       </c>
       <c r="F19" t="n">
-        <v>10.99</v>
+        <v>9.99</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1778,12 +1782,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1801,43 +1805,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>limao-cariorta-1kg-98981</t>
+          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Limão Cariorta 1Kg</t>
+          <t>Pão Francês Panetto  60g Com 4 unidades</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>98981</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Cariorta selecionados de coração.</t>
-        </is>
-      </c>
+          <t>96318</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>11.99</v>
+        <v>24.99</v>
       </c>
       <c r="F20" t="n">
-        <v>11.99</v>
+        <v>24.99</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2024-01-31T00:00:00Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1846,25 +1846,25 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>PANETTO</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2001012</v>
+        <v>2000307</v>
       </c>
       <c r="P20" t="n">
         <v>99999</v>
@@ -1873,43 +1873,43 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>100510</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2.29</v>
+        <v>10.99</v>
       </c>
       <c r="F21" t="n">
-        <v>2.69</v>
+        <v>10.99</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1922,21 +1922,21 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>LIMPOL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>2001413</v>
+        <v>2000015</v>
       </c>
       <c r="P21" t="n">
         <v>99999</v>
@@ -1945,48 +1945,48 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-238cm×218cm-50-unidades-129879</t>
+          <t>limao-cariorta-1kg-98981</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel 23,8cm×21,8cm 50 Unidades</t>
+          <t>Limão Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>129879</t>
+          <t>98981</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel 23,8cm×21,8cm 50 Unidades</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6.19</v>
+        <v>11.99</v>
       </c>
       <c r="F22" t="n">
-        <v>6.19</v>
+        <v>11.99</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3239421/VF4qT-qqCUAAAAAAAAVSfw.jpg?v=638362188224230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1994,66 +1994,66 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>9438</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2001400</v>
+        <v>2001012</v>
       </c>
       <c r="P22" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>coentro-unidade-200930</t>
+          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Coentro Unidade</t>
+          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>200930</t>
+          <t>100510</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
+          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.99</v>
+        <v>1.99</v>
       </c>
       <c r="F23" t="n">
-        <v>3.79</v>
+        <v>2.69</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2066,21 +2066,21 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>LIMPOL</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>2000015</v>
+        <v>2001413</v>
       </c>
       <c r="P23" t="n">
         <v>99999</v>
@@ -2089,43 +2089,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
+          <t>coentro-unidade-200930</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
+          <t>Coentro Unidade</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1180320</t>
+          <t>200930</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
+          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.79</v>
+        <v>3.79</v>
       </c>
       <c r="F24" t="n">
-        <v>2.79</v>
+        <v>3.79</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2025-07-17T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2138,21 +2138,21 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>41057</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>BOMBRIL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>2001389</v>
+        <v>2000015</v>
       </c>
       <c r="P24" t="n">
         <v>99999</v>
@@ -2161,43 +2161,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>1180320</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5.69</v>
+        <v>2.79</v>
       </c>
       <c r="F25" t="n">
-        <v>5.69</v>
+        <v>2.79</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2025-07-17T00:00:00Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2210,21 +2210,21 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>BOMBRIL</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>2000400</v>
+        <v>2001389</v>
       </c>
       <c r="P25" t="n">
         <v>99999</v>
@@ -2305,43 +2305,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-unidade-423513</t>
+          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>290564</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5.25</v>
+        <v>23.99</v>
       </c>
       <c r="F27" t="n">
-        <v>5.25</v>
+        <v>26.99</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2020-12-07T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2354,21 +2354,21 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SADIA</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>2000015</v>
+        <v>2000057</v>
       </c>
       <c r="P27" t="n">
         <v>99999</v>
@@ -2377,43 +2377,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>290564</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>23.99</v>
+        <v>6.29</v>
       </c>
       <c r="F28" t="n">
-        <v>26.99</v>
+        <v>6.29</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2426,21 +2426,21 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>SADIA</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>2000057</v>
+        <v>2000400</v>
       </c>
       <c r="P28" t="n">
         <v>99999</v>
@@ -2449,43 +2449,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>milho-em-conserva-quero-lata-200g-476625</t>
+          <t>abobrinha-italiana-unidade-423513</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Milho em Conserva Quero Lata 200g</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>476625</t>
+          <t>423513</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3.69</v>
+        <v>3.47</v>
       </c>
       <c r="F29" t="n">
-        <v>4.99</v>
+        <v>3.47</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-12-07T00:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2498,21 +2498,21 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>QUERO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2001778</v>
+        <v>2000015</v>
       </c>
       <c r="P29" t="n">
         <v>99999</v>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5.59</v>
+        <v>6.69</v>
       </c>
       <c r="F30" t="n">
-        <v>5.59</v>
+        <v>6.69</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2593,43 +2593,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
+          <t>milho-em-conserva-quero-lata-200g-476625</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
+          <t>Milho em Conserva Quero Lata 200g</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>129887</t>
+          <t>476625</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>12.99</v>
+        <v>3.69</v>
       </c>
       <c r="F31" t="n">
-        <v>12.99</v>
+        <v>4.99</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2642,21 +2642,21 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>QUERO</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>2001401</v>
+        <v>2001778</v>
       </c>
       <c r="P31" t="n">
         <v>99999</v>
@@ -2665,43 +2665,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sal-refinado-iodado-ita-1kg-117293</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>129887</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4.39</v>
+        <v>12.99</v>
       </c>
       <c r="F32" t="n">
-        <v>4.39</v>
+        <v>12.99</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2714,21 +2714,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2000066</v>
+        <v>2001401</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2737,29 +2737,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
+          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>429376</t>
+          <t>429392</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
       <c r="F33" t="n">
-        <v>3.99</v>
+        <v>5.69</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2809,43 +2809,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
+          <t>sal-refinado-iodado-ita-1kg-117293</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>429392</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4.99</v>
+        <v>4.39</v>
       </c>
       <c r="F34" t="n">
-        <v>5.69</v>
+        <v>4.39</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2858,21 +2858,21 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>2000027</v>
+        <v>2000066</v>
       </c>
       <c r="P34" t="n">
         <v>99999</v>
@@ -2881,43 +2881,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>couve-manteiga-unidade-201235</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Couve Manteiga Unidade</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>201235</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6.99</v>
+        <v>3.79</v>
       </c>
       <c r="F35" t="n">
-        <v>6.99</v>
+        <v>3.79</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2930,21 +2930,21 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2001532</v>
+        <v>2000015</v>
       </c>
       <c r="P35" t="n">
         <v>99999</v>
@@ -2953,43 +2953,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>couve-manteiga-unidade-201235</t>
+          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Couve Manteiga Unidade</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>201235</t>
+          <t>429376</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3.79</v>
+        <v>3.99</v>
       </c>
       <c r="F36" t="n">
-        <v>3.79</v>
+        <v>3.99</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3002,21 +3002,21 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2000015</v>
+        <v>2000027</v>
       </c>
       <c r="P36" t="n">
         <v>99999</v>
@@ -3025,70 +3025,70 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cebola-roxa-400g-38393</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cebola Roxa 400g</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
       <c r="F37" t="n">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2000015</v>
+        <v>2001532</v>
       </c>
       <c r="P37" t="n">
         <v>99999</v>
@@ -3097,22 +3097,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
+          <t>cebola-roxa-400g-38393</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Cebola Roxa 400g</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>105287</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -3123,44 +3123,44 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2020-07-06T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>DONA BENTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>2000701</v>
+        <v>2000015</v>
       </c>
       <c r="P38" t="n">
         <v>99999</v>
@@ -3169,44 +3169,48 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-cariorta-1kg-98663</t>
+          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Cariorta 1Kg</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>98663</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>105287</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
+        </is>
+      </c>
       <c r="E39" t="n">
-        <v>16.99</v>
+        <v>7.99</v>
       </c>
       <c r="F39" t="n">
-        <v>16.99</v>
+        <v>7.99</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-07-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -3214,21 +3218,21 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>DONA BENTA</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>2001012</v>
+        <v>2000701</v>
       </c>
       <c r="P39" t="n">
         <v>99999</v>
@@ -3237,61 +3241,61 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>melao-amarelo-metade-1-3-kg-63606</t>
+          <t>alface-crespa-unidade-200875</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Melão Amarelo Metade 1,3kg</t>
+          <t>Alface Crespa Unidade</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>200875</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
+          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6.99</v>
+        <v>3.79</v>
       </c>
       <c r="F40" t="n">
-        <v>7.99</v>
+        <v>3.79</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3309,48 +3313,44 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
+          <t>abobrinha-italiana-cariorta-1kg-98663</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
+          <t>Abobrinha Italiana Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>981168</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
-        </is>
-      </c>
+          <t>98663</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>32.19</v>
+        <v>16.99</v>
       </c>
       <c r="F41" t="n">
-        <v>32.19</v>
+        <v>16.99</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2020-09-22T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -3358,21 +3358,21 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>NEVE</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2000291</v>
+        <v>2001012</v>
       </c>
       <c r="P41" t="n">
         <v>99999</v>
@@ -3453,61 +3453,61 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>alface-crespa-unidade-200875</t>
+          <t>melao-amarelo-metade-1-3-kg-63606</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Alface Crespa Unidade</t>
+          <t>Melão Amarelo Metade 1,3kg</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>200875</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
+          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2.99</v>
+        <v>7.99</v>
       </c>
       <c r="F43" t="n">
-        <v>3.79</v>
+        <v>7.99</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3525,43 +3525,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>matte-leao-natural-pet-15l-118214</t>
+          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Matte Leão Natural Pet 1,5L</t>
+          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>118214</t>
+          <t>5106753</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
+          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>7.49</v>
+        <v>11.99</v>
       </c>
       <c r="F44" t="n">
-        <v>8.99</v>
+        <v>11.99</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2021-01-11T00:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3574,21 +3574,21 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>2000010</v>
+        <v>2003319</v>
       </c>
       <c r="P44" t="n">
         <v>99999</v>
@@ -3597,43 +3597,43 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
+          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
+          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1105795</t>
+          <t>981168</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
+          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3.99</v>
+        <v>32.19</v>
       </c>
       <c r="F45" t="n">
-        <v>5.99</v>
+        <v>32.19</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2023-07-26T00:00:00Z</t>
+          <t>2020-09-22T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3646,21 +3646,21 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>NEVE</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2000017</v>
+        <v>2000291</v>
       </c>
       <c r="P45" t="n">
         <v>99999</v>
@@ -3735,49 +3735,49 @@
         <v>2001329</v>
       </c>
       <c r="P46" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>azeite-italiano-extra-virgem-due-500ml-5472040</t>
+          <t>matte-leao-natural-pet-15l-118214</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Azeite Italiano Extravirgem Due 500ml</t>
+          <t>Matte Leão Natural Pet 1,5L</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>5472040</t>
+          <t>118214</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>O azeite Due é um blend de azeites do Mediterrâneo que confere um resultado clássico e ideal para o cotidiano da cozinha. Sua elaboração conta com uma seleção cautelosamente realizada pelo Expert em Azeites e Temperos Marcelo Scofano, que anualmente viaja à Toscana (Itália), onde o azeite é produzido, para cuidar de cada detalhe pessoalmente.Due é um azeite clássico, ideal para o dia a dia da cozinha: marinados, refogados, emulsão de molhos, finalização de saladas, massas e pratos do cotidiano. O azeite clássico é extraído de azeitonas maduras. Possui sabor amendoado, com notas amargas e picantes em equilíbrio.O azeite Due faz parte da grupo de marcas exclusivas Zona Sul, criada e pensada com carinho para os cariocas de coração. O planejamento de cada produto exclusivo conta com a participação dos Experts Zona Sul em todo o processo, até chegar na sua mesa. E com a linha Due não é diferente!</t>
+          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>24.98</v>
+        <v>7.49</v>
       </c>
       <c r="F47" t="n">
-        <v>29.97</v>
+        <v>8.99</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2025-05-06T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4116721/VF4qT-qqCUAAAAAAAAiyjQ.jpg?v=638846625781330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3790,21 +3790,21 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>40224</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>40151</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>DUE</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>2005138</v>
+        <v>2000010</v>
       </c>
       <c r="P47" t="n">
         <v>99999</v>
@@ -3813,43 +3813,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pao-de-forma-plus-vita-tradicional-500-g-252921</t>
+          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pão de Forma Tradicional Plusvita 480g</t>
+          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>252921</t>
+          <t>1105795</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Versátil, prático e para qualquer momento, trazendo a energia necessária para o seu dia. Perfeito para sanduíches, torradas, receitas para o café da manhã, café da tarde, almoço e jantar</t>
+          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>9.98</v>
+        <v>3.99</v>
       </c>
       <c r="F48" t="n">
-        <v>9.98</v>
+        <v>5.99</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2023-07-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3663691/VF4qT-qqCUAAAAAAAAb-gA.jpg?v=638592874910030000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3862,21 +3862,21 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>9715</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>PLUS VITA</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>2000316</v>
+        <v>2000017</v>
       </c>
       <c r="P48" t="n">
         <v>99999</v>
@@ -3885,70 +3885,70 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>abobora-japonesa-pedaco-500g-38229</t>
+          <t>azeite-italiano-extra-virgem-due-500ml-5472040</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Abóbora Japonesa Pedaço 500g</t>
+          <t>Azeite Italiano Extravirgem Due 500ml</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>38229</t>
+          <t>5472040</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Embalagem com 1 pedaço.</t>
+          <t>O azeite Due é um blend de azeites do Mediterrâneo que confere um resultado clássico e ideal para o cotidiano da cozinha. Sua elaboração conta com uma seleção cautelosamente realizada pelo Expert em Azeites e Temperos Marcelo Scofano, que anualmente viaja à Toscana (Itália), onde o azeite é produzido, para cuidar de cada detalhe pessoalmente.Due é um azeite clássico, ideal para o dia a dia da cozinha: marinados, refogados, emulsão de molhos, finalização de saladas, massas e pratos do cotidiano. O azeite clássico é extraído de azeitonas maduras. Possui sabor amendoado, com notas amargas e picantes em equilíbrio.O azeite Due faz parte da grupo de marcas exclusivas Zona Sul, criada e pensada com carinho para os cariocas de coração. O planejamento de cada produto exclusivo conta com a participação dos Experts Zona Sul em todo o processo, até chegar na sua mesa. E com a linha Due não é diferente!</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4.99</v>
+        <v>24.98</v>
       </c>
       <c r="F49" t="n">
-        <v>4.99</v>
+        <v>29.97</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>597</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2025-05-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3096862/VF4qT-qqCUAAAAAAAAS9Tw.jpg?v=638235593168230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4116721/VF4qT-qqCUAAAAAAAAiyjQ.jpg?v=638846625781330000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>40224</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>40151</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>DUE</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2000015</v>
+        <v>2005138</v>
       </c>
       <c r="P49" t="n">
         <v>99999</v>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3.79</v>
+        <v>2.99</v>
       </c>
       <c r="F2" t="n">
         <v>3.79</v>
@@ -585,43 +585,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>matte-leao-limao-pet-1-5l-118222</t>
+          <t>ovos-brancos-jumbo-mantiqueira-com-10-unidades-437638</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Matte Leão Limão Pet 1,5L</t>
+          <t>Ovos Brancos Jumbo Mantiqueira Com 10 Unidades</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>118222</t>
+          <t>437638</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
+          <t>Os Ovos Jumbo Mantiqueira possuem maior tamanho, ideais para quem busca uma alimentação rica em vitaminas, proteínas e minerais, ou para quem gosta de um maior rendimento em suas receitas. Um único ovo contém quase todos os nutrientes necessários para manter o corpo saudável, fortalecendo os ossos e auxiliando em dietas para perda de peso ou ganho de massa.O Ovo Jumbo Mantiqueira é um produto da linha Especial da marca e possui a qualidade superior, passando por um moderno sistema de seleção, limpeza e embalagem sem contato de mãos humanas.Especificações:Ovos maiores, tamanho família.Embalagem com 10 unidades.Ovos brancos e vermelhos tipo jumbo categoria A.</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7.49</v>
+        <v>10.9</v>
       </c>
       <c r="F3" t="n">
-        <v>8.99</v>
+        <v>10.9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3976126/VF4qT-qqCUAAAAAAAAh4RA.jpg?v=638769994856100000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -634,21 +634,21 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>MANTIQUEIRA</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2000010</v>
+        <v>2001056</v>
       </c>
       <c r="P3" t="n">
         <v>99999</v>
@@ -657,43 +657,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ovos-brancos-jumbo-mantiqueira-com-10-unidades-437638</t>
+          <t>matte-leao-limao-pet-1-5l-118222</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ovos Brancos Jumbo Mantiqueira Com 10 Unidades</t>
+          <t>Matte Leão Limão Pet 1,5L</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>437638</t>
+          <t>118222</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Os Ovos Jumbo Mantiqueira possuem maior tamanho, ideais para quem busca uma alimentação rica em vitaminas, proteínas e minerais, ou para quem gosta de um maior rendimento em suas receitas. Um único ovo contém quase todos os nutrientes necessários para manter o corpo saudável, fortalecendo os ossos e auxiliando em dietas para perda de peso ou ganho de massa.O Ovo Jumbo Mantiqueira é um produto da linha Especial da marca e possui a qualidade superior, passando por um moderno sistema de seleção, limpeza e embalagem sem contato de mãos humanas.Especificações:Ovos maiores, tamanho família.Embalagem com 10 unidades.Ovos brancos e vermelhos tipo jumbo categoria A.</t>
+          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10.9</v>
+        <v>7.49</v>
       </c>
       <c r="F4" t="n">
-        <v>10.9</v>
+        <v>8.99</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3976126/VF4qT-qqCUAAAAAAAAh4RA.jpg?v=638769994856100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -706,21 +706,21 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>MANTIQUEIRA</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>2001056</v>
+        <v>2000010</v>
       </c>
       <c r="P4" t="n">
         <v>99999</v>
@@ -873,43 +873,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
+          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>140805</t>
+          <t>828025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.29</v>
+        <v>29.98</v>
       </c>
       <c r="F7" t="n">
-        <v>5.29</v>
+        <v>43.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2020-09-25T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -922,21 +922,21 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>SAO LOURENCO</t>
+          <t>PILAO</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2000145</v>
+        <v>2000070</v>
       </c>
       <c r="P7" t="n">
         <v>99999</v>
@@ -945,43 +945,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
+          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>828025</t>
+          <t>140805</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>43.9</v>
+        <v>4.29</v>
       </c>
       <c r="F8" t="n">
-        <v>43.9</v>
+        <v>5.29</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-25T00:00:00Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -994,21 +994,21 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>PILAO</t>
+          <t>SAO LOURENCO</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2000070</v>
+        <v>2000145</v>
       </c>
       <c r="P8" t="n">
         <v>99999</v>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5.99</v>
+        <v>5.39</v>
       </c>
       <c r="F10" t="n">
         <v>5.99</v>
@@ -1449,39 +1449,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>cheiro-verde-unidade-201049</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Cheiro Verde Unidade</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>201049</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+        </is>
+      </c>
       <c r="E15" t="n">
-        <v>5.99</v>
+        <v>2.99</v>
       </c>
       <c r="F15" t="n">
-        <v>5.99</v>
+        <v>3.39</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1494,21 +1498,21 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2001952</v>
+        <v>2000015</v>
       </c>
       <c r="P15" t="n">
         <v>99999</v>
@@ -1517,43 +1521,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cheiro-verde-unidade-201049</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cheiro Verde Unidade</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>201049</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>3.39</v>
+        <v>5.99</v>
       </c>
       <c r="F16" t="n">
-        <v>3.39</v>
+        <v>5.99</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1566,21 +1566,21 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2000015</v>
+        <v>2001952</v>
       </c>
       <c r="P16" t="n">
         <v>99999</v>
@@ -1661,70 +1661,66 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>morango-250g-289612</t>
+          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Morango 250g</t>
+          <t>Pão Francês Panetto  60g Com 4 unidades</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>289612</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
-        </is>
-      </c>
+          <t>96318</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
       <c r="F18" t="n">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2024-01-31T00:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PANETTO</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2000015</v>
+        <v>2000307</v>
       </c>
       <c r="P18" t="n">
         <v>99999</v>
@@ -1733,22 +1729,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>couve-flor-unidade-189111</t>
+          <t>morango-250g-289612</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Couve Flor Unidade</t>
+          <t>Morango 250g</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>189111</t>
+          <t>289612</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
+          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1759,17 +1755,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1782,12 +1778,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1805,66 +1801,70 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
+          <t>couve-flor-unidade-189111</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pão Francês Panetto  60g Com 4 unidades</t>
+          <t>Couve Flor Unidade</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>96318</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>189111</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
+        </is>
+      </c>
       <c r="E20" t="n">
-        <v>24.99</v>
+        <v>9.59</v>
       </c>
       <c r="F20" t="n">
-        <v>24.99</v>
+        <v>9.99</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2024-01-31T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>PANETTO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2000307</v>
+        <v>2000015</v>
       </c>
       <c r="P20" t="n">
         <v>99999</v>
@@ -1873,48 +1873,48 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>limao-cariorta-1kg-98981</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Limão Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>98981</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>10.99</v>
+        <v>11.99</v>
       </c>
       <c r="F21" t="n">
-        <v>10.99</v>
+        <v>11.99</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1922,21 +1922,21 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P21" t="n">
         <v>99999</v>
@@ -1945,48 +1945,48 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>limao-cariorta-1kg-98981</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Limão Cariorta 1Kg</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>98981</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>11.99</v>
+        <v>9.99</v>
       </c>
       <c r="F22" t="n">
-        <v>11.99</v>
+        <v>10.99</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1994,21 +1994,21 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P22" t="n">
         <v>99999</v>
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.79</v>
+        <v>2.99</v>
       </c>
       <c r="F24" t="n">
         <v>3.79</v>
@@ -2377,43 +2377,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>abobrinha-italiana-unidade-423513</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>423513</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6.29</v>
+        <v>3.47</v>
       </c>
       <c r="F28" t="n">
-        <v>6.29</v>
+        <v>3.47</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-12-07T00:00:00Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2426,21 +2426,21 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>2000400</v>
+        <v>2000015</v>
       </c>
       <c r="P28" t="n">
         <v>99999</v>
@@ -2449,43 +2449,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-unidade-423513</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3.47</v>
+        <v>5.49</v>
       </c>
       <c r="F29" t="n">
-        <v>3.47</v>
+        <v>6.29</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2020-12-07T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2498,21 +2498,21 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2000015</v>
+        <v>2000400</v>
       </c>
       <c r="P29" t="n">
         <v>99999</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3.79</v>
+        <v>2.99</v>
       </c>
       <c r="F35" t="n">
         <v>3.79</v>
@@ -2953,115 +2953,115 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
+          <t>cebola-roxa-400g-38393</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
+          <t>Cebola Roxa 400g</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>429376</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3.99</v>
+        <v>7.99</v>
       </c>
       <c r="F36" t="n">
-        <v>3.99</v>
+        <v>7.99</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2000027</v>
+        <v>2000015</v>
       </c>
       <c r="P36" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>429376</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
       <c r="F37" t="n">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3074,21 +3074,21 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2001532</v>
+        <v>2000027</v>
       </c>
       <c r="P37" t="n">
         <v>99999</v>
@@ -3097,70 +3097,70 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cebola-roxa-400g-38393</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cebola Roxa 400g</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
       <c r="F38" t="n">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>2000015</v>
+        <v>2001532</v>
       </c>
       <c r="P38" t="n">
         <v>99999</v>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3.79</v>
+        <v>2.99</v>
       </c>
       <c r="F40" t="n">
         <v>3.79</v>
@@ -3313,39 +3313,43 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-cariorta-1kg-98663</t>
+          <t>melao-amarelo-metade-1-3-kg-63606</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Cariorta 1Kg</t>
+          <t>Melão Amarelo Metade 1,3kg</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>98663</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>63606</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
+        </is>
+      </c>
       <c r="E41" t="n">
-        <v>16.99</v>
+        <v>7.99</v>
       </c>
       <c r="F41" t="n">
-        <v>16.99</v>
+        <v>7.99</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3354,25 +3358,25 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P41" t="n">
         <v>99999</v>
@@ -3381,70 +3385,70 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
+          <t>azeite-italiano-extra-virgem-due-500ml-5472040</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
+          <t>Azeite Italiano Extravirgem Due 500ml</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>99279</t>
+          <t>5472040</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
+          <t>O azeite Due é um blend de azeites do Mediterrâneo que confere um resultado clássico e ideal para o cotidiano da cozinha. Sua elaboração conta com uma seleção cautelosamente realizada pelo Expert em Azeites e Temperos Marcelo Scofano, que anualmente viaja à Toscana (Itália), onde o azeite é produzido, para cuidar de cada detalhe pessoalmente.Due é um azeite clássico, ideal para o dia a dia da cozinha: marinados, refogados, emulsão de molhos, finalização de saladas, massas e pratos do cotidiano. O azeite clássico é extraído de azeitonas maduras. Possui sabor amendoado, com notas amargas e picantes em equilíbrio.O azeite Due faz parte da grupo de marcas exclusivas Zona Sul, criada e pensada com carinho para os cariocas de coração. O planejamento de cada produto exclusivo conta com a participação dos Experts Zona Sul em todo o processo, até chegar na sua mesa. E com a linha Due não é diferente!</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>59.99</v>
+        <v>24.98</v>
       </c>
       <c r="F42" t="n">
-        <v>59.99</v>
+        <v>29.97</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>597</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2020-05-27T00:00:00Z</t>
+          <t>2025-05-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4116721/VF4qT-qqCUAAAAAAAAiyjQ.jpg?v=638846625781330000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>24684</t>
+          <t>40224</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>40151</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>DUE</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2001012</v>
+        <v>2005138</v>
       </c>
       <c r="P42" t="n">
         <v>99999</v>
@@ -3453,61 +3457,61 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>melao-amarelo-metade-1-3-kg-63606</t>
+          <t>espinafre-unidade-200948</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Melão Amarelo Metade 1,3kg</t>
+          <t>Espinafre Unidade</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>200948</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
+          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>7.99</v>
+        <v>2.99</v>
       </c>
       <c r="F43" t="n">
-        <v>7.99</v>
+        <v>3.79</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3597,48 +3601,44 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
+          <t>abobrinha-italiana-cariorta-1kg-98663</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
+          <t>Abobrinha Italiana Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>981168</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
-        </is>
-      </c>
+          <t>98663</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>32.19</v>
+        <v>16.99</v>
       </c>
       <c r="F45" t="n">
-        <v>32.19</v>
+        <v>16.99</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2020-09-22T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3646,21 +3646,21 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>NEVE</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2000291</v>
+        <v>2001012</v>
       </c>
       <c r="P45" t="n">
         <v>99999</v>
@@ -3669,70 +3669,70 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>99279</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>29.98</v>
+        <v>59.99</v>
       </c>
       <c r="F46" t="n">
-        <v>37.9</v>
+        <v>59.99</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2020-05-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>2001329</v>
+        <v>2001012</v>
       </c>
       <c r="P46" t="n">
         <v>99999</v>
@@ -3741,43 +3741,43 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>matte-leao-natural-pet-15l-118214</t>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Matte Leão Natural Pet 1,5L</t>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>118214</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>7.49</v>
+        <v>29.98</v>
       </c>
       <c r="F47" t="n">
-        <v>8.99</v>
+        <v>37.9</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-07-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3790,21 +3790,21 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>MELITTA</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>2000010</v>
+        <v>2001329</v>
       </c>
       <c r="P47" t="n">
         <v>99999</v>
@@ -3885,43 +3885,43 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>azeite-italiano-extra-virgem-due-500ml-5472040</t>
+          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Azeite Italiano Extravirgem Due 500ml</t>
+          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>5472040</t>
+          <t>981168</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>O azeite Due é um blend de azeites do Mediterrâneo que confere um resultado clássico e ideal para o cotidiano da cozinha. Sua elaboração conta com uma seleção cautelosamente realizada pelo Expert em Azeites e Temperos Marcelo Scofano, que anualmente viaja à Toscana (Itália), onde o azeite é produzido, para cuidar de cada detalhe pessoalmente.Due é um azeite clássico, ideal para o dia a dia da cozinha: marinados, refogados, emulsão de molhos, finalização de saladas, massas e pratos do cotidiano. O azeite clássico é extraído de azeitonas maduras. Possui sabor amendoado, com notas amargas e picantes em equilíbrio.O azeite Due faz parte da grupo de marcas exclusivas Zona Sul, criada e pensada com carinho para os cariocas de coração. O planejamento de cada produto exclusivo conta com a participação dos Experts Zona Sul em todo o processo, até chegar na sua mesa. E com a linha Due não é diferente!</t>
+          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>24.98</v>
+        <v>32.19</v>
       </c>
       <c r="F49" t="n">
-        <v>29.97</v>
+        <v>32.19</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2025-05-06T00:00:00Z</t>
+          <t>2020-09-22T00:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4116721/VF4qT-qqCUAAAAAAAAiyjQ.jpg?v=638846625781330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3934,21 +3934,21 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>40224</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>40151</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>DUE</t>
+          <t>NEVE</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2005138</v>
+        <v>2000291</v>
       </c>
       <c r="P49" t="n">
         <v>99999</v>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2.99</v>
+        <v>3.79</v>
       </c>
       <c r="F2" t="n">
         <v>3.79</v>
@@ -651,7 +651,7 @@
         <v>2001056</v>
       </c>
       <c r="P3" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5.39</v>
+        <v>5.99</v>
       </c>
       <c r="F10" t="n">
         <v>5.99</v>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2.99</v>
+        <v>3.39</v>
       </c>
       <c r="F15" t="n">
         <v>3.39</v>
@@ -1521,66 +1521,66 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Pão Francês Panetto  60g Com 4 unidades</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>783250</t>
+          <t>96318</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>5.99</v>
+        <v>24.99</v>
       </c>
       <c r="F16" t="n">
-        <v>5.99</v>
+        <v>24.99</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2024-01-31T00:00:00Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>PANETTO</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2001952</v>
+        <v>2000307</v>
       </c>
       <c r="P16" t="n">
         <v>99999</v>
@@ -1661,66 +1661,66 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pão Francês Panetto  60g Com 4 unidades</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>96318</t>
+          <t>783250</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>24.99</v>
+        <v>5.99</v>
       </c>
       <c r="F18" t="n">
-        <v>24.99</v>
+        <v>5.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2024-01-31T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>PANETTO</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2000307</v>
+        <v>2001952</v>
       </c>
       <c r="P18" t="n">
         <v>99999</v>
@@ -1729,22 +1729,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>morango-250g-289612</t>
+          <t>couve-flor-unidade-189111</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Morango 250g</t>
+          <t>Couve Flor Unidade</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>289612</t>
+          <t>189111</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
+          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1755,17 +1755,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1801,43 +1801,43 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>couve-flor-unidade-189111</t>
+          <t>morango-250g-289612</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Couve Flor Unidade</t>
+          <t>Morango 250g</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>189111</t>
+          <t>289612</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
+          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9.59</v>
+        <v>9.99</v>
       </c>
       <c r="F20" t="n">
         <v>9.99</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
       <c r="F22" t="n">
         <v>10.99</v>
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.99</v>
+        <v>3.79</v>
       </c>
       <c r="F24" t="n">
         <v>3.79</v>
@@ -2161,43 +2161,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
+          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
+          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1180320</t>
+          <t>364738</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
+          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.79</v>
+        <v>4.89</v>
       </c>
       <c r="F25" t="n">
-        <v>2.79</v>
+        <v>4.89</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2025-07-17T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2210,21 +2210,21 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>41057</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>BOMBRIL</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>2001389</v>
+        <v>2000043</v>
       </c>
       <c r="P25" t="n">
         <v>99999</v>
@@ -2233,33 +2233,33 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
+          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
+          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>364738</t>
+          <t>290564</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
+          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4.89</v>
+        <v>23.99</v>
       </c>
       <c r="F26" t="n">
-        <v>4.89</v>
+        <v>26.99</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2282,66 +2282,66 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>SADIA</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>2000043</v>
+        <v>2000057</v>
       </c>
       <c r="P26" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
+          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
+          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>290564</t>
+          <t>1180320</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
+          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>23.99</v>
+        <v>2.79</v>
       </c>
       <c r="F27" t="n">
-        <v>26.99</v>
+        <v>2.79</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2025-07-17T00:00:00Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2354,21 +2354,21 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>SADIA</t>
+          <t>BOMBRIL</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>2000057</v>
+        <v>2001389</v>
       </c>
       <c r="P27" t="n">
         <v>99999</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5.49</v>
+        <v>6.29</v>
       </c>
       <c r="F29" t="n">
         <v>6.29</v>
@@ -2521,43 +2521,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>leite-uht-piracanjuba-integral-1l-865427</t>
+          <t>milho-em-conserva-quero-lata-200g-476625</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Leite Uht Piracanjuba Integral 1L</t>
+          <t>Milho em Conserva Quero Lata 200g</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>865427</t>
+          <t>476625</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
+          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6.69</v>
+        <v>3.69</v>
       </c>
       <c r="F30" t="n">
-        <v>6.69</v>
+        <v>4.99</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2017-04-12T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2570,21 +2570,21 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>QUERO</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2002038</v>
+        <v>2001778</v>
       </c>
       <c r="P30" t="n">
         <v>99999</v>
@@ -2593,43 +2593,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>milho-em-conserva-quero-lata-200g-476625</t>
+          <t>leite-uht-piracanjuba-integral-1l-865427</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Milho em Conserva Quero Lata 200g</t>
+          <t>Leite Uht Piracanjuba Integral 1L</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>476625</t>
+          <t>865427</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
+          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3.69</v>
+        <v>6.69</v>
       </c>
       <c r="F31" t="n">
-        <v>4.99</v>
+        <v>6.69</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2017-04-12T00:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2642,21 +2642,21 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>23232</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>23158</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>QUERO</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>2001778</v>
+        <v>2002038</v>
       </c>
       <c r="P31" t="n">
         <v>99999</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2.99</v>
+        <v>3.79</v>
       </c>
       <c r="F35" t="n">
         <v>3.79</v>
@@ -3241,43 +3241,43 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>alface-crespa-unidade-200875</t>
+          <t>azeite-italiano-extra-virgem-due-500ml-5472040</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Alface Crespa Unidade</t>
+          <t>Azeite Italiano Extravirgem Due 500ml</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>200875</t>
+          <t>5472040</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
+          <t>O azeite Due é um blend de azeites do Mediterrâneo que confere um resultado clássico e ideal para o cotidiano da cozinha. Sua elaboração conta com uma seleção cautelosamente realizada pelo Expert em Azeites e Temperos Marcelo Scofano, que anualmente viaja à Toscana (Itália), onde o azeite é produzido, para cuidar de cada detalhe pessoalmente.Due é um azeite clássico, ideal para o dia a dia da cozinha: marinados, refogados, emulsão de molhos, finalização de saladas, massas e pratos do cotidiano. O azeite clássico é extraído de azeitonas maduras. Possui sabor amendoado, com notas amargas e picantes em equilíbrio.O azeite Due faz parte da grupo de marcas exclusivas Zona Sul, criada e pensada com carinho para os cariocas de coração. O planejamento de cada produto exclusivo conta com a participação dos Experts Zona Sul em todo o processo, até chegar na sua mesa. E com a linha Due não é diferente!</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2.99</v>
+        <v>24.98</v>
       </c>
       <c r="F40" t="n">
-        <v>3.79</v>
+        <v>29.97</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>597</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2025-05-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4116721/VF4qT-qqCUAAAAAAAAiyjQ.jpg?v=638846625781330000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3290,21 +3290,21 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>40224</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>40151</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>DUE</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>2000015</v>
+        <v>2005138</v>
       </c>
       <c r="P40" t="n">
         <v>99999</v>
@@ -3313,61 +3313,61 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>melao-amarelo-metade-1-3-kg-63606</t>
+          <t>alface-crespa-unidade-200875</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Melão Amarelo Metade 1,3kg</t>
+          <t>Alface Crespa Unidade</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>200875</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
+          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>7.99</v>
+        <v>3.79</v>
       </c>
       <c r="F41" t="n">
-        <v>7.99</v>
+        <v>3.79</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3385,70 +3385,70 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>azeite-italiano-extra-virgem-due-500ml-5472040</t>
+          <t>melao-amarelo-metade-1-3-kg-63606</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Azeite Italiano Extravirgem Due 500ml</t>
+          <t>Melão Amarelo Metade 1,3kg</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5472040</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>O azeite Due é um blend de azeites do Mediterrâneo que confere um resultado clássico e ideal para o cotidiano da cozinha. Sua elaboração conta com uma seleção cautelosamente realizada pelo Expert em Azeites e Temperos Marcelo Scofano, que anualmente viaja à Toscana (Itália), onde o azeite é produzido, para cuidar de cada detalhe pessoalmente.Due é um azeite clássico, ideal para o dia a dia da cozinha: marinados, refogados, emulsão de molhos, finalização de saladas, massas e pratos do cotidiano. O azeite clássico é extraído de azeitonas maduras. Possui sabor amendoado, com notas amargas e picantes em equilíbrio.O azeite Due faz parte da grupo de marcas exclusivas Zona Sul, criada e pensada com carinho para os cariocas de coração. O planejamento de cada produto exclusivo conta com a participação dos Experts Zona Sul em todo o processo, até chegar na sua mesa. E com a linha Due não é diferente!</t>
+          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>24.98</v>
+        <v>7.99</v>
       </c>
       <c r="F42" t="n">
-        <v>29.97</v>
+        <v>7.99</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2025-05-06T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4116721/VF4qT-qqCUAAAAAAAAiyjQ.jpg?v=638846625781330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>40224</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>40151</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>DUE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2005138</v>
+        <v>2000015</v>
       </c>
       <c r="P42" t="n">
         <v>99999</v>
@@ -3457,43 +3457,43 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>espinafre-unidade-200948</t>
+          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Espinafre Unidade</t>
+          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>200948</t>
+          <t>5106753</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
+          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2.99</v>
+        <v>11.99</v>
       </c>
       <c r="F43" t="n">
-        <v>3.79</v>
+        <v>11.99</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2021-01-11T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3506,71 +3506,67 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>2000015</v>
+        <v>2003319</v>
       </c>
       <c r="P43" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
+          <t>abobrinha-italiana-cariorta-1kg-98663</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
+          <t>Abobrinha Italiana Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5106753</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
-        </is>
-      </c>
+          <t>98663</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>11.99</v>
+        <v>16.99</v>
       </c>
       <c r="F44" t="n">
-        <v>11.99</v>
+        <v>16.99</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2021-01-11T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3578,21 +3574,21 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>2003319</v>
+        <v>2001012</v>
       </c>
       <c r="P44" t="n">
         <v>99999</v>
@@ -3601,44 +3597,48 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-cariorta-1kg-98663</t>
+          <t>espinafre-unidade-200948</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Cariorta 1Kg</t>
+          <t>Espinafre Unidade</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>98663</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>200948</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
+        </is>
+      </c>
       <c r="E45" t="n">
-        <v>16.99</v>
+        <v>3.79</v>
       </c>
       <c r="F45" t="n">
-        <v>16.99</v>
+        <v>3.79</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3646,21 +3646,21 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P45" t="n">
         <v>99999</v>
@@ -3669,70 +3669,70 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
+          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
+          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>99279</t>
+          <t>1105795</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
+          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>59.99</v>
+        <v>3.99</v>
       </c>
       <c r="F46" t="n">
-        <v>59.99</v>
+        <v>5.99</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2020-05-27T00:00:00Z</t>
+          <t>2023-07-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>24684</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>2001012</v>
+        <v>2000017</v>
       </c>
       <c r="P46" t="n">
         <v>99999</v>
@@ -3741,70 +3741,70 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>99279</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>29.98</v>
+        <v>59.99</v>
       </c>
       <c r="F47" t="n">
-        <v>37.9</v>
+        <v>59.99</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2020-05-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>2001329</v>
+        <v>2001012</v>
       </c>
       <c r="P47" t="n">
         <v>99999</v>
@@ -3813,43 +3813,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1105795</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3.99</v>
+        <v>29.98</v>
       </c>
       <c r="F48" t="n">
-        <v>5.99</v>
+        <v>37.9</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2023-07-26T00:00:00Z</t>
+          <t>2020-07-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3862,21 +3862,21 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>MELITTA</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>2000017</v>
+        <v>2001329</v>
       </c>
       <c r="P48" t="n">
         <v>99999</v>
@@ -3885,43 +3885,43 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
+          <t>matte-leao-natural-pet-15l-118214</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
+          <t>Matte Leão Natural Pet 1,5L</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>981168</t>
+          <t>118214</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
+          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>32.19</v>
+        <v>7.49</v>
       </c>
       <c r="F49" t="n">
-        <v>32.19</v>
+        <v>8.99</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2020-09-22T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3934,21 +3934,21 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>NEVE</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2000291</v>
+        <v>2000010</v>
       </c>
       <c r="P49" t="n">
         <v>99999</v>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -873,43 +873,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
+          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
+          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>828025</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
+          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>29.98</v>
+        <v>24.99</v>
       </c>
       <c r="F7" t="n">
-        <v>43.9</v>
+        <v>24.99</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -922,24 +922,24 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>PILAO</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2000070</v>
+        <v>2003319</v>
       </c>
       <c r="P7" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -1017,43 +1017,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
+          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
+          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>370550</t>
+          <t>828025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
+          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>24.99</v>
+        <v>29.98</v>
       </c>
       <c r="F9" t="n">
-        <v>24.99</v>
+        <v>43.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1066,21 +1066,21 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>PILAO</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2003319</v>
+        <v>2000070</v>
       </c>
       <c r="P9" t="n">
         <v>99999</v>
@@ -1233,70 +1233,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>uva-preta-sem-semente-500-g-674583</t>
+          <t>batata-inglesa-cariorta-12kg-98698</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Uva Preta Sem Semente 500g</t>
+          <t>Batata Inglesa Cariorta 1,2Kg</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>674583</t>
+          <t>98698</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>11.99</v>
+        <v>7.99</v>
       </c>
       <c r="F12" t="n">
-        <v>11.99</v>
+        <v>7.99</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P12" t="n">
         <v>99999</v>
@@ -1305,70 +1305,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>batata-inglesa-cariorta-12kg-98698</t>
+          <t>uva-preta-sem-semente-500-g-674583</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Batata Inglesa Cariorta 1,2Kg</t>
+          <t>Uva Preta Sem Semente 500g</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>674583</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7.99</v>
+        <v>13.99</v>
       </c>
       <c r="F13" t="n">
-        <v>7.99</v>
+        <v>13.99</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P13" t="n">
         <v>99999</v>
@@ -1661,39 +1661,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>couve-flor-unidade-189111</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Couve Flor Unidade</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>189111</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
+        </is>
+      </c>
       <c r="E18" t="n">
-        <v>5.99</v>
+        <v>9.99</v>
       </c>
       <c r="F18" t="n">
-        <v>5.99</v>
+        <v>9.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1706,21 +1710,21 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2001952</v>
+        <v>2000015</v>
       </c>
       <c r="P18" t="n">
         <v>99999</v>
@@ -1729,22 +1733,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>couve-flor-unidade-189111</t>
+          <t>morango-250g-289612</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Couve Flor Unidade</t>
+          <t>Morango 250g</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>189111</t>
+          <t>289612</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
+          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1755,17 +1759,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1778,12 +1782,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1801,43 +1805,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>morango-250g-289612</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Morango 250g</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>289612</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>9.99</v>
+        <v>5.99</v>
       </c>
       <c r="F20" t="n">
-        <v>9.99</v>
+        <v>5.99</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1850,21 +1850,21 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2000015</v>
+        <v>2001952</v>
       </c>
       <c r="P20" t="n">
         <v>99999</v>
@@ -1873,48 +1873,48 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>limao-cariorta-1kg-98981</t>
+          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Limão Cariorta 1Kg</t>
+          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>98981</t>
+          <t>100510</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>11.99</v>
+        <v>1.99</v>
       </c>
       <c r="F21" t="n">
-        <v>11.99</v>
+        <v>2.69</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1922,21 +1922,21 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>LIMPOL</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>2001012</v>
+        <v>2001413</v>
       </c>
       <c r="P21" t="n">
         <v>99999</v>
@@ -1945,48 +1945,48 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>limao-cariorta-1kg-98981</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Limão Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>98981</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>10.99</v>
+        <v>11.99</v>
       </c>
       <c r="F22" t="n">
-        <v>10.99</v>
+        <v>11.99</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1994,21 +1994,21 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P22" t="n">
         <v>99999</v>
@@ -2017,43 +2017,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>100510</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.99</v>
+        <v>10.99</v>
       </c>
       <c r="F23" t="n">
-        <v>2.69</v>
+        <v>10.99</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2066,21 +2066,21 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>LIMPOL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>2001413</v>
+        <v>2000015</v>
       </c>
       <c r="P23" t="n">
         <v>99999</v>
@@ -2161,33 +2161,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
+          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
+          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>364738</t>
+          <t>290564</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
+          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4.89</v>
+        <v>23.99</v>
       </c>
       <c r="F25" t="n">
-        <v>4.89</v>
+        <v>26.99</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2210,21 +2210,21 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>SADIA</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>2000043</v>
+        <v>2000057</v>
       </c>
       <c r="P25" t="n">
         <v>99999</v>
@@ -2233,33 +2233,33 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
+          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
+          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>290564</t>
+          <t>364738</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
+          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>23.99</v>
+        <v>4.89</v>
       </c>
       <c r="F26" t="n">
-        <v>26.99</v>
+        <v>4.89</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2282,24 +2282,24 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>SADIA</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>2000057</v>
+        <v>2000043</v>
       </c>
       <c r="P26" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="27">
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="F28" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2449,29 +2449,29 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>leite-uht-piracanjuba-integral-1l-865427</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Leite Uht Piracanjuba Integral 1L</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>865427</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6.29</v>
+        <v>6.69</v>
       </c>
       <c r="F29" t="n">
-        <v>6.29</v>
+        <v>6.69</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2480,12 +2480,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2017-04-12T00:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2498,21 +2498,21 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>23232</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>23158</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2000400</v>
+        <v>2002038</v>
       </c>
       <c r="P29" t="n">
         <v>99999</v>
@@ -2593,29 +2593,29 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>leite-uht-piracanjuba-integral-1l-865427</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Leite Uht Piracanjuba Integral 1L</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>865427</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6.69</v>
+        <v>5.49</v>
       </c>
       <c r="F31" t="n">
-        <v>6.69</v>
+        <v>6.29</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2624,12 +2624,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2017-04-12T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2642,21 +2642,21 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>2002038</v>
+        <v>2000400</v>
       </c>
       <c r="P31" t="n">
         <v>99999</v>
@@ -2665,43 +2665,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
+          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>129887</t>
+          <t>429392</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>12.99</v>
+        <v>4.99</v>
       </c>
       <c r="F32" t="n">
-        <v>12.99</v>
+        <v>5.69</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2714,21 +2714,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2001401</v>
+        <v>2000027</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2737,43 +2737,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>429392</t>
+          <t>129887</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4.99</v>
+        <v>12.99</v>
       </c>
       <c r="F33" t="n">
-        <v>5.69</v>
+        <v>12.99</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2786,21 +2786,21 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2000027</v>
+        <v>2001401</v>
       </c>
       <c r="P33" t="n">
         <v>99999</v>
@@ -2953,115 +2953,115 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cebola-roxa-400g-38393</t>
+          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cebola Roxa 400g</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>429376</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>7.99</v>
+        <v>3.99</v>
       </c>
       <c r="F36" t="n">
-        <v>7.99</v>
+        <v>3.99</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2000015</v>
+        <v>2000027</v>
       </c>
       <c r="P36" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
+          <t>espinafre-unidade-200948</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
+          <t>Espinafre Unidade</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>429376</t>
+          <t>200948</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3.99</v>
+        <v>3.79</v>
       </c>
       <c r="F37" t="n">
-        <v>3.99</v>
+        <v>3.79</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3074,21 +3074,21 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2000027</v>
+        <v>2000015</v>
       </c>
       <c r="P37" t="n">
         <v>99999</v>
@@ -3097,70 +3097,70 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>melao-amarelo-metade-1-3-kg-63606</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Melão Amarelo Metade 1,3kg</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6.99</v>
+        <v>9.99</v>
       </c>
       <c r="F38" t="n">
-        <v>6.99</v>
+        <v>9.99</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>2001532</v>
+        <v>2000015</v>
       </c>
       <c r="P38" t="n">
         <v>99999</v>
@@ -3169,43 +3169,43 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
+          <t>alface-crespa-unidade-200875</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Alface Crespa Unidade</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>105287</t>
+          <t>200875</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>7.99</v>
+        <v>3.79</v>
       </c>
       <c r="F39" t="n">
-        <v>7.99</v>
+        <v>3.79</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2020-07-06T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3218,21 +3218,21 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>DONA BENTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>2000701</v>
+        <v>2000015</v>
       </c>
       <c r="P39" t="n">
         <v>99999</v>
@@ -3241,43 +3241,43 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>azeite-italiano-extra-virgem-due-500ml-5472040</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Azeite Italiano Extravirgem Due 500ml</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5472040</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>O azeite Due é um blend de azeites do Mediterrâneo que confere um resultado clássico e ideal para o cotidiano da cozinha. Sua elaboração conta com uma seleção cautelosamente realizada pelo Expert em Azeites e Temperos Marcelo Scofano, que anualmente viaja à Toscana (Itália), onde o azeite é produzido, para cuidar de cada detalhe pessoalmente.Due é um azeite clássico, ideal para o dia a dia da cozinha: marinados, refogados, emulsão de molhos, finalização de saladas, massas e pratos do cotidiano. O azeite clássico é extraído de azeitonas maduras. Possui sabor amendoado, com notas amargas e picantes em equilíbrio.O azeite Due faz parte da grupo de marcas exclusivas Zona Sul, criada e pensada com carinho para os cariocas de coração. O planejamento de cada produto exclusivo conta com a participação dos Experts Zona Sul em todo o processo, até chegar na sua mesa. E com a linha Due não é diferente!</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>24.98</v>
+        <v>6.99</v>
       </c>
       <c r="F40" t="n">
-        <v>29.97</v>
+        <v>6.99</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2025-05-06T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4116721/VF4qT-qqCUAAAAAAAAiyjQ.jpg?v=638846625781330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3290,21 +3290,21 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>40224</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>40151</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>DUE</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>2005138</v>
+        <v>2001532</v>
       </c>
       <c r="P40" t="n">
         <v>99999</v>
@@ -3313,43 +3313,43 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>alface-crespa-unidade-200875</t>
+          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Alface Crespa Unidade</t>
+          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>200875</t>
+          <t>5106753</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
+          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3.79</v>
+        <v>11.99</v>
       </c>
       <c r="F41" t="n">
-        <v>3.79</v>
+        <v>11.99</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2021-01-11T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3362,93 +3362,93 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2000015</v>
+        <v>2003319</v>
       </c>
       <c r="P41" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>melao-amarelo-metade-1-3-kg-63606</t>
+          <t>azeite-italiano-extra-virgem-due-500ml-5472040</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Melão Amarelo Metade 1,3kg</t>
+          <t>Azeite Italiano Extravirgem Due 500ml</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>5472040</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
+          <t>O azeite Due é um blend de azeites do Mediterrâneo que confere um resultado clássico e ideal para o cotidiano da cozinha. Sua elaboração conta com uma seleção cautelosamente realizada pelo Expert em Azeites e Temperos Marcelo Scofano, que anualmente viaja à Toscana (Itália), onde o azeite é produzido, para cuidar de cada detalhe pessoalmente.Due é um azeite clássico, ideal para o dia a dia da cozinha: marinados, refogados, emulsão de molhos, finalização de saladas, massas e pratos do cotidiano. O azeite clássico é extraído de azeitonas maduras. Possui sabor amendoado, com notas amargas e picantes em equilíbrio.O azeite Due faz parte da grupo de marcas exclusivas Zona Sul, criada e pensada com carinho para os cariocas de coração. O planejamento de cada produto exclusivo conta com a participação dos Experts Zona Sul em todo o processo, até chegar na sua mesa. E com a linha Due não é diferente!</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>7.99</v>
+        <v>22.98</v>
       </c>
       <c r="F42" t="n">
-        <v>7.99</v>
+        <v>29.97</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>597</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2025-05-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4116721/VF4qT-qqCUAAAAAAAAiyjQ.jpg?v=638846625781330000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>40224</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>40151</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>DUE</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2000015</v>
+        <v>2005138</v>
       </c>
       <c r="P42" t="n">
         <v>99999</v>
@@ -3457,43 +3457,43 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
+          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5106753</t>
+          <t>105287</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>11.99</v>
+        <v>7.99</v>
       </c>
       <c r="F43" t="n">
-        <v>11.99</v>
+        <v>7.99</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2021-01-11T00:00:00Z</t>
+          <t>2020-07-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3506,67 +3506,71 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>DONA BENTA</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>2003319</v>
+        <v>2000701</v>
       </c>
       <c r="P43" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-cariorta-1kg-98663</t>
+          <t>pao-de-forma-plus-vita-tradicional-500-g-252921</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Cariorta 1Kg</t>
+          <t>Pão de Forma Tradicional Plusvita 480g</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>98663</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>252921</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Versátil, prático e para qualquer momento, trazendo a energia necessária para o seu dia. Perfeito para sanduíches, torradas, receitas para o café da manhã, café da tarde, almoço e jantar</t>
+        </is>
+      </c>
       <c r="E44" t="n">
-        <v>16.99</v>
+        <v>9.98</v>
       </c>
       <c r="F44" t="n">
-        <v>16.99</v>
+        <v>9.98</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>183</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3663691/VF4qT-qqCUAAAAAAAAb-gA.jpg?v=638592874910030000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3574,66 +3578,66 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>PLUS VITA</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>2001012</v>
+        <v>2000316</v>
       </c>
       <c r="P44" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>espinafre-unidade-200948</t>
+          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Espinafre Unidade</t>
+          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>200948</t>
+          <t>1105795</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
+          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3.79</v>
+        <v>3.99</v>
       </c>
       <c r="F45" t="n">
-        <v>3.79</v>
+        <v>5.99</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2023-07-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3646,21 +3650,21 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2000015</v>
+        <v>2000017</v>
       </c>
       <c r="P45" t="n">
         <v>99999</v>
@@ -3669,48 +3673,44 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
+          <t>abobrinha-italiana-cariorta-1kg-98663</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
+          <t>Abobrinha Italiana Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1105795</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
-        </is>
-      </c>
+          <t>98663</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>3.99</v>
+        <v>10.99</v>
       </c>
       <c r="F46" t="n">
-        <v>5.99</v>
+        <v>10.99</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2023-07-26T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3718,93 +3718,93 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>2000017</v>
+        <v>2001012</v>
       </c>
       <c r="P46" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
+          <t>batata-palha-yoki-extra-fina-100g-989843</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>99279</t>
+          <t>989843</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>59.99</v>
+        <v>8.1</v>
       </c>
       <c r="F47" t="n">
-        <v>59.99</v>
+        <v>10.99</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020-05-27T00:00:00Z</t>
+          <t>2020-10-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>24684</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>13749</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>YOKI</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>2001012</v>
+        <v>2001336</v>
       </c>
       <c r="P47" t="n">
         <v>99999</v>
@@ -3813,43 +3813,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>818640</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>29.98</v>
+        <v>4.99</v>
       </c>
       <c r="F48" t="n">
-        <v>37.9</v>
+        <v>4.99</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2020-11-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3862,21 +3862,21 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>2001329</v>
+        <v>2002038</v>
       </c>
       <c r="P48" t="n">
         <v>99999</v>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -945,43 +945,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
+          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>140805</t>
+          <t>828025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.29</v>
+        <v>29.98</v>
       </c>
       <c r="F8" t="n">
-        <v>5.29</v>
+        <v>43.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2020-09-25T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -994,21 +994,21 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>SAO LOURENCO</t>
+          <t>PILAO</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2000145</v>
+        <v>2000070</v>
       </c>
       <c r="P8" t="n">
         <v>99999</v>
@@ -1017,43 +1017,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
+          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>828025</t>
+          <t>140805</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>29.98</v>
+        <v>4.29</v>
       </c>
       <c r="F9" t="n">
-        <v>43.9</v>
+        <v>5.29</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-25T00:00:00Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1066,21 +1066,21 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>PILAO</t>
+          <t>SAO LOURENCO</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2000070</v>
+        <v>2000145</v>
       </c>
       <c r="P9" t="n">
         <v>99999</v>
@@ -1305,43 +1305,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>uva-preta-sem-semente-500-g-674583</t>
+          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Uva Preta Sem Semente 500g</t>
+          <t>Detergente Para Louças Odd Clear 500ml</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>674583</t>
+          <t>982911</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
+          <t>ODD voltou!Alto rendimento , controle de odor.</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13.99</v>
+        <v>1.9</v>
       </c>
       <c r="F13" t="n">
-        <v>13.99</v>
+        <v>2.49</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1354,21 +1354,21 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>LIMPPANO</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2000015</v>
+        <v>2001341</v>
       </c>
       <c r="P13" t="n">
         <v>99999</v>
@@ -1377,43 +1377,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
+          <t>uva-preta-sem-semente-500-g-674583</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Odd Clear 500ml</t>
+          <t>Uva Preta Sem Semente 500g</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>982911</t>
+          <t>674583</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ODD voltou!Alto rendimento , controle de odor.</t>
+          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.9</v>
+        <v>13.99</v>
       </c>
       <c r="F14" t="n">
-        <v>2.49</v>
+        <v>13.99</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1426,21 +1426,21 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>LIMPPANO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2001341</v>
+        <v>2000015</v>
       </c>
       <c r="P14" t="n">
         <v>99999</v>
@@ -1805,29 +1805,33 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>100510</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
+        </is>
+      </c>
       <c r="E20" t="n">
-        <v>5.99</v>
+        <v>1.99</v>
       </c>
       <c r="F20" t="n">
-        <v>5.99</v>
+        <v>2.69</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1837,7 +1841,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1850,21 +1854,21 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>LIMPOL</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2001952</v>
+        <v>2001413</v>
       </c>
       <c r="P20" t="n">
         <v>99999</v>
@@ -1873,48 +1877,48 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
+          <t>limao-cariorta-1kg-98981</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
+          <t>Limão Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>100510</t>
+          <t>98981</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.99</v>
+        <v>11.99</v>
       </c>
       <c r="F21" t="n">
-        <v>2.69</v>
+        <v>11.99</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1922,21 +1926,21 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>LIMPOL</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>2001413</v>
+        <v>2001012</v>
       </c>
       <c r="P21" t="n">
         <v>99999</v>
@@ -1945,48 +1949,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>limao-cariorta-1kg-98981</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Limão Cariorta 1Kg</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>98981</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Cariorta selecionados de coração.</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
       <c r="F22" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1994,21 +1994,21 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2001012</v>
+        <v>2001952</v>
       </c>
       <c r="P22" t="n">
         <v>99999</v>
@@ -2227,7 +2227,7 @@
         <v>2000057</v>
       </c>
       <c r="P25" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
@@ -2593,43 +2593,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>couve-manteiga-unidade-201235</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Couve Manteiga Unidade</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>201235</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5.49</v>
+        <v>3.79</v>
       </c>
       <c r="F31" t="n">
-        <v>6.29</v>
+        <v>3.79</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2642,21 +2642,21 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>2000400</v>
+        <v>2000015</v>
       </c>
       <c r="P31" t="n">
         <v>99999</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4.99</v>
+        <v>5.69</v>
       </c>
       <c r="F32" t="n">
         <v>5.69</v>
@@ -2737,33 +2737,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>129887</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>12.99</v>
+        <v>5.49</v>
       </c>
       <c r="F33" t="n">
-        <v>12.99</v>
+        <v>6.29</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2786,21 +2786,21 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2001401</v>
+        <v>2000400</v>
       </c>
       <c r="P33" t="n">
         <v>99999</v>
@@ -2881,43 +2881,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>couve-manteiga-unidade-201235</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Couve Manteiga Unidade</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>201235</t>
+          <t>129887</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
+          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3.79</v>
+        <v>12.99</v>
       </c>
       <c r="F35" t="n">
-        <v>3.79</v>
+        <v>12.99</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2930,21 +2930,21 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2000015</v>
+        <v>2001401</v>
       </c>
       <c r="P35" t="n">
         <v>99999</v>
@@ -2953,43 +2953,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
+          <t>espinafre-unidade-200948</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
+          <t>Espinafre Unidade</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>429376</t>
+          <t>200948</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3.99</v>
+        <v>3.79</v>
       </c>
       <c r="F36" t="n">
-        <v>3.99</v>
+        <v>3.79</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3002,21 +3002,21 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2000027</v>
+        <v>2000015</v>
       </c>
       <c r="P36" t="n">
         <v>99999</v>
@@ -3025,43 +3025,43 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>espinafre-unidade-200948</t>
+          <t>desinfetante-banheiro-tira-limo-veja-x-14-sache-400ml-refil-economico-1066404</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Espinafre Unidade</t>
+          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>200948</t>
+          <t>1066404</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
+          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3.79</v>
+        <v>9.99</v>
       </c>
       <c r="F37" t="n">
-        <v>3.79</v>
+        <v>11.99</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2022-08-11T00:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3927710/VF4qT-qqCUAAAAAAAAOGFQ.jpg?v=638733705155570000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3074,21 +3074,21 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>VEJA</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2000015</v>
+        <v>2000523</v>
       </c>
       <c r="P37" t="n">
         <v>99999</v>
@@ -3097,61 +3097,61 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>melao-amarelo-metade-1-3-kg-63606</t>
+          <t>alface-crespa-unidade-200875</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Melão Amarelo Metade 1,3kg</t>
+          <t>Alface Crespa Unidade</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>200875</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
+          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9.99</v>
+        <v>3.79</v>
       </c>
       <c r="F38" t="n">
-        <v>9.99</v>
+        <v>3.79</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3169,48 +3169,44 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>alface-crespa-unidade-200875</t>
+          <t>abobrinha-italiana-cariorta-1kg-98663</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Alface Crespa Unidade</t>
+          <t>Abobrinha Italiana Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>200875</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
-        </is>
-      </c>
+          <t>98663</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>3.79</v>
+        <v>10.99</v>
       </c>
       <c r="F39" t="n">
-        <v>3.79</v>
+        <v>10.99</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -3218,21 +3214,21 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P39" t="n">
         <v>99999</v>
@@ -3241,43 +3237,43 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>batata-palha-yoki-extra-fina-100g-989843</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>989843</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6.99</v>
+        <v>8.1</v>
       </c>
       <c r="F40" t="n">
-        <v>6.99</v>
+        <v>10.99</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-10-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3290,21 +3286,21 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>13749</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>YOKI</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>2001532</v>
+        <v>2001336</v>
       </c>
       <c r="P40" t="n">
         <v>99999</v>
@@ -3313,115 +3309,115 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
+          <t>melao-amarelo-metade-1-3-kg-63606</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
+          <t>Melão Amarelo Metade 1,3kg</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5106753</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
+          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>11.99</v>
+        <v>9.99</v>
       </c>
       <c r="F41" t="n">
-        <v>11.99</v>
+        <v>9.99</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2021-01-11T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2003319</v>
+        <v>2000015</v>
       </c>
       <c r="P41" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>azeite-italiano-extra-virgem-due-500ml-5472040</t>
+          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Azeite Italiano Extravirgem Due 500ml</t>
+          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5472040</t>
+          <t>818640</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>O azeite Due é um blend de azeites do Mediterrâneo que confere um resultado clássico e ideal para o cotidiano da cozinha. Sua elaboração conta com uma seleção cautelosamente realizada pelo Expert em Azeites e Temperos Marcelo Scofano, que anualmente viaja à Toscana (Itália), onde o azeite é produzido, para cuidar de cada detalhe pessoalmente.Due é um azeite clássico, ideal para o dia a dia da cozinha: marinados, refogados, emulsão de molhos, finalização de saladas, massas e pratos do cotidiano. O azeite clássico é extraído de azeitonas maduras. Possui sabor amendoado, com notas amargas e picantes em equilíbrio.O azeite Due faz parte da grupo de marcas exclusivas Zona Sul, criada e pensada com carinho para os cariocas de coração. O planejamento de cada produto exclusivo conta com a participação dos Experts Zona Sul em todo o processo, até chegar na sua mesa. E com a linha Due não é diferente!</t>
+          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>22.98</v>
+        <v>4.99</v>
       </c>
       <c r="F42" t="n">
-        <v>29.97</v>
+        <v>4.99</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2025-05-06T00:00:00Z</t>
+          <t>2020-11-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4116721/VF4qT-qqCUAAAAAAAAiyjQ.jpg?v=638846625781330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3434,21 +3430,21 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>40224</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>40151</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>DUE</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2005138</v>
+        <v>2002038</v>
       </c>
       <c r="P42" t="n">
         <v>99999</v>
@@ -3457,43 +3453,43 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
+          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>105287</t>
+          <t>1105795</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>7.99</v>
+        <v>3.99</v>
       </c>
       <c r="F43" t="n">
-        <v>7.99</v>
+        <v>5.99</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2020-07-06T00:00:00Z</t>
+          <t>2023-07-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3506,21 +3502,21 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>DONA BENTA</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>2000701</v>
+        <v>2000017</v>
       </c>
       <c r="P43" t="n">
         <v>99999</v>
@@ -3529,43 +3525,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pao-de-forma-plus-vita-tradicional-500-g-252921</t>
+          <t>azeite-italiano-extra-virgem-due-500ml-5472040</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pão de Forma Tradicional Plusvita 480g</t>
+          <t>Azeite Italiano Extravirgem Due 500ml</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>252921</t>
+          <t>5472040</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Versátil, prático e para qualquer momento, trazendo a energia necessária para o seu dia. Perfeito para sanduíches, torradas, receitas para o café da manhã, café da tarde, almoço e jantar</t>
+          <t>O azeite Due é um blend de azeites do Mediterrâneo que confere um resultado clássico e ideal para o cotidiano da cozinha. Sua elaboração conta com uma seleção cautelosamente realizada pelo Expert em Azeites e Temperos Marcelo Scofano, que anualmente viaja à Toscana (Itália), onde o azeite é produzido, para cuidar de cada detalhe pessoalmente.Due é um azeite clássico, ideal para o dia a dia da cozinha: marinados, refogados, emulsão de molhos, finalização de saladas, massas e pratos do cotidiano. O azeite clássico é extraído de azeitonas maduras. Possui sabor amendoado, com notas amargas e picantes em equilíbrio.O azeite Due faz parte da grupo de marcas exclusivas Zona Sul, criada e pensada com carinho para os cariocas de coração. O planejamento de cada produto exclusivo conta com a participação dos Experts Zona Sul em todo o processo, até chegar na sua mesa. E com a linha Due não é diferente!</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>9.98</v>
+        <v>29.97</v>
       </c>
       <c r="F44" t="n">
-        <v>9.98</v>
+        <v>29.97</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>597</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2025-05-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3663691/VF4qT-qqCUAAAAAAAAb-gA.jpg?v=638592874910030000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4116721/VF4qT-qqCUAAAAAAAAiyjQ.jpg?v=638846625781330000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3578,66 +3574,66 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>9715</t>
+          <t>40224</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>40151</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>PLUS VITA</t>
+          <t>DUE</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>2000316</v>
+        <v>2005138</v>
       </c>
       <c r="P44" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
+          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1105795</t>
+          <t>429376</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E45" t="n">
         <v>3.99</v>
       </c>
       <c r="F45" t="n">
-        <v>5.99</v>
+        <v>3.99</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2023-07-26T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3650,21 +3646,21 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2000017</v>
+        <v>2000027</v>
       </c>
       <c r="P45" t="n">
         <v>99999</v>
@@ -3673,39 +3669,43 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-cariorta-1kg-98663</t>
+          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Cariorta 1Kg</t>
+          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>98663</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>99279</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
+        </is>
+      </c>
       <c r="E46" t="n">
-        <v>10.99</v>
+        <v>59.99</v>
       </c>
       <c r="F46" t="n">
-        <v>10.99</v>
+        <v>59.99</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-05-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3714,16 +3714,16 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3735,49 +3735,49 @@
         <v>2001012</v>
       </c>
       <c r="P46" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>batata-palha-yoki-extra-fina-100g-989843</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Batata Palha Yoki Extra Fina 100g</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>989843</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Batata Palha Yoki Extra Fina 100g</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>8.1</v>
+        <v>6.99</v>
       </c>
       <c r="F47" t="n">
-        <v>10.99</v>
+        <v>6.99</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020-10-30T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3790,21 +3790,21 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>YOKI</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>2001336</v>
+        <v>2001532</v>
       </c>
       <c r="P47" t="n">
         <v>99999</v>
@@ -3813,43 +3813,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>818640</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4.99</v>
+        <v>29.98</v>
       </c>
       <c r="F48" t="n">
-        <v>4.99</v>
+        <v>37.9</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2020-11-26T00:00:00Z</t>
+          <t>2020-07-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3862,21 +3862,21 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>MELITTA</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>2002038</v>
+        <v>2001329</v>
       </c>
       <c r="P48" t="n">
         <v>99999</v>
@@ -3885,43 +3885,43 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>matte-leao-natural-pet-15l-118214</t>
+          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Matte Leão Natural Pet 1,5L</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>118214</t>
+          <t>105287</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>7.49</v>
+        <v>7.99</v>
       </c>
       <c r="F49" t="n">
-        <v>8.99</v>
+        <v>7.99</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-07-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3934,21 +3934,21 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>DONA BENTA</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2000010</v>
+        <v>2000701</v>
       </c>
       <c r="P49" t="n">
         <v>99999</v>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -513,43 +513,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rucula-unidade-201006</t>
+          <t>ovos-brancos-jumbo-mantiqueira-com-10-unidades-437638</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rúcula Unidade</t>
+          <t>Ovos Brancos Jumbo Mantiqueira Com 10 Unidades</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>201006</t>
+          <t>437638</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A rúcula é uma hortaliça de baixa caloria (aprox. 29 kcal/100g) e rica em nutrientes como vitaminas A, C e K, além de cálcio, ferro e potássio. Seus principais benefícios incluem ação antioxidante, fortalecimento do sistema imunológico, melhoria da saúde ocular e óssea, auxílio na digestão, controle do colesterol e redução de riscos cardiovasculares.A melhor forma de comer rúcula é crua em saladas, temperada com azeite, sal e limão, mas também é versátil em pratos quentes como massas, risotos e sanduíches, ou refogada rapidamente</t>
+          <t>Os Ovos Jumbo Mantiqueira possuem maior tamanho, ideais para quem busca uma alimentação rica em vitaminas, proteínas e minerais, ou para quem gosta de um maior rendimento em suas receitas. Um único ovo contém quase todos os nutrientes necessários para manter o corpo saudável, fortalecendo os ossos e auxiliando em dietas para perda de peso ou ganho de massa.O Ovo Jumbo Mantiqueira é um produto da linha Especial da marca e possui a qualidade superior, passando por um moderno sistema de seleção, limpeza e embalagem sem contato de mãos humanas.Especificações:Ovos maiores, tamanho família.Embalagem com 10 unidades.Ovos brancos e vermelhos tipo jumbo categoria A.</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3.79</v>
+        <v>10.9</v>
       </c>
       <c r="F2" t="n">
-        <v>3.79</v>
+        <v>10.9</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3040890/VF4qT-qqCUAAAAAAAAHLpQ.jpg?v=637792545082200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3976126/VF4qT-qqCUAAAAAAAAh4RA.jpg?v=638769994856100000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -562,66 +562,66 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>MANTIQUEIRA</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>2000015</v>
+        <v>2001056</v>
       </c>
       <c r="P2" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ovos-brancos-jumbo-mantiqueira-com-10-unidades-437638</t>
+          <t>rucula-unidade-201006</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ovos Brancos Jumbo Mantiqueira Com 10 Unidades</t>
+          <t>Rúcula Unidade</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>437638</t>
+          <t>201006</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Os Ovos Jumbo Mantiqueira possuem maior tamanho, ideais para quem busca uma alimentação rica em vitaminas, proteínas e minerais, ou para quem gosta de um maior rendimento em suas receitas. Um único ovo contém quase todos os nutrientes necessários para manter o corpo saudável, fortalecendo os ossos e auxiliando em dietas para perda de peso ou ganho de massa.O Ovo Jumbo Mantiqueira é um produto da linha Especial da marca e possui a qualidade superior, passando por um moderno sistema de seleção, limpeza e embalagem sem contato de mãos humanas.Especificações:Ovos maiores, tamanho família.Embalagem com 10 unidades.Ovos brancos e vermelhos tipo jumbo categoria A.</t>
+          <t>A rúcula é uma hortaliça de baixa caloria (aprox. 29 kcal/100g) e rica em nutrientes como vitaminas A, C e K, além de cálcio, ferro e potássio. Seus principais benefícios incluem ação antioxidante, fortalecimento do sistema imunológico, melhoria da saúde ocular e óssea, auxílio na digestão, controle do colesterol e redução de riscos cardiovasculares.A melhor forma de comer rúcula é crua em saladas, temperada com azeite, sal e limão, mas também é versátil em pratos quentes como massas, risotos e sanduíches, ou refogada rapidamente</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10.9</v>
+        <v>2.99</v>
       </c>
       <c r="F3" t="n">
-        <v>10.9</v>
+        <v>3.79</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3976126/VF4qT-qqCUAAAAAAAAh4RA.jpg?v=638769994856100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3040890/VF4qT-qqCUAAAAAAAAHLpQ.jpg?v=637792545082200000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -634,24 +634,24 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MANTIQUEIRA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2001056</v>
+        <v>2000015</v>
       </c>
       <c r="P3" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="4">
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.96</v>
+        <v>1.52</v>
       </c>
       <c r="F6" t="n">
         <v>1.96</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.29</v>
+        <v>5.29</v>
       </c>
       <c r="F9" t="n">
         <v>5.29</v>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5.99</v>
+        <v>5.39</v>
       </c>
       <c r="F10" t="n">
         <v>5.99</v>
@@ -1227,7 +1227,7 @@
         <v>2000015</v>
       </c>
       <c r="P11" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -1377,70 +1377,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>uva-preta-sem-semente-500-g-674583</t>
+          <t>mamao-papaia-cariorta-12kg-99007</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Uva Preta Sem Semente 500g</t>
+          <t>Mamão Papaia Cariorta 1,2kg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>674583</t>
+          <t>99007</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13.99</v>
+        <v>9.99</v>
       </c>
       <c r="F14" t="n">
-        <v>13.99</v>
+        <v>9.99</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P14" t="n">
         <v>99999</v>
@@ -1449,33 +1449,33 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cheiro-verde-unidade-201049</t>
+          <t>couve-flor-unidade-189111</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cheiro Verde Unidade</t>
+          <t>Couve Flor Unidade</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>201049</t>
+          <t>189111</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3.39</v>
+        <v>9.59</v>
       </c>
       <c r="F15" t="n">
-        <v>3.39</v>
+        <v>9.99</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1521,66 +1521,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
+          <t>uva-preta-sem-semente-500-g-674583</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pão Francês Panetto  60g Com 4 unidades</t>
+          <t>Uva Preta Sem Semente 500g</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>96318</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>674583</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
+        </is>
+      </c>
       <c r="E16" t="n">
-        <v>24.99</v>
+        <v>12.49</v>
       </c>
       <c r="F16" t="n">
-        <v>24.99</v>
+        <v>13.99</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2024-01-31T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>PANETTO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2000307</v>
+        <v>2000015</v>
       </c>
       <c r="P16" t="n">
         <v>99999</v>
@@ -1589,70 +1593,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mamao-papaia-cariorta-12kg-99007</t>
+          <t>cheiro-verde-unidade-201049</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mamão Papaia Cariorta 1,2kg</t>
+          <t>Cheiro Verde Unidade</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>99007</t>
+          <t>201049</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9.99</v>
+        <v>2.99</v>
       </c>
       <c r="F17" t="n">
-        <v>9.99</v>
+        <v>3.39</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P17" t="n">
         <v>99999</v>
@@ -1661,70 +1665,66 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>couve-flor-unidade-189111</t>
+          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Couve Flor Unidade</t>
+          <t>Pão Francês Panetto  60g Com 4 unidades</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>189111</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
-        </is>
-      </c>
+          <t>96318</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
       <c r="F18" t="n">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2024-01-31T00:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PANETTO</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2000015</v>
+        <v>2000307</v>
       </c>
       <c r="P18" t="n">
         <v>99999</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.99</v>
+        <v>8.99</v>
       </c>
       <c r="F19" t="n">
         <v>9.99</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>10.99</v>
+        <v>9.85</v>
       </c>
       <c r="F23" t="n">
         <v>10.99</v>
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.79</v>
+        <v>2.99</v>
       </c>
       <c r="F24" t="n">
         <v>3.79</v>
@@ -2227,7 +2227,7 @@
         <v>2000057</v>
       </c>
       <c r="P25" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="26">
@@ -2449,43 +2449,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>leite-uht-piracanjuba-integral-1l-865427</t>
+          <t>milho-em-conserva-quero-lata-200g-476625</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Leite Uht Piracanjuba Integral 1L</t>
+          <t>Milho em Conserva Quero Lata 200g</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>865427</t>
+          <t>476625</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
+          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6.69</v>
+        <v>3.69</v>
       </c>
       <c r="F29" t="n">
-        <v>6.69</v>
+        <v>4.99</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2017-04-12T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2498,21 +2498,21 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>QUERO</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2002038</v>
+        <v>2001778</v>
       </c>
       <c r="P29" t="n">
         <v>99999</v>
@@ -2521,43 +2521,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>milho-em-conserva-quero-lata-200g-476625</t>
+          <t>couve-manteiga-unidade-201235</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Milho em Conserva Quero Lata 200g</t>
+          <t>Couve Manteiga Unidade</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>476625</t>
+          <t>201235</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
+          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3.69</v>
+        <v>2.99</v>
       </c>
       <c r="F30" t="n">
-        <v>4.99</v>
+        <v>3.79</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2570,21 +2570,21 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>QUERO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2001778</v>
+        <v>2000015</v>
       </c>
       <c r="P30" t="n">
         <v>99999</v>
@@ -2593,43 +2593,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>couve-manteiga-unidade-201235</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Couve Manteiga Unidade</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>201235</t>
+          <t>129887</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
+          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3.79</v>
+        <v>12.99</v>
       </c>
       <c r="F31" t="n">
-        <v>3.79</v>
+        <v>12.99</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2642,21 +2642,21 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>2000015</v>
+        <v>2001401</v>
       </c>
       <c r="P31" t="n">
         <v>99999</v>
@@ -2665,43 +2665,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>429392</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5.69</v>
+        <v>5.49</v>
       </c>
       <c r="F32" t="n">
-        <v>5.69</v>
+        <v>6.29</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2714,21 +2714,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2000027</v>
+        <v>2000400</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2737,29 +2737,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>leite-uht-piracanjuba-integral-1l-865427</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Leite Uht Piracanjuba Integral 1L</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>865427</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5.49</v>
+        <v>6.69</v>
       </c>
       <c r="F33" t="n">
-        <v>6.29</v>
+        <v>6.69</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2017-04-12T00:00:00Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2786,21 +2786,21 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>23232</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>23158</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2000400</v>
+        <v>2002038</v>
       </c>
       <c r="P33" t="n">
         <v>99999</v>
@@ -2809,43 +2809,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sal-refinado-iodado-ita-1kg-117293</t>
+          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>429392</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4.39</v>
+        <v>5.69</v>
       </c>
       <c r="F34" t="n">
-        <v>4.39</v>
+        <v>5.69</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2858,21 +2858,21 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>2000066</v>
+        <v>2000027</v>
       </c>
       <c r="P34" t="n">
         <v>99999</v>
@@ -2881,43 +2881,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
+          <t>sal-refinado-iodado-ita-1kg-117293</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>129887</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>12.99</v>
+        <v>4.39</v>
       </c>
       <c r="F35" t="n">
-        <v>12.99</v>
+        <v>4.39</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2930,21 +2930,21 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2001401</v>
+        <v>2000066</v>
       </c>
       <c r="P35" t="n">
         <v>99999</v>
@@ -2953,43 +2953,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>espinafre-unidade-200948</t>
+          <t>desinfetante-banheiro-tira-limo-veja-x-14-sache-400ml-refil-economico-1066404</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Espinafre Unidade</t>
+          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>200948</t>
+          <t>1066404</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
+          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3.79</v>
+        <v>9.99</v>
       </c>
       <c r="F36" t="n">
-        <v>3.79</v>
+        <v>11.99</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2022-08-11T00:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3927710/VF4qT-qqCUAAAAAAAAOGFQ.jpg?v=638733705155570000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3002,21 +3002,21 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>VEJA</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2000015</v>
+        <v>2000523</v>
       </c>
       <c r="P36" t="n">
         <v>99999</v>
@@ -3025,43 +3025,43 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>desinfetante-banheiro-tira-limo-veja-x-14-sache-400ml-refil-economico-1066404</t>
+          <t>espinafre-unidade-200948</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
+          <t>Espinafre Unidade</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1066404</t>
+          <t>200948</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
+          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>9.99</v>
+        <v>2.99</v>
       </c>
       <c r="F37" t="n">
-        <v>11.99</v>
+        <v>3.79</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2022-08-11T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3927710/VF4qT-qqCUAAAAAAAAOGFQ.jpg?v=638733705155570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3074,21 +3074,21 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>27159</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>27083</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>VEJA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2000523</v>
+        <v>2000015</v>
       </c>
       <c r="P37" t="n">
         <v>99999</v>
@@ -3097,48 +3097,44 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>alface-crespa-unidade-200875</t>
+          <t>abobrinha-italiana-cariorta-1kg-98663</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Alface Crespa Unidade</t>
+          <t>Abobrinha Italiana Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>200875</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
-        </is>
-      </c>
+          <t>98663</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>3.79</v>
+        <v>10.99</v>
       </c>
       <c r="F38" t="n">
-        <v>3.79</v>
+        <v>10.99</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -3146,21 +3142,21 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P38" t="n">
         <v>99999</v>
@@ -3169,39 +3165,43 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-cariorta-1kg-98663</t>
+          <t>melao-amarelo-metade-1-3-kg-63606</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Cariorta 1Kg</t>
+          <t>Melão Amarelo Metade 1,3kg</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>98663</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>63606</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
+        </is>
+      </c>
       <c r="E39" t="n">
-        <v>10.99</v>
+        <v>8.99</v>
       </c>
       <c r="F39" t="n">
-        <v>10.99</v>
+        <v>9.99</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P39" t="n">
         <v>99999</v>
@@ -3309,61 +3309,61 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>melao-amarelo-metade-1-3-kg-63606</t>
+          <t>alface-crespa-unidade-200875</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Melão Amarelo Metade 1,3kg</t>
+          <t>Alface Crespa Unidade</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>200875</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
+          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>9.99</v>
+        <v>2.99</v>
       </c>
       <c r="F41" t="n">
-        <v>9.99</v>
+        <v>3.79</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3381,43 +3381,43 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
+          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
+          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>818640</t>
+          <t>1105795</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
+          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4.99</v>
+        <v>3.99</v>
       </c>
       <c r="F42" t="n">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2020-11-26T00:00:00Z</t>
+          <t>2023-07-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3430,21 +3430,21 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2002038</v>
+        <v>2000017</v>
       </c>
       <c r="P42" t="n">
         <v>99999</v>
@@ -3453,43 +3453,43 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
+          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
+          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1105795</t>
+          <t>818640</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
+          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
       <c r="F43" t="n">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2023-07-26T00:00:00Z</t>
+          <t>2020-11-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3502,21 +3502,21 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>2000017</v>
+        <v>2002038</v>
       </c>
       <c r="P43" t="n">
         <v>99999</v>
@@ -3525,43 +3525,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>azeite-italiano-extra-virgem-due-500ml-5472040</t>
+          <t>pao-de-forma-plus-vita-tradicional-500-g-252921</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Azeite Italiano Extravirgem Due 500ml</t>
+          <t>Pão de Forma Tradicional Plusvita 480g</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5472040</t>
+          <t>252921</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>O azeite Due é um blend de azeites do Mediterrâneo que confere um resultado clássico e ideal para o cotidiano da cozinha. Sua elaboração conta com uma seleção cautelosamente realizada pelo Expert em Azeites e Temperos Marcelo Scofano, que anualmente viaja à Toscana (Itália), onde o azeite é produzido, para cuidar de cada detalhe pessoalmente.Due é um azeite clássico, ideal para o dia a dia da cozinha: marinados, refogados, emulsão de molhos, finalização de saladas, massas e pratos do cotidiano. O azeite clássico é extraído de azeitonas maduras. Possui sabor amendoado, com notas amargas e picantes em equilíbrio.O azeite Due faz parte da grupo de marcas exclusivas Zona Sul, criada e pensada com carinho para os cariocas de coração. O planejamento de cada produto exclusivo conta com a participação dos Experts Zona Sul em todo o processo, até chegar na sua mesa. E com a linha Due não é diferente!</t>
+          <t>Versátil, prático e para qualquer momento, trazendo a energia necessária para o seu dia. Perfeito para sanduíches, torradas, receitas para o café da manhã, café da tarde, almoço e jantar</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>29.97</v>
+        <v>9.98</v>
       </c>
       <c r="F44" t="n">
-        <v>29.97</v>
+        <v>9.98</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>183</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2025-05-06T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4116721/VF4qT-qqCUAAAAAAAAiyjQ.jpg?v=638846625781330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3663691/VF4qT-qqCUAAAAAAAAb-gA.jpg?v=638592874910030000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3574,66 +3574,66 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>40224</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>40151</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>DUE</t>
+          <t>PLUS VITA</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>2005138</v>
+        <v>2000316</v>
       </c>
       <c r="P44" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-lata-350-ml-429376</t>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Lata 350ml</t>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>429376</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Uma Lata de Coca-Cola Sem Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3.99</v>
+        <v>29.98</v>
       </c>
       <c r="F45" t="n">
-        <v>3.99</v>
+        <v>37.9</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-07-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483405/VF4qT-qqCUAAAAAAAAoaow.jpg?v=639052524439630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3646,21 +3646,21 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>MELITTA</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2000027</v>
+        <v>2001329</v>
       </c>
       <c r="P45" t="n">
         <v>99999</v>
@@ -3813,43 +3813,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>matte-leao-natural-pet-15l-118214</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Matte Leão Natural Pet 1,5L</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>118214</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>29.98</v>
+        <v>7.49</v>
       </c>
       <c r="F48" t="n">
-        <v>37.9</v>
+        <v>8.99</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3862,21 +3862,21 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>2001329</v>
+        <v>2000010</v>
       </c>
       <c r="P48" t="n">
         <v>99999</v>
@@ -3885,43 +3885,39 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
+          <t>file-de-peito-de-frango-congelado-rivelli-bandeja-1kg-1023799</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Filé de Peito de Frango Congelado Rivelli Bandeja 1kg</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>105287</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
-        </is>
-      </c>
+          <t>1023799</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>7.99</v>
+        <v>19.99</v>
       </c>
       <c r="F49" t="n">
-        <v>7.99</v>
+        <v>25.99</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2020-07-06T00:00:00Z</t>
+          <t>2021-07-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038302/VF4qT-qqCUAAAAAAAAKY8g.jpg?v=637792395730970000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3934,21 +3930,21 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>DONA BENTA</t>
+          <t>Rivelli</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2000701</v>
+        <v>2004122</v>
       </c>
       <c r="P49" t="n">
         <v>99999</v>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -513,43 +513,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ovos-brancos-jumbo-mantiqueira-com-10-unidades-437638</t>
+          <t>mamao-papaia-unidade-5130786</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ovos Brancos Jumbo Mantiqueira Com 10 Unidades</t>
+          <t>Mamão Papaia Unidade</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>437638</t>
+          <t>5130786</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Os Ovos Jumbo Mantiqueira possuem maior tamanho, ideais para quem busca uma alimentação rica em vitaminas, proteínas e minerais, ou para quem gosta de um maior rendimento em suas receitas. Um único ovo contém quase todos os nutrientes necessários para manter o corpo saudável, fortalecendo os ossos e auxiliando em dietas para perda de peso ou ganho de massa.O Ovo Jumbo Mantiqueira é um produto da linha Especial da marca e possui a qualidade superior, passando por um moderno sistema de seleção, limpeza e embalagem sem contato de mãos humanas.Especificações:Ovos maiores, tamanho família.Embalagem com 10 unidades.Ovos brancos e vermelhos tipo jumbo categoria A.</t>
+          <t>O Mamão Papaia é uma fruta tropical leve, nutritiva e muito apreciada pelo seu sabor suave, polpa macia e alto rendimento. Perfeito para o consumo diário, traz frescor e saúde para a alimentação.Benefícios Nutricionais-Auxilia a digestão, graças à presença natural da enzima papaína-Rico em fibras, contribuindo para o bom funcionamento intestinal-Fonte de vitamina C, que fortalece o sistema imunológico-Contém vitamina A, importante para a saúde da pele e da visão-Possui ação antioxidante</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10.9</v>
+        <v>5.19</v>
       </c>
       <c r="F2" t="n">
-        <v>10.9</v>
+        <v>5.19</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2017-02-17T00:00:00Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3976126/VF4qT-qqCUAAAAAAAAh4RA.jpg?v=638769994856100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500752/VF4qT-qqCUAAAAAAAAQ0fA.jpg?v=639071532100230000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -562,66 +562,66 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>32822</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>32747</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>MANTIQUEIRA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>2001056</v>
+        <v>2000015</v>
       </c>
       <c r="P2" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rucula-unidade-201006</t>
+          <t>ovos-brancos-jumbo-mantiqueira-com-10-unidades-437638</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rúcula Unidade</t>
+          <t>Ovos Brancos Jumbo Mantiqueira Com 10 Unidades</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>201006</t>
+          <t>437638</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A rúcula é uma hortaliça de baixa caloria (aprox. 29 kcal/100g) e rica em nutrientes como vitaminas A, C e K, além de cálcio, ferro e potássio. Seus principais benefícios incluem ação antioxidante, fortalecimento do sistema imunológico, melhoria da saúde ocular e óssea, auxílio na digestão, controle do colesterol e redução de riscos cardiovasculares.A melhor forma de comer rúcula é crua em saladas, temperada com azeite, sal e limão, mas também é versátil em pratos quentes como massas, risotos e sanduíches, ou refogada rapidamente</t>
+          <t>Os Ovos Jumbo Mantiqueira possuem maior tamanho, ideais para quem busca uma alimentação rica em vitaminas, proteínas e minerais, ou para quem gosta de um maior rendimento em suas receitas. Um único ovo contém quase todos os nutrientes necessários para manter o corpo saudável, fortalecendo os ossos e auxiliando em dietas para perda de peso ou ganho de massa.O Ovo Jumbo Mantiqueira é um produto da linha Especial da marca e possui a qualidade superior, passando por um moderno sistema de seleção, limpeza e embalagem sem contato de mãos humanas.Especificações:Ovos maiores, tamanho família.Embalagem com 10 unidades.Ovos brancos e vermelhos tipo jumbo categoria A.</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2.99</v>
+        <v>10.9</v>
       </c>
       <c r="F3" t="n">
-        <v>3.79</v>
+        <v>10.9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3040890/VF4qT-qqCUAAAAAAAAHLpQ.jpg?v=637792545082200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3976126/VF4qT-qqCUAAAAAAAAh4RA.jpg?v=638769994856100000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -634,24 +634,24 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>MANTIQUEIRA</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2000015</v>
+        <v>2001056</v>
       </c>
       <c r="P3" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7.49</v>
+        <v>7.95</v>
       </c>
       <c r="F4" t="n">
         <v>8.99</v>
@@ -873,43 +873,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
+          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
+          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>370550</t>
+          <t>828025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
+          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>24.99</v>
+        <v>32.98</v>
       </c>
       <c r="F7" t="n">
-        <v>24.99</v>
+        <v>43.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -922,66 +922,66 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>PILAO</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2003319</v>
+        <v>2000070</v>
       </c>
       <c r="P7" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
+          <t>manga-palmer-unidade-5130760</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
+          <t>Manga Palmer Unidade</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>828025</t>
+          <t>5130760</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
+          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>29.98</v>
+        <v>5.39</v>
       </c>
       <c r="F8" t="n">
-        <v>43.9</v>
+        <v>5.99</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2023-02-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -994,21 +994,21 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>31902</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>PILAO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2000070</v>
+        <v>2000015</v>
       </c>
       <c r="P8" t="n">
         <v>99999</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5.29</v>
+        <v>4.19</v>
       </c>
       <c r="F9" t="n">
         <v>5.29</v>
@@ -1089,61 +1089,61 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>manga-palmer-unidade-5130760</t>
+          <t>mucarela-em-fatias-92363</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Manga Palmer Unidade</t>
+          <t>Muçarela  em Fatias 200g</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5130760</t>
+          <t>92363</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
+          <t>Muçarela em Fatias</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5.39</v>
+        <v>59.9</v>
       </c>
       <c r="F10" t="n">
-        <v>5.99</v>
+        <v>59.9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2023-02-16T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1161,43 +1161,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mucarela-em-fatias-92363</t>
+          <t>batata-inglesa-cariorta-12kg-98698</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Muçarela  em Fatias 200g</t>
+          <t>Batata Inglesa Cariorta 1,2Kg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>92363</t>
+          <t>98698</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Muçarela em Fatias</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>59.9</v>
+        <v>7.99</v>
       </c>
       <c r="F11" t="n">
-        <v>59.9</v>
+        <v>7.99</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1206,97 +1206,97 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P11" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>batata-inglesa-cariorta-12kg-98698</t>
+          <t>couve-flor-unidade-189111</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Batata Inglesa Cariorta 1,2Kg</t>
+          <t>Couve Flor Unidade</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>189111</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.99</v>
+        <v>9.59</v>
       </c>
       <c r="F12" t="n">
-        <v>7.99</v>
+        <v>9.99</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P12" t="n">
         <v>99999</v>
@@ -1305,43 +1305,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
+          <t>cheiro-verde-unidade-201049</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Odd Clear 500ml</t>
+          <t>Cheiro Verde Unidade</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>982911</t>
+          <t>201049</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ODD voltou!Alto rendimento , controle de odor.</t>
+          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.9</v>
+        <v>2.99</v>
       </c>
       <c r="F13" t="n">
-        <v>2.49</v>
+        <v>3.39</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1354,21 +1354,21 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>LIMPPANO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2001341</v>
+        <v>2000015</v>
       </c>
       <c r="P13" t="n">
         <v>99999</v>
@@ -1449,70 +1449,66 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>couve-flor-unidade-189111</t>
+          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Couve Flor Unidade</t>
+          <t>Pão Francês Panetto  60g Com 4 unidades</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>189111</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
-        </is>
-      </c>
+          <t>96318</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>9.59</v>
+        <v>24.99</v>
       </c>
       <c r="F15" t="n">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2024-01-31T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PANETTO</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2000015</v>
+        <v>2000307</v>
       </c>
       <c r="P15" t="n">
         <v>99999</v>
@@ -1593,43 +1589,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cheiro-verde-unidade-201049</t>
+          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cheiro Verde Unidade</t>
+          <t>Detergente Para Louças Odd Clear 500ml</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>201049</t>
+          <t>982911</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+          <t>ODD voltou!Alto rendimento , controle de odor.</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.99</v>
+        <v>2.49</v>
       </c>
       <c r="F17" t="n">
-        <v>3.39</v>
+        <v>2.49</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1642,21 +1638,21 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>LIMPPANO</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2000015</v>
+        <v>2001341</v>
       </c>
       <c r="P17" t="n">
         <v>99999</v>
@@ -1665,66 +1661,70 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
+          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pão Francês Panetto  60g Com 4 unidades</t>
+          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>96318</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>100510</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
+        </is>
+      </c>
       <c r="E18" t="n">
-        <v>24.99</v>
+        <v>1.99</v>
       </c>
       <c r="F18" t="n">
-        <v>24.99</v>
+        <v>2.69</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2024-01-31T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>PANETTO</t>
+          <t>LIMPOL</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2000307</v>
+        <v>2001413</v>
       </c>
       <c r="P18" t="n">
         <v>99999</v>
@@ -1805,33 +1805,29 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>100510</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>1.99</v>
+        <v>5.99</v>
       </c>
       <c r="F20" t="n">
-        <v>2.69</v>
+        <v>5.99</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1841,7 +1837,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1854,21 +1850,21 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>LIMPOL</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2001413</v>
+        <v>2001952</v>
       </c>
       <c r="P20" t="n">
         <v>99999</v>
@@ -1949,39 +1945,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>290564</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
+        </is>
+      </c>
       <c r="E22" t="n">
-        <v>5.99</v>
+        <v>23.99</v>
       </c>
       <c r="F22" t="n">
-        <v>5.99</v>
+        <v>26.99</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1994,21 +1994,21 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>SADIA</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2001952</v>
+        <v>2000057</v>
       </c>
       <c r="P22" t="n">
         <v>99999</v>
@@ -2017,43 +2017,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>coentro-unidade-200930</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Coentro Unidade</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>200930</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
+          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>9.85</v>
+        <v>2.99</v>
       </c>
       <c r="F23" t="n">
-        <v>10.99</v>
+        <v>3.79</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2089,43 +2089,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>coentro-unidade-200930</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Coentro Unidade</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>200930</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.99</v>
+        <v>9.85</v>
       </c>
       <c r="F24" t="n">
-        <v>3.79</v>
+        <v>10.99</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2161,33 +2161,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
+          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
+          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>290564</t>
+          <t>364738</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
+          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>23.99</v>
+        <v>3.97</v>
       </c>
       <c r="F25" t="n">
-        <v>26.99</v>
+        <v>4.89</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2210,21 +2210,21 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>SADIA</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>2000057</v>
+        <v>2000043</v>
       </c>
       <c r="P25" t="n">
         <v>99999</v>
@@ -2233,43 +2233,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
+          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
+          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>364738</t>
+          <t>1180320</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
+          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4.89</v>
+        <v>2.79</v>
       </c>
       <c r="F26" t="n">
-        <v>4.89</v>
+        <v>2.79</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2025-07-17T00:00:00Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2282,21 +2282,21 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>BOMBRIL</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>2000043</v>
+        <v>2001389</v>
       </c>
       <c r="P26" t="n">
         <v>99999</v>
@@ -2305,43 +2305,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
+          <t>abobrinha-italiana-unidade-423513</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1180320</t>
+          <t>423513</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.79</v>
+        <v>3.5</v>
       </c>
       <c r="F27" t="n">
-        <v>2.79</v>
+        <v>3.5</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2025-07-17T00:00:00Z</t>
+          <t>2020-12-07T00:00:00Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2354,21 +2354,21 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>41057</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>BOMBRIL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>2001389</v>
+        <v>2000015</v>
       </c>
       <c r="P27" t="n">
         <v>99999</v>
@@ -2377,43 +2377,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-unidade-423513</t>
+          <t>couve-manteiga-unidade-201235</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Couve Manteiga Unidade</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>201235</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="F28" t="n">
-        <v>3.5</v>
+        <v>3.79</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2020-12-07T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2449,43 +2449,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>milho-em-conserva-quero-lata-200g-476625</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Milho em Conserva Quero Lata 200g</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>476625</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3.69</v>
+        <v>6.29</v>
       </c>
       <c r="F29" t="n">
-        <v>4.99</v>
+        <v>6.29</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2498,21 +2498,21 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>QUERO</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2001778</v>
+        <v>2000400</v>
       </c>
       <c r="P29" t="n">
         <v>99999</v>
@@ -2521,43 +2521,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>couve-manteiga-unidade-201235</t>
+          <t>milho-em-conserva-quero-lata-200g-476625</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Couve Manteiga Unidade</t>
+          <t>Milho em Conserva Quero Lata 200g</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>201235</t>
+          <t>476625</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
+          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.99</v>
+        <v>3.69</v>
       </c>
       <c r="F30" t="n">
-        <v>3.79</v>
+        <v>4.99</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2570,21 +2570,21 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>QUERO</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2000015</v>
+        <v>2001778</v>
       </c>
       <c r="P30" t="n">
         <v>99999</v>
@@ -2665,43 +2665,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>429392</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5.49</v>
+        <v>4.99</v>
       </c>
       <c r="F32" t="n">
-        <v>6.29</v>
+        <v>5.69</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2714,21 +2714,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2000400</v>
+        <v>2000027</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2737,43 +2737,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>leite-uht-piracanjuba-integral-1l-865427</t>
+          <t>sal-refinado-iodado-ita-1kg-117293</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Leite Uht Piracanjuba Integral 1L</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>865427</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6.69</v>
+        <v>4.39</v>
       </c>
       <c r="F33" t="n">
-        <v>6.69</v>
+        <v>4.39</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2017-04-12T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2786,21 +2786,21 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2002038</v>
+        <v>2000066</v>
       </c>
       <c r="P33" t="n">
         <v>99999</v>
@@ -2809,43 +2809,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
+          <t>leite-uht-piracanjuba-integral-1l-865427</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
+          <t>Leite Uht Piracanjuba Integral 1L</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>429392</t>
+          <t>865427</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5.69</v>
+        <v>6.69</v>
       </c>
       <c r="F34" t="n">
-        <v>5.69</v>
+        <v>6.69</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2017-04-12T00:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2858,21 +2858,21 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>23232</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>23158</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>2000027</v>
+        <v>2002038</v>
       </c>
       <c r="P34" t="n">
         <v>99999</v>
@@ -2881,43 +2881,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sal-refinado-iodado-ita-1kg-117293</t>
+          <t>espinafre-unidade-200948</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Espinafre Unidade</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>200948</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4.39</v>
+        <v>2.99</v>
       </c>
       <c r="F35" t="n">
-        <v>4.39</v>
+        <v>3.79</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2930,21 +2930,21 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2000066</v>
+        <v>2000015</v>
       </c>
       <c r="P35" t="n">
         <v>99999</v>
@@ -3025,22 +3025,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>espinafre-unidade-200948</t>
+          <t>alface-crespa-unidade-200875</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Espinafre Unidade</t>
+          <t>Alface Crespa Unidade</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>200948</t>
+          <t>200875</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
+          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>8.1</v>
+        <v>8.99</v>
       </c>
       <c r="F40" t="n">
         <v>10.99</v>
@@ -3309,29 +3309,29 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>alface-crespa-unidade-200875</t>
+          <t>cebola-roxa-400g-38393</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Alface Crespa Unidade</t>
+          <t>Cebola Roxa 400g</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>200875</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
+          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2.99</v>
+        <v>7.99</v>
       </c>
       <c r="F41" t="n">
-        <v>3.79</v>
+        <v>7.99</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3340,30 +3340,30 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3375,49 +3375,49 @@
         <v>2000015</v>
       </c>
       <c r="P41" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
+          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
+          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1105795</t>
+          <t>818640</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
+          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>3.99</v>
       </c>
       <c r="F42" t="n">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2023-07-26T00:00:00Z</t>
+          <t>2020-11-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3430,21 +3430,21 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2000017</v>
+        <v>2002038</v>
       </c>
       <c r="P42" t="n">
         <v>99999</v>
@@ -3453,43 +3453,39 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
+          <t>file-de-peito-de-frango-congelado-rivelli-bandeja-1kg-1023799</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
+          <t>Filé de Peito de Frango Congelado Rivelli Bandeja 1kg</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>818640</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
-        </is>
-      </c>
+          <t>1023799</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>4.99</v>
+        <v>19.99</v>
       </c>
       <c r="F43" t="n">
-        <v>4.99</v>
+        <v>25.99</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2020-11-26T00:00:00Z</t>
+          <t>2021-07-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038302/VF4qT-qqCUAAAAAAAAKY8g.jpg?v=637792395730970000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3502,21 +3498,21 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>Rivelli</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>2002038</v>
+        <v>2004122</v>
       </c>
       <c r="P43" t="n">
         <v>99999</v>
@@ -3525,43 +3521,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pao-de-forma-plus-vita-tradicional-500-g-252921</t>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pão de Forma Tradicional Plusvita 480g</t>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>252921</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Versátil, prático e para qualquer momento, trazendo a energia necessária para o seu dia. Perfeito para sanduíches, torradas, receitas para o café da manhã, café da tarde, almoço e jantar</t>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>9.98</v>
+        <v>29.98</v>
       </c>
       <c r="F44" t="n">
-        <v>9.98</v>
+        <v>37.9</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-07-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3663691/VF4qT-qqCUAAAAAAAAb-gA.jpg?v=638592874910030000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3574,21 +3570,21 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>9715</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>PLUS VITA</t>
+          <t>MELITTA</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>2000316</v>
+        <v>2001329</v>
       </c>
       <c r="P44" t="n">
         <v>100</v>
@@ -3597,43 +3593,43 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>1105795</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>29.98</v>
+        <v>3.99</v>
       </c>
       <c r="F45" t="n">
-        <v>37.9</v>
+        <v>5.99</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2023-07-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3646,21 +3642,21 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2001329</v>
+        <v>2000017</v>
       </c>
       <c r="P45" t="n">
         <v>99999</v>
@@ -3669,70 +3665,70 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>99279</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>59.99</v>
+        <v>5.99</v>
       </c>
       <c r="F46" t="n">
-        <v>59.99</v>
+        <v>6.99</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2020-05-27T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>24684</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>2001012</v>
+        <v>2001532</v>
       </c>
       <c r="P46" t="n">
         <v>99999</v>
@@ -3741,43 +3737,43 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>matte-leao-natural-pet-15l-118214</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Matte Leão Natural Pet 1,5L</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>118214</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6.99</v>
+        <v>7.95</v>
       </c>
       <c r="F47" t="n">
-        <v>6.99</v>
+        <v>8.99</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3790,21 +3786,21 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>2001532</v>
+        <v>2000010</v>
       </c>
       <c r="P47" t="n">
         <v>99999</v>
@@ -3813,43 +3809,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>matte-leao-natural-pet-15l-118214</t>
+          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Matte Leão Natural Pet 1,5L</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>118214</t>
+          <t>105287</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
+          <t>Farinha De Trigo Dona Benta 1kg</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>7.49</v>
+        <v>6.99</v>
       </c>
       <c r="F48" t="n">
-        <v>8.99</v>
+        <v>6.99</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-07-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3862,21 +3858,21 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>31</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>DONA BENTA</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>2000010</v>
+        <v>2000701</v>
       </c>
       <c r="P48" t="n">
         <v>99999</v>
@@ -3885,66 +3881,70 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-congelado-rivelli-bandeja-1kg-1023799</t>
+          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Congelado Rivelli Bandeja 1kg</t>
+          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1023799</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>99279</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
+        </is>
+      </c>
       <c r="E49" t="n">
-        <v>19.99</v>
+        <v>59.99</v>
       </c>
       <c r="F49" t="n">
-        <v>25.99</v>
+        <v>59.99</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2021-07-30T00:00:00Z</t>
+          <t>2020-05-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038302/VF4qT-qqCUAAAAAAAAKY8g.jpg?v=637792395730970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>21449</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Rivelli</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2004122</v>
+        <v>2001012</v>
       </c>
       <c r="P49" t="n">
         <v>99999</v>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -513,43 +513,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mamao-papaia-unidade-5130786</t>
+          <t>leite-condensado-moca-lata-395g-1136321</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mamão Papaia Unidade</t>
+          <t>Leite Condensado Moça Lata 395g</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5130786</t>
+          <t>1136321</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>O Mamão Papaia é uma fruta tropical leve, nutritiva e muito apreciada pelo seu sabor suave, polpa macia e alto rendimento. Perfeito para o consumo diário, traz frescor e saúde para a alimentação.Benefícios Nutricionais-Auxilia a digestão, graças à presença natural da enzima papaína-Rico em fibras, contribuindo para o bom funcionamento intestinal-Fonte de vitamina C, que fortalece o sistema imunológico-Contém vitamina A, importante para a saúde da pele e da visão-Possui ação antioxidante</t>
+          <t>Moça® faz todas as receitas darem certo desde 1921, com seu sabor único e original, tem consistência perfeita, é sem comparação! É leite condensado obtido a partir de leite fresco, puro e integral. É um clássico no preparo de sobremesas, também é uma delícia na colher, na salada de frutas e o que mais você imaginar.</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5.19</v>
+        <v>7.95</v>
       </c>
       <c r="F2" t="n">
-        <v>5.19</v>
+        <v>9.99</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>67</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2017-02-17T00:00:00Z</t>
+          <t>2024-05-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500752/VF4qT-qqCUAAAAAAAAQ0fA.jpg?v=639071532100230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3561021/VF4qT-qqCUAAAAAAAAbPyA.jpg?v=638987191686300000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -562,21 +562,21 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>32822</t>
+          <t>37022</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>32747</t>
+          <t>36949</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>2000015</v>
+        <v>2000043</v>
       </c>
       <c r="P2" t="n">
         <v>99999</v>
@@ -585,43 +585,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ovos-brancos-jumbo-mantiqueira-com-10-unidades-437638</t>
+          <t>matte-leao-limao-pet-1-5l-118222</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ovos Brancos Jumbo Mantiqueira Com 10 Unidades</t>
+          <t>Matte Leão Limão Pet 1,5L</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>437638</t>
+          <t>118222</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Os Ovos Jumbo Mantiqueira possuem maior tamanho, ideais para quem busca uma alimentação rica em vitaminas, proteínas e minerais, ou para quem gosta de um maior rendimento em suas receitas. Um único ovo contém quase todos os nutrientes necessários para manter o corpo saudável, fortalecendo os ossos e auxiliando em dietas para perda de peso ou ganho de massa.O Ovo Jumbo Mantiqueira é um produto da linha Especial da marca e possui a qualidade superior, passando por um moderno sistema de seleção, limpeza e embalagem sem contato de mãos humanas.Especificações:Ovos maiores, tamanho família.Embalagem com 10 unidades.Ovos brancos e vermelhos tipo jumbo categoria A.</t>
+          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10.9</v>
+        <v>7.95</v>
       </c>
       <c r="F3" t="n">
-        <v>10.9</v>
+        <v>8.99</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3976126/VF4qT-qqCUAAAAAAAAh4RA.jpg?v=638769994856100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -634,66 +634,66 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MANTIQUEIRA</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2001056</v>
+        <v>2000010</v>
       </c>
       <c r="P3" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>matte-leao-limao-pet-1-5l-118222</t>
+          <t>alcool-montenegro-46-1-l-780570</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Matte Leão Limão Pet 1,5L</t>
+          <t>Álcool Montenegro 46% 1 L</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118222</t>
+          <t>780570</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
+          <t>Álcool Montenegro 46% 1 L</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7.95</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>8.99</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-10-06T10:47:00Z</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051579/VF4qT-qqCUAAAAAAAAG3pQ.jpg?v=637793390624870000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -706,21 +706,21 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>11598</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>MONTENEGRO</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>2000010</v>
+        <v>2000527</v>
       </c>
       <c r="P4" t="n">
         <v>99999</v>
@@ -729,43 +729,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>alcool-montenegro-46-1-l-780570</t>
+          <t>tomate-italiano-unidade-495212</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Álcool Montenegro 46% 1 L</t>
+          <t>Tomate Italiano Unidade</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>780570</t>
+          <t>495212</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Álcool Montenegro 46% 1 L</t>
+          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8.789999999999999</v>
+        <v>1.96</v>
       </c>
       <c r="F5" t="n">
-        <v>8.789999999999999</v>
+        <v>1.96</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2020-10-06T10:47:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051579/VF4qT-qqCUAAAAAAAAG3pQ.jpg?v=637793390624870000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -778,21 +778,21 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>11598</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>MONTENEGRO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2000527</v>
+        <v>2000015</v>
       </c>
       <c r="P5" t="n">
         <v>99999</v>
@@ -801,43 +801,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tomate-italiano-unidade-495212</t>
+          <t>manga-palmer-unidade-5130760</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tomate Italiano Unidade</t>
+          <t>Manga Palmer Unidade</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>495212</t>
+          <t>5130760</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
+          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.52</v>
+        <v>5.99</v>
       </c>
       <c r="F6" t="n">
-        <v>1.96</v>
+        <v>5.99</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2023-02-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>31902</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -945,43 +945,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>manga-palmer-unidade-5130760</t>
+          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Manga Palmer Unidade</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5130760</t>
+          <t>140805</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5.39</v>
+        <v>4.19</v>
       </c>
       <c r="F8" t="n">
-        <v>5.99</v>
+        <v>5.29</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2023-02-16T00:00:00Z</t>
+          <t>2020-09-25T00:00:00Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -994,21 +994,21 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SAO LOURENCO</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2000015</v>
+        <v>2000145</v>
       </c>
       <c r="P8" t="n">
         <v>99999</v>
@@ -1017,70 +1017,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
+          <t>mucarela-em-fatias-92363</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Muçarela  em Fatias 200g</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>140805</t>
+          <t>92363</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Muçarela em Fatias</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.19</v>
+        <v>59.9</v>
       </c>
       <c r="F9" t="n">
-        <v>5.29</v>
+        <v>59.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2020-09-25T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>SAO LOURENCO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2000145</v>
+        <v>2000015</v>
       </c>
       <c r="P9" t="n">
         <v>99999</v>
@@ -1089,43 +1089,43 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mucarela-em-fatias-92363</t>
+          <t>batata-inglesa-cariorta-12kg-98698</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Muçarela  em Fatias 200g</t>
+          <t>Batata Inglesa Cariorta 1,2Kg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>92363</t>
+          <t>98698</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Muçarela em Fatias</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>59.9</v>
+        <v>7.99</v>
       </c>
       <c r="F10" t="n">
-        <v>59.9</v>
+        <v>7.99</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1134,25 +1134,25 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P10" t="n">
         <v>99999</v>
@@ -1161,70 +1161,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>batata-inglesa-cariorta-12kg-98698</t>
+          <t>couve-flor-unidade-189111</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Batata Inglesa Cariorta 1,2Kg</t>
+          <t>Couve Flor Unidade</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>189111</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.99</v>
+        <v>9.99</v>
       </c>
       <c r="F11" t="n">
-        <v>7.99</v>
+        <v>9.99</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P11" t="n">
         <v>99999</v>
@@ -1233,70 +1233,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>couve-flor-unidade-189111</t>
+          <t>mamao-papaia-cariorta-12kg-99007</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Couve Flor Unidade</t>
+          <t>Mamão Papaia Cariorta 1,2kg</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>189111</t>
+          <t>99007</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>9.59</v>
+        <v>9.99</v>
       </c>
       <c r="F12" t="n">
         <v>9.99</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P12" t="n">
         <v>99999</v>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.99</v>
+        <v>3.39</v>
       </c>
       <c r="F13" t="n">
         <v>3.39</v>
@@ -1377,43 +1377,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mamao-papaia-cariorta-12kg-99007</t>
+          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mamão Papaia Cariorta 1,2kg</t>
+          <t>Pão Francês Panetto  60g Com 4 unidades</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>99007</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Cariorta selecionados de coração.</t>
-        </is>
-      </c>
+          <t>96318</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
       <c r="F14" t="n">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2024-01-31T00:00:00Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1422,25 +1418,25 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1.2</v>
+        <v>0.24</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>PANETTO</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2001012</v>
+        <v>2000307</v>
       </c>
       <c r="P14" t="n">
         <v>99999</v>
@@ -1449,66 +1445,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
+          <t>uva-preta-sem-semente-500-g-674583</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pão Francês Panetto  60g Com 4 unidades</t>
+          <t>Uva Preta Sem Semente 500g</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>96318</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>674583</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
+        </is>
+      </c>
       <c r="E15" t="n">
-        <v>24.99</v>
+        <v>13.99</v>
       </c>
       <c r="F15" t="n">
-        <v>24.99</v>
+        <v>13.99</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2024-01-31T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>PANETTO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2000307</v>
+        <v>2000015</v>
       </c>
       <c r="P15" t="n">
         <v>99999</v>
@@ -1517,43 +1517,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>uva-preta-sem-semente-500-g-674583</t>
+          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Uva Preta Sem Semente 500g</t>
+          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>674583</t>
+          <t>100510</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
+          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12.49</v>
+        <v>1.99</v>
       </c>
       <c r="F16" t="n">
-        <v>13.99</v>
+        <v>2.69</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1566,21 +1566,21 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>LIMPOL</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2000015</v>
+        <v>2001413</v>
       </c>
       <c r="P16" t="n">
         <v>99999</v>
@@ -1661,43 +1661,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
+          <t>morango-250g-289612</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
+          <t>Morango 250g</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>100510</t>
+          <t>289612</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
+          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.99</v>
+        <v>9.99</v>
       </c>
       <c r="F18" t="n">
-        <v>2.69</v>
+        <v>9.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1710,21 +1710,21 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>LIMPOL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2001413</v>
+        <v>2000015</v>
       </c>
       <c r="P18" t="n">
         <v>99999</v>
@@ -1733,43 +1733,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>morango-250g-289612</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Morango 250g</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>289612</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>8.99</v>
+        <v>5.99</v>
       </c>
       <c r="F19" t="n">
-        <v>9.99</v>
+        <v>5.99</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1782,21 +1778,21 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2000015</v>
+        <v>2001952</v>
       </c>
       <c r="P19" t="n">
         <v>99999</v>
@@ -1805,44 +1801,48 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>limao-cariorta-1kg-98981</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Limão Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>98981</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Cariorta selecionados de coração.</t>
+        </is>
+      </c>
       <c r="E20" t="n">
-        <v>5.99</v>
+        <v>11.99</v>
       </c>
       <c r="F20" t="n">
-        <v>5.99</v>
+        <v>11.99</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1850,21 +1850,21 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2001952</v>
+        <v>2001012</v>
       </c>
       <c r="P20" t="n">
         <v>99999</v>
@@ -1873,48 +1873,48 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>limao-cariorta-1kg-98981</t>
+          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Limão Cariorta 1Kg</t>
+          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>98981</t>
+          <t>290564</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>11.99</v>
+        <v>23.99</v>
       </c>
       <c r="F21" t="n">
-        <v>11.99</v>
+        <v>26.99</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1922,21 +1922,21 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>SADIA</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>2001012</v>
+        <v>2000057</v>
       </c>
       <c r="P21" t="n">
         <v>99999</v>
@@ -1945,43 +1945,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>290564</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>23.99</v>
+        <v>10.99</v>
       </c>
       <c r="F22" t="n">
-        <v>26.99</v>
+        <v>10.99</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1994,21 +1994,21 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>SADIA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2000057</v>
+        <v>2000015</v>
       </c>
       <c r="P22" t="n">
         <v>99999</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.99</v>
+        <v>3.79</v>
       </c>
       <c r="F23" t="n">
         <v>3.79</v>
@@ -2089,43 +2089,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>364738</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
+          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9.85</v>
+        <v>3.97</v>
       </c>
       <c r="F24" t="n">
-        <v>10.99</v>
+        <v>4.89</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2138,21 +2138,21 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>2000015</v>
+        <v>2000043</v>
       </c>
       <c r="P24" t="n">
         <v>99999</v>
@@ -2161,43 +2161,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
+          <t>abobrinha-italiana-unidade-423513</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>364738</t>
+          <t>423513</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3.97</v>
+        <v>3.5</v>
       </c>
       <c r="F25" t="n">
-        <v>4.89</v>
+        <v>3.5</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-12-07T00:00:00Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2210,21 +2210,21 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>2000043</v>
+        <v>2000015</v>
       </c>
       <c r="P25" t="n">
         <v>99999</v>
@@ -2305,43 +2305,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-unidade-423513</t>
+          <t>couve-manteiga-unidade-201235</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Couve Manteiga Unidade</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>201235</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3.5</v>
+        <v>3.79</v>
       </c>
       <c r="F27" t="n">
-        <v>3.5</v>
+        <v>3.79</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2020-12-07T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2377,43 +2377,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>couve-manteiga-unidade-201235</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Couve Manteiga Unidade</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>201235</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.99</v>
+        <v>6.29</v>
       </c>
       <c r="F28" t="n">
-        <v>3.79</v>
+        <v>6.29</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2426,21 +2426,21 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>2000015</v>
+        <v>2000400</v>
       </c>
       <c r="P28" t="n">
         <v>99999</v>
@@ -2449,43 +2449,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>milho-em-conserva-quero-lata-200g-476625</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Milho em Conserva Quero Lata 200g</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>476625</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6.29</v>
+        <v>3.69</v>
       </c>
       <c r="F29" t="n">
-        <v>6.29</v>
+        <v>4.99</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2498,21 +2498,21 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>QUERO</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2000400</v>
+        <v>2001778</v>
       </c>
       <c r="P29" t="n">
         <v>99999</v>
@@ -2521,43 +2521,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>milho-em-conserva-quero-lata-200g-476625</t>
+          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Milho em Conserva Quero Lata 200g</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>476625</t>
+          <t>429392</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3.69</v>
+        <v>4.99</v>
       </c>
       <c r="F30" t="n">
-        <v>4.99</v>
+        <v>5.69</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2570,21 +2570,21 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>QUERO</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2001778</v>
+        <v>2000027</v>
       </c>
       <c r="P30" t="n">
         <v>99999</v>
@@ -2665,43 +2665,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
+          <t>espinafre-unidade-200948</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
+          <t>Espinafre Unidade</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>429392</t>
+          <t>200948</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4.99</v>
+        <v>3.79</v>
       </c>
       <c r="F32" t="n">
-        <v>5.69</v>
+        <v>3.79</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2714,21 +2714,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2000027</v>
+        <v>2000015</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2809,43 +2809,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>leite-uht-piracanjuba-integral-1l-865427</t>
+          <t>desinfetante-banheiro-tira-limo-veja-x-14-sache-400ml-refil-economico-1066404</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Leite Uht Piracanjuba Integral 1L</t>
+          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>865427</t>
+          <t>1066404</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
+          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6.69</v>
+        <v>9.99</v>
       </c>
       <c r="F34" t="n">
-        <v>6.69</v>
+        <v>11.99</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2017-04-12T00:00:00Z</t>
+          <t>2022-08-11T00:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3927710/VF4qT-qqCUAAAAAAAAOGFQ.jpg?v=638733705155570000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2858,21 +2858,21 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>VEJA</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>2002038</v>
+        <v>2000523</v>
       </c>
       <c r="P34" t="n">
         <v>99999</v>
@@ -2881,26 +2881,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>espinafre-unidade-200948</t>
+          <t>alface-crespa-unidade-200875</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Espinafre Unidade</t>
+          <t>Alface Crespa Unidade</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>200948</t>
+          <t>200875</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
+          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2.99</v>
+        <v>3.79</v>
       </c>
       <c r="F35" t="n">
         <v>3.79</v>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2953,48 +2953,44 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>desinfetante-banheiro-tira-limo-veja-x-14-sache-400ml-refil-economico-1066404</t>
+          <t>abobrinha-italiana-cariorta-1kg-98663</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
+          <t>Abobrinha Italiana Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1066404</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
-        </is>
-      </c>
+          <t>98663</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
       <c r="F36" t="n">
-        <v>11.99</v>
+        <v>10.99</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2022-08-11T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3927710/VF4qT-qqCUAAAAAAAAOGFQ.jpg?v=638733705155570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -3002,66 +2998,66 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>27159</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>27083</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>VEJA</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2000523</v>
+        <v>2001012</v>
       </c>
       <c r="P36" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>alface-crespa-unidade-200875</t>
+          <t>leite-uht-piracanjuba-integral-1l-865427</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Alface Crespa Unidade</t>
+          <t>Leite Uht Piracanjuba Integral 1L</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>200875</t>
+          <t>865427</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
+          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2.99</v>
+        <v>6.69</v>
       </c>
       <c r="F37" t="n">
-        <v>3.79</v>
+        <v>6.69</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2017-04-12T00:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3074,21 +3070,21 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>23232</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>23158</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2000015</v>
+        <v>2002038</v>
       </c>
       <c r="P37" t="n">
         <v>99999</v>
@@ -3097,39 +3093,43 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-cariorta-1kg-98663</t>
+          <t>melao-amarelo-metade-1-3-kg-63606</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Cariorta 1Kg</t>
+          <t>Melão Amarelo Metade 1,3kg</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>98663</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>63606</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
+        </is>
+      </c>
       <c r="E38" t="n">
-        <v>10.99</v>
+        <v>9.99</v>
       </c>
       <c r="F38" t="n">
-        <v>10.99</v>
+        <v>9.99</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3138,25 +3138,25 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P38" t="n">
         <v>99999</v>
@@ -3165,70 +3165,70 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>melao-amarelo-metade-1-3-kg-63606</t>
+          <t>batata-palha-yoki-extra-fina-100g-989843</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Melão Amarelo Metade 1,3kg</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>989843</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>8.99</v>
       </c>
       <c r="F39" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>13749</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>YOKI</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>2000015</v>
+        <v>2001336</v>
       </c>
       <c r="P39" t="n">
         <v>99999</v>
@@ -3237,43 +3237,43 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>batata-palha-yoki-extra-fina-100g-989843</t>
+          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Batata Palha Yoki Extra Fina 100g</t>
+          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>989843</t>
+          <t>818640</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Batata Palha Yoki Extra Fina 100g</t>
+          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>8.99</v>
+        <v>3.99</v>
       </c>
       <c r="F40" t="n">
-        <v>10.99</v>
+        <v>4.99</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2020-10-30T00:00:00Z</t>
+          <t>2020-11-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3286,21 +3286,21 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>YOKI</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>2001336</v>
+        <v>2002038</v>
       </c>
       <c r="P40" t="n">
         <v>99999</v>
@@ -3309,115 +3309,111 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cebola-roxa-400g-38393</t>
+          <t>file-de-peito-de-frango-congelado-rivelli-bandeja-1kg-1023799</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cebola Roxa 400g</t>
+          <t>Filé de Peito de Frango Congelado Rivelli Bandeja 1kg</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>38393</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
-        </is>
-      </c>
+          <t>1023799</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>7.99</v>
+        <v>19.99</v>
       </c>
       <c r="F41" t="n">
-        <v>7.99</v>
+        <v>25.99</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2021-07-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038302/VF4qT-qqCUAAAAAAAAKY8g.jpg?v=637792395730970000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>Rivelli</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2000015</v>
+        <v>2004122</v>
       </c>
       <c r="P41" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
+          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
+          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>818640</t>
+          <t>1105795</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
+          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>3.99</v>
       </c>
       <c r="F42" t="n">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2020-11-26T00:00:00Z</t>
+          <t>2023-07-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3430,21 +3426,21 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2002038</v>
+        <v>2000017</v>
       </c>
       <c r="P42" t="n">
         <v>99999</v>
@@ -3453,39 +3449,43 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-congelado-rivelli-bandeja-1kg-1023799</t>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Congelado Rivelli Bandeja 1kg</t>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1023799</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>103845</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+        </is>
+      </c>
       <c r="E43" t="n">
-        <v>19.99</v>
+        <v>29.98</v>
       </c>
       <c r="F43" t="n">
-        <v>25.99</v>
+        <v>37.9</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2021-07-30T00:00:00Z</t>
+          <t>2020-07-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038302/VF4qT-qqCUAAAAAAAAKY8g.jpg?v=637792395730970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3498,21 +3498,21 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>21449</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Rivelli</t>
+          <t>MELITTA</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>2004122</v>
+        <v>2001329</v>
       </c>
       <c r="P43" t="n">
         <v>99999</v>
@@ -3521,43 +3521,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>29.98</v>
+        <v>5.99</v>
       </c>
       <c r="F44" t="n">
-        <v>37.9</v>
+        <v>6.99</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3570,66 +3570,66 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>2001329</v>
+        <v>2001532</v>
       </c>
       <c r="P44" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
+          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
+          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1105795</t>
+          <t>981168</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
+          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3.99</v>
+        <v>30.99</v>
       </c>
       <c r="F45" t="n">
-        <v>5.99</v>
+        <v>32.19</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2023-07-26T00:00:00Z</t>
+          <t>2020-09-22T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3642,21 +3642,21 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>NEVE</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2000017</v>
+        <v>2000291</v>
       </c>
       <c r="P45" t="n">
         <v>99999</v>
@@ -3665,43 +3665,43 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>5106753</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5.99</v>
+        <v>11.99</v>
       </c>
       <c r="F46" t="n">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2021-01-11T00:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3714,93 +3714,93 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>2001532</v>
+        <v>2003319</v>
       </c>
       <c r="P46" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>matte-leao-natural-pet-15l-118214</t>
+          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Matte Leão Natural Pet 1,5L</t>
+          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>118214</t>
+          <t>99279</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
+          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>7.95</v>
+        <v>59.99</v>
       </c>
       <c r="F47" t="n">
-        <v>8.99</v>
+        <v>59.99</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-05-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>2000010</v>
+        <v>2001012</v>
       </c>
       <c r="P47" t="n">
         <v>99999</v>
@@ -3809,43 +3809,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>farinha-de-trigo-dona-benta-1kg-105287</t>
+          <t>matte-leao-natural-pet-15l-118214</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Matte Leão Natural Pet 1,5L</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>105287</t>
+          <t>118214</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Farinha De Trigo Dona Benta 1kg</t>
+          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6.99</v>
+        <v>7.95</v>
       </c>
       <c r="F48" t="n">
-        <v>6.99</v>
+        <v>8.99</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2020-07-06T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3079291/VF4qT-qqCUAAAAAAAANuog.jpg?v=637897755804270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3858,21 +3858,21 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>DONA BENTA</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>2000701</v>
+        <v>2000010</v>
       </c>
       <c r="P48" t="n">
         <v>99999</v>
@@ -3881,70 +3881,70 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
+          <t>tomate-pelado-italiano-due-lata-400g-5459389</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
+          <t>Tomate Pelado Italiano Due Lata 400g</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>99279</t>
+          <t>5459389</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
+          <t>Due é sua dupla perfeita para criar o verdadeiro sabor italiano!Due o melhor da culinária italiana com ingredientes genuínos, que você só encontra no Zona SulExperimente e surpreenda-se!</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>59.99</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>59.99</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2020-05-27T00:00:00Z</t>
+          <t>2025-01-21T00:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3928345/VF4qT-qqCUAAAAAAAAhGgQ.jpg?v=638736295014200000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>24684</t>
+          <t>39142</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>39069</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>DUE</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2001012</v>
+        <v>2005138</v>
       </c>
       <c r="P49" t="n">
         <v>99999</v>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3561021/VF4qT-qqCUAAAAAAAAbPyA.jpg?v=638987191686300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4530596/VF4qT-qqCUAAAAAAAAbPyA.jpg?v=639095725127130000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -748,10 +748,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="F5" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -801,43 +801,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>manga-palmer-unidade-5130760</t>
+          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Manga Palmer Unidade</t>
+          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5130760</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
+          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5.99</v>
+        <v>24.99</v>
       </c>
       <c r="F6" t="n">
-        <v>5.99</v>
+        <v>24.99</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-02-16T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -850,66 +850,66 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2000015</v>
+        <v>2003319</v>
       </c>
       <c r="P6" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
+          <t>manga-palmer-unidade-5130760</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
+          <t>Manga Palmer Unidade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>828025</t>
+          <t>5130760</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
+          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>32.98</v>
+        <v>5.39</v>
       </c>
       <c r="F7" t="n">
-        <v>43.9</v>
+        <v>5.99</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2023-02-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -922,21 +922,21 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>31902</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>PILAO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2000070</v>
+        <v>2000015</v>
       </c>
       <c r="P7" t="n">
         <v>99999</v>
@@ -945,43 +945,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
+          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>140805</t>
+          <t>828025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.19</v>
+        <v>32.98</v>
       </c>
       <c r="F8" t="n">
-        <v>5.29</v>
+        <v>43.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2020-09-25T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -994,21 +994,21 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>SAO LOURENCO</t>
+          <t>PILAO</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2000145</v>
+        <v>2000070</v>
       </c>
       <c r="P8" t="n">
         <v>99999</v>
@@ -1017,70 +1017,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mucarela-em-fatias-92363</t>
+          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Muçarela  em Fatias 200g</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>92363</t>
+          <t>140805</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Muçarela em Fatias</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>59.9</v>
+        <v>4.19</v>
       </c>
       <c r="F9" t="n">
-        <v>59.9</v>
+        <v>5.29</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-25T00:00:00Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SAO LOURENCO</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2000015</v>
+        <v>2000145</v>
       </c>
       <c r="P9" t="n">
         <v>99999</v>
@@ -1089,43 +1089,43 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>batata-inglesa-cariorta-12kg-98698</t>
+          <t>mucarela-em-fatias-92363</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Batata Inglesa Cariorta 1,2Kg</t>
+          <t>Muçarela  em Fatias 200g</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>92363</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>Muçarela em Fatias</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.99</v>
+        <v>59.9</v>
       </c>
       <c r="F10" t="n">
-        <v>7.99</v>
+        <v>59.9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1134,25 +1134,25 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P10" t="n">
         <v>99999</v>
@@ -1161,22 +1161,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>couve-flor-unidade-189111</t>
+          <t>mamao-papaia-cariorta-12kg-99007</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Couve Flor Unidade</t>
+          <t>Mamão Papaia Cariorta 1,2kg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>189111</t>
+          <t>99007</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1187,44 +1187,44 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P11" t="n">
         <v>99999</v>
@@ -1233,70 +1233,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mamao-papaia-cariorta-12kg-99007</t>
+          <t>couve-flor-unidade-189111</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mamão Papaia Cariorta 1,2kg</t>
+          <t>Couve Flor Unidade</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>99007</t>
+          <t>189111</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>9.99</v>
+        <v>9.59</v>
       </c>
       <c r="F12" t="n">
         <v>9.99</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P12" t="n">
         <v>99999</v>
@@ -1305,70 +1305,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cheiro-verde-unidade-201049</t>
+          <t>batata-inglesa-cariorta-12kg-98698</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cheiro Verde Unidade</t>
+          <t>Batata Inglesa Cariorta 1,2Kg</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>201049</t>
+          <t>98698</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3.39</v>
+        <v>7.99</v>
       </c>
       <c r="F13" t="n">
-        <v>3.39</v>
+        <v>7.99</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P13" t="n">
         <v>99999</v>
@@ -1377,66 +1377,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
+          <t>cheiro-verde-unidade-201049</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pão Francês Panetto  60g Com 4 unidades</t>
+          <t>Cheiro Verde Unidade</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>96318</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>201049</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+        </is>
+      </c>
       <c r="E14" t="n">
-        <v>24.99</v>
+        <v>2.99</v>
       </c>
       <c r="F14" t="n">
-        <v>24.99</v>
+        <v>3.39</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2024-01-31T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>PANETTO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2000307</v>
+        <v>2000015</v>
       </c>
       <c r="P14" t="n">
         <v>99999</v>
@@ -1445,43 +1449,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>uva-preta-sem-semente-500-g-674583</t>
+          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Uva Preta Sem Semente 500g</t>
+          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>674583</t>
+          <t>100510</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
+          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>13.99</v>
+        <v>2.69</v>
       </c>
       <c r="F15" t="n">
-        <v>13.99</v>
+        <v>2.69</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1494,21 +1498,21 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>LIMPOL</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2000015</v>
+        <v>2001413</v>
       </c>
       <c r="P15" t="n">
         <v>99999</v>
@@ -1517,70 +1521,66 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
+          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
+          <t>Pão Francês Panetto  60g Com 4 unidades</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>100510</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
-        </is>
-      </c>
+          <t>96318</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>1.99</v>
+        <v>24.99</v>
       </c>
       <c r="F16" t="n">
-        <v>2.69</v>
+        <v>24.99</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2024-01-31T00:00:00Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>LIMPOL</t>
+          <t>PANETTO</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2001413</v>
+        <v>2000307</v>
       </c>
       <c r="P16" t="n">
         <v>99999</v>
@@ -1589,43 +1589,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
+          <t>morango-250g-289612</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Odd Clear 500ml</t>
+          <t>Morango 250g</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>982911</t>
+          <t>289612</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ODD voltou!Alto rendimento , controle de odor.</t>
+          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.49</v>
+        <v>9.99</v>
       </c>
       <c r="F17" t="n">
-        <v>2.49</v>
+        <v>9.99</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1638,21 +1638,21 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>LIMPPANO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2001341</v>
+        <v>2000015</v>
       </c>
       <c r="P17" t="n">
         <v>99999</v>
@@ -1661,29 +1661,29 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>morango-250g-289612</t>
+          <t>uva-preta-sem-semente-500-g-674583</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Morango 250g</t>
+          <t>Uva Preta Sem Semente 500g</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>289612</t>
+          <t>674583</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
+          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9.99</v>
+        <v>12.49</v>
       </c>
       <c r="F18" t="n">
-        <v>9.99</v>
+        <v>13.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1733,29 +1733,33 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Detergente Para Louças Odd Clear 500ml</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>982911</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ODD voltou!Alto rendimento , controle de odor.</t>
+        </is>
+      </c>
       <c r="E19" t="n">
-        <v>5.99</v>
+        <v>2.49</v>
       </c>
       <c r="F19" t="n">
-        <v>5.99</v>
+        <v>2.49</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1765,7 +1769,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1778,21 +1782,21 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>LIMPPANO</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2001952</v>
+        <v>2001341</v>
       </c>
       <c r="P19" t="n">
         <v>99999</v>
@@ -1945,43 +1949,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>10.99</v>
+        <v>5.99</v>
       </c>
       <c r="F22" t="n">
-        <v>10.99</v>
+        <v>5.99</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1994,21 +1994,21 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2000015</v>
+        <v>2001952</v>
       </c>
       <c r="P22" t="n">
         <v>99999</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.79</v>
+        <v>2.99</v>
       </c>
       <c r="F23" t="n">
         <v>3.79</v>
@@ -2089,43 +2089,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>364738</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.97</v>
+        <v>9.99</v>
       </c>
       <c r="F24" t="n">
-        <v>4.89</v>
+        <v>10.99</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2138,21 +2138,21 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>2000043</v>
+        <v>2000015</v>
       </c>
       <c r="P24" t="n">
         <v>99999</v>
@@ -2161,43 +2161,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-unidade-423513</t>
+          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>364738</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3.5</v>
+        <v>3.97</v>
       </c>
       <c r="F25" t="n">
-        <v>3.5</v>
+        <v>4.89</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2020-12-07T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2210,21 +2210,21 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>2000015</v>
+        <v>2000043</v>
       </c>
       <c r="P25" t="n">
         <v>99999</v>
@@ -2233,43 +2233,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
+          <t>abobrinha-italiana-unidade-423513</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1180320</t>
+          <t>423513</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.79</v>
+        <v>2.45</v>
       </c>
       <c r="F26" t="n">
-        <v>2.79</v>
+        <v>2.45</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2025-07-17T00:00:00Z</t>
+          <t>2020-12-07T00:00:00Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2282,21 +2282,21 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>41057</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>BOMBRIL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>2001389</v>
+        <v>2000015</v>
       </c>
       <c r="P26" t="n">
         <v>99999</v>
@@ -2305,43 +2305,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>couve-manteiga-unidade-201235</t>
+          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Couve Manteiga Unidade</t>
+          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>201235</t>
+          <t>1180320</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
+          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3.79</v>
+        <v>2.79</v>
       </c>
       <c r="F27" t="n">
-        <v>3.79</v>
+        <v>2.79</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2025-07-17T00:00:00Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2354,21 +2354,21 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>BOMBRIL</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>2000015</v>
+        <v>2001389</v>
       </c>
       <c r="P27" t="n">
         <v>99999</v>
@@ -2449,43 +2449,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>milho-em-conserva-quero-lata-200g-476625</t>
+          <t>couve-manteiga-unidade-201235</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Milho em Conserva Quero Lata 200g</t>
+          <t>Couve Manteiga Unidade</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>476625</t>
+          <t>201235</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
+          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3.69</v>
+        <v>2.99</v>
       </c>
       <c r="F29" t="n">
-        <v>4.99</v>
+        <v>3.79</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2498,21 +2498,21 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>QUERO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2001778</v>
+        <v>2000015</v>
       </c>
       <c r="P29" t="n">
         <v>99999</v>
@@ -2521,43 +2521,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
+          <t>milho-em-conserva-quero-lata-200g-476625</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
+          <t>Milho em Conserva Quero Lata 200g</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>429392</t>
+          <t>476625</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
         </is>
       </c>
       <c r="E30" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F30" t="n">
         <v>4.99</v>
       </c>
-      <c r="F30" t="n">
-        <v>5.69</v>
-      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2570,21 +2570,21 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>QUERO</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2000027</v>
+        <v>2001778</v>
       </c>
       <c r="P30" t="n">
         <v>99999</v>
@@ -2593,43 +2593,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
+          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>129887</t>
+          <t>429392</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>12.99</v>
+        <v>4.99</v>
       </c>
       <c r="F31" t="n">
-        <v>12.99</v>
+        <v>5.69</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2642,21 +2642,21 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>2001401</v>
+        <v>2000027</v>
       </c>
       <c r="P31" t="n">
         <v>99999</v>
@@ -2665,43 +2665,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>espinafre-unidade-200948</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Espinafre Unidade</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>200948</t>
+          <t>129887</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
+          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3.79</v>
+        <v>12.99</v>
       </c>
       <c r="F32" t="n">
-        <v>3.79</v>
+        <v>12.99</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2714,21 +2714,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2000015</v>
+        <v>2001401</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2737,43 +2737,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>sal-refinado-iodado-ita-1kg-117293</t>
+          <t>espinafre-unidade-200948</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Espinafre Unidade</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>200948</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4.39</v>
+        <v>2.99</v>
       </c>
       <c r="F33" t="n">
-        <v>4.39</v>
+        <v>3.79</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2786,21 +2786,21 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2000066</v>
+        <v>2000015</v>
       </c>
       <c r="P33" t="n">
         <v>99999</v>
@@ -2809,43 +2809,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>desinfetante-banheiro-tira-limo-veja-x-14-sache-400ml-refil-economico-1066404</t>
+          <t>alface-crespa-unidade-200875</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
+          <t>Alface Crespa Unidade</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1066404</t>
+          <t>200875</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
+          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>9.99</v>
+        <v>3.79</v>
       </c>
       <c r="F34" t="n">
-        <v>11.99</v>
+        <v>3.79</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2022-08-11T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3927710/VF4qT-qqCUAAAAAAAAOGFQ.jpg?v=638733705155570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2858,21 +2858,21 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>27159</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>27083</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>VEJA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>2000523</v>
+        <v>2000015</v>
       </c>
       <c r="P34" t="n">
         <v>99999</v>
@@ -2881,43 +2881,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>alface-crespa-unidade-200875</t>
+          <t>sal-refinado-iodado-ita-1kg-117293</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Alface Crespa Unidade</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>200875</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3.79</v>
+        <v>4.39</v>
       </c>
       <c r="F35" t="n">
-        <v>3.79</v>
+        <v>4.39</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2930,21 +2930,21 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2000015</v>
+        <v>2000066</v>
       </c>
       <c r="P35" t="n">
         <v>99999</v>
@@ -2953,44 +2953,48 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-cariorta-1kg-98663</t>
+          <t>desinfetante-banheiro-tira-limo-veja-x-14-sache-400ml-refil-economico-1066404</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Cariorta 1Kg</t>
+          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>98663</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>1066404</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
+        </is>
+      </c>
       <c r="E36" t="n">
-        <v>10.99</v>
+        <v>9.99</v>
       </c>
       <c r="F36" t="n">
-        <v>10.99</v>
+        <v>11.99</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2022-08-11T00:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3927710/VF4qT-qqCUAAAAAAAAOGFQ.jpg?v=638733705155570000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2998,71 +3002,67 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>VEJA</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2001012</v>
+        <v>2000523</v>
       </c>
       <c r="P36" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>leite-uht-piracanjuba-integral-1l-865427</t>
+          <t>abobrinha-italiana-cariorta-1kg-98663</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Leite Uht Piracanjuba Integral 1L</t>
+          <t>Abobrinha Italiana Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>865427</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
-        </is>
-      </c>
+          <t>98663</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>6.69</v>
+        <v>7.99</v>
       </c>
       <c r="F37" t="n">
-        <v>6.69</v>
+        <v>7.99</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2017-04-12T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -3070,93 +3070,89 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2002038</v>
+        <v>2001012</v>
       </c>
       <c r="P37" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>melao-amarelo-metade-1-3-kg-63606</t>
+          <t>file-de-peito-de-frango-congelado-rivelli-bandeja-1kg-1023799</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Melão Amarelo Metade 1,3kg</t>
+          <t>Filé de Peito de Frango Congelado Rivelli Bandeja 1kg</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>63606</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
-        </is>
-      </c>
+          <t>1023799</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>9.99</v>
+        <v>25.99</v>
       </c>
       <c r="F38" t="n">
-        <v>9.99</v>
+        <v>25.99</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2021-07-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038302/VF4qT-qqCUAAAAAAAAKY8g.jpg?v=637792395730970000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>Rivelli</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>2000015</v>
+        <v>2004122</v>
       </c>
       <c r="P38" t="n">
         <v>99999</v>
@@ -3165,43 +3161,43 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>batata-palha-yoki-extra-fina-100g-989843</t>
+          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Batata Palha Yoki Extra Fina 100g</t>
+          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>989843</t>
+          <t>818640</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Batata Palha Yoki Extra Fina 100g</t>
+          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>8.99</v>
+        <v>3.99</v>
       </c>
       <c r="F39" t="n">
-        <v>10.99</v>
+        <v>4.99</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2020-10-30T00:00:00Z</t>
+          <t>2020-11-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3214,21 +3210,21 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>YOKI</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>2001336</v>
+        <v>2002038</v>
       </c>
       <c r="P39" t="n">
         <v>99999</v>
@@ -3237,70 +3233,70 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
+          <t>melao-amarelo-metade-1-3-kg-63606</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
+          <t>Melão Amarelo Metade 1,3kg</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>818640</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
+          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3.99</v>
+        <v>8.99</v>
       </c>
       <c r="F40" t="n">
-        <v>4.99</v>
+        <v>9.99</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2020-11-26T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>2002038</v>
+        <v>2000015</v>
       </c>
       <c r="P40" t="n">
         <v>99999</v>
@@ -3309,39 +3305,43 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-congelado-rivelli-bandeja-1kg-1023799</t>
+          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Congelado Rivelli Bandeja 1kg</t>
+          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1023799</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>1105795</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
+        </is>
+      </c>
       <c r="E41" t="n">
-        <v>19.99</v>
+        <v>3.99</v>
       </c>
       <c r="F41" t="n">
-        <v>25.99</v>
+        <v>5.99</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2021-07-30T00:00:00Z</t>
+          <t>2023-07-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038302/VF4qT-qqCUAAAAAAAAKY8g.jpg?v=637792395730970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3354,21 +3354,21 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>21449</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Rivelli</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2004122</v>
+        <v>2000017</v>
       </c>
       <c r="P41" t="n">
         <v>99999</v>
@@ -3377,43 +3377,43 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
+          <t>leite-uht-piracanjuba-integral-1l-865427</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
+          <t>Leite Uht Piracanjuba Integral 1L</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1105795</t>
+          <t>865427</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
+          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3.99</v>
+        <v>6.69</v>
       </c>
       <c r="F42" t="n">
-        <v>5.99</v>
+        <v>6.69</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2023-07-26T00:00:00Z</t>
+          <t>2017-04-12T00:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3426,21 +3426,21 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>23232</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>23158</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2000017</v>
+        <v>2002038</v>
       </c>
       <c r="P42" t="n">
         <v>99999</v>
@@ -3449,115 +3449,115 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>cebola-roxa-400g-38393</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Cebola Roxa 400g</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>29.98</v>
+        <v>7.99</v>
       </c>
       <c r="F43" t="n">
-        <v>37.9</v>
+        <v>7.99</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>2001329</v>
+        <v>2000015</v>
       </c>
       <c r="P43" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>batata-palha-yoki-extra-fina-100g-989843</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>989843</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5.99</v>
+        <v>8.99</v>
       </c>
       <c r="F44" t="n">
-        <v>6.99</v>
+        <v>10.99</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-10-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3570,21 +3570,21 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>13749</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>YOKI</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>2001532</v>
+        <v>2001336</v>
       </c>
       <c r="P44" t="n">
         <v>99999</v>
@@ -3593,43 +3593,43 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>981168</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>30.99</v>
+        <v>29.98</v>
       </c>
       <c r="F45" t="n">
-        <v>32.19</v>
+        <v>37.9</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2020-09-22T00:00:00Z</t>
+          <t>2020-07-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3642,66 +3642,66 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>NEVE</t>
+          <t>MELITTA</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2000291</v>
+        <v>2001329</v>
       </c>
       <c r="P45" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
+          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
+          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5106753</t>
+          <t>981168</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
+          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>11.99</v>
+        <v>30.99</v>
       </c>
       <c r="F46" t="n">
-        <v>11.99</v>
+        <v>32.19</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2021-01-11T00:00:00Z</t>
+          <t>2020-09-22T00:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3714,93 +3714,93 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>NEVE</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>2003319</v>
+        <v>2000291</v>
       </c>
       <c r="P46" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>99279</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>59.99</v>
+        <v>6.99</v>
       </c>
       <c r="F47" t="n">
-        <v>59.99</v>
+        <v>6.99</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020-05-27T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>24684</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>2001012</v>
+        <v>2001532</v>
       </c>
       <c r="P47" t="n">
         <v>99999</v>
@@ -3809,43 +3809,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>matte-leao-natural-pet-15l-118214</t>
+          <t>tomate-pelado-italiano-due-lata-400g-5459389</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Matte Leão Natural Pet 1,5L</t>
+          <t>Tomate Pelado Italiano Due Lata 400g</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>118214</t>
+          <t>5459389</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
+          <t>Due é sua dupla perfeita para criar o verdadeiro sabor italiano!Due o melhor da culinária italiana com ingredientes genuínos, que você só encontra no Zona SulExperimente e surpreenda-se!</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>7.95</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>8.99</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2025-01-21T00:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3928345/VF4qT-qqCUAAAAAAAAhGgQ.jpg?v=638736295014200000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3858,21 +3858,21 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>39142</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>39069</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>DUE</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>2000010</v>
+        <v>2005138</v>
       </c>
       <c r="P48" t="n">
         <v>99999</v>
@@ -3881,70 +3881,70 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>tomate-pelado-italiano-due-lata-400g-5459389</t>
+          <t>abobora-japonesa-pedaco-500g-38229</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tomate Pelado Italiano Due Lata 400g</t>
+          <t>Abóbora Japonesa Pedaço 500g</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>5459389</t>
+          <t>38229</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Due é sua dupla perfeita para criar o verdadeiro sabor italiano!Due o melhor da culinária italiana com ingredientes genuínos, que você só encontra no Zona SulExperimente e surpreenda-se!</t>
+          <t>Embalagem com 1 pedaço.</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>8.369999999999999</v>
+        <v>4.99</v>
       </c>
       <c r="F49" t="n">
-        <v>8.369999999999999</v>
+        <v>4.99</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2025-01-21T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3928345/VF4qT-qqCUAAAAAAAAhGgQ.jpg?v=638736295014200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3096862/VF4qT-qqCUAAAAAAAAS9Tw.jpg?v=638235593168230000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>39142</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>39069</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>DUE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2005138</v>
+        <v>2000015</v>
       </c>
       <c r="P49" t="n">
         <v>99999</v>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -513,43 +513,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>leite-condensado-moca-lata-395g-1136321</t>
+          <t>refrigerante-coca-cola-zero-pet--2-l-429384</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Leite Condensado Moça Lata 395g</t>
+          <t>Refrigerante Coca Cola Zero PET 2 L</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1136321</t>
+          <t>429384</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Moça® faz todas as receitas darem certo desde 1921, com seu sabor único e original, tem consistência perfeita, é sem comparação! É leite condensado obtido a partir de leite fresco, puro e integral. É um clássico no preparo de sobremesas, também é uma delícia na colher, na salada de frutas e o que mais você imaginar.</t>
+          <t>COCA COLA ZERO PET 2L</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7.95</v>
+        <v>9.69</v>
       </c>
       <c r="F2" t="n">
         <v>9.99</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-13T00:00:00Z</t>
+          <t>2020-10-01T22:50:00Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4530596/VF4qT-qqCUAAAAAAAAbPyA.jpg?v=639095725127130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483406/VF4qT-qqCUAAAAAAAAoaqQ.jpg?v=639052524530730000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -562,21 +562,21 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>37022</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>36949</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>2000043</v>
+        <v>2000027</v>
       </c>
       <c r="P2" t="n">
         <v>99999</v>
@@ -585,43 +585,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>matte-leao-limao-pet-1-5l-118222</t>
+          <t>leite-condensado-moca-lata-395g-1136321</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Matte Leão Limão Pet 1,5L</t>
+          <t>Leite Condensado Moça Lata 395g</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>118222</t>
+          <t>1136321</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
+          <t>Moça® faz todas as receitas darem certo desde 1921, com seu sabor único e original, tem consistência perfeita, é sem comparação! É leite condensado obtido a partir de leite fresco, puro e integral. É um clássico no preparo de sobremesas, também é uma delícia na colher, na salada de frutas e o que mais você imaginar.</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>7.95</v>
       </c>
       <c r="F3" t="n">
-        <v>8.99</v>
+        <v>9.99</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>67</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2024-05-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4530894/VF4qT-qqCUAAAAAAAAojYw.jpg?v=639096587928800000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -634,21 +634,21 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>37022</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>36949</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2000010</v>
+        <v>2000043</v>
       </c>
       <c r="P3" t="n">
         <v>99999</v>
@@ -729,43 +729,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tomate-italiano-unidade-495212</t>
+          <t>matte-leao-limao-pet-1-5l-118222</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tomate Italiano Unidade</t>
+          <t>Matte Leão Limão Pet 1,5L</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>495212</t>
+          <t>118222</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
+          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.7</v>
+        <v>7.95</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7</v>
+        <v>8.99</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -778,21 +778,21 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2000015</v>
+        <v>2000010</v>
       </c>
       <c r="P5" t="n">
         <v>99999</v>
@@ -801,33 +801,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
+          <t>tomate-italiano-unidade-495212</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
+          <t>Tomate Italiano Unidade</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>370550</t>
+          <t>495212</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
+          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>24.99</v>
+        <v>1.7</v>
       </c>
       <c r="F6" t="n">
-        <v>24.99</v>
+        <v>1.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -850,66 +850,66 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2003319</v>
+        <v>2000015</v>
       </c>
       <c r="P6" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>manga-palmer-unidade-5130760</t>
+          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Manga Palmer Unidade</t>
+          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5130760</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
+          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5.39</v>
+        <v>24.99</v>
       </c>
       <c r="F7" t="n">
-        <v>5.99</v>
+        <v>24.99</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-02-16T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -922,66 +922,66 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2000015</v>
+        <v>2003319</v>
       </c>
       <c r="P7" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
+          <t>manga-palmer-unidade-5130760</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
+          <t>Manga Palmer Unidade</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>828025</t>
+          <t>5130760</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
+          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>32.98</v>
+        <v>5.99</v>
       </c>
       <c r="F8" t="n">
-        <v>43.9</v>
+        <v>5.99</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2023-02-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -994,21 +994,21 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>31902</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>PILAO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2000070</v>
+        <v>2000015</v>
       </c>
       <c r="P8" t="n">
         <v>99999</v>
@@ -1017,43 +1017,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
+          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>140805</t>
+          <t>828025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.19</v>
+        <v>32.98</v>
       </c>
       <c r="F9" t="n">
-        <v>5.29</v>
+        <v>43.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2020-09-25T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1066,21 +1066,21 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>SAO LOURENCO</t>
+          <t>PILAO</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2000145</v>
+        <v>2000070</v>
       </c>
       <c r="P9" t="n">
         <v>99999</v>
@@ -1161,70 +1161,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mamao-papaia-cariorta-12kg-99007</t>
+          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mamão Papaia Cariorta 1,2kg</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>99007</t>
+          <t>140805</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.99</v>
+        <v>4.19</v>
       </c>
       <c r="F11" t="n">
-        <v>9.99</v>
+        <v>5.29</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-09-25T00:00:00Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>SAO LOURENCO</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2001012</v>
+        <v>2000145</v>
       </c>
       <c r="P11" t="n">
         <v>99999</v>
@@ -1233,70 +1233,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>couve-flor-unidade-189111</t>
+          <t>mamao-papaia-cariorta-12kg-99007</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Couve Flor Unidade</t>
+          <t>Mamão Papaia Cariorta 1,2kg</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>189111</t>
+          <t>99007</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>9.59</v>
+        <v>9.99</v>
       </c>
       <c r="F12" t="n">
         <v>9.99</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P12" t="n">
         <v>99999</v>
@@ -1305,70 +1305,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>batata-inglesa-cariorta-12kg-98698</t>
+          <t>couve-flor-unidade-189111</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Batata Inglesa Cariorta 1,2Kg</t>
+          <t>Couve Flor Unidade</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>189111</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7.99</v>
+        <v>9.99</v>
       </c>
       <c r="F13" t="n">
-        <v>7.99</v>
+        <v>9.99</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P13" t="n">
         <v>99999</v>
@@ -1377,70 +1377,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cheiro-verde-unidade-201049</t>
+          <t>batata-inglesa-cariorta-12kg-98698</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cheiro Verde Unidade</t>
+          <t>Batata Inglesa Cariorta 1,2Kg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>201049</t>
+          <t>98698</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.99</v>
+        <v>7.99</v>
       </c>
       <c r="F14" t="n">
-        <v>3.39</v>
+        <v>7.99</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P14" t="n">
         <v>99999</v>
@@ -1449,43 +1449,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
+          <t>cheiro-verde-unidade-201049</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
+          <t>Cheiro Verde Unidade</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>100510</t>
+          <t>201049</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
+          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2.69</v>
+        <v>3.39</v>
       </c>
       <c r="F15" t="n">
-        <v>2.69</v>
+        <v>3.39</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1498,21 +1498,21 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>LIMPOL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2001413</v>
+        <v>2000015</v>
       </c>
       <c r="P15" t="n">
         <v>99999</v>
@@ -1521,66 +1521,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
+          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pão Francês Panetto  60g Com 4 unidades</t>
+          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>96318</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>100510</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
+        </is>
+      </c>
       <c r="E16" t="n">
-        <v>24.99</v>
+        <v>2.69</v>
       </c>
       <c r="F16" t="n">
-        <v>24.99</v>
+        <v>2.69</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2024-01-31T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>PANETTO</t>
+          <t>LIMPOL</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2000307</v>
+        <v>2001413</v>
       </c>
       <c r="P16" t="n">
         <v>99999</v>
@@ -1589,70 +1593,66 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>morango-250g-289612</t>
+          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Morango 250g</t>
+          <t>Pão Francês Panetto  60g Com 4 unidades</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>289612</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
-        </is>
-      </c>
+          <t>96318</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
       <c r="F17" t="n">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2024-01-31T00:00:00Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PANETTO</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2000015</v>
+        <v>2000307</v>
       </c>
       <c r="P17" t="n">
         <v>99999</v>
@@ -1661,29 +1661,29 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>uva-preta-sem-semente-500-g-674583</t>
+          <t>morango-250g-289612</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Uva Preta Sem Semente 500g</t>
+          <t>Morango 250g</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>674583</t>
+          <t>289612</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
+          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12.49</v>
+        <v>9.99</v>
       </c>
       <c r="F18" t="n">
-        <v>13.99</v>
+        <v>9.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1733,43 +1733,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
+          <t>uva-preta-sem-semente-500-g-674583</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Odd Clear 500ml</t>
+          <t>Uva Preta Sem Semente 500g</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>982911</t>
+          <t>674583</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ODD voltou!Alto rendimento , controle de odor.</t>
+          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.49</v>
+        <v>13.99</v>
       </c>
       <c r="F19" t="n">
-        <v>2.49</v>
+        <v>13.99</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1782,21 +1782,21 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>LIMPPANO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2001341</v>
+        <v>2000015</v>
       </c>
       <c r="P19" t="n">
         <v>99999</v>
@@ -1805,48 +1805,48 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>limao-cariorta-1kg-98981</t>
+          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Limão Cariorta 1Kg</t>
+          <t>Detergente Para Louças Odd Clear 500ml</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>98981</t>
+          <t>982911</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>ODD voltou!Alto rendimento , controle de odor.</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>11.99</v>
+        <v>2.49</v>
       </c>
       <c r="F20" t="n">
-        <v>11.99</v>
+        <v>2.49</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1854,21 +1854,21 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>LIMPPANO</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2001012</v>
+        <v>2001341</v>
       </c>
       <c r="P20" t="n">
         <v>99999</v>
@@ -1877,48 +1877,48 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
+          <t>limao-cariorta-1kg-98981</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
+          <t>Limão Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>290564</t>
+          <t>98981</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>23.99</v>
+        <v>11.99</v>
       </c>
       <c r="F21" t="n">
-        <v>26.99</v>
+        <v>11.99</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1926,21 +1926,21 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>SADIA</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>2000057</v>
+        <v>2001012</v>
       </c>
       <c r="P21" t="n">
         <v>99999</v>
@@ -1949,39 +1949,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>290564</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
+        </is>
+      </c>
       <c r="E22" t="n">
-        <v>5.99</v>
+        <v>23.99</v>
       </c>
       <c r="F22" t="n">
-        <v>5.99</v>
+        <v>26.99</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1994,66 +1998,62 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>SADIA</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2001952</v>
+        <v>2000057</v>
       </c>
       <c r="P22" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>coentro-unidade-200930</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Coentro Unidade</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>200930</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>2.99</v>
+        <v>5.99</v>
       </c>
       <c r="F23" t="n">
-        <v>3.79</v>
+        <v>5.99</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2066,21 +2066,21 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>2000015</v>
+        <v>2001952</v>
       </c>
       <c r="P23" t="n">
         <v>99999</v>
@@ -2089,43 +2089,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>coentro-unidade-200930</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Coentro Unidade</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>200930</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
+          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9.99</v>
+        <v>3.79</v>
       </c>
       <c r="F24" t="n">
-        <v>10.99</v>
+        <v>3.79</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2233,43 +2233,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-unidade-423513</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.45</v>
+        <v>10.99</v>
       </c>
       <c r="F26" t="n">
-        <v>2.45</v>
+        <v>10.99</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2020-12-07T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2305,43 +2305,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
+          <t>abobrinha-italiana-unidade-423513</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1180320</t>
+          <t>423513</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.79</v>
+        <v>2.45</v>
       </c>
       <c r="F27" t="n">
-        <v>2.79</v>
+        <v>2.45</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2025-07-17T00:00:00Z</t>
+          <t>2020-12-07T00:00:00Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2354,21 +2354,21 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>41057</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>BOMBRIL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>2001389</v>
+        <v>2000015</v>
       </c>
       <c r="P27" t="n">
         <v>99999</v>
@@ -2377,43 +2377,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>1180320</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6.29</v>
+        <v>2.79</v>
       </c>
       <c r="F28" t="n">
-        <v>6.29</v>
+        <v>2.79</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2025-07-17T00:00:00Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2426,21 +2426,21 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>BOMBRIL</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>2000400</v>
+        <v>2001389</v>
       </c>
       <c r="P28" t="n">
         <v>99999</v>
@@ -2449,43 +2449,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>couve-manteiga-unidade-201235</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Couve Manteiga Unidade</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>201235</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.99</v>
+        <v>6.29</v>
       </c>
       <c r="F29" t="n">
-        <v>3.79</v>
+        <v>6.29</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2498,21 +2498,21 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2000015</v>
+        <v>2000400</v>
       </c>
       <c r="P29" t="n">
         <v>99999</v>
@@ -2521,43 +2521,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>milho-em-conserva-quero-lata-200g-476625</t>
+          <t>couve-manteiga-unidade-201235</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Milho em Conserva Quero Lata 200g</t>
+          <t>Couve Manteiga Unidade</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>476625</t>
+          <t>201235</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
+          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="F30" t="n">
-        <v>4.99</v>
+        <v>3.79</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2570,21 +2570,21 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>QUERO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2001778</v>
+        <v>2000015</v>
       </c>
       <c r="P30" t="n">
         <v>99999</v>
@@ -2593,43 +2593,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
+          <t>milho-em-conserva-quero-lata-200g-476625</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
+          <t>Milho em Conserva Quero Lata 200g</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>429392</t>
+          <t>476625</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
         </is>
       </c>
       <c r="E31" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F31" t="n">
         <v>4.99</v>
       </c>
-      <c r="F31" t="n">
-        <v>5.69</v>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2642,21 +2642,21 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>QUERO</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>2000027</v>
+        <v>2001778</v>
       </c>
       <c r="P31" t="n">
         <v>99999</v>
@@ -2665,43 +2665,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
+          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>129887</t>
+          <t>429392</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>12.99</v>
+        <v>4.99</v>
       </c>
       <c r="F32" t="n">
-        <v>12.99</v>
+        <v>5.69</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2714,21 +2714,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2001401</v>
+        <v>2000027</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2737,43 +2737,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>espinafre-unidade-200948</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Espinafre Unidade</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>200948</t>
+          <t>129887</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
+          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2.99</v>
+        <v>12.99</v>
       </c>
       <c r="F33" t="n">
-        <v>3.79</v>
+        <v>12.99</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2786,21 +2786,21 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2000015</v>
+        <v>2001401</v>
       </c>
       <c r="P33" t="n">
         <v>99999</v>
@@ -2881,43 +2881,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sal-refinado-iodado-ita-1kg-117293</t>
+          <t>espinafre-unidade-200948</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Espinafre Unidade</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>200948</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4.39</v>
+        <v>3.79</v>
       </c>
       <c r="F35" t="n">
-        <v>4.39</v>
+        <v>3.79</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2930,21 +2930,21 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2000066</v>
+        <v>2000015</v>
       </c>
       <c r="P35" t="n">
         <v>99999</v>
@@ -3040,10 +3040,10 @@
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>7.99</v>
+        <v>8.99</v>
       </c>
       <c r="F37" t="n">
-        <v>7.99</v>
+        <v>8.99</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3093,39 +3093,43 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-congelado-rivelli-bandeja-1kg-1023799</t>
+          <t>sal-refinado-iodado-ita-1kg-117293</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Congelado Rivelli Bandeja 1kg</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1023799</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>117293</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sal Refinado Iodado Ita 1kg</t>
+        </is>
+      </c>
       <c r="E38" t="n">
-        <v>25.99</v>
+        <v>4.39</v>
       </c>
       <c r="F38" t="n">
-        <v>25.99</v>
+        <v>4.39</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2021-07-30T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038302/VF4qT-qqCUAAAAAAAAKY8g.jpg?v=637792395730970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3138,21 +3142,21 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>21449</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Rivelli</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>2004122</v>
+        <v>2000066</v>
       </c>
       <c r="P38" t="n">
         <v>99999</v>
@@ -3161,43 +3165,39 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
+          <t>file-de-peito-de-frango-congelado-rivelli-bandeja-1kg-1023799</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
+          <t>Filé de Peito de Frango Congelado Rivelli Bandeja 1kg</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>818640</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
-        </is>
-      </c>
+          <t>1023799</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>3.99</v>
+        <v>19.99</v>
       </c>
       <c r="F39" t="n">
-        <v>4.99</v>
+        <v>25.99</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2020-11-26T00:00:00Z</t>
+          <t>2021-07-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038302/VF4qT-qqCUAAAAAAAAKY8g.jpg?v=637792395730970000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3210,21 +3210,21 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>Rivelli</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>2002038</v>
+        <v>2004122</v>
       </c>
       <c r="P39" t="n">
         <v>99999</v>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>8.99</v>
+        <v>9.99</v>
       </c>
       <c r="F40" t="n">
         <v>9.99</v>
@@ -3305,43 +3305,43 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
+          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
+          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1105795</t>
+          <t>818640</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
+          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
         </is>
       </c>
       <c r="E41" t="n">
         <v>3.99</v>
       </c>
       <c r="F41" t="n">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2023-07-26T00:00:00Z</t>
+          <t>2020-11-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3354,21 +3354,21 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2000017</v>
+        <v>2002038</v>
       </c>
       <c r="P41" t="n">
         <v>99999</v>
@@ -3377,43 +3377,43 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>leite-uht-piracanjuba-integral-1l-865427</t>
+          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Leite Uht Piracanjuba Integral 1L</t>
+          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>865427</t>
+          <t>1105795</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
+          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6.69</v>
+        <v>3.99</v>
       </c>
       <c r="F42" t="n">
-        <v>6.69</v>
+        <v>5.99</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2017-04-12T00:00:00Z</t>
+          <t>2023-07-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3426,21 +3426,21 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2002038</v>
+        <v>2000017</v>
       </c>
       <c r="P42" t="n">
         <v>99999</v>
@@ -3449,115 +3449,115 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cebola-roxa-400g-38393</t>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cebola Roxa 400g</t>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>7.99</v>
+        <v>29.98</v>
       </c>
       <c r="F43" t="n">
-        <v>7.99</v>
+        <v>37.9</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-07-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>MELITTA</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>2000015</v>
+        <v>2001329</v>
       </c>
       <c r="P43" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>batata-palha-yoki-extra-fina-100g-989843</t>
+          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Batata Palha Yoki Extra Fina 100g</t>
+          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>989843</t>
+          <t>981168</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Batata Palha Yoki Extra Fina 100g</t>
+          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>8.99</v>
+        <v>30.99</v>
       </c>
       <c r="F44" t="n">
-        <v>10.99</v>
+        <v>32.19</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2020-10-30T00:00:00Z</t>
+          <t>2020-09-22T00:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3570,21 +3570,21 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>YOKI</t>
+          <t>NEVE</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>2001336</v>
+        <v>2000291</v>
       </c>
       <c r="P44" t="n">
         <v>99999</v>
@@ -3593,43 +3593,43 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>batata-palha-yoki-extra-fina-100g-989843</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>989843</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>29.98</v>
+        <v>8.99</v>
       </c>
       <c r="F45" t="n">
-        <v>37.9</v>
+        <v>10.99</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2020-10-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3642,66 +3642,66 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>13749</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>YOKI</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2001329</v>
+        <v>2001336</v>
       </c>
       <c r="P45" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
+          <t>leite-uht-piracanjuba-integral-1l-865427</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
+          <t>Leite Uht Piracanjuba Integral 1L</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>981168</t>
+          <t>865427</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
+          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>30.99</v>
+        <v>6.69</v>
       </c>
       <c r="F46" t="n">
-        <v>32.19</v>
+        <v>6.69</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2020-09-22T00:00:00Z</t>
+          <t>2017-04-12T00:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3714,21 +3714,21 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>23232</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>23158</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>NEVE</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>2000291</v>
+        <v>2002038</v>
       </c>
       <c r="P46" t="n">
         <v>99999</v>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6.99</v>
+        <v>5.99</v>
       </c>
       <c r="F47" t="n">
         <v>6.99</v>
@@ -3881,33 +3881,33 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>abobora-japonesa-pedaco-500g-38229</t>
+          <t>mamao-formosa-metade-cariorta-800g-63584</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Abóbora Japonesa Pedaço 500g</t>
+          <t>Mamão Formosa Metade Cariorta 800g</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>38229</t>
+          <t>63584</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Embalagem com 1 pedaço.</t>
+          <t>"Por ser rico em fibras o mamão formosa é grande amigo do funcionamento do intestino. A cor alaranjada vem do licopeno que, por ser carotenoide, é antioxidante."</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4.99</v>
+        <v>7.99</v>
       </c>
       <c r="F49" t="n">
-        <v>4.99</v>
+        <v>7.99</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3096862/VF4qT-qqCUAAAAAAAAS9Tw.jpg?v=638235593168230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3095891/VF4qT-qqCUAAAAAAAASvtw.jpg?v=638221188789530000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3926,25 +3926,25 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P49" t="n">
         <v>99999</v>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -513,43 +513,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-zero-pet--2-l-429384</t>
+          <t>tomate-italiano-unidade-495212</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Zero PET 2 L</t>
+          <t>Tomate Italiano Unidade</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>429384</t>
+          <t>495212</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>COCA COLA ZERO PET 2L</t>
+          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9.69</v>
+        <v>1.7</v>
       </c>
       <c r="F2" t="n">
-        <v>9.99</v>
+        <v>1.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2020-10-01T22:50:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483406/VF4qT-qqCUAAAAAAAAoaqQ.jpg?v=639052524530730000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -562,21 +562,21 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8832</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>8844</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>2000027</v>
+        <v>2000015</v>
       </c>
       <c r="P2" t="n">
         <v>99999</v>
@@ -585,43 +585,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>leite-condensado-moca-lata-395g-1136321</t>
+          <t>matte-leao-limao-pet-1-5l-118222</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Leite Condensado Moça Lata 395g</t>
+          <t>Matte Leão Limão Pet 1,5L</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1136321</t>
+          <t>118222</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Moça® faz todas as receitas darem certo desde 1921, com seu sabor único e original, tem consistência perfeita, é sem comparação! É leite condensado obtido a partir de leite fresco, puro e integral. É um clássico no preparo de sobremesas, também é uma delícia na colher, na salada de frutas e o que mais você imaginar.</t>
+          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>7.95</v>
       </c>
       <c r="F3" t="n">
-        <v>9.99</v>
+        <v>8.99</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-13T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4530894/VF4qT-qqCUAAAAAAAAojYw.jpg?v=639096587928800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -634,21 +634,21 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>37022</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>36949</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2000043</v>
+        <v>2000010</v>
       </c>
       <c r="P3" t="n">
         <v>99999</v>
@@ -657,43 +657,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>alcool-montenegro-46-1-l-780570</t>
+          <t>leite-condensado-moca-lata-395g-1136321</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Álcool Montenegro 46% 1 L</t>
+          <t>Leite Condensado Moça Lata 395g</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>780570</t>
+          <t>1136321</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Álcool Montenegro 46% 1 L</t>
+          <t>Moça® faz todas as receitas darem certo desde 1921, com seu sabor único e original, tem consistência perfeita, é sem comparação! É leite condensado obtido a partir de leite fresco, puro e integral. É um clássico no preparo de sobremesas, também é uma delícia na colher, na salada de frutas e o que mais você imaginar.</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8.789999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="F4" t="n">
-        <v>8.789999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>67</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2020-10-06T10:47:00Z</t>
+          <t>2024-05-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051579/VF4qT-qqCUAAAAAAAAG3pQ.jpg?v=637793390624870000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4530894/VF4qT-qqCUAAAAAAAAojYw.jpg?v=639096587928800000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -706,21 +706,21 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>11598</t>
+          <t>37022</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>36949</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>MONTENEGRO</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>2000527</v>
+        <v>2000043</v>
       </c>
       <c r="P4" t="n">
         <v>99999</v>
@@ -729,43 +729,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>matte-leao-limao-pet-1-5l-118222</t>
+          <t>manga-palmer-unidade-5130760</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Matte Leão Limão Pet 1,5L</t>
+          <t>Manga Palmer Unidade</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>118222</t>
+          <t>5130760</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
+          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7.95</v>
+        <v>5.99</v>
       </c>
       <c r="F5" t="n">
-        <v>8.99</v>
+        <v>5.99</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2023-02-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -778,21 +778,21 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>31902</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2000010</v>
+        <v>2000015</v>
       </c>
       <c r="P5" t="n">
         <v>99999</v>
@@ -801,43 +801,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tomate-italiano-unidade-495212</t>
+          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tomate Italiano Unidade</t>
+          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>495212</t>
+          <t>828025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
+          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.7</v>
+        <v>32.98</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7</v>
+        <v>43.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -850,21 +850,21 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PILAO</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2000015</v>
+        <v>2000070</v>
       </c>
       <c r="P6" t="n">
         <v>99999</v>
@@ -873,133 +873,133 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
+          <t>mamao-papaia-cariorta-12kg-99007</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
+          <t>Mamão Papaia Cariorta 1,2kg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>370550</t>
+          <t>99007</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>24.99</v>
+        <v>9.99</v>
       </c>
       <c r="F7" t="n">
-        <v>24.99</v>
+        <v>9.99</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2003319</v>
+        <v>2001012</v>
       </c>
       <c r="P7" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>manga-palmer-unidade-5130760</t>
+          <t>mucarela-em-fatias-92363</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Manga Palmer Unidade</t>
+          <t>Muçarela  em Fatias 200g</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5130760</t>
+          <t>92363</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
+          <t>Muçarela em Fatias</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5.99</v>
+        <v>59.9</v>
       </c>
       <c r="F8" t="n">
-        <v>5.99</v>
+        <v>59.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2023-02-16T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1017,43 +1017,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
+          <t>couve-flor-unidade-189111</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
+          <t>Couve Flor Unidade</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>828025</t>
+          <t>189111</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
+          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>32.98</v>
+        <v>9.99</v>
       </c>
       <c r="F9" t="n">
-        <v>43.9</v>
+        <v>9.99</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1066,21 +1066,21 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>PILAO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2000070</v>
+        <v>2000015</v>
       </c>
       <c r="P9" t="n">
         <v>99999</v>
@@ -1089,70 +1089,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mucarela-em-fatias-92363</t>
+          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Muçarela  em Fatias 200g</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>92363</t>
+          <t>140805</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Muçarela em Fatias</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>59.9</v>
+        <v>4.19</v>
       </c>
       <c r="F10" t="n">
-        <v>59.9</v>
+        <v>5.29</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-25T00:00:00Z</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SAO LOURENCO</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2000015</v>
+        <v>2000145</v>
       </c>
       <c r="P10" t="n">
         <v>99999</v>
@@ -1161,70 +1161,66 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
+          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Pão Francês Panetto  60g Com 4 unidades</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>140805</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
-        </is>
-      </c>
+          <t>96318</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>4.19</v>
+        <v>24.99</v>
       </c>
       <c r="F11" t="n">
-        <v>5.29</v>
+        <v>24.99</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2020-09-25T00:00:00Z</t>
+          <t>2024-01-31T00:00:00Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>SAO LOURENCO</t>
+          <t>PANETTO</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2000145</v>
+        <v>2000307</v>
       </c>
       <c r="P11" t="n">
         <v>99999</v>
@@ -1233,17 +1229,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mamao-papaia-cariorta-12kg-99007</t>
+          <t>batata-inglesa-cariorta-12kg-98698</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mamão Papaia Cariorta 1,2kg</t>
+          <t>Batata Inglesa Cariorta 1,2Kg</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>99007</t>
+          <t>98698</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1252,24 +1248,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>9.99</v>
+        <v>7.99</v>
       </c>
       <c r="F12" t="n">
-        <v>9.99</v>
+        <v>7.99</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1282,12 +1278,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1305,33 +1301,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>couve-flor-unidade-189111</t>
+          <t>cheiro-verde-unidade-201049</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Couve Flor Unidade</t>
+          <t>Cheiro Verde Unidade</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>189111</t>
+          <t>201049</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
+          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9.99</v>
+        <v>3.39</v>
       </c>
       <c r="F13" t="n">
-        <v>9.99</v>
+        <v>3.39</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1341,7 +1337,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1354,12 +1350,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1377,70 +1373,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>batata-inglesa-cariorta-12kg-98698</t>
+          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Batata Inglesa Cariorta 1,2Kg</t>
+          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>100510</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7.99</v>
+        <v>2.69</v>
       </c>
       <c r="F14" t="n">
-        <v>7.99</v>
+        <v>2.69</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>LIMPOL</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2001012</v>
+        <v>2001413</v>
       </c>
       <c r="P14" t="n">
         <v>99999</v>
@@ -1449,43 +1445,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cheiro-verde-unidade-201049</t>
+          <t>morango-250g-289612</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cheiro Verde Unidade</t>
+          <t>Morango 250g</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>201049</t>
+          <t>289612</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3.39</v>
+        <v>9.99</v>
       </c>
       <c r="F15" t="n">
-        <v>3.39</v>
+        <v>9.99</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1498,12 +1494,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1521,43 +1517,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
+          <t>uva-preta-sem-semente-500-g-674583</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
+          <t>Uva Preta Sem Semente 500g</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>100510</t>
+          <t>674583</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
+          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.69</v>
+        <v>13.99</v>
       </c>
       <c r="F16" t="n">
-        <v>2.69</v>
+        <v>13.99</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1570,21 +1566,21 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>LIMPOL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2001413</v>
+        <v>2000015</v>
       </c>
       <c r="P16" t="n">
         <v>99999</v>
@@ -1593,66 +1589,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
+          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pão Francês Panetto  60g Com 4 unidades</t>
+          <t>Detergente Para Louças Odd Clear 500ml</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>96318</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>982911</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ODD voltou!Alto rendimento , controle de odor.</t>
+        </is>
+      </c>
       <c r="E17" t="n">
-        <v>24.99</v>
+        <v>2.49</v>
       </c>
       <c r="F17" t="n">
-        <v>24.99</v>
+        <v>2.49</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2024-01-31T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>PANETTO</t>
+          <t>LIMPPANO</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2000307</v>
+        <v>2001341</v>
       </c>
       <c r="P17" t="n">
         <v>99999</v>
@@ -1661,43 +1661,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>morango-250g-289612</t>
+          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Morango 250g</t>
+          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>289612</t>
+          <t>290564</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
+          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9.99</v>
+        <v>23.99</v>
       </c>
       <c r="F18" t="n">
-        <v>9.99</v>
+        <v>26.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1710,21 +1710,21 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SADIA</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2000015</v>
+        <v>2000057</v>
       </c>
       <c r="P18" t="n">
         <v>99999</v>
@@ -1733,43 +1733,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>uva-preta-sem-semente-500-g-674583</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Uva Preta Sem Semente 500g</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>674583</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>13.99</v>
+        <v>5.99</v>
       </c>
       <c r="F19" t="n">
-        <v>13.99</v>
+        <v>5.99</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1782,21 +1778,21 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2000015</v>
+        <v>2001952</v>
       </c>
       <c r="P19" t="n">
         <v>99999</v>
@@ -1805,48 +1801,48 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
+          <t>limao-cariorta-1kg-98981</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Odd Clear 500ml</t>
+          <t>Limão Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>982911</t>
+          <t>98981</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ODD voltou!Alto rendimento , controle de odor.</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2.49</v>
+        <v>11.99</v>
       </c>
       <c r="F20" t="n">
-        <v>2.49</v>
+        <v>11.99</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1854,21 +1850,21 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>LIMPPANO</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2001341</v>
+        <v>2001012</v>
       </c>
       <c r="P20" t="n">
         <v>99999</v>
@@ -1877,48 +1873,48 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>limao-cariorta-1kg-98981</t>
+          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Limão Cariorta 1Kg</t>
+          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>98981</t>
+          <t>364738</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>11.99</v>
+        <v>3.97</v>
       </c>
       <c r="F21" t="n">
-        <v>11.99</v>
+        <v>4.89</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1926,21 +1922,21 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>2001012</v>
+        <v>2000043</v>
       </c>
       <c r="P21" t="n">
         <v>99999</v>
@@ -1949,43 +1945,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
+          <t>coentro-unidade-200930</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
+          <t>Coentro Unidade</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>290564</t>
+          <t>200930</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
+          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>23.99</v>
+        <v>3.79</v>
       </c>
       <c r="F22" t="n">
-        <v>26.99</v>
+        <v>3.79</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1998,62 +1994,66 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>SADIA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2000057</v>
+        <v>2000015</v>
       </c>
       <c r="P22" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>abobrinha-italiana-unidade-423513</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>423513</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Abobrinha Italiana Unidade</t>
+        </is>
+      </c>
       <c r="E23" t="n">
-        <v>5.99</v>
+        <v>2.8</v>
       </c>
       <c r="F23" t="n">
-        <v>5.99</v>
+        <v>2.8</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-12-07T00:00:00Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2066,21 +2066,21 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>2001952</v>
+        <v>2000015</v>
       </c>
       <c r="P23" t="n">
         <v>99999</v>
@@ -2089,43 +2089,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>coentro-unidade-200930</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Coentro Unidade</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>200930</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.79</v>
+        <v>10.99</v>
       </c>
       <c r="F24" t="n">
-        <v>3.79</v>
+        <v>10.99</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2155,49 +2155,49 @@
         <v>2000015</v>
       </c>
       <c r="P24" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>364738</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3.97</v>
+        <v>6.29</v>
       </c>
       <c r="F25" t="n">
-        <v>4.89</v>
+        <v>6.29</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2210,21 +2210,21 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>2000043</v>
+        <v>2000400</v>
       </c>
       <c r="P25" t="n">
         <v>99999</v>
@@ -2233,43 +2233,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>1180320</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
+          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>10.99</v>
+        <v>2.79</v>
       </c>
       <c r="F26" t="n">
-        <v>10.99</v>
+        <v>2.79</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2025-07-17T00:00:00Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2282,21 +2282,21 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>BOMBRIL</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>2000015</v>
+        <v>2001389</v>
       </c>
       <c r="P26" t="n">
         <v>99999</v>
@@ -2305,43 +2305,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-unidade-423513</t>
+          <t>couve-manteiga-unidade-201235</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Couve Manteiga Unidade</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>201235</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.45</v>
+        <v>3.79</v>
       </c>
       <c r="F27" t="n">
-        <v>2.45</v>
+        <v>3.79</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2020-12-07T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2377,43 +2377,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
+          <t>milho-em-conserva-quero-lata-200g-476625</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
+          <t>Milho em Conserva Quero Lata 200g</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1180320</t>
+          <t>476625</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
+          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.79</v>
+        <v>3.69</v>
       </c>
       <c r="F28" t="n">
-        <v>2.79</v>
+        <v>4.99</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2025-07-17T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2426,21 +2426,21 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>41057</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>BOMBRIL</t>
+          <t>QUERO</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>2001389</v>
+        <v>2001778</v>
       </c>
       <c r="P28" t="n">
         <v>99999</v>
@@ -2449,43 +2449,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>429392</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6.29</v>
+        <v>4.99</v>
       </c>
       <c r="F29" t="n">
-        <v>6.29</v>
+        <v>5.69</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2498,21 +2498,21 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2000400</v>
+        <v>2000027</v>
       </c>
       <c r="P29" t="n">
         <v>99999</v>
@@ -2521,43 +2521,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>couve-manteiga-unidade-201235</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Couve Manteiga Unidade</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>201235</t>
+          <t>129887</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
+          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3.79</v>
+        <v>12.99</v>
       </c>
       <c r="F30" t="n">
-        <v>3.79</v>
+        <v>12.99</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2570,21 +2570,21 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2000015</v>
+        <v>2001401</v>
       </c>
       <c r="P30" t="n">
         <v>99999</v>
@@ -2593,43 +2593,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>milho-em-conserva-quero-lata-200g-476625</t>
+          <t>espinafre-unidade-200948</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Milho em Conserva Quero Lata 200g</t>
+          <t>Espinafre Unidade</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>476625</t>
+          <t>200948</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
+          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="F31" t="n">
-        <v>4.99</v>
+        <v>3.79</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2642,21 +2642,21 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>QUERO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>2001778</v>
+        <v>2000015</v>
       </c>
       <c r="P31" t="n">
         <v>99999</v>
@@ -2665,43 +2665,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
+          <t>desinfetante-banheiro-tira-limo-veja-x-14-sache-400ml-refil-economico-1066404</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
+          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>429392</t>
+          <t>1066404</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4.99</v>
+        <v>9.99</v>
       </c>
       <c r="F32" t="n">
-        <v>5.69</v>
+        <v>11.99</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2022-08-11T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3927710/VF4qT-qqCUAAAAAAAAOGFQ.jpg?v=638733705155570000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2714,21 +2714,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>VEJA</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2000027</v>
+        <v>2000523</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2737,43 +2737,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
+          <t>alface-crespa-unidade-200875</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
+          <t>Alface Crespa Unidade</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>129887</t>
+          <t>200875</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>12.99</v>
+        <v>3.79</v>
       </c>
       <c r="F33" t="n">
-        <v>12.99</v>
+        <v>3.79</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2786,21 +2786,21 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2001401</v>
+        <v>2000015</v>
       </c>
       <c r="P33" t="n">
         <v>99999</v>
@@ -2809,48 +2809,44 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>alface-crespa-unidade-200875</t>
+          <t>abobrinha-italiana-cariorta-1kg-98663</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Alface Crespa Unidade</t>
+          <t>Abobrinha Italiana Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>200875</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
-        </is>
-      </c>
+          <t>98663</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>3.79</v>
+        <v>8.99</v>
       </c>
       <c r="F34" t="n">
-        <v>3.79</v>
+        <v>8.99</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2858,66 +2854,66 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P34" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>espinafre-unidade-200948</t>
+          <t>sal-refinado-iodado-ita-1kg-117293</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Espinafre Unidade</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>200948</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3.79</v>
+        <v>4.39</v>
       </c>
       <c r="F35" t="n">
-        <v>3.79</v>
+        <v>4.39</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2930,21 +2926,21 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2000015</v>
+        <v>2000066</v>
       </c>
       <c r="P35" t="n">
         <v>99999</v>
@@ -2953,43 +2949,39 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>desinfetante-banheiro-tira-limo-veja-x-14-sache-400ml-refil-economico-1066404</t>
+          <t>file-de-peito-de-frango-congelado-rivelli-bandeja-1kg-1023799</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
+          <t>Filé de Peito de Frango Congelado Rivelli Bandeja 1kg</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1066404</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
-        </is>
-      </c>
+          <t>1023799</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
-        <v>9.99</v>
+        <v>19.99</v>
       </c>
       <c r="F36" t="n">
-        <v>11.99</v>
+        <v>25.99</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2022-08-11T00:00:00Z</t>
+          <t>2021-07-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3927710/VF4qT-qqCUAAAAAAAAOGFQ.jpg?v=638733705155570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038302/VF4qT-qqCUAAAAAAAAKY8g.jpg?v=637792395730970000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3002,21 +2994,21 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>27159</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>27083</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>VEJA</t>
+          <t>Rivelli</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2000523</v>
+        <v>2004122</v>
       </c>
       <c r="P36" t="n">
         <v>99999</v>
@@ -3025,44 +3017,48 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-cariorta-1kg-98663</t>
+          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Cariorta 1Kg</t>
+          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>98663</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>818640</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
+        </is>
+      </c>
       <c r="E37" t="n">
-        <v>8.99</v>
+        <v>3.99</v>
       </c>
       <c r="F37" t="n">
-        <v>8.99</v>
+        <v>4.99</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-11-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -3070,93 +3066,93 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2001012</v>
+        <v>2002038</v>
       </c>
       <c r="P37" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>sal-refinado-iodado-ita-1kg-117293</t>
+          <t>melao-amarelo-metade-1-3-kg-63606</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Melão Amarelo Metade 1,3kg</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4.39</v>
+        <v>9.99</v>
       </c>
       <c r="F38" t="n">
-        <v>4.39</v>
+        <v>9.99</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>2000066</v>
+        <v>2000015</v>
       </c>
       <c r="P38" t="n">
         <v>99999</v>
@@ -3165,39 +3161,43 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-congelado-rivelli-bandeja-1kg-1023799</t>
+          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Congelado Rivelli Bandeja 1kg</t>
+          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1023799</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>1105795</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
+        </is>
+      </c>
       <c r="E39" t="n">
-        <v>19.99</v>
+        <v>3.99</v>
       </c>
       <c r="F39" t="n">
-        <v>25.99</v>
+        <v>5.99</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2021-07-30T00:00:00Z</t>
+          <t>2023-07-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038302/VF4qT-qqCUAAAAAAAAKY8g.jpg?v=637792395730970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3210,21 +3210,21 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>21449</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Rivelli</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>2004122</v>
+        <v>2000017</v>
       </c>
       <c r="P39" t="n">
         <v>99999</v>
@@ -3233,70 +3233,70 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>melao-amarelo-metade-1-3-kg-63606</t>
+          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Melão Amarelo Metade 1,3kg</t>
+          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>981168</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
+          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>9.99</v>
+        <v>30.99</v>
       </c>
       <c r="F40" t="n">
-        <v>9.99</v>
+        <v>32.19</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-22T00:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>NEVE</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>2000015</v>
+        <v>2000291</v>
       </c>
       <c r="P40" t="n">
         <v>99999</v>
@@ -3305,43 +3305,43 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>818640</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3.99</v>
+        <v>29.98</v>
       </c>
       <c r="F41" t="n">
-        <v>4.99</v>
+        <v>37.9</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2020-11-26T00:00:00Z</t>
+          <t>2020-07-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3354,21 +3354,21 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>MELITTA</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2002038</v>
+        <v>2001329</v>
       </c>
       <c r="P41" t="n">
         <v>99999</v>
@@ -3377,43 +3377,43 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1105795</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3.99</v>
+        <v>5.99</v>
       </c>
       <c r="F42" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2023-07-26T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3426,21 +3426,21 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2000017</v>
+        <v>2001532</v>
       </c>
       <c r="P42" t="n">
         <v>99999</v>
@@ -3449,43 +3449,43 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>batata-palha-yoki-extra-fina-100g-989843</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>989843</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>29.98</v>
+        <v>8.99</v>
       </c>
       <c r="F43" t="n">
-        <v>37.9</v>
+        <v>10.99</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2020-10-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3498,21 +3498,21 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>13749</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>YOKI</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>2001329</v>
+        <v>2001336</v>
       </c>
       <c r="P43" t="n">
         <v>99999</v>
@@ -3521,43 +3521,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
+          <t>tomate-pelado-italiano-due-lata-400g-5459389</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
+          <t>Tomate Pelado Italiano Due Lata 400g</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>981168</t>
+          <t>5459389</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
+          <t>Due é sua dupla perfeita para criar o verdadeiro sabor italiano!Due o melhor da culinária italiana com ingredientes genuínos, que você só encontra no Zona SulExperimente e surpreenda-se!</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>30.99</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>32.19</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2020-09-22T00:00:00Z</t>
+          <t>2025-01-21T00:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3928345/VF4qT-qqCUAAAAAAAAhGgQ.jpg?v=638736295014200000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3570,21 +3570,21 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>39142</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>39069</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>NEVE</t>
+          <t>DUE</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>2000291</v>
+        <v>2005138</v>
       </c>
       <c r="P44" t="n">
         <v>99999</v>
@@ -3593,70 +3593,70 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>batata-palha-yoki-extra-fina-100g-989843</t>
+          <t>mamao-formosa-metade-cariorta-800g-63584</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Batata Palha Yoki Extra Fina 100g</t>
+          <t>Mamão Formosa Metade Cariorta 800g</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>989843</t>
+          <t>63584</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Batata Palha Yoki Extra Fina 100g</t>
+          <t>"Por ser rico em fibras o mamão formosa é grande amigo do funcionamento do intestino. A cor alaranjada vem do licopeno que, por ser carotenoide, é antioxidante."</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>8.99</v>
+        <v>7.99</v>
       </c>
       <c r="F45" t="n">
-        <v>10.99</v>
+        <v>7.99</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2020-10-30T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3095891/VF4qT-qqCUAAAAAAAASvtw.jpg?v=638221188789530000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>YOKI</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2001336</v>
+        <v>2001012</v>
       </c>
       <c r="P45" t="n">
         <v>99999</v>
@@ -3737,70 +3737,70 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>99279</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5.99</v>
+        <v>59.99</v>
       </c>
       <c r="F47" t="n">
-        <v>6.99</v>
+        <v>59.99</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-05-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>2001532</v>
+        <v>2001012</v>
       </c>
       <c r="P47" t="n">
         <v>99999</v>
@@ -3809,70 +3809,70 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>tomate-pelado-italiano-due-lata-400g-5459389</t>
+          <t>cebola-roxa-400g-38393</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tomate Pelado Italiano Due Lata 400g</t>
+          <t>Cebola Roxa 400g</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>5459389</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Due é sua dupla perfeita para criar o verdadeiro sabor italiano!Due o melhor da culinária italiana com ingredientes genuínos, que você só encontra no Zona SulExperimente e surpreenda-se!</t>
+          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8.369999999999999</v>
+        <v>7.99</v>
       </c>
       <c r="F48" t="n">
-        <v>8.369999999999999</v>
+        <v>7.99</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2025-01-21T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3928345/VF4qT-qqCUAAAAAAAAhGgQ.jpg?v=638736295014200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>39142</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>39069</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>DUE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>2005138</v>
+        <v>2000015</v>
       </c>
       <c r="P48" t="n">
         <v>99999</v>
@@ -3881,70 +3881,70 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>mamao-formosa-metade-cariorta-800g-63584</t>
+          <t>matte-leao-natural-pet-15l-118214</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mamão Formosa Metade Cariorta 800g</t>
+          <t>Matte Leão Natural Pet 1,5L</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>63584</t>
+          <t>118214</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"Por ser rico em fibras o mamão formosa é grande amigo do funcionamento do intestino. A cor alaranjada vem do licopeno que, por ser carotenoide, é antioxidante."</t>
+          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>7.99</v>
+        <v>7.95</v>
       </c>
       <c r="F49" t="n">
-        <v>7.99</v>
+        <v>8.99</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3095891/VF4qT-qqCUAAAAAAAASvtw.jpg?v=638221188789530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2001012</v>
+        <v>2000010</v>
       </c>
       <c r="P49" t="n">
         <v>99999</v>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -513,43 +513,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tomate-italiano-unidade-495212</t>
+          <t>refrigerante-coca-cola-zero-pet--2-l-429384</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tomate Italiano Unidade</t>
+          <t>Refrigerante Coca Cola Zero PET 2 L</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>495212</t>
+          <t>429384</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
+          <t>COCA COLA ZERO PET 2L</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.7</v>
+        <v>6.99</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7</v>
+        <v>9.99</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-10-01T22:50:00Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483406/VF4qT-qqCUAAAAAAAAoaqQ.jpg?v=639052524530730000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -562,21 +562,21 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>2000015</v>
+        <v>2000027</v>
       </c>
       <c r="P2" t="n">
         <v>99999</v>
@@ -585,43 +585,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>matte-leao-limao-pet-1-5l-118222</t>
+          <t>alcool-montenegro-46-1-l-780570</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Matte Leão Limão Pet 1,5L</t>
+          <t>Álcool Montenegro 46% 1 L</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>118222</t>
+          <t>780570</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
+          <t>Álcool Montenegro 46% 1 L</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7.95</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>8.99</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-10-06T10:47:00Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051579/VF4qT-qqCUAAAAAAAAG3pQ.jpg?v=637793390624870000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -634,21 +634,21 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>11598</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>MONTENEGRO</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2000010</v>
+        <v>2000527</v>
       </c>
       <c r="P3" t="n">
         <v>99999</v>
@@ -657,43 +657,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>leite-condensado-moca-lata-395g-1136321</t>
+          <t>tomate-italiano-unidade-495212</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Leite Condensado Moça Lata 395g</t>
+          <t>Tomate Italiano Unidade</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1136321</t>
+          <t>495212</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Moça® faz todas as receitas darem certo desde 1921, com seu sabor único e original, tem consistência perfeita, é sem comparação! É leite condensado obtido a partir de leite fresco, puro e integral. É um clássico no preparo de sobremesas, também é uma delícia na colher, na salada de frutas e o que mais você imaginar.</t>
+          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7.95</v>
+        <v>1.7</v>
       </c>
       <c r="F4" t="n">
-        <v>9.99</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-13T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4530894/VF4qT-qqCUAAAAAAAAojYw.jpg?v=639096587928800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -706,21 +706,21 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>37022</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>36949</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>2000043</v>
+        <v>2000015</v>
       </c>
       <c r="P4" t="n">
         <v>99999</v>
@@ -729,43 +729,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>manga-palmer-unidade-5130760</t>
+          <t>matte-leao-limao-pet-1-5l-118222</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manga Palmer Unidade</t>
+          <t>Matte Leão Limão Pet 1,5L</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5130760</t>
+          <t>118222</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
+          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5.99</v>
+        <v>7.95</v>
       </c>
       <c r="F5" t="n">
-        <v>5.99</v>
+        <v>8.99</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-02-16T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -778,21 +778,21 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2000015</v>
+        <v>2000010</v>
       </c>
       <c r="P5" t="n">
         <v>99999</v>
@@ -801,43 +801,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
+          <t>leite-condensado-moca-lata-395g-1136321</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
+          <t>Leite Condensado Moça Lata 395g</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>828025</t>
+          <t>1136321</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
+          <t>Moça® faz todas as receitas darem certo desde 1921, com seu sabor único e original, tem consistência perfeita, é sem comparação! É leite condensado obtido a partir de leite fresco, puro e integral. É um clássico no preparo de sobremesas, também é uma delícia na colher, na salada de frutas e o que mais você imaginar.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>32.98</v>
+        <v>7.95</v>
       </c>
       <c r="F6" t="n">
-        <v>43.9</v>
+        <v>9.99</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>67</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2024-05-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4530894/VF4qT-qqCUAAAAAAAAojYw.jpg?v=639096587928800000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -850,21 +850,21 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>37022</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>36949</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>PILAO</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2000070</v>
+        <v>2000043</v>
       </c>
       <c r="P6" t="n">
         <v>99999</v>
@@ -873,133 +873,133 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mamao-papaia-cariorta-12kg-99007</t>
+          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mamão Papaia Cariorta 1,2kg</t>
+          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>99007</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
       <c r="F7" t="n">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2001012</v>
+        <v>2003319</v>
       </c>
       <c r="P7" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mucarela-em-fatias-92363</t>
+          <t>manga-palmer-unidade-5130760</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Muçarela  em Fatias 200g</t>
+          <t>Manga Palmer Unidade</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>92363</t>
+          <t>5130760</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Muçarela em Fatias</t>
+          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>59.9</v>
+        <v>5.99</v>
       </c>
       <c r="F8" t="n">
-        <v>59.9</v>
+        <v>5.99</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2023-02-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>31902</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1017,43 +1017,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>couve-flor-unidade-189111</t>
+          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Couve Flor Unidade</t>
+          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>189111</t>
+          <t>828025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
+          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>9.99</v>
+        <v>32.98</v>
       </c>
       <c r="F9" t="n">
-        <v>9.99</v>
+        <v>43.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1066,93 +1066,93 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PILAO</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2000015</v>
+        <v>2000070</v>
       </c>
       <c r="P9" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
+          <t>mamao-papaia-cariorta-12kg-99007</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Mamão Papaia Cariorta 1,2kg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>140805</t>
+          <t>99007</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.19</v>
+        <v>9.99</v>
       </c>
       <c r="F10" t="n">
-        <v>5.29</v>
+        <v>9.99</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2020-09-25T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>SAO LOURENCO</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2000145</v>
+        <v>2001012</v>
       </c>
       <c r="P10" t="n">
         <v>99999</v>
@@ -1161,66 +1161,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
+          <t>couve-flor-unidade-189111</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pão Francês Panetto  60g Com 4 unidades</t>
+          <t>Couve Flor Unidade</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>96318</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>189111</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
+        </is>
+      </c>
       <c r="E11" t="n">
-        <v>24.99</v>
+        <v>9.99</v>
       </c>
       <c r="F11" t="n">
-        <v>24.99</v>
+        <v>9.99</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2024-01-31T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>PANETTO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2000307</v>
+        <v>2000015</v>
       </c>
       <c r="P11" t="n">
         <v>99999</v>
@@ -1229,43 +1233,43 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>batata-inglesa-cariorta-12kg-98698</t>
+          <t>mucarela-em-fatias-92363</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Batata Inglesa Cariorta 1,2Kg</t>
+          <t>Muçarela  em Fatias 200g</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>92363</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>Muçarela em Fatias</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.99</v>
+        <v>59.9</v>
       </c>
       <c r="F12" t="n">
-        <v>7.99</v>
+        <v>59.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1274,25 +1278,25 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P12" t="n">
         <v>99999</v>
@@ -1301,43 +1305,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cheiro-verde-unidade-201049</t>
+          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cheiro Verde Unidade</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>201049</t>
+          <t>140805</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3.39</v>
+        <v>4.19</v>
       </c>
       <c r="F13" t="n">
-        <v>3.39</v>
+        <v>5.29</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-25T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1350,21 +1354,21 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SAO LOURENCO</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2000015</v>
+        <v>2000145</v>
       </c>
       <c r="P13" t="n">
         <v>99999</v>
@@ -1373,70 +1377,66 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
+          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
+          <t>Pão Francês Panetto  60g Com 4 unidades</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>100510</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
-        </is>
-      </c>
+          <t>96318</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>2.69</v>
+        <v>24.99</v>
       </c>
       <c r="F14" t="n">
-        <v>2.69</v>
+        <v>24.99</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2024-01-31T00:00:00Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>LIMPOL</t>
+          <t>PANETTO</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2001413</v>
+        <v>2000307</v>
       </c>
       <c r="P14" t="n">
         <v>99999</v>
@@ -1445,70 +1445,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>morango-250g-289612</t>
+          <t>batata-inglesa-cariorta-12kg-98698</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Morango 250g</t>
+          <t>Batata Inglesa Cariorta 1,2Kg</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>289612</t>
+          <t>98698</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9.99</v>
+        <v>7.99</v>
       </c>
       <c r="F15" t="n">
-        <v>9.99</v>
+        <v>7.99</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P15" t="n">
         <v>99999</v>
@@ -1517,43 +1517,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>uva-preta-sem-semente-500-g-674583</t>
+          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Uva Preta Sem Semente 500g</t>
+          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>674583</t>
+          <t>100510</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
+          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13.99</v>
+        <v>2.69</v>
       </c>
       <c r="F16" t="n">
-        <v>13.99</v>
+        <v>2.69</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1566,21 +1566,21 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>LIMPOL</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2000015</v>
+        <v>2001413</v>
       </c>
       <c r="P16" t="n">
         <v>99999</v>
@@ -1589,43 +1589,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
+          <t>cheiro-verde-unidade-201049</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Odd Clear 500ml</t>
+          <t>Cheiro Verde Unidade</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>982911</t>
+          <t>201049</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ODD voltou!Alto rendimento , controle de odor.</t>
+          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.49</v>
+        <v>3.39</v>
       </c>
       <c r="F17" t="n">
-        <v>2.49</v>
+        <v>3.39</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1638,21 +1638,21 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>LIMPPANO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2001341</v>
+        <v>2000015</v>
       </c>
       <c r="P17" t="n">
         <v>99999</v>
@@ -1661,43 +1661,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
+          <t>morango-250g-289612</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
+          <t>Morango 250g</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>290564</t>
+          <t>289612</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
+          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>23.99</v>
+        <v>9.99</v>
       </c>
       <c r="F18" t="n">
-        <v>26.99</v>
+        <v>9.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1710,21 +1710,21 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>SADIA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2000057</v>
+        <v>2000015</v>
       </c>
       <c r="P18" t="n">
         <v>99999</v>
@@ -1733,39 +1733,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>290564</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
+        </is>
+      </c>
       <c r="E19" t="n">
-        <v>5.99</v>
+        <v>23.99</v>
       </c>
       <c r="F19" t="n">
-        <v>5.99</v>
+        <v>26.99</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1778,71 +1782,71 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>SADIA</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2001952</v>
+        <v>2000057</v>
       </c>
       <c r="P19" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>limao-cariorta-1kg-98981</t>
+          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Limão Cariorta 1Kg</t>
+          <t>Detergente Para Louças Odd Clear 500ml</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>98981</t>
+          <t>982911</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>ODD voltou!Alto rendimento , controle de odor.</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>11.99</v>
+        <v>2.49</v>
       </c>
       <c r="F20" t="n">
-        <v>11.99</v>
+        <v>2.49</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1850,21 +1854,21 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>LIMPPANO</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2001012</v>
+        <v>2001341</v>
       </c>
       <c r="P20" t="n">
         <v>99999</v>
@@ -1873,43 +1877,43 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
+          <t>uva-preta-sem-semente-500-g-674583</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
+          <t>Uva Preta Sem Semente 500g</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>364738</t>
+          <t>674583</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
+          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.97</v>
+        <v>13.99</v>
       </c>
       <c r="F21" t="n">
-        <v>4.89</v>
+        <v>13.99</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1922,21 +1926,21 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>2000043</v>
+        <v>2000015</v>
       </c>
       <c r="P21" t="n">
         <v>99999</v>
@@ -1945,43 +1949,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>coentro-unidade-200930</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Coentro Unidade</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>200930</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>3.79</v>
+        <v>5.99</v>
       </c>
       <c r="F22" t="n">
-        <v>3.79</v>
+        <v>5.99</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1994,21 +1994,21 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2000015</v>
+        <v>2001952</v>
       </c>
       <c r="P22" t="n">
         <v>99999</v>
@@ -2017,48 +2017,48 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-unidade-423513</t>
+          <t>limao-cariorta-1kg-98981</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Limão Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>98981</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.8</v>
+        <v>11.99</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8</v>
+        <v>11.99</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2020-12-07T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -2066,21 +2066,21 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P23" t="n">
         <v>99999</v>
@@ -2089,43 +2089,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>364738</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
+          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>10.99</v>
+        <v>3.97</v>
       </c>
       <c r="F24" t="n">
-        <v>10.99</v>
+        <v>4.89</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2138,66 +2138,66 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>2000015</v>
+        <v>2000043</v>
       </c>
       <c r="P24" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>coentro-unidade-200930</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Coentro Unidade</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>200930</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6.29</v>
+        <v>3.79</v>
       </c>
       <c r="F25" t="n">
-        <v>6.29</v>
+        <v>3.79</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2210,21 +2210,21 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>2000400</v>
+        <v>2000015</v>
       </c>
       <c r="P25" t="n">
         <v>99999</v>
@@ -2233,43 +2233,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
+          <t>abobrinha-italiana-unidade-423513</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1180320</t>
+          <t>423513</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="F26" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2025-07-17T00:00:00Z</t>
+          <t>2020-12-07T00:00:00Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2282,21 +2282,21 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>41057</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>BOMBRIL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>2001389</v>
+        <v>2000015</v>
       </c>
       <c r="P26" t="n">
         <v>99999</v>
@@ -2305,43 +2305,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>couve-manteiga-unidade-201235</t>
+          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Couve Manteiga Unidade</t>
+          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>201235</t>
+          <t>1180320</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
+          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3.79</v>
+        <v>2.79</v>
       </c>
       <c r="F27" t="n">
-        <v>3.79</v>
+        <v>2.79</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2025-07-17T00:00:00Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2354,21 +2354,21 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>BOMBRIL</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>2000015</v>
+        <v>2001389</v>
       </c>
       <c r="P27" t="n">
         <v>99999</v>
@@ -2377,43 +2377,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>milho-em-conserva-quero-lata-200g-476625</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Milho em Conserva Quero Lata 200g</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>476625</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3.69</v>
+        <v>6.29</v>
       </c>
       <c r="F28" t="n">
-        <v>4.99</v>
+        <v>6.29</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2426,21 +2426,21 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>QUERO</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>2001778</v>
+        <v>2000400</v>
       </c>
       <c r="P28" t="n">
         <v>99999</v>
@@ -2449,43 +2449,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
+          <t>couve-manteiga-unidade-201235</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
+          <t>Couve Manteiga Unidade</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>429392</t>
+          <t>201235</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
+          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4.99</v>
+        <v>3.79</v>
       </c>
       <c r="F29" t="n">
-        <v>5.69</v>
+        <v>3.79</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2498,21 +2498,21 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2000027</v>
+        <v>2000015</v>
       </c>
       <c r="P29" t="n">
         <v>99999</v>
@@ -2521,43 +2521,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>129887</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>12.99</v>
+        <v>10.99</v>
       </c>
       <c r="F30" t="n">
-        <v>12.99</v>
+        <v>10.99</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2570,66 +2570,66 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2001401</v>
+        <v>2000015</v>
       </c>
       <c r="P30" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>espinafre-unidade-200948</t>
+          <t>milho-em-conserva-quero-lata-200g-476625</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Espinafre Unidade</t>
+          <t>Milho em Conserva Quero Lata 200g</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>200948</t>
+          <t>476625</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
+          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3.79</v>
+        <v>3.69</v>
       </c>
       <c r="F31" t="n">
-        <v>3.79</v>
+        <v>4.99</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2642,21 +2642,21 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>QUERO</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>2000015</v>
+        <v>2001778</v>
       </c>
       <c r="P31" t="n">
         <v>99999</v>
@@ -2665,43 +2665,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>desinfetante-banheiro-tira-limo-veja-x-14-sache-400ml-refil-economico-1066404</t>
+          <t>espinafre-unidade-200948</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
+          <t>Espinafre Unidade</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1066404</t>
+          <t>200948</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
+          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>9.99</v>
+        <v>3.79</v>
       </c>
       <c r="F32" t="n">
-        <v>11.99</v>
+        <v>3.79</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2022-08-11T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3927710/VF4qT-qqCUAAAAAAAAOGFQ.jpg?v=638733705155570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2714,21 +2714,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>27159</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>27083</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>VEJA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2000523</v>
+        <v>2000015</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2737,43 +2737,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>alface-crespa-unidade-200875</t>
+          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Alface Crespa Unidade</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>200875</t>
+          <t>429392</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3.79</v>
+        <v>4.99</v>
       </c>
       <c r="F33" t="n">
-        <v>3.79</v>
+        <v>5.69</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2786,67 +2786,71 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2000015</v>
+        <v>2000027</v>
       </c>
       <c r="P33" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-cariorta-1kg-98663</t>
+          <t>desinfetante-banheiro-tira-limo-veja-x-14-sache-400ml-refil-economico-1066404</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Cariorta 1Kg</t>
+          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>98663</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>1066404</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
+        </is>
+      </c>
       <c r="E34" t="n">
-        <v>8.99</v>
+        <v>11.99</v>
       </c>
       <c r="F34" t="n">
-        <v>8.99</v>
+        <v>11.99</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2022-08-11T00:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3927710/VF4qT-qqCUAAAAAAAAOGFQ.jpg?v=638733705155570000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2854,66 +2858,66 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>VEJA</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>2001012</v>
+        <v>2000523</v>
       </c>
       <c r="P34" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sal-refinado-iodado-ita-1kg-117293</t>
+          <t>alface-crespa-unidade-200875</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Alface Crespa Unidade</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>200875</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4.39</v>
+        <v>3.79</v>
       </c>
       <c r="F35" t="n">
-        <v>4.39</v>
+        <v>3.79</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2926,21 +2930,21 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2000066</v>
+        <v>2000015</v>
       </c>
       <c r="P35" t="n">
         <v>99999</v>
@@ -2949,39 +2953,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-congelado-rivelli-bandeja-1kg-1023799</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Congelado Rivelli Bandeja 1kg</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1023799</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>129887</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+        </is>
+      </c>
       <c r="E36" t="n">
-        <v>19.99</v>
+        <v>12.99</v>
       </c>
       <c r="F36" t="n">
-        <v>25.99</v>
+        <v>12.99</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2021-07-30T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038302/VF4qT-qqCUAAAAAAAAKY8g.jpg?v=637792395730970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2994,21 +3002,21 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>21449</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Rivelli</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2004122</v>
+        <v>2001401</v>
       </c>
       <c r="P36" t="n">
         <v>99999</v>
@@ -3017,48 +3025,44 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
+          <t>abobrinha-italiana-cariorta-1kg-98663</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
+          <t>Abobrinha Italiana Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>818640</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
-        </is>
-      </c>
+          <t>98663</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>3.99</v>
+        <v>8.99</v>
       </c>
       <c r="F37" t="n">
-        <v>4.99</v>
+        <v>8.99</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2020-11-26T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -3066,21 +3070,21 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2002038</v>
+        <v>2001012</v>
       </c>
       <c r="P37" t="n">
         <v>99999</v>
@@ -3089,70 +3093,66 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>melao-amarelo-metade-1-3-kg-63606</t>
+          <t>file-de-peito-de-frango-congelado-rivelli-bandeja-1kg-1023799</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Melão Amarelo Metade 1,3kg</t>
+          <t>Filé de Peito de Frango Congelado Rivelli Bandeja 1kg</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>63606</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
-        </is>
-      </c>
+          <t>1023799</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>9.99</v>
+        <v>15.99</v>
       </c>
       <c r="F38" t="n">
-        <v>9.99</v>
+        <v>25.99</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2021-07-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038302/VF4qT-qqCUAAAAAAAAKY8g.jpg?v=637792395730970000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>Rivelli</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>2000015</v>
+        <v>2004122</v>
       </c>
       <c r="P38" t="n">
         <v>99999</v>
@@ -3161,43 +3161,43 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
+          <t>sal-refinado-iodado-ita-1kg-117293</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1105795</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3.99</v>
+        <v>4.39</v>
       </c>
       <c r="F39" t="n">
-        <v>5.99</v>
+        <v>4.39</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2023-07-26T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3210,21 +3210,21 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>2000017</v>
+        <v>2000066</v>
       </c>
       <c r="P39" t="n">
         <v>99999</v>
@@ -3233,43 +3233,43 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
+          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
+          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>981168</t>
+          <t>1105795</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
+          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>30.99</v>
+        <v>3.99</v>
       </c>
       <c r="F40" t="n">
-        <v>32.19</v>
+        <v>5.99</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2020-09-22T00:00:00Z</t>
+          <t>2023-07-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3282,21 +3282,21 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>NEVE</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>2000291</v>
+        <v>2000017</v>
       </c>
       <c r="P40" t="n">
         <v>99999</v>
@@ -3305,43 +3305,43 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>981168</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>29.98</v>
+        <v>30.99</v>
       </c>
       <c r="F41" t="n">
-        <v>37.9</v>
+        <v>32.19</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2020-09-22T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3354,21 +3354,21 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>NEVE</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2001329</v>
+        <v>2000291</v>
       </c>
       <c r="P41" t="n">
         <v>99999</v>
@@ -3377,43 +3377,43 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>818640</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5.99</v>
+        <v>3.99</v>
       </c>
       <c r="F42" t="n">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-11-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3426,21 +3426,21 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2001532</v>
+        <v>2002038</v>
       </c>
       <c r="P42" t="n">
         <v>99999</v>
@@ -3449,70 +3449,70 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>batata-palha-yoki-extra-fina-100g-989843</t>
+          <t>melao-amarelo-metade-1-3-kg-63606</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Batata Palha Yoki Extra Fina 100g</t>
+          <t>Melão Amarelo Metade 1,3kg</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>989843</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Batata Palha Yoki Extra Fina 100g</t>
+          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8.99</v>
+        <v>9.99</v>
       </c>
       <c r="F43" t="n">
-        <v>10.99</v>
+        <v>9.99</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2020-10-30T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>YOKI</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>2001336</v>
+        <v>2000015</v>
       </c>
       <c r="P43" t="n">
         <v>99999</v>
@@ -3521,43 +3521,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>tomate-pelado-italiano-due-lata-400g-5459389</t>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tomate Pelado Italiano Due Lata 400g</t>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5459389</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Due é sua dupla perfeita para criar o verdadeiro sabor italiano!Due o melhor da culinária italiana com ingredientes genuínos, que você só encontra no Zona SulExperimente e surpreenda-se!</t>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>8.369999999999999</v>
+        <v>29.98</v>
       </c>
       <c r="F44" t="n">
-        <v>8.369999999999999</v>
+        <v>37.9</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2025-01-21T00:00:00Z</t>
+          <t>2020-07-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3928345/VF4qT-qqCUAAAAAAAAhGgQ.jpg?v=638736295014200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3570,138 +3570,138 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>39142</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>39069</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>DUE</t>
+          <t>MELITTA</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>2005138</v>
+        <v>2001329</v>
       </c>
       <c r="P44" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>mamao-formosa-metade-cariorta-800g-63584</t>
+          <t>batata-palha-yoki-extra-fina-100g-989843</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mamão Formosa Metade Cariorta 800g</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>63584</t>
+          <t>989843</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>"Por ser rico em fibras o mamão formosa é grande amigo do funcionamento do intestino. A cor alaranjada vem do licopeno que, por ser carotenoide, é antioxidante."</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>7.99</v>
+        <v>8.99</v>
       </c>
       <c r="F45" t="n">
-        <v>7.99</v>
+        <v>10.99</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3095891/VF4qT-qqCUAAAAAAAASvtw.jpg?v=638221188789530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>13749</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>YOKI</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2001012</v>
+        <v>2001336</v>
       </c>
       <c r="P45" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>leite-uht-piracanjuba-integral-1l-865427</t>
+          <t>tomate-pelado-italiano-due-lata-400g-5459389</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Leite Uht Piracanjuba Integral 1L</t>
+          <t>Tomate Pelado Italiano Due Lata 400g</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>865427</t>
+          <t>5459389</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>No café da manhã, em um delicioso lanche da tarde ou até mesmo antes de dormir, o Leite Piracanjuba cumpre bem o seu papel principal: trazer mais sabor para os seus momentos especiais e para as suas receitas. Mais sabor para todos os momentos.</t>
+          <t>Due é sua dupla perfeita para criar o verdadeiro sabor italiano!Due o melhor da culinária italiana com ingredientes genuínos, que você só encontra no Zona SulExperimente e surpreenda-se!</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6.69</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>6.69</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2017-04-12T00:00:00Z</t>
+          <t>2025-01-21T00:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3294485/VF4qT-qqCUAAAAAAAAWbgQ.jpg?v=638412300289570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3928345/VF4qT-qqCUAAAAAAAAhGgQ.jpg?v=638736295014200000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3714,21 +3714,21 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>39142</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>39069</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>DUE</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>2002038</v>
+        <v>2005138</v>
       </c>
       <c r="P46" t="n">
         <v>99999</v>
@@ -3737,70 +3737,70 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>99279</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>59.99</v>
+        <v>5.99</v>
       </c>
       <c r="F47" t="n">
-        <v>59.99</v>
+        <v>6.99</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020-05-27T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>24684</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>2001012</v>
+        <v>2001532</v>
       </c>
       <c r="P47" t="n">
         <v>99999</v>
@@ -3809,33 +3809,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cebola-roxa-400g-38393</t>
+          <t>abobora-japonesa-pedaco-500g-38229</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cebola Roxa 400g</t>
+          <t>Abóbora Japonesa Pedaço 500g</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>38229</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
+          <t>Embalagem com 1 pedaço.</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>7.99</v>
+        <v>4.99</v>
       </c>
       <c r="F48" t="n">
-        <v>7.99</v>
+        <v>4.99</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3096862/VF4qT-qqCUAAAAAAAAS9Tw.jpg?v=638235593168230000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3854,16 +3854,16 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3875,76 +3875,76 @@
         <v>2000015</v>
       </c>
       <c r="P48" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>matte-leao-natural-pet-15l-118214</t>
+          <t>mamao-formosa-metade-cariorta-800g-63584</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Matte Leão Natural Pet 1,5L</t>
+          <t>Mamão Formosa Metade Cariorta 800g</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>118214</t>
+          <t>63584</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Renove seu humor, recicle seu ritmo e siga em frente. Experimente combinar o seu dia com o sabor inconfundível de Matte Leão.Matte Leão é feito com folhas de ervamate selecionadas e tostadas num processo único, especialmente para você.Porção de 200 mL (1 copo) = 68 kcal.</t>
+          <t>"Por ser rico em fibras o mamão formosa é grande amigo do funcionamento do intestino. A cor alaranjada vem do licopeno que, por ser carotenoide, é antioxidante."</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>7.95</v>
+        <v>7.99</v>
       </c>
       <c r="F49" t="n">
-        <v>8.99</v>
+        <v>7.99</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704453/VF4qT-qqCUAAAAAAAAGyOQ.jpg?v=638609291247270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3095891/VF4qT-qqCUAAAAAAAASvtw.jpg?v=638221188789530000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2000010</v>
+        <v>2001012</v>
       </c>
       <c r="P49" t="n">
         <v>99999</v>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,43 +513,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-zero-pet--2-l-429384</t>
+          <t>tomate-italiano-unidade-495212</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Zero PET 2 L</t>
+          <t>Tomate Italiano Unidade</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>429384</t>
+          <t>495212</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>COCA COLA ZERO PET 2L</t>
+          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6.99</v>
+        <v>1.35</v>
       </c>
       <c r="F2" t="n">
-        <v>9.99</v>
+        <v>1.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2020-10-01T22:50:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483406/VF4qT-qqCUAAAAAAAAoaqQ.jpg?v=639052524530730000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -562,21 +562,21 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8832</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>8844</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>2000027</v>
+        <v>2000015</v>
       </c>
       <c r="P2" t="n">
         <v>99999</v>
@@ -585,43 +585,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>alcool-montenegro-46-1-l-780570</t>
+          <t>matte-leao-limao-pet-1-5l-118222</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Álcool Montenegro 46% 1 L</t>
+          <t>Matte Leão Limão Pet 1,5L</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>780570</t>
+          <t>118222</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Álcool Montenegro 46% 1 L</t>
+          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8.789999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="F3" t="n">
-        <v>8.789999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2020-10-06T10:47:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051579/VF4qT-qqCUAAAAAAAAG3pQ.jpg?v=637793390624870000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -634,21 +634,21 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>11598</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MONTENEGRO</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2000527</v>
+        <v>2000010</v>
       </c>
       <c r="P3" t="n">
         <v>99999</v>
@@ -657,43 +657,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tomate-italiano-unidade-495212</t>
+          <t>leite-condensado-moca-lata-395g-1136321</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tomate Italiano Unidade</t>
+          <t>Leite Condensado Moça Lata 395g</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>495212</t>
+          <t>1136321</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>O Tomate Italiano é conhecido por sua polpa firme, formato alongado e sabor equilibrado, sendo a escolha ideal para quem busca qualidade e rendimento na cozinha. Versátil e nutritivo, é perfeito tanto para o consumo in natura quanto para preparações culinárias.Benefícios NutricionaisRico em licopeno, antioxidante que auxilia na proteção das célulasFonte de vitamina C, contribuindo para o fortalecimento da imunidadePossui fibras, que ajudam no bom funcionamento do intestinoBaixo teor calórico, ideal para uma alimentação equilibrada</t>
+          <t>Moça® faz todas as receitas darem certo desde 1921, com seu sabor único e original, tem consistência perfeita, é sem comparação! É leite condensado obtido a partir de leite fresco, puro e integral. É um clássico no preparo de sobremesas, também é uma delícia na colher, na salada de frutas e o que mais você imaginar.</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.7</v>
+        <v>7.95</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7</v>
+        <v>9.99</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>67</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2024-05-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500745/VF4qT-qqCUAAAAAAAASLmg.jpg?v=639071532027200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4531395/VF4qT-qqCUAAAAAAAAojmg.jpg?v=639099179974200000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -706,21 +706,21 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>37022</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>36949</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>2000015</v>
+        <v>2000043</v>
       </c>
       <c r="P4" t="n">
         <v>99999</v>
@@ -729,43 +729,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>matte-leao-limao-pet-1-5l-118222</t>
+          <t>manga-palmer-unidade-5130760</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Matte Leão Limão Pet 1,5L</t>
+          <t>Manga Palmer Unidade</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>118222</t>
+          <t>5130760</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
+          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7.95</v>
+        <v>5.99</v>
       </c>
       <c r="F5" t="n">
-        <v>8.99</v>
+        <v>5.99</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2023-02-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -778,21 +778,21 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>31902</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2000010</v>
+        <v>2000015</v>
       </c>
       <c r="P5" t="n">
         <v>99999</v>
@@ -801,70 +801,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>leite-condensado-moca-lata-395g-1136321</t>
+          <t>mamao-papaia-cariorta-12kg-99007</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Leite Condensado Moça Lata 395g</t>
+          <t>Mamão Papaia Cariorta 1,2kg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1136321</t>
+          <t>99007</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Moça® faz todas as receitas darem certo desde 1921, com seu sabor único e original, tem consistência perfeita, é sem comparação! É leite condensado obtido a partir de leite fresco, puro e integral. É um clássico no preparo de sobremesas, também é uma delícia na colher, na salada de frutas e o que mais você imaginar.</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7.95</v>
+        <v>9.99</v>
       </c>
       <c r="F6" t="n">
         <v>9.99</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-13T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4530894/VF4qT-qqCUAAAAAAAAojYw.jpg?v=639096587928800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>37022</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>36949</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2000043</v>
+        <v>2001012</v>
       </c>
       <c r="P6" t="n">
         <v>99999</v>
@@ -873,43 +873,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
+          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
+          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>370550</t>
+          <t>828025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
+          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>24.99</v>
+        <v>32.98</v>
       </c>
       <c r="F7" t="n">
-        <v>24.99</v>
+        <v>43.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -922,66 +922,66 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>PILAO</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2003319</v>
+        <v>2000070</v>
       </c>
       <c r="P7" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>manga-palmer-unidade-5130760</t>
+          <t>couve-flor-unidade-189111</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Manga Palmer Unidade</t>
+          <t>Couve Flor Unidade</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5130760</t>
+          <t>189111</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
+          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5.99</v>
+        <v>9.59</v>
       </c>
       <c r="F8" t="n">
-        <v>5.99</v>
+        <v>9.99</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2023-02-16T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1017,142 +1017,142 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
+          <t>mucarela-em-fatias-92363</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
+          <t>Muçarela  em Fatias 200g</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>828025</t>
+          <t>92363</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
+          <t>Muçarela em Fatias</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>32.98</v>
+        <v>59.9</v>
       </c>
       <c r="F9" t="n">
-        <v>43.9</v>
+        <v>59.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>PILAO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2000070</v>
+        <v>2000015</v>
       </c>
       <c r="P9" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mamao-papaia-cariorta-12kg-99007</t>
+          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mamão Papaia Cariorta 1,2kg</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>99007</t>
+          <t>140805</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9.99</v>
+        <v>4.19</v>
       </c>
       <c r="F10" t="n">
-        <v>9.99</v>
+        <v>5.29</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-09-25T00:00:00Z</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>SAO LOURENCO</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2001012</v>
+        <v>2000145</v>
       </c>
       <c r="P10" t="n">
         <v>99999</v>
@@ -1161,70 +1161,66 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>couve-flor-unidade-189111</t>
+          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Couve Flor Unidade</t>
+          <t>Pão Francês Panetto  60g Com 4 unidades</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>189111</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
-        </is>
-      </c>
+          <t>96318</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
       <c r="F11" t="n">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2024-01-31T00:00:00Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PANETTO</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2000015</v>
+        <v>2000307</v>
       </c>
       <c r="P11" t="n">
         <v>99999</v>
@@ -1233,43 +1229,43 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mucarela-em-fatias-92363</t>
+          <t>batata-inglesa-cariorta-12kg-98698</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Muçarela  em Fatias 200g</t>
+          <t>Batata Inglesa Cariorta 1,2Kg</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>92363</t>
+          <t>98698</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Muçarela em Fatias</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>59.9</v>
+        <v>7.99</v>
       </c>
       <c r="F12" t="n">
-        <v>59.9</v>
+        <v>7.99</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1278,25 +1274,25 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P12" t="n">
         <v>99999</v>
@@ -1305,43 +1301,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
+          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>140805</t>
+          <t>100510</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4.19</v>
+        <v>2.69</v>
       </c>
       <c r="F13" t="n">
-        <v>5.29</v>
+        <v>2.69</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2020-09-25T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1354,21 +1350,21 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>SAO LOURENCO</t>
+          <t>LIMPOL</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2000145</v>
+        <v>2001413</v>
       </c>
       <c r="P13" t="n">
         <v>99999</v>
@@ -1377,66 +1373,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
+          <t>morango-250g-289612</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pão Francês Panetto  60g Com 4 unidades</t>
+          <t>Morango 250g</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>96318</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>289612</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
+        </is>
+      </c>
       <c r="E14" t="n">
-        <v>24.99</v>
+        <v>10.99</v>
       </c>
       <c r="F14" t="n">
-        <v>24.99</v>
+        <v>10.99</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2024-01-31T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>PANETTO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2000307</v>
+        <v>2000015</v>
       </c>
       <c r="P14" t="n">
         <v>99999</v>
@@ -1445,70 +1445,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>batata-inglesa-cariorta-12kg-98698</t>
+          <t>cheiro-verde-unidade-201049</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Batata Inglesa Cariorta 1,2Kg</t>
+          <t>Cheiro Verde Unidade</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>201049</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7.99</v>
+        <v>2.99</v>
       </c>
       <c r="F15" t="n">
-        <v>7.99</v>
+        <v>3.39</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082670/VF4qT-qqCUAAAAAAAAOOew.jpg?v=637979987993130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P15" t="n">
         <v>99999</v>
@@ -1517,43 +1517,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
+          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
+          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>100510</t>
+          <t>290564</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
+          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.69</v>
+        <v>23.99</v>
       </c>
       <c r="F16" t="n">
-        <v>2.69</v>
+        <v>26.99</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1566,66 +1566,66 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>LIMPOL</t>
+          <t>SADIA</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2001413</v>
+        <v>2000057</v>
       </c>
       <c r="P16" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cheiro-verde-unidade-201049</t>
+          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cheiro Verde Unidade</t>
+          <t>Detergente Para Louças Odd Clear 500ml</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>201049</t>
+          <t>982911</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+          <t>ODD voltou!Alto rendimento , controle de odor.</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3.39</v>
+        <v>2.49</v>
       </c>
       <c r="F17" t="n">
-        <v>3.39</v>
+        <v>2.49</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1638,21 +1638,21 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>LIMPPANO</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2000015</v>
+        <v>2001341</v>
       </c>
       <c r="P17" t="n">
         <v>99999</v>
@@ -1661,48 +1661,48 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>morango-250g-289612</t>
+          <t>limao-cariorta-1kg-98981</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Morango 250g</t>
+          <t>Limão Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>289612</t>
+          <t>98981</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9.99</v>
+        <v>11.99</v>
       </c>
       <c r="F18" t="n">
-        <v>9.99</v>
+        <v>11.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1710,21 +1710,21 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P18" t="n">
         <v>99999</v>
@@ -1733,43 +1733,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
+          <t>uva-preta-sem-semente-500-g-674583</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
+          <t>Uva Preta Sem Semente 500g</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>290564</t>
+          <t>674583</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
+          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>23.99</v>
+        <v>12.49</v>
       </c>
       <c r="F19" t="n">
-        <v>26.99</v>
+        <v>13.99</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1782,56 +1782,52 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>SADIA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2000057</v>
+        <v>2000015</v>
       </c>
       <c r="P19" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Odd Clear 500ml</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>982911</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ODD voltou!Alto rendimento , controle de odor.</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>2.49</v>
+        <v>5.99</v>
       </c>
       <c r="F20" t="n">
-        <v>2.49</v>
+        <v>5.99</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1841,7 +1837,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1854,21 +1850,21 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>LIMPPANO</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2001341</v>
+        <v>2001952</v>
       </c>
       <c r="P20" t="n">
         <v>99999</v>
@@ -1877,43 +1873,43 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>uva-preta-sem-semente-500-g-674583</t>
+          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Uva Preta Sem Semente 500g</t>
+          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>674583</t>
+          <t>364738</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
+          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>13.99</v>
+        <v>3.97</v>
       </c>
       <c r="F21" t="n">
-        <v>13.99</v>
+        <v>4.89</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1926,21 +1922,21 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>2000015</v>
+        <v>2000043</v>
       </c>
       <c r="P21" t="n">
         <v>99999</v>
@@ -1949,39 +1945,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>abobrinha-italiana-unidade-423513</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>423513</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Abobrinha Italiana Unidade</t>
+        </is>
+      </c>
       <c r="E22" t="n">
-        <v>5.99</v>
+        <v>2.8</v>
       </c>
       <c r="F22" t="n">
-        <v>5.99</v>
+        <v>2.8</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-12-07T00:00:00Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1994,21 +1994,21 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2001952</v>
+        <v>2000015</v>
       </c>
       <c r="P22" t="n">
         <v>99999</v>
@@ -2017,48 +2017,48 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>limao-cariorta-1kg-98981</t>
+          <t>coentro-unidade-200930</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Limão Cariorta 1Kg</t>
+          <t>Coentro Unidade</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>98981</t>
+          <t>200930</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>11.99</v>
+        <v>2.99</v>
       </c>
       <c r="F23" t="n">
-        <v>11.99</v>
+        <v>3.79</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -2066,21 +2066,21 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P23" t="n">
         <v>99999</v>
@@ -2089,43 +2089,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>364738</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.97</v>
+        <v>6.29</v>
       </c>
       <c r="F24" t="n">
-        <v>4.89</v>
+        <v>6.29</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2138,21 +2138,21 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>2000043</v>
+        <v>2000400</v>
       </c>
       <c r="P24" t="n">
         <v>99999</v>
@@ -2161,43 +2161,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>coentro-unidade-200930</t>
+          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Coentro Unidade</t>
+          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>200930</t>
+          <t>1180320</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
+          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3.79</v>
+        <v>2.79</v>
       </c>
       <c r="F25" t="n">
-        <v>3.79</v>
+        <v>2.79</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2025-07-17T00:00:00Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2210,21 +2210,21 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>BOMBRIL</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>2000015</v>
+        <v>2001389</v>
       </c>
       <c r="P25" t="n">
         <v>99999</v>
@@ -2233,43 +2233,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-unidade-423513</t>
+          <t>couve-manteiga-unidade-201235</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Couve Manteiga Unidade</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>201235</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="F26" t="n">
-        <v>2.8</v>
+        <v>3.79</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2020-12-07T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2305,43 +2305,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1180320</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.79</v>
+        <v>9.99</v>
       </c>
       <c r="F27" t="n">
-        <v>2.79</v>
+        <v>10.99</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2025-07-17T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2354,66 +2354,66 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>41057</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>BOMBRIL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>2001389</v>
+        <v>2000015</v>
       </c>
       <c r="P27" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>espinafre-unidade-200948</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Espinafre Unidade</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>200948</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6.29</v>
+        <v>2.99</v>
       </c>
       <c r="F28" t="n">
-        <v>6.29</v>
+        <v>3.79</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2426,21 +2426,21 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>2000400</v>
+        <v>2000015</v>
       </c>
       <c r="P28" t="n">
         <v>99999</v>
@@ -2449,43 +2449,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>couve-manteiga-unidade-201235</t>
+          <t>milho-em-conserva-quero-lata-200g-476625</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Couve Manteiga Unidade</t>
+          <t>Milho em Conserva Quero Lata 200g</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>201235</t>
+          <t>476625</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
+          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3.79</v>
+        <v>3.69</v>
       </c>
       <c r="F29" t="n">
-        <v>3.79</v>
+        <v>4.99</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2498,21 +2498,21 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>QUERO</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2000015</v>
+        <v>2001778</v>
       </c>
       <c r="P29" t="n">
         <v>99999</v>
@@ -2521,43 +2521,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>desinfetante-banheiro-tira-limo-veja-x-14-sache-400ml-refil-economico-1066404</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>1066404</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
+          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>10.99</v>
+        <v>9.99</v>
       </c>
       <c r="F30" t="n">
-        <v>10.99</v>
+        <v>11.99</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2022-08-11T00:00:00Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3927710/VF4qT-qqCUAAAAAAAAOGFQ.jpg?v=638733705155570000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2570,66 +2570,62 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>VEJA</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2000015</v>
+        <v>2000523</v>
       </c>
       <c r="P30" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>milho-em-conserva-quero-lata-200g-476625</t>
+          <t>file-de-peito-de-frango-congelado-rivelli-bandeja-1kg-1023799</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Milho em Conserva Quero Lata 200g</t>
+          <t>Filé de Peito de Frango Congelado Rivelli Bandeja 1kg</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>476625</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
-        </is>
-      </c>
+          <t>1023799</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>3.69</v>
+        <v>15.99</v>
       </c>
       <c r="F31" t="n">
-        <v>4.99</v>
+        <v>25.99</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2021-07-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038302/VF4qT-qqCUAAAAAAAAKY8g.jpg?v=637792395730970000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2642,21 +2638,21 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>QUERO</t>
+          <t>Rivelli</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>2001778</v>
+        <v>2004122</v>
       </c>
       <c r="P31" t="n">
         <v>99999</v>
@@ -2665,43 +2661,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>espinafre-unidade-200948</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Espinafre Unidade</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>200948</t>
+          <t>129887</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
+          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3.79</v>
+        <v>12.99</v>
       </c>
       <c r="F32" t="n">
-        <v>3.79</v>
+        <v>12.99</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2714,21 +2710,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2000015</v>
+        <v>2001401</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2737,48 +2733,44 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
+          <t>abobrinha-italiana-cariorta-1kg-98663</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
+          <t>Abobrinha Italiana Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>429392</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
-        </is>
-      </c>
+          <t>98663</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>4.99</v>
+        <v>8.99</v>
       </c>
       <c r="F33" t="n">
-        <v>5.69</v>
+        <v>8.99</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2786,21 +2778,21 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>COCA COLA</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2000027</v>
+        <v>2001012</v>
       </c>
       <c r="P33" t="n">
         <v>100</v>
@@ -2809,43 +2801,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>desinfetante-banheiro-tira-limo-veja-x-14-sache-400ml-refil-economico-1066404</t>
+          <t>alface-crespa-unidade-200875</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
+          <t>Alface Crespa Unidade</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1066404</t>
+          <t>200875</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
+          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>11.99</v>
+        <v>2.99</v>
       </c>
       <c r="F34" t="n">
-        <v>11.99</v>
+        <v>3.79</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2022-08-11T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3927710/VF4qT-qqCUAAAAAAAAOGFQ.jpg?v=638733705155570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2858,21 +2850,21 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>27159</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>27083</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>VEJA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>2000523</v>
+        <v>2000015</v>
       </c>
       <c r="P34" t="n">
         <v>99999</v>
@@ -2881,43 +2873,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>alface-crespa-unidade-200875</t>
+          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Alface Crespa Unidade</t>
+          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>200875</t>
+          <t>981168</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
+          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3.79</v>
+        <v>30.99</v>
       </c>
       <c r="F35" t="n">
-        <v>3.79</v>
+        <v>32.19</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-22T00:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2930,21 +2922,21 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>NEVE</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2000015</v>
+        <v>2000291</v>
       </c>
       <c r="P35" t="n">
         <v>99999</v>
@@ -2953,43 +2945,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
+          <t>sal-refinado-iodado-ita-1kg-117293</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>129887</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>12.99</v>
+        <v>4.39</v>
       </c>
       <c r="F36" t="n">
-        <v>12.99</v>
+        <v>4.39</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3002,21 +2994,21 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2001401</v>
+        <v>2000066</v>
       </c>
       <c r="P36" t="n">
         <v>99999</v>
@@ -3025,44 +3017,48 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-cariorta-1kg-98663</t>
+          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Cariorta 1Kg</t>
+          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>98663</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>818640</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
+        </is>
+      </c>
       <c r="E37" t="n">
-        <v>8.99</v>
+        <v>3.99</v>
       </c>
       <c r="F37" t="n">
-        <v>8.99</v>
+        <v>4.99</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-11-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -3070,21 +3066,21 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2001012</v>
+        <v>2002038</v>
       </c>
       <c r="P37" t="n">
         <v>99999</v>
@@ -3093,39 +3089,43 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-congelado-rivelli-bandeja-1kg-1023799</t>
+          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Congelado Rivelli Bandeja 1kg</t>
+          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1023799</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>1105795</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
+        </is>
+      </c>
       <c r="E38" t="n">
-        <v>15.99</v>
+        <v>3.99</v>
       </c>
       <c r="F38" t="n">
-        <v>25.99</v>
+        <v>5.99</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2021-07-30T00:00:00Z</t>
+          <t>2023-07-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038302/VF4qT-qqCUAAAAAAAAKY8g.jpg?v=637792395730970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3138,21 +3138,21 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>21449</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Rivelli</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>2004122</v>
+        <v>2000017</v>
       </c>
       <c r="P38" t="n">
         <v>99999</v>
@@ -3161,70 +3161,70 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sal-refinado-iodado-ita-1kg-117293</t>
+          <t>melao-amarelo-metade-1-3-kg-63606</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Melão Amarelo Metade 1,3kg</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4.39</v>
+        <v>8.99</v>
       </c>
       <c r="F39" t="n">
-        <v>4.39</v>
+        <v>9.99</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>2000066</v>
+        <v>2000015</v>
       </c>
       <c r="P39" t="n">
         <v>99999</v>
@@ -3233,43 +3233,43 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1105795</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3.99</v>
+        <v>29.98</v>
       </c>
       <c r="F40" t="n">
-        <v>5.99</v>
+        <v>37.9</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2023-07-26T00:00:00Z</t>
+          <t>2020-07-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3282,21 +3282,21 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>MELITTA</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>2000017</v>
+        <v>2001329</v>
       </c>
       <c r="P40" t="n">
         <v>99999</v>
@@ -3305,43 +3305,43 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
+          <t>batata-palha-yoki-extra-fina-100g-989843</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>981168</t>
+          <t>989843</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>30.99</v>
+        <v>8.99</v>
       </c>
       <c r="F41" t="n">
-        <v>32.19</v>
+        <v>10.99</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2020-09-22T00:00:00Z</t>
+          <t>2020-10-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3354,66 +3354,66 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>13749</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>NEVE</t>
+          <t>YOKI</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2000291</v>
+        <v>2001336</v>
       </c>
       <c r="P41" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>818640</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3.99</v>
+        <v>5.99</v>
       </c>
       <c r="F42" t="n">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2020-11-26T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3426,21 +3426,21 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2002038</v>
+        <v>2001532</v>
       </c>
       <c r="P42" t="n">
         <v>99999</v>
@@ -3449,70 +3449,70 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>melao-amarelo-metade-1-3-kg-63606</t>
+          <t>tomate-pelado-italiano-due-lata-400g-5459389</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Melão Amarelo Metade 1,3kg</t>
+          <t>Tomate Pelado Italiano Due Lata 400g</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>5459389</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
+          <t>Due é sua dupla perfeita para criar o verdadeiro sabor italiano!Due o melhor da culinária italiana com ingredientes genuínos, que você só encontra no Zona SulExperimente e surpreenda-se!</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>9.99</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>9.99</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2025-01-21T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3928345/VF4qT-qqCUAAAAAAAAhGgQ.jpg?v=638736295014200000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>39142</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>39069</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>DUE</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>2000015</v>
+        <v>2005138</v>
       </c>
       <c r="P43" t="n">
         <v>99999</v>
@@ -3521,214 +3521,214 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>abobora-japonesa-pedaco-500g-38229</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Abóbora Japonesa Pedaço 500g</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>38229</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+          <t>Embalagem com 1 pedaço.</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>29.98</v>
+        <v>2.95</v>
       </c>
       <c r="F44" t="n">
-        <v>37.9</v>
+        <v>4.99</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3096862/VF4qT-qqCUAAAAAAAAS9Tw.jpg?v=638235593168230000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>2001329</v>
+        <v>2000015</v>
       </c>
       <c r="P44" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>batata-palha-yoki-extra-fina-100g-989843</t>
+          <t>mamao-formosa-metade-cariorta-800g-63584</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Batata Palha Yoki Extra Fina 100g</t>
+          <t>Mamão Formosa Metade Cariorta 800g</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>989843</t>
+          <t>63584</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Batata Palha Yoki Extra Fina 100g</t>
+          <t>"Por ser rico em fibras o mamão formosa é grande amigo do funcionamento do intestino. A cor alaranjada vem do licopeno que, por ser carotenoide, é antioxidante."</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>8.99</v>
+        <v>6.99</v>
       </c>
       <c r="F45" t="n">
-        <v>10.99</v>
+        <v>7.99</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2020-10-30T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3095891/VF4qT-qqCUAAAAAAAASvtw.jpg?v=638221188789530000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>YOKI</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2001336</v>
+        <v>2001012</v>
       </c>
       <c r="P45" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>tomate-pelado-italiano-due-lata-400g-5459389</t>
+          <t>queijo-mucarela-em-fatias-bandeja-100g-38954</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tomate Pelado Italiano Due Lata 400g</t>
+          <t>Queijo Muçarela Em Fatias Bandeja 100g</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5459389</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Due é sua dupla perfeita para criar o verdadeiro sabor italiano!Due o melhor da culinária italiana com ingredientes genuínos, que você só encontra no Zona SulExperimente e surpreenda-se!</t>
+          <t>Queijo Muçarela Em Fatias Bandeja 100g</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>8.369999999999999</v>
+        <v>49.9</v>
       </c>
       <c r="F46" t="n">
-        <v>8.369999999999999</v>
+        <v>59.9</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>325</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2025-01-21T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3928345/VF4qT-qqCUAAAAAAAAhGgQ.jpg?v=638736295014200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3049627/VF4qT-qqCUAAAAAAAAHtlQ.jpg?v=637793305547330000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>39142</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>39069</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>DUE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>2005138</v>
+        <v>2000015</v>
       </c>
       <c r="P46" t="n">
         <v>99999</v>
@@ -3737,70 +3737,70 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>99279</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5.99</v>
+        <v>59.99</v>
       </c>
       <c r="F47" t="n">
-        <v>6.99</v>
+        <v>59.99</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-05-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>2001532</v>
+        <v>2001012</v>
       </c>
       <c r="P47" t="n">
         <v>99999</v>
@@ -3809,94 +3809,94 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>abobora-japonesa-pedaco-500g-38229</t>
+          <t>pao-de-queijo-forno-de-minas-tradicional--400-g-456110</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Abóbora Japonesa Pedaço 500g</t>
+          <t>Pão De Queijo Forno De Minas Tradicional 400g</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>38229</t>
+          <t>456110</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Embalagem com 1 pedaço.</t>
+          <t>Pão De Queijo Forno De Minas Tradicional 400g</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4.99</v>
+        <v>14.99</v>
       </c>
       <c r="F48" t="n">
-        <v>4.99</v>
+        <v>21.99</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3096862/VF4qT-qqCUAAAAAAAAS9Tw.jpg?v=638235593168230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041185/VF4qT-qqCUAAAAAAAAHIag.jpg?v=637792557833470000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>13564</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>FORNO MINAS</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>2000015</v>
+        <v>2001500</v>
       </c>
       <c r="P48" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>mamao-formosa-metade-cariorta-800g-63584</t>
+          <t>cebola-roxa-400g-38393</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mamão Formosa Metade Cariorta 800g</t>
+          <t>Cebola Roxa 400g</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>63584</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"Por ser rico em fibras o mamão formosa é grande amigo do funcionamento do intestino. A cor alaranjada vem do licopeno que, por ser carotenoide, é antioxidante."</t>
+          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3095891/VF4qT-qqCUAAAAAAAASvtw.jpg?v=638221188789530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3926,28 +3926,172 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P49" t="n">
-        <v>99999</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>alcool-montenegro-46-1-l-780570</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Álcool Montenegro 46% 1 L</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>780570</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Álcool Montenegro 46% 1 L</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="F50" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2020-10-06T10:47:00Z</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051579/VF4qT-qqCUAAAAAAAAG3pQ.jpg?v=637793390624870000</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>11598</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>11621</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>MONTENEGRO</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>2000527</v>
+      </c>
+      <c r="P50" t="n">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>370550</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="F51" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2020-09-27T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>6939</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>6957</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>HAPPY EGGS</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>2003319</v>
+      </c>
+      <c r="P51" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7.95</v>
+        <v>8.99</v>
       </c>
       <c r="F3" t="n">
         <v>8.99</v>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7.95</v>
+        <v>9.99</v>
       </c>
       <c r="F4" t="n">
         <v>9.99</v>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5.99</v>
+        <v>5.39</v>
       </c>
       <c r="F5" t="n">
         <v>5.99</v>
@@ -873,43 +873,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
+          <t>couve-flor-unidade-189111</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
+          <t>Couve Flor Unidade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>828025</t>
+          <t>189111</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
+          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>32.98</v>
+        <v>9.59</v>
       </c>
       <c r="F7" t="n">
-        <v>43.9</v>
+        <v>9.99</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -922,21 +922,21 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>PILAO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2000070</v>
+        <v>2000015</v>
       </c>
       <c r="P7" t="n">
         <v>99999</v>
@@ -945,43 +945,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>couve-flor-unidade-189111</t>
+          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Couve Flor Unidade</t>
+          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>189111</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
+          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9.59</v>
+        <v>24.99</v>
       </c>
       <c r="F8" t="n">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -994,93 +994,93 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2000015</v>
+        <v>2003319</v>
       </c>
       <c r="P8" t="n">
-        <v>99999</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mucarela-em-fatias-92363</t>
+          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Muçarela  em Fatias 200g</t>
+          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>92363</t>
+          <t>828025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Muçarela em Fatias</t>
+          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>59.9</v>
+        <v>43.9</v>
       </c>
       <c r="F9" t="n">
-        <v>59.9</v>
+        <v>43.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PILAO</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2000015</v>
+        <v>2000070</v>
       </c>
       <c r="P9" t="n">
         <v>99999</v>
@@ -1089,138 +1089,142 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
+          <t>mucarela-em-fatias-92363</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Muçarela  em Fatias 200g</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>140805</t>
+          <t>92363</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Muçarela em Fatias</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.19</v>
+        <v>59.9</v>
       </c>
       <c r="F10" t="n">
-        <v>5.29</v>
+        <v>59.9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2020-09-25T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>SAO LOURENCO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2000145</v>
+        <v>2000015</v>
       </c>
       <c r="P10" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
+          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pão Francês Panetto  60g Com 4 unidades</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>96318</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>140805</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+        </is>
+      </c>
       <c r="E11" t="n">
-        <v>24.99</v>
+        <v>5.29</v>
       </c>
       <c r="F11" t="n">
-        <v>24.99</v>
+        <v>5.29</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2024-01-31T00:00:00Z</t>
+          <t>2020-09-25T00:00:00Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>PANETTO</t>
+          <t>SAO LOURENCO</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2000307</v>
+        <v>2000145</v>
       </c>
       <c r="P11" t="n">
         <v>99999</v>
@@ -1301,70 +1305,66 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
+          <t>pao-frances-panetto-60g-com-4-unidades-96318</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
+          <t>Pão Francês Panetto  60g Com 4 unidades</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>100510</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
-        </is>
-      </c>
+          <t>96318</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>2.69</v>
+        <v>24.99</v>
       </c>
       <c r="F13" t="n">
-        <v>2.69</v>
+        <v>24.99</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2024-01-31T00:00:00Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3307700/VF4qT-qqCUAAAAAAAAWnXQ.jpg?v=638932898013670000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>LIMPOL</t>
+          <t>PANETTO</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2001413</v>
+        <v>2000307</v>
       </c>
       <c r="P13" t="n">
         <v>99999</v>
@@ -1373,43 +1373,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>morango-250g-289612</t>
+          <t>cheiro-verde-unidade-201049</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Morango 250g</t>
+          <t>Cheiro Verde Unidade</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>289612</t>
+          <t>201049</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
+          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>10.99</v>
+        <v>2.99</v>
       </c>
       <c r="F14" t="n">
-        <v>10.99</v>
+        <v>3.39</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1445,43 +1445,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cheiro-verde-unidade-201049</t>
+          <t>morango-250g-289612</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cheiro Verde Unidade</t>
+          <t>Morango 250g</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>201049</t>
+          <t>289612</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2.99</v>
+        <v>10.99</v>
       </c>
       <c r="F15" t="n">
-        <v>3.39</v>
+        <v>10.99</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1517,43 +1517,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
+          <t>detergente-para-loucas-biodegradavel-limpol-neutro-500-ml-100510</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
+          <t>Detergente Para Louças Biodegradável Limpol Neutro 500ml</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>290564</t>
+          <t>100510</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
+          <t>O Lava-Louças Limpol é eficiente no poder da limpeza, remoção da gordura e sujeiras e no combate aos maus odores indesejados da cozinha. Sua fórmula é dermatologicamente testada e contém glicerina, tornando-a mais suave para as mãos.</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>23.99</v>
+        <v>2.09</v>
       </c>
       <c r="F16" t="n">
-        <v>26.99</v>
+        <v>2.69</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3269221/12054_1.jpg?v=638386029717470000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1566,66 +1566,66 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>SADIA</t>
+          <t>LIMPOL</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2000057</v>
+        <v>2001413</v>
       </c>
       <c r="P16" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
+          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Odd Clear 500ml</t>
+          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>982911</t>
+          <t>290564</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ODD voltou!Alto rendimento , controle de odor.</t>
+          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.49</v>
+        <v>26.99</v>
       </c>
       <c r="F17" t="n">
-        <v>2.49</v>
+        <v>26.99</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1638,71 +1638,71 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>LIMPPANO</t>
+          <t>SADIA</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2001341</v>
+        <v>2000057</v>
       </c>
       <c r="P17" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>limao-cariorta-1kg-98981</t>
+          <t>uva-preta-sem-semente-500-g-674583</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Limão Cariorta 1Kg</t>
+          <t>Uva Preta Sem Semente 500g</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>98981</t>
+          <t>674583</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.99</v>
+        <v>12.49</v>
       </c>
       <c r="F18" t="n">
-        <v>11.99</v>
+        <v>13.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1710,21 +1710,21 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P18" t="n">
         <v>99999</v>
@@ -1733,48 +1733,48 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>uva-preta-sem-semente-500-g-674583</t>
+          <t>limao-cariorta-1kg-98981</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Uva Preta Sem Semente 500g</t>
+          <t>Limão Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>674583</t>
+          <t>98981</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>12.49</v>
+        <v>11.99</v>
       </c>
       <c r="F19" t="n">
-        <v>13.99</v>
+        <v>11.99</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1782,21 +1782,21 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P19" t="n">
         <v>99999</v>
@@ -1805,29 +1805,33 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Detergente Para Louças Odd Clear 500ml</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>982911</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ODD voltou!Alto rendimento , controle de odor.</t>
+        </is>
+      </c>
       <c r="E20" t="n">
-        <v>5.99</v>
+        <v>2.49</v>
       </c>
       <c r="F20" t="n">
-        <v>5.99</v>
+        <v>2.49</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1837,7 +1841,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1850,21 +1854,21 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>LIMPPANO</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2001952</v>
+        <v>2001341</v>
       </c>
       <c r="P20" t="n">
         <v>99999</v>
@@ -1873,43 +1877,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>364738</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>3.97</v>
+        <v>5.99</v>
       </c>
       <c r="F21" t="n">
-        <v>4.89</v>
+        <v>5.99</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1922,21 +1922,21 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>2000043</v>
+        <v>2001952</v>
       </c>
       <c r="P21" t="n">
         <v>99999</v>
@@ -1945,43 +1945,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-unidade-423513</t>
+          <t>iogurte-integral-nestle-natural-copo-170-g-364738</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Iogurte Integral Nestlé Natural Copo 170g</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>364738</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Descubra a pureza e a qualidade do Iogurte Natural Nestlé® Integral. Este iogurte foi pensado em todos que buscam uma experiência simples e natural. Ele é feito apenas com dois ingredientes: leite e fermento, sendo uma opção para quem procura uma alimentação mais equilibrada, livre de produtos que contém diversos ingredientes. Com o Iogurte Natural Integral você pode aproveitar os benefícios do leite e do fermento de forma pura e autêntica. A versatilidade deste iogurte é outro diferencial, pois permite que seja usado conforme o gosto de cada um. Pode ser consumido puro, servido com frutas, adicionado a smoothies ou utilizado em receitas. Linha Nestlé® é tradição e qualidade!</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2.8</v>
+        <v>4.89</v>
       </c>
       <c r="F22" t="n">
-        <v>2.8</v>
+        <v>4.89</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020-12-07T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3959333/VF4qT-qqCUAAAAAAAAUrxw.jpg?v=638755307288170000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1994,21 +1994,21 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2000015</v>
+        <v>2000043</v>
       </c>
       <c r="P22" t="n">
         <v>99999</v>
@@ -2017,43 +2017,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>coentro-unidade-200930</t>
+          <t>abobrinha-italiana-unidade-423513</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Coentro Unidade</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>200930</t>
+          <t>423513</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="F23" t="n">
-        <v>3.79</v>
+        <v>2.8</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-12-07T00:00:00Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2089,43 +2089,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>coentro-unidade-200930</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Coentro Unidade</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>200930</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6.29</v>
+        <v>2.99</v>
       </c>
       <c r="F24" t="n">
-        <v>6.29</v>
+        <v>3.79</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2138,21 +2138,21 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>2000400</v>
+        <v>2000015</v>
       </c>
       <c r="P24" t="n">
         <v>99999</v>
@@ -2161,43 +2161,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
+          <t>couve-manteiga-unidade-201235</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
+          <t>Couve Manteiga Unidade</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1180320</t>
+          <t>201235</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
+          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.79</v>
+        <v>2.99</v>
       </c>
       <c r="F25" t="n">
-        <v>2.79</v>
+        <v>3.79</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2025-07-17T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2210,21 +2210,21 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>41057</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>BOMBRIL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>2001389</v>
+        <v>2000015</v>
       </c>
       <c r="P25" t="n">
         <v>99999</v>
@@ -2233,43 +2233,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>couve-manteiga-unidade-201235</t>
+          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Couve Manteiga Unidade</t>
+          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>201235</t>
+          <t>1180320</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
+          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.99</v>
+        <v>2.79</v>
       </c>
       <c r="F26" t="n">
-        <v>3.79</v>
+        <v>2.79</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2025-07-17T00:00:00Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2282,21 +2282,21 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>BOMBRIL</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>2000015</v>
+        <v>2001389</v>
       </c>
       <c r="P26" t="n">
         <v>99999</v>
@@ -2305,43 +2305,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>9.99</v>
+        <v>6.29</v>
       </c>
       <c r="F27" t="n">
-        <v>10.99</v>
+        <v>6.29</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2354,66 +2354,66 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>2000015</v>
+        <v>2000400</v>
       </c>
       <c r="P27" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>espinafre-unidade-200948</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Espinafre Unidade</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>200948</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.99</v>
+        <v>9.99</v>
       </c>
       <c r="F28" t="n">
-        <v>3.79</v>
+        <v>10.99</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2449,43 +2449,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>milho-em-conserva-quero-lata-200g-476625</t>
+          <t>espinafre-unidade-200948</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Milho em Conserva Quero Lata 200g</t>
+          <t>Espinafre Unidade</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>476625</t>
+          <t>200948</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
+          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3.69</v>
+        <v>2.99</v>
       </c>
       <c r="F29" t="n">
-        <v>4.99</v>
+        <v>3.79</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2498,21 +2498,21 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>QUERO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2001778</v>
+        <v>2000015</v>
       </c>
       <c r="P29" t="n">
         <v>99999</v>
@@ -2521,43 +2521,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>desinfetante-banheiro-tira-limo-veja-x-14-sache-400ml-refil-economico-1066404</t>
+          <t>milho-em-conserva-quero-lata-200g-476625</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
+          <t>Milho em Conserva Quero Lata 200g</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1066404</t>
+          <t>476625</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
+          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>9.99</v>
+        <v>4.99</v>
       </c>
       <c r="F30" t="n">
-        <v>11.99</v>
+        <v>4.99</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2022-08-11T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3927710/VF4qT-qqCUAAAAAAAAOGFQ.jpg?v=638733705155570000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2570,21 +2570,21 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>27159</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>27083</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>VEJA</t>
+          <t>QUERO</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2000523</v>
+        <v>2001778</v>
       </c>
       <c r="P30" t="n">
         <v>99999</v>
@@ -2593,39 +2593,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-congelado-rivelli-bandeja-1kg-1023799</t>
+          <t>desinfetante-banheiro-tira-limo-veja-x-14-sache-400ml-refil-economico-1066404</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Congelado Rivelli Bandeja 1kg</t>
+          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1023799</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>1066404</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Desinfetante Banheiro Tira-Limo Veja X-14 Sachê 400ml Refil Econômico</t>
+        </is>
+      </c>
       <c r="E31" t="n">
-        <v>15.99</v>
+        <v>9.99</v>
       </c>
       <c r="F31" t="n">
-        <v>25.99</v>
+        <v>11.99</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2021-07-30T00:00:00Z</t>
+          <t>2022-08-11T00:00:00Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038302/VF4qT-qqCUAAAAAAAAKY8g.jpg?v=637792395730970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3927710/VF4qT-qqCUAAAAAAAAOGFQ.jpg?v=638733705155570000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2638,21 +2642,21 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>21449</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Rivelli</t>
+          <t>VEJA</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>2004122</v>
+        <v>2000523</v>
       </c>
       <c r="P31" t="n">
         <v>99999</v>
@@ -2661,43 +2665,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
+          <t>alface-crespa-unidade-200875</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
+          <t>Alface Crespa Unidade</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>129887</t>
+          <t>200875</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>12.99</v>
+        <v>2.99</v>
       </c>
       <c r="F32" t="n">
-        <v>12.99</v>
+        <v>3.79</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2710,21 +2714,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2001401</v>
+        <v>2000015</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2733,44 +2737,48 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-cariorta-1kg-98663</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Cariorta 1Kg</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>98663</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>129887</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+        </is>
+      </c>
       <c r="E33" t="n">
-        <v>8.99</v>
+        <v>12.99</v>
       </c>
       <c r="F33" t="n">
-        <v>8.99</v>
+        <v>12.99</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2778,71 +2786,67 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2001012</v>
+        <v>2001401</v>
       </c>
       <c r="P33" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>alface-crespa-unidade-200875</t>
+          <t>abobrinha-italiana-cariorta-1kg-98663</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Alface Crespa Unidade</t>
+          <t>Abobrinha Italiana Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>200875</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
-        </is>
-      </c>
+          <t>98663</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>2.99</v>
+        <v>8.99</v>
       </c>
       <c r="F34" t="n">
-        <v>3.79</v>
+        <v>8.99</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2850,66 +2854,66 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>2000015</v>
+        <v>2001012</v>
       </c>
       <c r="P34" t="n">
-        <v>99999</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
+          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
+          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>981168</t>
+          <t>818640</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
+          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>30.99</v>
+        <v>4.99</v>
       </c>
       <c r="F35" t="n">
-        <v>32.19</v>
+        <v>4.99</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-09-22T00:00:00Z</t>
+          <t>2020-11-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2922,21 +2926,21 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>NEVE</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2000291</v>
+        <v>2002038</v>
       </c>
       <c r="P35" t="n">
         <v>99999</v>
@@ -2945,43 +2949,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>sal-refinado-iodado-ita-1kg-117293</t>
+          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>981168</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4.39</v>
+        <v>32.19</v>
       </c>
       <c r="F36" t="n">
-        <v>4.39</v>
+        <v>32.19</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-22T00:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2994,66 +2998,66 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>NEVE</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2000066</v>
+        <v>2000291</v>
       </c>
       <c r="P36" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
+          <t>sal-refinado-iodado-ita-1kg-117293</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>818640</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3.99</v>
+        <v>4.39</v>
       </c>
       <c r="F37" t="n">
-        <v>4.99</v>
+        <v>4.39</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2020-11-26T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3066,66 +3070,66 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2002038</v>
+        <v>2000066</v>
       </c>
       <c r="P37" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1105795</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3.99</v>
+        <v>29.98</v>
       </c>
       <c r="F38" t="n">
-        <v>5.99</v>
+        <v>37.9</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2023-07-26T00:00:00Z</t>
+          <t>2020-07-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3138,21 +3142,21 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>PIRAQUE</t>
+          <t>MELITTA</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>2000017</v>
+        <v>2001329</v>
       </c>
       <c r="P38" t="n">
         <v>99999</v>
@@ -3233,43 +3237,43 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>batata-palha-yoki-extra-fina-100g-989843</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>989843</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>29.98</v>
+        <v>10.99</v>
       </c>
       <c r="F40" t="n">
-        <v>37.9</v>
+        <v>10.99</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2020-10-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3282,21 +3286,21 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>13749</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>YOKI</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>2001329</v>
+        <v>2001336</v>
       </c>
       <c r="P40" t="n">
         <v>99999</v>
@@ -3305,43 +3309,43 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>batata-palha-yoki-extra-fina-100g-989843</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Batata Palha Yoki Extra Fina 100g</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>989843</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Batata Palha Yoki Extra Fina 100g</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>8.99</v>
+        <v>6.99</v>
       </c>
       <c r="F41" t="n">
-        <v>10.99</v>
+        <v>6.99</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2020-10-30T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3354,93 +3358,93 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>YOKI</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2001336</v>
+        <v>2001532</v>
       </c>
       <c r="P41" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>abobora-japonesa-pedaco-500g-38229</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Abóbora Japonesa Pedaço 500g</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>38229</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>Embalagem com 1 pedaço.</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5.99</v>
+        <v>2.95</v>
       </c>
       <c r="F42" t="n">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3096862/VF4qT-qqCUAAAAAAAAS9Tw.jpg?v=638235593168230000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2001532</v>
+        <v>2000015</v>
       </c>
       <c r="P42" t="n">
         <v>99999</v>
@@ -3521,70 +3525,70 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>abobora-japonesa-pedaco-500g-38229</t>
+          <t>ovos-vermelhos-mantiqueira-happy-eggs-com-10-unidades-5106753</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Abóbora Japonesa Pedaço 500g</t>
+          <t>Ovos Vermelhos Mantiqueira Happy Eggs com 10 Unidades</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>38229</t>
+          <t>5106753</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Embalagem com 1 pedaço.</t>
+          <t>Produzidos por galinhas criadas livres de gaiolas. Garantia de Bem-Estar Animal. Ovos Vermelhos Tipo Grande Categoria A. Embalagem com 10 unidades.</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2.95</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>4.99</v>
+        <v>12.99</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2021-01-11T00:00:00Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3096862/VF4qT-qqCUAAAAAAAAS9Tw.jpg?v=638235593168230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4222023/VF4qT-qqCUAAAAAAAAStHA.jpg?v=638894405636230000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>2000015</v>
+        <v>2003319</v>
       </c>
       <c r="P44" t="n">
         <v>99999</v>
@@ -3684,7 +3688,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>49.9</v>
+        <v>59.9</v>
       </c>
       <c r="F46" t="n">
         <v>59.9</v>
@@ -3737,142 +3741,142 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
+          <t>pao-de-queijo-forno-de-minas-tradicional--400-g-456110</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
+          <t>Pão De Queijo Forno De Minas Tradicional 400g</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>99279</t>
+          <t>456110</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
+          <t>Pão De Queijo Forno De Minas Tradicional 400g</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>59.99</v>
+        <v>14.99</v>
       </c>
       <c r="F47" t="n">
-        <v>59.99</v>
+        <v>21.99</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020-05-27T00:00:00Z</t>
+          <t>2020-10-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041185/VF4qT-qqCUAAAAAAAAHIag.jpg?v=637792557833470000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>24684</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>13564</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>FORNO MINAS</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>2001012</v>
+        <v>2001500</v>
       </c>
       <c r="P47" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pao-de-queijo-forno-de-minas-tradicional--400-g-456110</t>
+          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pão De Queijo Forno De Minas Tradicional 400g</t>
+          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>456110</t>
+          <t>99279</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Pão De Queijo Forno De Minas Tradicional 400g</t>
+          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>14.99</v>
+        <v>59.99</v>
       </c>
       <c r="F48" t="n">
-        <v>21.99</v>
+        <v>59.99</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2020-10-20T00:00:00Z</t>
+          <t>2020-05-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041185/VF4qT-qqCUAAAAAAAAHIag.jpg?v=637792557833470000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>13544</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>13564</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>FORNO MINAS</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>2001500</v>
+        <v>2001012</v>
       </c>
       <c r="P48" t="n">
         <v>99999</v>
@@ -3947,150 +3951,6 @@
         <v>2000015</v>
       </c>
       <c r="P49" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>alcool-montenegro-46-1-l-780570</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Álcool Montenegro 46% 1 L</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>780570</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Álcool Montenegro 46% 1 L</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="F50" t="n">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2020-10-06T10:47:00Z</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051579/VF4qT-qqCUAAAAAAAAG3pQ.jpg?v=637793390624870000</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>11598</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>11621</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>MONTENEGRO</t>
-        </is>
-      </c>
-      <c r="O50" t="n">
-        <v>2000527</v>
-      </c>
-      <c r="P50" t="n">
-        <v>99999</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>370550</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>24.99</v>
-      </c>
-      <c r="F51" t="n">
-        <v>24.99</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2020-09-27T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>6939</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>6957</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>HAPPY EGGS</t>
-        </is>
-      </c>
-      <c r="O51" t="n">
-        <v>2003319</v>
-      </c>
-      <c r="P51" t="n">
         <v>100</v>
       </c>
     </row>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="F2" t="n">
         <v>1.7</v>
@@ -585,43 +585,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>matte-leao-limao-pet-1-5l-118222</t>
+          <t>alcool-montenegro-46-1-l-780570</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Matte Leão Limão Pet 1,5L</t>
+          <t>Álcool Montenegro 46% 1 L</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>118222</t>
+          <t>780570</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
+          <t>Álcool Montenegro 46% 1 L</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8.99</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>8.99</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2020-10-01T00:00:00Z</t>
+          <t>2020-10-06T10:47:00Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051579/VF4qT-qqCUAAAAAAAAG3pQ.jpg?v=637793390624870000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -634,21 +634,21 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>11598</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>LEAO</t>
+          <t>MONTENEGRO</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2000010</v>
+        <v>2000527</v>
       </c>
       <c r="P3" t="n">
         <v>99999</v>
@@ -657,43 +657,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>leite-condensado-moca-lata-395g-1136321</t>
+          <t>matte-leao-limao-pet-1-5l-118222</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Leite Condensado Moça Lata 395g</t>
+          <t>Matte Leão Limão Pet 1,5L</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1136321</t>
+          <t>118222</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Moça® faz todas as receitas darem certo desde 1921, com seu sabor único e original, tem consistência perfeita, é sem comparação! É leite condensado obtido a partir de leite fresco, puro e integral. É um clássico no preparo de sobremesas, também é uma delícia na colher, na salada de frutas e o que mais você imaginar.</t>
+          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>9.99</v>
+        <v>7.95</v>
       </c>
       <c r="F4" t="n">
-        <v>9.99</v>
+        <v>8.99</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-13T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4531395/VF4qT-qqCUAAAAAAAAojmg.jpg?v=639099179974200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -706,21 +706,21 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>37022</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>36949</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>NESTLE</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>2000043</v>
+        <v>2000010</v>
       </c>
       <c r="P4" t="n">
         <v>99999</v>
@@ -729,43 +729,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>manga-palmer-unidade-5130760</t>
+          <t>leite-condensado-moca-lata-395g-1136321</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manga Palmer Unidade</t>
+          <t>Leite Condensado Moça Lata 395g</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5130760</t>
+          <t>1136321</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
+          <t>Moça® faz todas as receitas darem certo desde 1921, com seu sabor único e original, tem consistência perfeita, é sem comparação! É leite condensado obtido a partir de leite fresco, puro e integral. É um clássico no preparo de sobremesas, também é uma delícia na colher, na salada de frutas e o que mais você imaginar.</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5.39</v>
+        <v>9.99</v>
       </c>
       <c r="F5" t="n">
-        <v>5.99</v>
+        <v>9.99</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>67</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-02-16T00:00:00Z</t>
+          <t>2024-05-13T00:00:00Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4531395/VF4qT-qqCUAAAAAAAAojmg.jpg?v=639099179974200000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -778,21 +778,21 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>37022</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>36949</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>NESTLE</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2000015</v>
+        <v>2000043</v>
       </c>
       <c r="P5" t="n">
         <v>99999</v>
@@ -801,70 +801,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mamao-papaia-cariorta-12kg-99007</t>
+          <t>manga-palmer-unidade-5130760</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mamão Papaia Cariorta 1,2kg</t>
+          <t>Manga Palmer Unidade</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>99007</t>
+          <t>5130760</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e sabor doce e suave, com baixa quantidade de fibras. Muito versátil, é perfeita tanto para o consumo in natura quanto para o preparo de receitas doces e salgadas.Benefícios NutricionaisRica em vitamina C, que fortalece o sistema imunológicoFonte de vitamina A, importante para a saúde da pele e da visãoPossui fibras, auxiliando na digestãoContém antioxidantes naturais</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>9.99</v>
+        <v>5.99</v>
       </c>
       <c r="F6" t="n">
-        <v>9.99</v>
+        <v>5.99</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2023-02-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500750/VF4qT-qqCUAAAAAAAAUnKA.jpg?v=639071532077200000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>31902</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P6" t="n">
         <v>99999</v>
@@ -873,43 +873,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>couve-flor-unidade-189111</t>
+          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Couve Flor Unidade</t>
+          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>189111</t>
+          <t>828025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
+          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9.59</v>
+        <v>29.95</v>
       </c>
       <c r="F7" t="n">
-        <v>9.99</v>
+        <v>43.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -922,138 +922,138 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>PILAO</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2000015</v>
+        <v>2000070</v>
       </c>
       <c r="P7" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
+          <t>mamao-papaia-cariorta-12kg-99007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
+          <t>Mamão Papaia Cariorta 1,2kg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>370550</t>
+          <t>99007</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
+          <t>Cariorta selecionados de coração.</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>24.99</v>
+        <v>9.99</v>
       </c>
       <c r="F8" t="n">
-        <v>24.99</v>
+        <v>9.99</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082688/VF4qT-qqCUAAAAAAAAOOog.jpg?v=637980006057500000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>HAPPY EGGS</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2003319</v>
+        <v>2001012</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-pilao-tradicional-500g-828025</t>
+          <t>couve-flor-unidade-189111</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Café Torrado E Moído Pilão Tradicional Fresh Pack 500g</t>
+          <t>Couve Flor Unidade</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>828025</t>
+          <t>189111</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tem um ponto de torra acentuado e um processo de moagem fina e uniforme, que garantem e preservam seu sabor forte e encorpado.É perfeito para servir em dia de casa cheia, pois seu sabor tradicional agrada a todo mundo.</t>
+          <t>A couveflor é uma hortaliça rica em cálcio e fósforo e fonte de ácido fólico e vitamina C . Como Conservar:Na geladeira pode ser conservada por 3 a 5 dias, dentro de saco plástico perfurado. Antes de guardar, remova as partes escuras e folhas, mas não lave a cabeça.Como Consumir:Pode ser consumida assada, frita ou cozinhe em água e sal. [Fonte: 50 Hortaliças – Como Comprar, Conservar e Consumir. Editora: Embrapa]</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>43.9</v>
+        <v>9.99</v>
       </c>
       <c r="F9" t="n">
-        <v>43.9</v>
+        <v>9.99</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051146/VF4qT-qqCUAAAAAAAAG1sQ.jpg?v=637793369863530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041615/VF4qT-qqCUAAAAAAAAGF4Q.jpg?v=637792579893500000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1066,21 +1066,21 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>PILAO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2000070</v>
+        <v>2000015</v>
       </c>
       <c r="P9" t="n">
         <v>99999</v>
@@ -1089,33 +1089,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mucarela-em-fatias-92363</t>
+          <t>ovos-vermelhos-caipira-happy-eggs-com-20-unidades-370550</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Muçarela  em Fatias 200g</t>
+          <t>Ovos Vermelhos Caipira Happy Eggs Com 20 Unidades</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>92363</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Muçarela em Fatias</t>
+          <t>Os Ovos Vermelhos Caipira Happy Eggs são produzidos com foco em bem-estar animal, qualidade e sabor. Provenientes de galinhas criadas soltas, oferecem ovos frescos, nutritivos e com gema de coloração intensa, ideais para quem valoriza uma alimentação mais natural.Diferenciais do ProdutoOvos vermelhos caipiraGalinhas criadas soltas (free range)Maior bem-estar animalGemas mais intensasSabor e qualidade superiores</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>59.9</v>
+        <v>24.99</v>
       </c>
       <c r="F10" t="n">
-        <v>59.9</v>
+        <v>24.99</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1125,34 +1125,34 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4343192/VF4qT-qqCUAAAAAAAAn9QA.jpg?v=639071198945030000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>HAPPY EGGS</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2000015</v>
+        <v>2003319</v>
       </c>
       <c r="P10" t="n">
         <v>100</v>
@@ -1161,70 +1161,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
+          <t>mucarela-em-fatias-92363</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Muçarela  em Fatias 200g</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>140805</t>
+          <t>92363</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
+          <t>Muçarela em Fatias</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.29</v>
+        <v>59.9</v>
       </c>
       <c r="F11" t="n">
-        <v>5.29</v>
+        <v>59.9</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2020-09-25T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3052070/VF4qT-qqCUAAAAAAAAI4-w.jpg?v=637793416889100000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>SAO LOURENCO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2000145</v>
+        <v>2000015</v>
       </c>
       <c r="P11" t="n">
         <v>99999</v>
@@ -1373,43 +1373,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cheiro-verde-unidade-201049</t>
+          <t>agua-mineral-com-gas-sao-lourenco-pet-1-26-l-140805</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cheiro Verde Unidade</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>201049</t>
+          <t>140805</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
+          <t>Água Mineral Com Gás São Lourenço Pet 1,26 L</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.99</v>
+        <v>4.49</v>
       </c>
       <c r="F14" t="n">
-        <v>3.39</v>
+        <v>5.29</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-25T00:00:00Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076277/VF4qT-qqCUAAAAAAAAHMBQ.jpg?v=637877821166370000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1422,21 +1422,21 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SAO LOURENCO</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2000015</v>
+        <v>2000145</v>
       </c>
       <c r="P14" t="n">
         <v>99999</v>
@@ -1445,43 +1445,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>morango-250g-289612</t>
+          <t>cheiro-verde-unidade-201049</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Morango 250g</t>
+          <t>Cheiro Verde Unidade</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>289612</t>
+          <t>201049</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
+          <t>O cheiro verde é a combinação da cebolinha e salsinha .Como conservar:Em geladeira por até 5 dias em saco ou vasilha de plástico.Como consumir:Podem ser adicionadas cruas, em saladas e recheios de sanduíches e como ingredientes em marinadas.</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>10.99</v>
+        <v>3.39</v>
       </c>
       <c r="F15" t="n">
-        <v>10.99</v>
+        <v>3.39</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3457712/VF4qT-qqCUAAAAAAAAXvTg.jpg?v=638507335658200000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1589,43 +1589,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
+          <t>morango-250g-289612</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
+          <t>Morango 250g</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>290564</t>
+          <t>289612</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
+          <t>Embalagem com 250g "O morango é rico em vitamina C e, por isso, o consumo da fruta evita a fragilidade dos ossos e a má formação dos dentes. Ele também dá resistência aos tecidos, age contra infecções ajudando na cicatrização. O morango também possui, em menor quantidade, vitamina B5, conhecida como niacina. Ela tem a função de evitar problemas de pele, do aparelho digestivo e do sistema nervoso. Na fruta, também é encontrado ferro, que faz parte da formação do sangue."</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>26.99</v>
+        <v>14.99</v>
       </c>
       <c r="F17" t="n">
-        <v>26.99</v>
+        <v>14.99</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2020-09-29T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3226559/VF4qT-qqCUAAAAAAAAHKNA.jpg?v=638352676547800000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1638,66 +1638,66 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>SADIA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2000057</v>
+        <v>2000015</v>
       </c>
       <c r="P17" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>uva-preta-sem-semente-500-g-674583</t>
+          <t>file-de-peito-de-frango-sadia-bandeja-1kg-290564</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Uva Preta Sem Semente 500g</t>
+          <t>Filé de Peito de Frango Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>674583</t>
+          <t>290564</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
+          <t>Peito De Frango Em Filés Sadia Bandeja 1kg</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12.49</v>
+        <v>23.99</v>
       </c>
       <c r="F18" t="n">
-        <v>13.99</v>
+        <v>26.99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3538840/VF4qT-qqCUAAAAAAAAa5gg.jpg?v=638550537679130000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1710,21 +1710,21 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>SADIA</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2000015</v>
+        <v>2000057</v>
       </c>
       <c r="P18" t="n">
         <v>99999</v>
@@ -1733,48 +1733,48 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>limao-cariorta-1kg-98981</t>
+          <t>uva-preta-sem-semente-500-g-674583</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Limão Cariorta 1Kg</t>
+          <t>Uva Preta Sem Semente 500g</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>98981</t>
+          <t>674583</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.</t>
+          <t>Eventualmente, devido à variações climáticas, essa variedade pode apresentar traços de sementes comestíveis As uvas são, sem dúvidas, uma das frutas mais nutritivas de todas. Apesar de seu tamanho relativamente pequeno, elas são extremamente poderosas nutricionalmente e consumilas é muito importante para o bom funcionamento do corpo.As calorias presentes nas uvas também são poucas: apenas 90 em cerca de 150g. Por isso, é uma ótima opção também para aqueles que estão em processo de redução da massa corporal, desde que consumida com cautela.Rica em antioxidantes que são responsáveis por ‘’limpar’’ e proteger as nossas células dos chamados radicais livres, compostos potencialmente perigosos que podem danificar essas estruturas.Os antioxidantes estão mais comumente presentes na casca da fruta, o que é indicado pela coloração delas. Quanto mais escuras, maior é a concentração desses compostos na uva. Os principais exemplos são os polifenois, e o mais famoso deles chamase resveratrol.</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>11.99</v>
+        <v>13.99</v>
       </c>
       <c r="F19" t="n">
-        <v>11.99</v>
+        <v>13.99</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2020-05-20T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4501193/VF4qT-qqCUAAAAAAAAGXCQ.jpg?v=639072395991300000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1782,21 +1782,21 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2001012</v>
+        <v>2000015</v>
       </c>
       <c r="P19" t="n">
         <v>99999</v>
@@ -1805,33 +1805,29 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
+          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Detergente Para Louças Odd Clear 500ml</t>
+          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>982911</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ODD voltou!Alto rendimento , controle de odor.</t>
-        </is>
-      </c>
+          <t>783250</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>2.49</v>
+        <v>5.99</v>
       </c>
       <c r="F20" t="n">
-        <v>2.49</v>
+        <v>5.99</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1841,7 +1837,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1854,21 +1850,21 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>LIMPPANO</t>
+          <t>SOCIAL CLEAN</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2001341</v>
+        <v>2001952</v>
       </c>
       <c r="P20" t="n">
         <v>99999</v>
@@ -1877,44 +1873,48 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>papel-toalha-social-clean-19cm-x-19cm-com-2-rolos-com-50-folhas-cada-783250</t>
+          <t>limao-cariorta-1kg-98981</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Papel Toalha Social Clean 19cm X 19cm com 2 Rolos com 50 Folhas Cada</t>
+          <t>Limão Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>783250</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>98981</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Cariorta selecionados de coração.</t>
+        </is>
+      </c>
       <c r="E21" t="n">
-        <v>5.99</v>
+        <v>11.99</v>
       </c>
       <c r="F21" t="n">
-        <v>5.99</v>
+        <v>11.99</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-05-20T00:00:00Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051599/VF4qT-qqCUAAAAAAAAKPYw.jpg?v=637793391583770000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3084385/VF4qT-qqCUAAAAAAAAOgIg.jpg?v=638000868147970000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1922,21 +1922,21 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>SOCIAL CLEAN</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>2001952</v>
+        <v>2001012</v>
       </c>
       <c r="P21" t="n">
         <v>99999</v>
@@ -2017,43 +2017,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-unidade-423513</t>
+          <t>detergente-para-loucas-odd-clear-500ml-982911</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>Detergente Para Louças Odd Clear 500ml</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>982911</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Unidade</t>
+          <t>ODD voltou!Alto rendimento , controle de odor.</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2020-12-07T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3056732/VF4qT-qqCUAAAAAAAAHzRQ.jpg?v=637793635376800000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2066,21 +2066,21 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>LIMPPANO</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>2000015</v>
+        <v>2001341</v>
       </c>
       <c r="P23" t="n">
         <v>99999</v>
@@ -2089,43 +2089,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>coentro-unidade-200930</t>
+          <t>abobrinha-italiana-unidade-423513</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Coentro Unidade</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>200930</t>
+          <t>423513</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
+          <t>Abobrinha Italiana Unidade</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="F24" t="n">
-        <v>3.79</v>
+        <v>2.8</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-12-07T00:00:00Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4500744/VF4qT-qqCUAAAAAAAASlGA.jpg?v=639071532017170000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2161,26 +2161,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>couve-manteiga-unidade-201235</t>
+          <t>coentro-unidade-200930</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Couve Manteiga Unidade</t>
+          <t>Coentro Unidade</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>201235</t>
+          <t>200930</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
+          <t>O coentro é uma erva rica em antioxidantes, vitaminas A, C e K, além de minerais como potássio, que oferecem benefícios como fortalecimento da imunidade, redução do colesterol ruim (LDL), melhora da digestão e controle da glicemia. Também possui propriedades anti-inflamatórias, diuréticas e ajuda na saúde cardiovascular e da pele</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.99</v>
+        <v>3.79</v>
       </c>
       <c r="F25" t="n">
         <v>3.79</v>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076728/VF4qT-qqCUAAAAAAAAGF4g.jpg?v=637877840364830000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2233,43 +2233,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
+          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1180320</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
+          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.79</v>
+        <v>6.49</v>
       </c>
       <c r="F26" t="n">
-        <v>2.79</v>
+        <v>6.49</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2025-07-17T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2282,21 +2282,21 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>41057</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>BOMBRIL</t>
+          <t>ELEGE</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>2001389</v>
+        <v>2000400</v>
       </c>
       <c r="P26" t="n">
         <v>99999</v>
@@ -2305,43 +2305,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>leite-longa-vida-integral-elege-tetra-pak-1l-371289</t>
+          <t>couve-manteiga-unidade-201235</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>Couve Manteiga Unidade</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>371289</t>
+          <t>201235</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Leite Longa Vida Integral Elegê Tetra Pak 1L</t>
+          <t>A couve é uma hortaliça muito rica em nutriente,cálcio, ferro e vitaminas A,C, K e B5.Como conservar:Em geladeira, inteira ou picada deve ser mantida em saco plástico fechado ou em vasilha de plástico tampada.Como consumir:Pode ser consumida crua, em saladas e sucos, refogada ou como ingrediente de sopas, farofas e cozidos.</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6.29</v>
+        <v>3.79</v>
       </c>
       <c r="F27" t="n">
-        <v>6.29</v>
+        <v>3.79</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3129041/VF4qT-qqCUAAAAAAAAUbaw.jpg?v=638309476429500000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3083631/VF4qT-qqCUAAAAAAAAOZOA.jpg?v=637994955185970000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2354,21 +2354,21 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>ELEGE</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>2000400</v>
+        <v>2000015</v>
       </c>
       <c r="P27" t="n">
         <v>99999</v>
@@ -2377,43 +2377,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>abacaxi-unidade-221</t>
+          <t>la-de-aco-bombril-com-6-unidades-45g-1180320</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Abacaxi Unidade</t>
+          <t>Lã de Aço Bombril com 6 Unidades 45g</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>1180320</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
+          <t>Uso: Ideal para limpeza de panelas, utensílios de cozinha, superfícies metálicas e outras áreas que necessitam de uma limpeza mais intensa.Remove sujeiras difíceis, incluindo resíduos de alimentos queimados e ferrugem.</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>9.99</v>
+        <v>2.79</v>
       </c>
       <c r="F28" t="n">
-        <v>10.99</v>
+        <v>2.79</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2025-07-17T00:00:00Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4216409/VF4qT-qqCUAAAAAAAAko5g.jpg?v=638889221726300000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2426,21 +2426,21 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>BOMBRIL</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>2000015</v>
+        <v>2001389</v>
       </c>
       <c r="P28" t="n">
         <v>99999</v>
@@ -2449,43 +2449,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>espinafre-unidade-200948</t>
+          <t>abacaxi-unidade-221</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Espinafre Unidade</t>
+          <t>Abacaxi Unidade</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>200948</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
+          <t>O Abacaxi é rico em Vitaminas A, B5, B6, C, BetaCaroteno, Tiamina, Antioxidantes e Fibras, auxiliando na saciedade e regulação do peso. É uma Importante fonte de energia póstreino. Auxilia nos processos antiinflamatórios por conter Bromelina, enzima encontrada principalmente no talo da fruta. Como preparar: no seu estado natural cortado, em saladas, assado, grelhado, sucos, geleias, sorvetes e chás.</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.99</v>
+        <v>10.99</v>
       </c>
       <c r="F29" t="n">
-        <v>3.79</v>
+        <v>10.99</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3041923/VF4qT-qqCUAAAAAAAAFtXw.jpg?v=637792593143530000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2515,49 +2515,49 @@
         <v>2000015</v>
       </c>
       <c r="P29" t="n">
-        <v>99999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>milho-em-conserva-quero-lata-200g-476625</t>
+          <t>espinafre-unidade-200948</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Milho em Conserva Quero Lata 200g</t>
+          <t>Espinafre Unidade</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>476625</t>
+          <t>200948</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
+          <t>O espinafre é um superalimento rico em ferro, fibras, vitaminas A, C, E, K e antioxidantes (luteína, zeaxantina) que fortalecem a imunidade, promovem a saúde ocular e óssea, e ajudam a controlar a pressão arterial. Com poucas calorias, auxilia na perda de peso e tem ação anti-inflamatóriaA melhor forma de comer espinafre depende do objetivo: cru em saladas para crocância e luteína (com gordura, como iogurte, para absorção); cozido (no vapor ou refogado) para reduzir oxalatos e melhorar a absorção de ferro, misturado em sopas, cremes, omeletes ou com leguminosas; congelado para usar em receitas diversas como recheios e massas</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4.99</v>
+        <v>3.79</v>
       </c>
       <c r="F30" t="n">
-        <v>4.99</v>
+        <v>3.79</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2020-10-06T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076729/VF4qT-qqCUAAAAAAAAKBdQ.jpg?v=637877840409270000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2570,21 +2570,21 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>QUERO</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2001778</v>
+        <v>2000015</v>
       </c>
       <c r="P30" t="n">
         <v>99999</v>
@@ -2665,43 +2665,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>alface-crespa-unidade-200875</t>
+          <t>milho-em-conserva-quero-lata-200g-476625</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Alface Crespa Unidade</t>
+          <t>Milho em Conserva Quero Lata 200g</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>200875</t>
+          <t>476625</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
+          <t>Sabor inigualável e cozimento na medida certa são os segredos do Milho Quero. O Milho Verde em Conserva Quero Lata 170g é ideal para receitas em pequenas quantidades. Se você prefere embalagens em lata, essa opção é ideal pra você! Para garantir a qualidade da sua receita, a Quero seleciona os vegetais com todo o cuidado, deixando o resultado final impecável. Pode confiar que seus pratos vão ficar uma delícia. Sabor e frescor para o seu dia a dia! Que tal experimentar? Quero cabe na panela, no prato e no bolso, sendo a marca queridinha entre os brasileiros.* Pode confiar que quando você tem Quero, você faz acontecer!</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2.99</v>
+        <v>3.69</v>
       </c>
       <c r="F32" t="n">
-        <v>3.79</v>
+        <v>4.99</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2020-09-28T00:00:00Z</t>
+          <t>2020-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3090347/476625_1.jpg?v=638126891970330000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2714,21 +2714,21 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>QUERO</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2000015</v>
+        <v>2001778</v>
       </c>
       <c r="P32" t="n">
         <v>99999</v>
@@ -2737,43 +2737,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
+          <t>alface-crespa-unidade-200875</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
+          <t>Alface Crespa Unidade</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>129887</t>
+          <t>200875</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+          <t>A alface é uma hortaliça essencial para as saladas devido ao seu sabor agradável e refrescante. Além de ter um fácil preparo é uma importante fonte de sais minerais, cálcio e vitaminas, principalmente a vitamina A .Como conservar :Sem refrigeração – Deve ser conservada com a parte de baixo dentro de uma vasilha com água ou dentro de saco plástico aberto, por até 1 dia.Com refrigeração (geladeira) – Manter em uma vasilha de plástico tampada ou em saco plástico, retirandose as folhas de acordo com a necessidade de consumo, por até 3 a 4 dias. Como consumir :Lavar as folhas em água corrente, depois deixalas de molho em solução de hipoclorito de sódio, por até 30 min. e em seguida enxagualas com água filtrada.</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>12.99</v>
+        <v>3.79</v>
       </c>
       <c r="F33" t="n">
-        <v>12.99</v>
+        <v>3.79</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-28T00:00:00Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076722/VF4qT-qqCUAAAAAAAAHLog.jpg?v=637877840103000000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2786,21 +2786,21 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>GRANDE HOTEL</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2001401</v>
+        <v>2000015</v>
       </c>
       <c r="P33" t="n">
         <v>99999</v>
@@ -2809,44 +2809,48 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>abobrinha-italiana-cariorta-1kg-98663</t>
+          <t>guardanapo-folha-dupla-scott-grand-hotel-jantar-33×33-cm-com-50-unidades-129887</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Abobrinha Italiana Cariorta 1Kg</t>
+          <t>Guardanapo Folha Dupla Scott Grand Hotel Jantar 33×33 Cm Com 50 Unidades</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>98663</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>129887</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>O Guardanapo Grand Hotel folha tripla é mais sofisticado e garante uma maciez superior para todos os momentos. Contém 50 folhas de tamanho 31,8x32,8 cm cada.</t>
+        </is>
+      </c>
       <c r="E34" t="n">
-        <v>8.99</v>
+        <v>12.99</v>
       </c>
       <c r="F34" t="n">
-        <v>8.99</v>
+        <v>12.99</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2020-12-16T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3078100/129887_1.jpg?v=637895346534630000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2854,66 +2858,62 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>GRANDE HOTEL</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>2001012</v>
+        <v>2001401</v>
       </c>
       <c r="P34" t="n">
-        <v>10</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
+          <t>file-de-peito-de-frango-congelado-rivelli-bandeja-1kg-1023799</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
+          <t>Filé de Peito de Frango Congelado Rivelli Bandeja 1kg</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>818640</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
-        </is>
-      </c>
+          <t>1023799</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>4.99</v>
+        <v>25.99</v>
       </c>
       <c r="F35" t="n">
-        <v>4.99</v>
+        <v>25.99</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-11-26T00:00:00Z</t>
+          <t>2021-07-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038302/VF4qT-qqCUAAAAAAAAKY8g.jpg?v=637792395730970000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2926,71 +2926,67 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>PIRACANJUBA</t>
+          <t>Rivelli</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2002038</v>
+        <v>2004122</v>
       </c>
       <c r="P35" t="n">
-        <v>99999</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
+          <t>abobrinha-italiana-cariorta-1kg-98663</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
+          <t>Abobrinha Italiana Cariorta 1Kg</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>981168</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
-        </is>
-      </c>
+          <t>98663</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
-        <v>32.19</v>
+        <v>8.99</v>
       </c>
       <c r="F36" t="n">
-        <v>32.19</v>
+        <v>8.99</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2020-09-22T00:00:00Z</t>
+          <t>2020-12-16T00:00:00Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3082667/VF4qT-qqCUAAAAAAAAOOdQ.jpg?v=637979987909700000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2998,66 +2994,66 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>NEVE</t>
+          <t>CARIORTA</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2000291</v>
+        <v>2001012</v>
       </c>
       <c r="P36" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>sal-refinado-iodado-ita-1kg-117293</t>
+          <t>creme-de-leite-piracanjuba-tetra-pak-200g-818640</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>Creme de Leite Piracanjuba Tetra Pak 200g</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>818640</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sal Refinado Iodado Ita 1kg</t>
+          <t>O sabor é incomparável e com textura aveludada. O resultado não poderia ser melhor: receitas perfeitas e deliciosas. Você pode ter dúvida quanto à receita, mas o Creme de Leite é Piracanjuba. Modo de conservação: Mantenha em local seco e arejado. Antes do uso, não necessita de refrigeração. Após aberto, manter em geladeira (1°C - 10°C) e consumir em até 2 dias. Ingredientes: Creme de leite padronizado a 17% de gordura, leite em pó desnatado, estabilizantes celulose microcristalina e citrato de sódio e espessantes carboximetilcelulose sódica, goma xantana e carragena. Alergênicos: CONTÉM LEITE E DERIVADOS. CONTÉM LACTOSE. NÃO CONTÉM GLÚTEN. Porção de 15 g (1 colher e 1/2 de sopa) = 26 kcal</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4.39</v>
+        <v>4.99</v>
       </c>
       <c r="F37" t="n">
-        <v>4.39</v>
+        <v>4.99</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2020-09-15T00:00:00Z</t>
+          <t>2020-11-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3296613/VF4qT-qqCUAAAAAAAAWc6A.jpg?v=638413165673100000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3070,66 +3066,66 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>PIRACANJUBA</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2000066</v>
+        <v>2002038</v>
       </c>
       <c r="P37" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
+          <t>papel-higienico-folha-tripla-neve-supreme-dermacare-pacote-leve-16-pague-15-unidades-981168</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
+          <t>Papel Higiênico Folha Tripla Neve Supreme Dermacare Pacote Leve 16 Pague 15 Unidades</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>981168</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
+          <t>Papel higiênico neutro folha tripla de alta qualidade. Neve quer ajudar as pessoas a cuidarem de si, por isso desenvolveu um produto que proporciona maciez insuperável com mais absorção e resistência.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>29.98</v>
+        <v>32.19</v>
       </c>
       <c r="F38" t="n">
-        <v>37.9</v>
+        <v>32.19</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2020-07-13T00:00:00Z</t>
+          <t>2020-09-22T00:00:00Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4430737/VF4qT-qqCUAAAAAAAAoMMw.jpg?v=639014499358300000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3142,21 +3138,21 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>MELITTA</t>
+          <t>NEVE</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>2001329</v>
+        <v>2000291</v>
       </c>
       <c r="P38" t="n">
         <v>99999</v>
@@ -3165,70 +3161,70 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>melao-amarelo-metade-1-3-kg-63606</t>
+          <t>sal-refinado-iodado-ita-1kg-117293</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Melão Amarelo Metade 1,3kg</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
+          <t>Sal Refinado Iodado Ita 1kg</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>8.99</v>
+        <v>4.39</v>
       </c>
       <c r="F39" t="n">
-        <v>9.99</v>
+        <v>4.39</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-15T00:00:00Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3076051/VF4qT-qqCUAAAAAAAAKZcQ.jpg?v=637877811480070000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>2000015</v>
+        <v>2000066</v>
       </c>
       <c r="P39" t="n">
         <v>99999</v>
@@ -3237,43 +3233,43 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>batata-palha-yoki-extra-fina-100g-989843</t>
+          <t>biscoito-cream-cracker-piraque-pacote-184g-1105795</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Batata Palha Yoki Extra Fina 100g</t>
+          <t>Biscoito Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>989843</t>
+          <t>1105795</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Batata Palha Yoki Extra Fina 100g</t>
+          <t>Biscoito Salgado Cream Cracker Piraquê Pacote 184g</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>10.99</v>
+        <v>4.29</v>
       </c>
       <c r="F40" t="n">
-        <v>10.99</v>
+        <v>5.99</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2020-10-30T00:00:00Z</t>
+          <t>2023-07-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3099416/VF4qT-qqCUAAAAAAAATd0w.jpg?v=638264204522930000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3286,21 +3282,21 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>YOKI</t>
+          <t>PIRAQUE</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>2001336</v>
+        <v>2000017</v>
       </c>
       <c r="P40" t="n">
         <v>99999</v>
@@ -3309,70 +3305,70 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
+          <t>melao-amarelo-metade-1-3-kg-63606</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
+          <t>Melão Amarelo Metade 1,3kg</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>897795</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Envolve , protege e conserva.</t>
+          <t>Peso Aproximado 1,3Kg/ Unidade.O melão tem muitos nutrientes incluindo cálcio, vitamina C, vitamina A e as vitaminas do Complexo B, que dão muita energia. Uma atenção para o potássio que é importante para diminuir a pressão arterial. O melão é rico em zeaxantina, que aumenta a saúde da retina. Quanto mais madura a fruta maior a concentração de substâncias ativas. O melão é muito rico em bioflavonóides , que são excelentes fontes de antioxidantes e antiinflamatórios. A fruta também tem muitos carotenóides, que diminuem os riscos de várias doenças.</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6.99</v>
+        <v>9.99</v>
       </c>
       <c r="F41" t="n">
-        <v>6.99</v>
+        <v>9.99</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2020-10-05T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3044509/VF4qT-qqCUAAAAAAAAF_6w.jpg?v=637792722888230000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>KENTINHA</t>
+          <t>Zona Sul</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2001532</v>
+        <v>2000015</v>
       </c>
       <c r="P41" t="n">
         <v>99999</v>
@@ -3381,70 +3377,70 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>abobora-japonesa-pedaco-500g-38229</t>
+          <t>cafe-torrado-e-moido-melitta-a-vacuo-500g-103845</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Abóbora Japonesa Pedaço 500g</t>
+          <t>Café Torrado e Moído Melitta A Vácuo 500g</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>38229</t>
+          <t>103845</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Embalagem com 1 pedaço.</t>
+          <t>Feitos com uma cuidadosa seleção dos grãos que passam por um processo de torra a ar quente que resultam em cafés marcantes e fortes.</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2.95</v>
+        <v>29.98</v>
       </c>
       <c r="F42" t="n">
-        <v>4.99</v>
+        <v>37.9</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2020-07-13T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3038677/VF4qT-qqCUAAAAAAAAGwhg.jpg?v=637792444870400000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2020-09-26T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3096862/VF4qT-qqCUAAAAAAAAS9Tw.jpg?v=638235593168230000</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>5593</t>
-        </is>
-      </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Zona Sul</t>
+          <t>MELITTA</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2000015</v>
+        <v>2001329</v>
       </c>
       <c r="P42" t="n">
         <v>99999</v>
@@ -3453,43 +3449,43 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>tomate-pelado-italiano-due-lata-400g-5459389</t>
+          <t>refrigerante-coca-cola-sem-acucar-pet-600-ml-429392</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tomate Pelado Italiano Due Lata 400g</t>
+          <t>Refrigerante Coca Cola Sem Açúcar Pet 600ml</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5459389</t>
+          <t>429392</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Due é sua dupla perfeita para criar o verdadeiro sabor italiano!Due o melhor da culinária italiana com ingredientes genuínos, que você só encontra no Zona SulExperimente e surpreenda-se!</t>
+          <t>A Coca-Cola Sem Açúcar é um refrigerante que não contém calorias! Com certeza você já se perguntou: “Então, de onde vem aquele gostinho doce? ” A Coca-Cola Sem Açúcar é produzida especialmente com adoçantes para manter o delicioso sabor de Coca-Cola porém com 0% Açucar. Perfeita para matar sua sede a qualquer hora do dia!</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8.369999999999999</v>
+        <v>4.99</v>
       </c>
       <c r="F43" t="n">
-        <v>8.369999999999999</v>
+        <v>5.69</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2025-01-21T00:00:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3928345/VF4qT-qqCUAAAAAAAAhGgQ.jpg?v=638736295014200000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4483407/VF4qT-qqCUAAAAAAAAoapA.jpg?v=639052524553700000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3502,21 +3498,21 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>39142</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>39069</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>DUE</t>
+          <t>COCA COLA</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>2005138</v>
+        <v>2000027</v>
       </c>
       <c r="P43" t="n">
         <v>99999</v>
@@ -3544,7 +3540,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>8.949999999999999</v>
+        <v>12.99</v>
       </c>
       <c r="F44" t="n">
         <v>12.99</v>
@@ -3597,70 +3593,70 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>mamao-formosa-metade-cariorta-800g-63584</t>
+          <t>papel-aluminio-rolitto-30cm-x-75-m-897795</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mamão Formosa Metade Cariorta 800g</t>
+          <t>Papel Alumínio Rolitto 30Cm X 7,5 M</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>63584</t>
+          <t>897795</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>"Por ser rico em fibras o mamão formosa é grande amigo do funcionamento do intestino. A cor alaranjada vem do licopeno que, por ser carotenoide, é antioxidante."</t>
+          <t>Envolve , protege e conserva.</t>
         </is>
       </c>
       <c r="E45" t="n">
         <v>6.99</v>
       </c>
       <c r="F45" t="n">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-10-05T00:00:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3095891/VF4qT-qqCUAAAAAAAASvtw.jpg?v=638221188789530000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/4502488/VF4qT-qqCUAAAAAAAAoePA.jpg?v=639074988068370000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>KENTINHA</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>2001012</v>
+        <v>2001532</v>
       </c>
       <c r="P45" t="n">
         <v>99999</v>
@@ -3669,43 +3665,43 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>queijo-mucarela-em-fatias-bandeja-100g-38954</t>
+          <t>abobora-japonesa-pedaco-500g-38229</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Queijo Muçarela Em Fatias Bandeja 100g</t>
+          <t>Abóbora Japonesa Pedaço 500g</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38229</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Queijo Muçarela Em Fatias Bandeja 100g</t>
+          <t>Embalagem com 1 pedaço.</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>59.9</v>
+        <v>4.99</v>
       </c>
       <c r="F46" t="n">
-        <v>59.9</v>
+        <v>4.99</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2020-09-27T00:00:00Z</t>
+          <t>2020-09-26T00:00:00Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3049627/VF4qT-qqCUAAAAAAAAHtlQ.jpg?v=637793305547330000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3096862/VF4qT-qqCUAAAAAAAAS9Tw.jpg?v=638235593168230000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3714,16 +3710,16 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3741,43 +3737,43 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pao-de-queijo-forno-de-minas-tradicional--400-g-456110</t>
+          <t>tomate-pelado-italiano-due-lata-400g-5459389</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pão De Queijo Forno De Minas Tradicional 400g</t>
+          <t>Tomate Pelado Italiano Due Lata 400g</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>456110</t>
+          <t>5459389</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Pão De Queijo Forno De Minas Tradicional 400g</t>
+          <t>Due é sua dupla perfeita para criar o verdadeiro sabor italiano!Due o melhor da culinária italiana com ingredientes genuínos, que você só encontra no Zona SulExperimente e surpreenda-se!</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>14.99</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>21.99</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020-10-20T00:00:00Z</t>
+          <t>2025-01-21T00:00:00Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3041185/VF4qT-qqCUAAAAAAAAHIag.jpg?v=637792557833470000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3928345/VF4qT-qqCUAAAAAAAAhGgQ.jpg?v=638736295014200000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3790,93 +3786,93 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>13544</t>
+          <t>39142</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>13564</t>
+          <t>39069</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>FORNO MINAS</t>
+          <t>DUE</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>2001500</v>
+        <v>2005138</v>
       </c>
       <c r="P47" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>alho-roxo-cariorta-4-a-5-unidades-250g-99279</t>
+          <t>batata-palha-yoki-extra-fina-100g-989843</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Alho Roxo Cariorta 4 a 5 unidades 250g</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>99279</t>
+          <t>989843</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cariorta selecionados de coração.O Alho Roxo Carioca Selecionado é reconhecido pelo seu sabor intenso, aroma marcante e alta qualidade. Cuidadosamente selecionado, apresenta bulbos firmes, bem formados e com excelente rendimento, sendo indispensável na cozinha para realçar o sabor das receitas.Benefícios NutricionaisPossui ação antioxidante e anti-inflamatóriaAuxilia no fortalecimento do sistema imunológicoContribui para a saúde cardiovascularContém compostos naturais como a alicina, responsável pelo sabor e aroma característicos</t>
+          <t>Batata Palha Yoki Extra Fina 100g</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>59.99</v>
+        <v>8.99</v>
       </c>
       <c r="F48" t="n">
-        <v>59.99</v>
+        <v>10.99</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2020-05-27T00:00:00Z</t>
+          <t>2020-10-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3082698/VF4qT-qqCUAAAAAAAAOOtg.jpg?v=637980006345970000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3793279/VF4qT-qqCUAAAAAAAAdSYw.png?v=638647300647970000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>un</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>24684</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>13749</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>CARIORTA</t>
+          <t>YOKI</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>2001012</v>
+        <v>2001336</v>
       </c>
       <c r="P48" t="n">
         <v>99999</v>
@@ -3885,43 +3881,43 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>cebola-roxa-400g-38393</t>
+          <t>queijo-mucarela-em-fatias-bandeja-100g-38954</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cebola Roxa 400g</t>
+          <t>Queijo Muçarela Em Fatias Bandeja 100g</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Embalagem com 2 a 3 unidades. Melhor para comer cru; Use : no guacamole, em conserva, na salada, no sanduíche.</t>
+          <t>Queijo Muçarela Em Fatias Bandeja 100g</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>7.99</v>
+        <v>49.9</v>
       </c>
       <c r="F49" t="n">
-        <v>7.99</v>
+        <v>59.9</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>325</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2020-09-26T00:00:00Z</t>
+          <t>2020-09-27T00:00:00Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3081506/VF4qT-qqCUAAAAAAAAOBng.jpg?v=637947101712670000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3049627/VF4qT-qqCUAAAAAAAAHtlQ.jpg?v=637793305547330000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3930,16 +3926,16 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3951,7 +3947,7 @@
         <v>2000015</v>
       </c>
       <c r="P49" t="n">
-        <v>100</v>
+        <v>99999</v>
       </c>
     </row>
   </sheetData>

--- a/zonasul.xlsx
+++ b/zonasul.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,43 +585,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>alcool-montenegro-46-1-l-780570</t>
+          <t>matte-leao-limao-pet-1-5l-118222</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Álcool Montenegro 46% 1 L</t>
+          <t>Matte Leão Limão Pet 1,5L</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>780570</t>
+          <t>118222</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Álcool Montenegro 46% 1 L</t>
+          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8.789999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="F3" t="n">
-        <v>8.789999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2020-10-06T10:47:00Z</t>
+          <t>2020-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://zonasul.vtexassets.com/arquivos/ids/3051579/VF4qT-qqCUAAAAAAAAG3pQ.jpg?v=637793390624870000</t>
+          <t>https://zonasul.vtexassets.com/arquivos/ids/3704455/VF4qT-qqCUAAAAAAAAcePQ.jpg?v=638609291270100000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -634,21 +634,21 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>11598</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MONTENEGRO</t>
+          <t>LEAO</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2000527</v>
+        <v>2000010</v>
       </c>
       <c r="P3" t="n">
         <v>99999</v>
@@ -657,43 +657,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>matte-leao-limao-pet-1-5l-118222</t>
+          <t>manga-palmer-unidade-5130760</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Matte Leão Limão Pet 1,5L</t>
+          <t>Manga Palmer Unidade</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118222</t>
+          <t>5130760</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>O Chá MATTE Limão Leão é um dos tipos de chás preferido dos consumidores. A marca Chá Mate Leão está presente no mercado há mais de 100 anos, sendo a marca de chá mais vendida e tradicional. Produzido com extrato aquoso de mate, açúcar e suco de limão, o Chá MATTE LEÃO Limão é a opção ideal para refrescar o seu dia! Compre e compartilhe com amigos e familiares!</t>
+          <t>A Manga Palmer é conhecida por seu tamanho grande, polpa firme e 